--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3814,6 +3814,899 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:27:06 +0000</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>人形赋能·智领未来｜申昊科技携手宇树科技打造“电力+算力”双场景人形机器人</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12064</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>申昊科技与宇树科技达成重磅深度战略合作。双方优势高度互补，采用宇树人形双臂上身+申昊工业轮式底盘的组合架构，围绕战略协同、联合研发、共创市场三维发力，打造工业人形机器人智能解决方案。</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:26:49 +0000</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>松延动力与鲸海拾贝达成战略合作，共启具身智能文旅场景应用新篇章</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12058</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>近日，松延动力与鲸海拾贝围绕具身智能文旅场景生态落地展开深入交流，并达成战略合作。</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 07:24:37 +0000</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>矩侨工业连续完成Pre-A+&amp;Pre-A++轮融资，织物具身电子皮肤量产突破</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12046</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>矩侨工业获数千万融资，电子皮肤赋能具身智能、智能座舱、智慧养老等场景。</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>What Robotics Companies Think About the U.S. Foreign Robot Ban</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/fcc-covered-list-mobile-robots</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The U.S. Federal Communications Commission (FCC) “Covered List,” originally published in 2021, identifies communications equipment and services that it says …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:02:59  +0800</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>8点1氪丨马斯克个人财富亏掉2个“黄仁勋”；上海雪花膏母公司破产；日本半导体或面临断供</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/p/3925868626360706?f=rss</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>&lt;h2&gt;今日热点导览&lt;/h2&gt;
+  &lt;p&gt;一架上海飞东京航班险撞机，两机垂直高度差仅约20米&lt;/p&gt;
+  &lt;p&gt;阿里云容器服务Agent开启商业化收费&lt;/p&gt;
+  &lt;p&gt;今年以来港股IPO数量同比增长132%，科技类公司占比过半&lt;/p&gt;
+  &lt;p&gt;苹果新任CEO据悉邀请已退休的硬件部门负责人加入管理团队&lt;/p&gt;
+  &lt;p&gt;SpaceX上市后首份财报前夕，“木头姐”持续加仓&lt;/p&gt;
+  &lt;h2&gt;TOP3大新闻&lt;/h2&gt;
+  &lt;p&gt;&lt;strong&gt;马斯克个人财富缩水约合人民币2.45万亿元，相当于亏掉2个“黄仁勋”&amp;nbsp;&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;据微信公众号“福布斯”消息，6月12日SpaceX上市，马斯克成为全球首位万亿富豪。但他13位数字的身家并未维保持多久——SpaceX的股价此前一路飞升，如今却跌回地表，马斯克在7月单月财富缩水3630亿美元（约合人民币2.45万亿元），创下纪录。这一缩水幅度，甚至超过了全球第2至第10大富豪中任何一人的全部身家，是英伟达CEO黄仁勋身家（1740亿美元）的两倍多。截至美国东部时间8月1日零点，排名第2的拉里·佩奇身家微增10亿美元，约为2920亿美元；而马斯克的身家约为6900亿美元，降至去年12月以来的最低水平。（红星新闻）&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;上海雪花膏母公司破产，财产不足以支付破产费&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;近日，上海市浦东新区人民法院出具（2024）沪0115破151号民事裁定书，宣告上海美兰化妆品有限公司（以下简称“美兰”）破产并终结清算程序。裁定书援引《企业破产法》第四十三条认为，企业现有财产不足以支付破产费用，管理人提请法院直接终止清算，普通债权人无财产可分配。&lt;/p&gt;
+  &lt;p&gt;据裁定书配套管理人清算数据，美兰可处置资产仅9.58万元，法院确认债权总额1941.67万元，账面资产连诉讼费、管理人报酬等基础办案成本都无法覆盖。这家诞生于1984年、依靠老上海雪花膏走红的本土老牌日化企业彻底退场。（红星新闻）&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;受地震影响，日本半导体或面临断供&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;7月28日，日本熊本县发生强震，多家半导体相关企业停产至今。九州地区因聚集大量半导体相关企业被称为“硅岛”，熊本县自1970年前后开始吸引半导体企业落户，逐步发展成为日本重要的半导体产业基地。&lt;/p&gt;
+  &lt;p&gt;熊本县内聚集着大量半导体相关企业和汽车工厂，有专家表示强震将给相关产业带来严重冲击。不仅是半导体，受零部件供应延迟影响，日本部分汽车制造商的生产也已受到波及。丰田汽车已决定暂停福冈县3家工厂的生产至8月5日，位于爱知县的田原工厂也将于8月3日至7日停产。本田宣布，熊本县大津町的摩托车工厂将停产至8月7日。日产汽车则决定，将福冈县两家工厂的部分生产线停工至8月5日。（金融界、央视网）&lt;/p&gt;
+  &lt;h2&gt;AI最前沿&lt;/h2&gt;
+  &lt;p&gt;&lt;strong&gt;面壁智能开源全球首个Stencil优化AI系统&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;36氪获悉，8月4日，面壁智能联合OpenBMB开源社区正式发布并开源全球首个Stencil（模板计算）优化“自动研究+自动部署”大闭环AI系统ForgeStencil。实测数据显示，ForgeStencil在同精度（fp32）下几何平均加速2.35倍，混合精度下额外提速1.95倍。在真实应用场景中，通用CAE求解器hypre加速3.86倍，电磁仿真FDTD加速2.47倍，核反应堆中子学计算minisweep加速最高达5.78倍。&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;阿里云容器服务Agent开启商业化收费&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;36氪获悉，阿里云宣布，容器服务Agent将于北京时间9月3日10时增加新的技能中心和IM频道等功能并开启商业化收费。本次调整后，相关对话、自主智能运维及定时任务等功能将开始收费。调整过程不会影响存量用户已有设置和历史任务记录。容器服务Agent以积分（Credit）作为计量单位，免费开通，支持按量付费及预付费资源包抵扣。使用容器服务Agent的对话、自主智能运维及定时任务等功能时产生的模型资源消耗会折算为积分进行计费。&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;腾讯混元发布最新语音识别模型Hy ASR 3.0 preview&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;36氪获悉，腾讯混元正式发布新一代语音识别模型Hy ASR 3.0 preview。在开源评测集中，Hy ASR 3.0 preview在多语种的WER（Word Error Rate,词错误率）上都控制在3%左右，其中中文普通话WER 3.34%、英语WER 2.62%、粤语WER 3.12%。&lt;/p</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 23:46:22  +0800</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>“车企牌”电池相继上车，不只是PK宁德时代</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/p/3925382191708552?f=rss</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;“车企牌”电池正在不断涌现，并交付上车。鸿蒙智行推出了巨鲸电池，理想汽车推出了理想牌电池，不久前的7月30日晚，小米正式对外发布了龙甲电池。&lt;/p&gt;
+  &lt;p&gt;车企正试图通过自有电池品牌，将电池的每个技术点攥在手中，并抢占用户心智。&lt;/p&gt;
+  &lt;p&gt;这些汽车品牌的统一做法，就是“穿透式管理”，从电芯到电池包的技术和性能标准，车企全部主导定义，甚至部分参与电芯材料开发，并对核心供应链和生产制造环节全流程介入和监管。换句话说，“车企牌”电池是车企技术和标准的全面贯彻。&lt;/p&gt;
+  &lt;p&gt;“甚至电池厂的核心岗位招聘，车企都要参与面试把关。”有行业人士透露。&lt;/p&gt;
+  &lt;p&gt;这与过往的动力电池合作有着明显区别。据36氪了解，长期以来，头部动力电池公司如宁德时代等凭借技术实力，常常为车企供应相对成熟的系统级方案，尤其是旗舰类产品，如麒麟电池、神行电池等，车企能做的往往是提出需求，而定制开发的空间则相对有限。&lt;/p&gt;
+  &lt;p&gt;但从“车企牌”电池的核心指标来看，车企往往有着更多的开发需要。比如巨鲸电池主打全温度周期的热防护标准，小米龙甲电池强调2000次循环和500J底部撞击标准等，理想汽车牌电池也追求“8年16万公里电池健康度不低于75%”，蔚来也提出过15年循环寿命的电池研发计划。&lt;/p&gt;
+  &lt;p&gt;此外，动力电池做为电动汽车的心脏级零部件，常年占据30%成本结构，车企来把控电池开发和生产的全流程，从长期来看，也能确保供应链的稳定性和成本掌控力。&lt;/p&gt;
+  &lt;p&gt;综合来看，车企对动力电池的全流程掌控需要，注定了“车企牌”电池今天开枝散叶的局面。&lt;/p&gt;
+  &lt;p&gt;但与此同时，动力电池头部供应商宁德时代，也在竭力塑造消费者对宁德时代电池性能、安全性的认知。在机场、高铁站、商超等人群密集的地方，经常能看到“选电车看电池，认准宁德时代”的广告语。&lt;/p&gt;
+  &lt;p&gt;据36氪了解，即便理想i6为欣旺达电池多给了两年延保，但售出的车型中，仍有超过一半的消费者选择了宁德时代电池。&lt;/p&gt;
+  &lt;p&gt;因此，当车企试图将自有电池品牌推向台前时，经受过宁德时代“Intel Inside”战略洗礼的消费者，往往会提出这样的质疑——车企自研的电池包能否比得上宁德时代。&lt;/p&gt;
+  &lt;p&gt;某种程度上，这似乎是个目前难有定论的问题。&lt;/p&gt;
+  &lt;p&gt;不少电池行业人士对36氪表示，宁德时代的壁垒在于工艺管控能力、生产一致性。而且无论车企的自建产线，还是二三线电池厂商都很难在短时间内，追平宁德时代的这一优势，因为“一定要有足够大的生产体量，才能做有效的筛选和试错”。&lt;/p&gt;
+  &lt;p&gt;通常情况下，更高的一致性，意味着更低的续航跳水、补能异常，甚至安全事故的概率。但车企自建的产线，和二三线电池厂的生产一致性水平，也可以通过增加测试工序等手段进行一定弥补。&lt;/p&gt;
+  &lt;p&gt;而且，尽管在产品一致性上不及宁德时代，但“车企牌”电池亦有其优势。&lt;/p&gt;
+  &lt;p&gt;36氪从一些行业人士处了解到，“车企牌”电池的产品定义、设计、生产通常由车企进行全方位管控，部分自研电池的车企，还会监督到电池的二三级子零件供应商，以确保最终的产品性能符合自己的高标准。&lt;/p&gt;
+  &lt;p&gt;除此之外，车企对整车更为熟悉，因此“车企牌”电池的BMS算法，“在应用端可能比电池厂更好”。或许未来相当一段时间内，“车企牌”电池都会保持与宁德时代相持而行。&lt;/p&gt;
+  &lt;h3&gt;&lt;strong&gt;生产一致性，宁德时代的竞争壁垒&lt;/strong&gt;&lt;/h3&gt;
+  &lt;p&gt;动力电池行业历经多年发展，动力电池技术、设备的成熟与普及，令各电池厂商间的技术代差逐渐拉齐。&lt;/p&gt;
+  &lt;p&gt;电池产品间的竞争，越来越聚焦于生产的一致性。&lt;/p&gt;
+  &lt;p&gt;许多行业人士都承认，宁德时代的电芯一致性，领先一众二三线电池厂。一个相对直观的体现是——“国内电芯，唯一不分档次的厂家就是宁德时代，因为都是一样的”。&lt;/p&gt;
+  &lt;p&gt;“一致性不是那么好做的”。有行业人士告诉36氪，几乎所有的生产要素都会到动力电池的工艺控制，包括现场的湿度、温度、杂质、原材料选用等。&lt;/p&gt;
+  &lt;p&gt;而电池厂商“一定要有足够大的生产体量，才能做有效的筛选和试错”。因而短期内，二三线电池厂商的生产一致性，很难赶上宁德时代。&lt;/p&gt;
+  &lt;p&gt;而一致性之所以重要，是因为它能够直接影响到电池包的容量，甚至有可能引发安全事故。有电池行业人士表示，即便是行业公认更具本征安全的磷酸铁锂电池包，同样强调生产的一致性。&lt;/p&gt;
+  &lt;p&gt;评估生产一致性的直接指标，是压差、内阻差异、尺寸差异等。&lt;/p&gt;
+  &lt;p&gt;有行业人士举了个例子解释压差对电池包容量的影响：“原本电池包按100度电的容量去设计，但如果其中有颗电芯的电压只能达到98度，那BMS的均衡策略，会</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 18:27:21  +0800</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>自研高性能分布式解决方案，「芯晓科技」将芯片电源签核周期从几周缩短至几天 | 水下项目</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/p/3925067918227591?f=rss</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;一枚先进制程芯片从设计、验证，到流片、制造，需要经过上百个环节。其中电源签核（Sign-off）是设计流程最后的、也最重要的一环，相当于建造一栋大楼时对全楼供电系统进行竣工验收。&lt;/p&gt;
+  &lt;p&gt;具体来说，电源核签是通过对电源网络的上亿个节点进行整体分析，测试供电网络的功耗、电压降与电迁移等表现，从而决定芯片能否顺利进入量产流片。一旦结果出错，不仅导致芯片性能不达标，甚至会造成流片失败。&lt;/p&gt;
+  &lt;p&gt;由于芯片电源网络是由大量金属线组成的互联结构，因此电源签核时必须将其作为一个整体进行分析，“相当于求解一个维度高达数亿的稀疏矩阵方程，完成一次需要大量时间。”「芯晓科技」总经理谢卓解释道。&lt;/p&gt;
+  &lt;p&gt;而随着芯片工艺制程不断缩小，晶体管数量指数级增加，电源核签的周期被进一步不断拉长，一次完整的电源签核往往需要几周时间之久。如果分析结果不理想，设计工程师还需要根据反馈修改版图，再重复一轮电源签核。&lt;/p&gt;
+  &lt;p&gt;针对这一行业痛点，芯晓科技运用分布式矩阵求解技术，打破电源核签效率制约芯片交付周期瓶颈。公司推出的首款数字电源签核工具“IcPower”，支持7nm等先进工艺，能满足百亿门级芯片电源，在典型测试用例中速度是国外大厂工具的4.5-8.5倍，目前已在国内多家芯片厂商的芯片设计环节投入使用。&lt;/p&gt;
+  &lt;h2&gt;&lt;strong&gt;1.采用分布式求解技术，提高电源核签效率3-10倍&lt;/strong&gt;&lt;/h2&gt;
+  &lt;p&gt;谢卓在创办芯晓科技以前，曾任国际知名EDA厂商Cadence电源完整性分析工具Voltus的中国技术团队负责人。&lt;/p&gt;
+  &lt;p&gt;据他介绍，分布式求解的核心技术思路，来源于计算数学领域的“区域分解法”，通过将电源核签的巨大矩阵拆分为许多可以高效计算的小矩阵，用多台计算机并行运算，从而缩短整体求解时间，每个分析工具在求解大规模问题时候都会采用类似方法，但难点在于各个工具求解的效率会参差不齐。&lt;/p&gt;
+  &lt;p&gt;谢卓表示，难点同时集中在算法和工程两方面。&lt;/p&gt;
+  &lt;p&gt;一是要切得“科学”，也就是针对电源网络稀疏矩阵的特性，采用基于图论的智能区域分解算法，将百亿级的全局矩阵科学地切分为多个子矩阵，最小化子矩阵间的边界耦合。&lt;/p&gt;
+  &lt;p&gt;二是需要运用分布式矩阵求解器优化节点间的通信拓扑和消息传递机制，大幅降低分布式环境下的网络通信开销。在分布式切分求解过程中，还需要引入严格的数值稳定性控制算法，确保分布式计算与单机高精度求解器的结果，达到数学意义上的严格一致，从而满足先进制程严苛的签核精度要求。&lt;/p&gt;
+  &lt;p&gt;芯晓科技正是凭借团队在算法和工程层面的技术积累和创新，使IcPower相比国外工具速度提升上3-5倍，“对于一些耗时特别长的动态分析，部分测试水平可以做到10倍以上的速度提升，以前需要跑几周的电源签核，IcPower几天就能完成。”谢卓表示。&lt;/p&gt;
+  &lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/20260804/v2_210c834470104dd991a6a16952f88525@5688585_oswg35555oswg1031oswg440_img_000?x-oss-process=image/format,jpg/interlace,1" /&gt;&lt;/p&gt;
+  &lt;p class="img-desc"&gt;IcPower实测性能对比&lt;/p&gt;
+  &lt;h2&gt;&lt;strong&gt;2.抓住国产替代红利，致力于打造芯片设计平台&lt;/strong&gt;&lt;/h2&gt;
+  &lt;p&gt;和许多近几年出现的EDA工具初创企业一样，芯晓科技切入电源签核赛道也是想抓住当下EDA行业“国产替代”的窗口期。&lt;/p&gt;
+  &lt;p&gt;全球EDA市场长期被Synopsys（新思科技）、Cadence（楷登电子）、Siemens EDA（西门子EDA）三大巨头垄断。中国银河证券报告显示，三家在全球市场中的份额约为74%。而近年来不断升级的中美科技博弈，使越来越多国内芯片开始重视使用国产工具，将其作为替代或备份方案。&lt;/p&gt;
+  &lt;p&gt;基于性能自信，芯晓科技在商业模式上选择对标国外工具，以软件授权为主，定价与国外工具相当。目前IcPower已在国内多家芯片设计公司投入使用，覆盖国产CPU、GPU、智驾芯片等类型，并在应用过程中借助客户的广泛设计用例与测试平台，不断迭代自身产品性能。&lt;/p&gt;
+  &lt;p&gt;谢卓透露，2025年芯晓科技营收达到数百万元。“软件的研发成本基本是固定的，客户越多，盈利能力就能越强。”&lt;/p&gt;
+  &lt;p&gt;但他也坦承，拓展客户是当下商业化的难点。“客户往往担心创业公司难以保证产品供应的持续性，因此首选规模更大的企业规模，虽然大公司</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:31:59  +0800</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>一层“布”涨价270%之后，投资机构用数亿元投票玻璃基板，巽霖科技完成近2亿元B轮融资</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/p/3924953058605444?f=rss</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;【导语】当前，电子级玻纤布价格较2025年低点翻倍、FR-4覆铜板涨幅超270%，AI封装载板部分交期拉长至6个月以上，有机基��供给危机持续加深。在此背景下，&lt;/strong&gt;国内玻璃基板领军企业巽霖科技宣布完成近2亿元B轮融资——这已是该公司半年内完成的第三轮次融资。本轮由英诺基金、千乘资本、海目星、光莆股份、同鑫资本等新股东投资，金雨茂物、海通开元、北岸产投等老股东持续加码。募集资金将主要投向玻璃基板产能扩张、封装产线建设投产、制程精度升级研发，以及光通讯前沿应用布局。&lt;/p&gt;
+  &lt;p&gt;&amp;nbsp;&lt;/p&gt;
+  &lt;h2&gt;&lt;strong&gt;股东结构：市场化资本、产业资本、区域国资同席，老股东再投票&lt;/strong&gt;&lt;/h2&gt;
+  &lt;p&gt;这一轮的股东阵容，呈现鲜明的“三重奏”：以英诺基金、千乘资本、同鑫资本为代表的市场化硬科技基金，长期深耕半导体与先进制造；以海目星、光莆股份为代表的产业资本，分别来自激光装备与光通讯两大与玻璃基板强相关的产业上下游；以金雨茂物、北岸产投、海通开元为代表的市场化基金、区域国资与券商系资本，则在本轮继续加码。多元股东的持续投入，为公司的产业化进程提供了坚实支撑，也是对其量产进展最直接的确认。&lt;/p&gt;
+  &lt;h2&gt;&lt;strong&gt;行业背景：载板紧缺与涨价潮叠加，玻璃基板迎来确定性窗口&lt;/strong&gt;&lt;/h2&gt;
+  &lt;p&gt;这轮融资本质上是一次对时间窗口的卡位。AI算力狂飙之下，封装载板持续紧缺，ABF载板供不应求、交期一再拉长；而当芯片封装尺寸不断突破、光模块速率持续跃升，有机基板在热膨胀匹配、高频损耗与布线密度上，正在逼近物理极限。巨头的选择已经给出答案——英特尔宣布玻璃芯基板（GCS）进入大规模量产，台积电CoPoS试产线年内通线，三星、SKC Absolics加速送样与量产准备。玻璃基板，正在从巨头的实验室走向产业的中心。&lt;/p&gt;
+  &lt;p&gt;&amp;nbsp;&lt;/p&gt;
+  &lt;h2&gt;&lt;strong&gt;替代大逻辑：一层“布”卡住了有机基板，三大应用走向全面玻璃基化&lt;/strong&gt;&lt;/h2&gt;
+  &lt;p&gt;比巨头动向更值得关注的，是有机基板的成本地基正在松动。2025年下半年以来，PCB产业链经历了一轮罕见涨价：覆铜板价格大幅攀升，PCB厂商全线调价。而涨价的真正源头，不是铜箔，也不是树脂，而是一层“布”——电子级玻璃纤维布。它的价格较2025年低点翻倍，行业库存降至历史极低位，高端低介电产品被海外厂商高度垄断，而扩产以年计。这层“布”的紧缺，短期内无解。&lt;/p&gt;
+  &lt;p&gt;玻纤布之所以不可或缺，是因为它是有机基板的“骨架”，核心使命之一正是热应力匹配：AI服务器PCB层数不断攀升，为了让有机基材的热膨胀系数贴近硅芯片，行业不得不大量使用昂贵的低CTE特种玻纤布。换句话说，&lt;strong&gt;有机基板正在用越来越贵的“布”，去模仿玻璃与生俱来的性能&lt;/strong&gt;——玻璃CTE天然与硅匹配，介电损耗远低于有机材料，而且根本不需要这层“布”。当“补丁”的成本越过材料替代的成本拐点，玻璃基化就从可选项变成了必然项。但“玻璃基化”并不是一件事，而是三件事——三大应用的需求逻辑、技术指标与产业节奏，截然不同：&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;第一类，PCB替代——一场由经济性驱动的存量替代，节奏最快。&lt;/strong&gt;面向AI服务器背板、高频通信板与新型显示基板，替代对象是FR-4与传统PCB，逻辑简单而锋利：性能更好，成本更低。信号损耗显著降低，显示与HDI基板场景的综合成本大幅优于PCB基板。这一类比拼的是大规模制造与成本控制能力，是当前放量的主战场——2026年，将是玻璃基PCB的替代元年。&lt;/p&gt;
+  &lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/20260804/v2_347f933315314b7bacecb2f9f9a631a8@5284654_oswg3007833oswg2000oswg1123_img_png?x-oss-process=image/quality,q_80/format,jpg/interlace,1" /&gt;&lt;/p&gt;
+  &lt;p class="img-desc"&gt;玻璃基板替代传统PCB示意图&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;第二类，ABF载板替代——由可靠性与供给安全驱动，节奏居中。&lt;/strong&gt;面向超大尺寸FC-BGA封装、Chiplet与HBM高带宽存储，替代被海外垄断且持续紧缺的载板。这是一场硬指标的对决：翘曲、线宽线距、孔径与深宽比全面收紧，考验的是精细制程与可靠性验证的深水区能力。相关产品将</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:18:21  +0800</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东山精密涨停背后：36氪企业全情报捕捉市场机会</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/p/3924913931679877?f=rss</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/20260804/v2_2e223b3f6f994090a3d4944d9162d843@5284654_oswg647144oswg1080oswg459_img_000?x-oss-process=image/format,jpg/interlace,1" /&gt;&lt;/p&gt;
+  &lt;p class="img-desc"&gt;36氪企业全情报带你发现涨停背后的机会&lt;/p&gt;
+  &lt;h3&gt;&lt;strong&gt;开篇，先给大家送个福利&lt;/strong&gt;&lt;/h3&gt;
+  &lt;p&gt;最近不少朋友在体验企业全情报，我们也准备了一波奖品回馈大家。&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;体验小程序，完成15秒阅读+任意订阅一家企业即可免费参与抽奖。&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;奖品有影石Insta360&amp;nbsp;Luna&amp;nbsp;Ultra、运动相机挂脖支架、36氪航天徽章。&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;祝大家都能中奖，点击即可参与：👇&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;&lt;a href="https://lucky.nocode.com/v2/s/8VhKju6Ehgy" rel="noopener noreferrer" target="_blank"&gt;&lt;strong&gt;https://lucky.nocode.com/v2/s/8VhKju6Ehgy&lt;/strong&gt;&lt;/a&gt;&lt;/p&gt;
+  &lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/20260804/v2_a300936239e240d7a177ec6cfcc50c1d@5284654_oswg1734654oswg943oswg1668_img_png?x-oss-process=image/quality,q_90/format,jpg/interlace,1" /&gt;&lt;/p&gt;
+  &lt;p class="img-desc"&gt;扫码抽奖！&lt;/p&gt;
+  &lt;h3&gt;&lt;strong&gt;今日A股收盘数据&lt;/strong&gt;&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;上证指数：&lt;/strong&gt;3822.28&amp;nbsp;点，+0.33%&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;深证成指：&lt;/strong&gt;13885.71&amp;nbsp;点，+3.25%&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;创业板指：&lt;/strong&gt;3488.97&amp;nbsp;点，+5.64%&lt;/p&gt;
+  &lt;p&gt;&amp;nbsp;&lt;/p&gt;
+  &lt;h3&gt;&lt;strong&gt;东山精密8月4日上涨10.00%&lt;/strong&gt;&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;179.09 &amp;nbsp;+16.28 &amp;nbsp;+10.00%&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;当日开盘价168.76；交易量86.82万手；&lt;/p&gt;
+  &lt;p&gt;换手率6.26%；放量幅度0.07%&lt;/p&gt;
+  &lt;p&gt;3日涨幅+10.69%；5日涨幅-6.09%&lt;/p&gt;
+  &lt;p&gt;成交额：153.29亿；总市值：3280.23亿&lt;/p&gt;
+  &lt;p&gt;&amp;nbsp;&lt;/p&gt;
+  &lt;h3&gt;&lt;strong&gt;舆情分析：积极信息占比超九成，市场关注度持续提升&lt;/strong&gt;&lt;/h3&gt;
+  &lt;p&gt;近日，深市存储产业链相关公司接连释放积极信号，业界看好行业高景气度持续性。大普微发布自研SLC+QLC双模SSD方案，已进入客户灰度验证阶段，其2026年半年度预计归母净利润12亿-13.5亿元。江波龙控股股东提议回购股份，2026年上半年预计归母净利润92亿-110亿元。北京君正上半年预计营业总收入约39.89亿元，净利润10.79亿-12.82亿元。东山精密虽非存储企业，但业务相关，看好AI算力产业中长期发展，将依托协同布局把握机遇。&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;｜事件正负面性质分析&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;截止8月4日，此事件匹配的到全网舆情信息总量为56&lt;strong&gt;条&lt;/strong&gt;，正面信息&lt;strong&gt;52条&lt;/strong&gt;，占比&lt;strong&gt;92.9%&lt;/strong&gt;，负面信息&lt;strong&gt;0条&lt;/strong&gt;，占比&lt;strong&gt;0%&lt;/strong&gt;，中性信息&lt;strong&gt;4条&lt;/strong&gt;，占比&lt;strong&gt;7.1%&lt;/strong&gt;，&lt;strong&gt;事件舆论呈现出显著正面的倾向。&lt;/strong&gt;&lt;/p&gt;
+  &lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/202608</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 14:32:05  +0800</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Kimi K3与DeepSeek V4之间，隔着原生多模态的时间差</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/p/3924826666301831?f=rss</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+  &lt;p&gt;文 | 李炤锋&lt;/p&gt;
+  &lt;p&gt;编辑 | 张雨忻&lt;/p&gt;
+  &lt;p&gt;“长链任务如果只通过代码层面的反馈，误差可能会不断累积，最终效果会非常差。”谈及原生多模态的意义，一位多模态研究员表示，“视觉是一种更准确的反馈，也更贴近用户意图。”&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;过去一年，Coding与Agent能力不断改写大模型的排名，也成为AI最快兑现商业价值的场景之一。与此同时，随着Agent开始接管更多长链任务，越来越多的通用大模型开始匹配原生多模态能力。&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;今年1月，OpenAI发布的一份企业使用报告显示，在研发岗位最常使用的三类ChatGPT工具中，图片上传排在搜索和数据分析之后，位列第三。&lt;/p&gt;
+  &lt;p&gt;随着Agent开始生成网页、操作软件并检查运行结果，视觉的作用正在逐步进化：它不再只是用户交给模型的一张图片，也开始成为模型检查工作、发现错误和调整行动的反馈。&lt;/p&gt;
+  &lt;p&gt;刚刚过去的7月，月之暗面发布Kimi K3。这款总参数2.8万亿、支持100万token上下文的MoE（混合专家模型），在Coding和长程Agent能力之外，出色的原生多模态能力是K3的另一个标签。&lt;/p&gt;
+  &lt;p&gt;所谓原生多模态，是让图像、文字等数据从预训练或持续预训练阶段就共同塑造主模型，并在后训练中继续优化，最终参与Agent（智能体）的感知与决策。&lt;/p&gt;
+  &lt;p&gt;K3发布后曾以1679分登顶Arena Frontend Code榜单。该榜单由用户盲选模型生成的可交互网页进行排名，评判的不只是代码能否运行，也包括页面的最终效果。&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;浏览器开发平台Puter曾在测试网页中制造5处视觉偏差，K3对照目标页与运行页截图，全部找出且没有误报。得益于出色的原生多模态能力，K3能够看懂代码运行后的视觉问题，为下一轮修改提供依据。Kimi方面将这种在代码与截图之间反复迭代的方式称为“vision in the loop”：模型写完代码后查看页面，再根据视觉结果继续调整。&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;这些都离不开模型的多模态能力。&lt;/p&gt;
+  &lt;p&gt;除了月之暗面，阿里和字节也沿着原生多模态路线，将视觉作为通用模型的基础能力，在最新的Qwen3.8-Max和Doubao-Seed-2.1上，可以看到视觉理解和多模态输入都作为主要功能出现。&lt;/p&gt;
+  &lt;p&gt;而在国产模型头部梯队的另一边，DeepSeek、智谱和腾讯混元的最新通用基座则仍以文本输入为主。&lt;/p&gt;
+  &lt;p&gt;此前，DeepSeek创始人梁文锋曾说：“把AI训练做好，并不需要世界模型，甚至不用多模态。”但他同时表示：“多模态最终还是要做的。”&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;这两句话并不矛盾。各家公司对多模态的长期价值没有太大分歧，真正的分歧在于时机和代价。&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;在Coding快速迭代的阶段，要不要同步训练视觉，以及为此投入多少模型容量、数据和算力，正在影响国产头部模型的技术路线。&lt;/p&gt;
+  &lt;p&gt;&amp;nbsp;&lt;/p&gt;
+  &lt;h3&gt;&amp;nbsp;Agent为什么需要眼睛&lt;/h3&gt;
+  &lt;p&gt;做原生多模态，到底有没有必要？随着当下Agent的任务链越来越长，这个问题开始变得愈发具体。&lt;/p&gt;
+  &lt;p&gt;“很多时候我就喜欢截图输入。”一位来自某头部基模团队的研究员表示，“可能文本也能做到同样的需求，但是你得花很多上下文去描述视觉关系。”&lt;/p&gt;
+  &lt;p&gt;视觉输入能够带来更多便利，但不同用户对它的感知并不相同。“一般人可能感觉不到，但对于开发者群体而言，有多模态还是很方便。”&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;不过，这种需求并不只属于开发者。上述研究员提到，他身边一些并非AI从业者的用户，使用模型最多的场景之一就是制作PPT。“更专业的人可能需要更多能力、更多模态，但普通用户也会在具体场景里用到它。”&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;纯文本模型本身仍然“看不见”。实际系统可以调用OCR或独立VLM（视觉语言模型），先把图片转换成文字、标签、坐标或结构化字段，再交给文本模型推理。这些工具可以通过Agent框架或MCP接入，用“外挂”的形式获得视觉能力。&lt;/p&gt;
+  &lt;p&gt;从这个角度来看，“如何让Agent获得视觉输入能力”这个命题，不仅是一个基模研发问题，也是一道产品题。&lt;/p&gt;
+  &lt;p&gt;如果系统调得足够好，上游一个大的语言模型做中枢，下游放一个小一些的视觉模型，就像老板把一件小事分配给员工，足以解决大量普通任务。&lt;/p&gt;
+  &lt;p&gt;但在多模态研究员看来，这种模块化方案仍有边界。“如果调用一个工具，总归还是两个模型：一个LLM是‘瞎子’，下</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 11:05:05  +0800</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>36氪首发 | 两位“三清”博士联合创业做空间态势感知服务，完成数千万天使+轮融资</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/p/3924634192673153?f=rss</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;作者&amp;nbsp;|&amp;nbsp;乔钰杰&lt;/p&gt;
+  &lt;p&gt;编辑&amp;nbsp;|&amp;nbsp;袁斯来&lt;/p&gt;
+  &lt;p&gt;硬氪获悉，空间态势感知公司「清博空天」近日完成数千万元天使+轮融资。本轮融资由明荟投资领投，兴湘投资、泰亚投资共同参与。Maple Pledge 枫承资本出任私募股权融资顾问。本轮资金将主要用于空间目标监测网络建设、空间态势感知算法平台迭代、核心技术团队扩充及重点客户开拓。&lt;/p&gt;
+  &lt;p&gt;随着低轨卫星和空间碎片数量快速增长，近地轨道正在变得更加拥挤，卫星碰撞风险随之提升，空间态势感知（Space Situational Awareness，SSA）逐渐成为卫星运营的重要基础能力。&lt;/p&gt;
+  &lt;p&gt;此前，国内空间目标监测、轨道预警等任务主要由国家级科研与工程体系承担。但随着商业航天进入规模化发展阶段，大量商业卫星进入轨道运行，卫星运营方对于碰撞预警、轨道安全管理等服务的需求不断增加，市场亟需商业化空间态势感知解决方案。&lt;/p&gt;
+  &lt;p&gt;清博空天成立于2025年8月，是一家专注于太空安全领域的科技服务公司，主要面向卫星运营方、星座建设方等客户，为在轨卫星提供空间态势感知、空间碎片监测以及碰撞预警服务。&lt;/p&gt;
+  &lt;p&gt;空间态势感知解决的是“看清太空、预测风险”的问题，它可以类比为地面交通中的地图导航系统，高德地图关注的是城市道路中的车辆流动，而SSA关注的是近地轨道中的“星流”；天网系统通过海量数据识别风险目标，而SSA则需要在轨道环境中预测卫星之间可能发生的碰撞风险。&lt;/p&gt;
+  &lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/20260804/v2_417460d9d05146619a1941f2534593f9@5920579_oswg383119oswg868oswg482_img_000?x-oss-process=image/format,jpg/interlace,1" /&gt;&lt;/p&gt;
+  &lt;p class="img-desc"&gt;（图源/企业）&lt;/p&gt;
+  &lt;p&gt;公司两位联合创始人曾毅强、班曹活均为清华大学“三清”博士（本硕博阶段均就读于清华大学），长期从事航天动力学、空间态势感知相关研究。其中，班曹活曾参与空间站精密定轨预报相关工作。清华大学航空航天学院宝音教授作为两人的共同博士导师，目前担任清博空天首席战略科学家，为公司在航天动力学与空间安全方向提供战略和技术指导。&lt;/p&gt;
+  &lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/20260804/v2_c0e90809488a47159a812c2a2e0a80a5@5920579_oswg589124oswg868oswg578_img_000?x-oss-process=image/format,jpg/interlace,1" /&gt;&lt;/p&gt;
+  &lt;p class="img-desc"&gt;（图源/企业）&lt;/p&gt;
+  &lt;p&gt;公司的创始人曾毅强博士期间的主要研究方向为空间态势感知，解决了我国某重点卫星的核心太空安全问题，相关成果得到工程化落地和批量部署，获得某部科学技术进步奖。&lt;/p&gt;
+  &lt;p&gt;公司联合创始人班曹活曾参与空间站的精密定轨与预报工作，通过融合历史数据、实测大气密度数据及现有大气密度模型，构建了新型修正模型，将空间站定轨预报一天的精度提升至500米，使其年均碰撞规避次数从三十余次降至3至5次，大幅降低了运营成本和操作风险。工作贡献获得中国科学院的付费订单和书面表彰。&lt;/p&gt;
+  &lt;p&gt;曾毅强介绍称，目前公司已经建成空间态势感知数据服务平台，并实现对下游重点客户的商业化服务。为了进一步提升平台服务能力和服务质量，公司正在建设天地一体化的监测体系，包括光学望远镜、无线电监测设备以及相控阵雷达等多种数据采集方式。&lt;/p&gt;
+  &lt;p&gt;在空间态势感知领域，数据采集只是第一步。达标的原始观测数据在经过轨道计算、目标识别、风险分析等多个环节处理后，才能转化为实际可用的决策信息。清博空天团队在数据处理、分析和应用环节拥有世界领先的核心优势。&lt;/p&gt;
+  &lt;p&gt;商业化方面，清博空天目前已与我国某巨型星座运营企业围绕软件系统和数据服务开展业务合作，提供接口建设和标准化碰撞预警信息服务。目前相关系统正在进行测试，后续将长期为客户提供碰撞预警信息服务。&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;以下是创始人问答节选：&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;硬氪：相比于火箭制造和卫星通信，空间态势感知和预警在中国还处在更早期的阶段，商业公司在这个领域有什么优势？&lt;/strong&gt;&lt;</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04 10:59:50  +0800</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>36氪首发 | 为果链、头部灵巧手公司供货，新型减速器厂商完成超亿元融资，估值破10亿</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/p/3924628805351811?f=rss</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;作者&amp;nbsp;|&amp;nbsp;乔钰杰&lt;/p&gt;
+  &lt;p&gt;编辑&amp;nbsp;|&amp;nbsp;袁斯来&lt;/p&gt;
+  &lt;p&gt;硬氪获悉，精密减速器企业陶世智能科技有限公司（以下简称“陶世”）近日完成超亿元融资。本轮融资由国创集团，海川聚义，杭州众燊，新智资本参与，德太资本担任财务顾问。融资资金将主要用于产品研发、产线扩建以及机器人领域市场拓展。&lt;/p&gt;
+  &lt;p&gt;陶世成立于2016年，总部位于深圳，主要研发和生产正交90度微型减速器及机器人关节模组。公司核心产品为微型环面包络蜗轮蜗杆减速器，通过将减速与转角功能集成在单一结构中，实现更小体积、更高精度的动力传输。&lt;/p&gt;
+  &lt;p&gt;目前，陶世产品已进入多家消费电子与智能制造领域头部企业的供应链，并在人形机器人领域与近百家上下游企业建立合作。其中，面向灵巧手推出的关节模组已签署10万台供货协议，客户覆盖灵巧手产业链核心企业。&lt;/p&gt;
+  &lt;p&gt;随着人形机器人进入产业化阶段，核心零部件供应链正在加速成熟。行业数据显示，人形机器人中执行器系统（电机、减速器、丝杠等）约占整机成本45%，传感器系统约占15%，两者合计超过60%。作为连接动力源与执行端的核心部件，减速器承担着动力传递和精度控制作用，直接影响机器人关节的力量、速度、稳定性和灵活性。目前，减速器也是机器人产业链国产替代的重要环节之一。&lt;/p&gt;
+  &lt;p&gt;与传统谐波、RV、行星减速器不同，陶世选择的是正交传动路线。“传统方案中，要实现90度转向通常需要额外增加转角器，这种方式会带来体积增加、精度损失以及成本提升等问题。”陶世创始人陶玉龙向硬氪介绍。&lt;/p&gt;
+  &lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/20260804/v2_4892712f032541ed9fa28ea9f6975611@5920579_oswg321742oswg1080oswg496_img_000?x-oss-process=image/format,jpg/interlace,1" /&gt;&lt;/p&gt;
+  &lt;p class="img-desc"&gt;（图源/企业）&lt;/p&gt;
+  &lt;p&gt;陶世的技术基础来自环面包络蜗轮蜗杆结构。传统蜗轮蜗杆虽然天然具备正交传动能力，但由于通常采用单齿啮合方式，在微型化之后容易出现承载能力不足、效率下降以及寿命降低等问题。陶世通过优化齿面接触结构，引入环面包络设计，使多个齿同时参与传动，提高承载能力和传动稳定性。&lt;/p&gt;
+  &lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/20260804/v2_50efc4944cd540bdb18b64ab1ce1419d@5920579_oswg94990oswg641oswg406_img_000?x-oss-process=image/format,jpg/interlace,1" /&gt;&lt;/p&gt;
+  &lt;p class="img-desc"&gt;（图源/企业）&lt;/p&gt;
+  &lt;p&gt;为了实现量产，陶世从加工设备、检测体系、热处理工艺以及润滑材料等多个环节进行了自研开发。加工端，公司基于进口设备结构进行重新设计，开发7轴5联动磨削方案，解决环面蜗杆高精度加工难题；检测端，公司自主搭建测试设备，对产品精度、寿命和可靠性进行验证；同时，通过优化材料和润滑体系，提高产品运行效率和寿命。&lt;/p&gt;
+  &lt;p&gt;经过多年研发，陶世形成了一套围绕微型正交减速器的制造体系。目前，公司环面包络蜗轮蜗杆减速器相比传统方案体积缩小约40%，精度达到±0.5弧分左右，抗拉强度达到1300兆帕，寿命可达到1万小时。&lt;/p&gt;
+  &lt;p&gt;成立初期，陶世主要面向工业自动化市场。2024年，公司获得航天领域客户的首笔订单，并随后进入多家消费电子制造龙头企业的供应链体系，完成了产品在工业场景中的初步验证。&lt;/p&gt;
+  &lt;p class="image-wrapper"&gt;&lt;img src="https://img.36krcdn.com/hsossms/20260804/v2_f249eee5df624350979f6f8dbbbc4f04@5920579_oswg199287oswg1080oswg438_img_000?x-oss-process=image/format,jpg/interlace,1" /&gt;&lt;/p&gt;
+  &lt;p class="img-desc"&gt;（图源/企业）&lt;/p&gt;
+  &lt;p&gt;2025年，公司订单的进一步增长来自具身智能产业的发展。随着人形机器人产业进入商业化探索阶段，灵巧手逐渐成为产业链关注的核心部件之一。相比传统机械臂，人形机器人的灵巧手需要完成抓取</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:14:17  +0800</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>中信证券：传统主业稳健+AI收入渐显，美股应用软件迎来估值修复契机</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/newsflashes/3925919120259207?f=rss</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>36氪获悉，中信证券研报表示，当下“AI吞噬软件”叙事正在逐步证伪：龙头厂商收入与在手订单仍保持稳健增长，应用软件基本面尚未出现市场此前担忧的结构性失速；同时模型厂商通过嵌入CRM、ERP、ITSM和HCM等既有工作流推进企业级落地，传统软件厂商的数据、行业知识及客户服务能力仍构成核心壁垒。短期看，模型同质化属性提升、软件企业AI收入占比提升等有望推动美股软件板块估值持续向上修复。中期维度，板块能否由估值修复走向反转，仍取决于AI产品能否带动软件企业整体营收增速回升，未来1—2个季度可能是重要观察窗口。</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:12:51  +0800</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>“哲源科技”完成近2亿元A2轮融资</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/newsflashes/3925940167325829?f=rss</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>36氪获悉，北京哲源科技有限责任公司在A2轮获得近2亿人民币融资。本轮融资由圣湘生物携产业基金领投，中科创星作为老股东持续跟进，张江科投等联合跟投。本轮融资将主要用于高价值创新IP的持续产出与全球资产布局，以及基于生命世界模型驱动的AI4S平台升级。</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:03:40  +0800</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>分红回购持续推进，券商多管齐下增强投资者信心</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/newsflashes/3925915502852233?f=rss</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>从多家券商筹划回购事宜或披露股份回购最新进展，到2025年年度分红密集落地增强投资者获得感，近期上市券商提振投资者信心动作频频，部分券商控股股东计划增持股份，也向市场传递出对国内资本市场长期投资价值的看好。在业内人士看来，在市场风格经历再平衡的过程中，低估值、有业绩的券商板块具备修复空间，ROE持续创新高、业务结构持续优化、盈利成长性提升是券商板块估值提升的重要驱动因素。就投资布局而言，优质头部券商、一级投资具备特色的券商以及衍生品、财富管理等特色业务突出的中型券商值得关注。（中证报）</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:50:30  +0800</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Lucid将在“运营重整”期间推迟推出平价电动车</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/newsflashes/3925900711442816?f=rss</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Lucid 首席执行官周二表示，该公司计划于2027年下半年推出更实惠的电动汽车，将原定于今年晚些时候的上市计划推迟，目前公司正在进行重大业务审查并削减成本。作为公司所谓“ 运营重置” 计划的一部分，Lucid 计划今年节省14亿美元现金，主要通过削减产量和库存来实现，此前该公司第二季度亏损持续扩大。（新浪财经）</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05 08:47:57  +0800</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>36氪</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>两市融资余额增加119.71亿元</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>https://36kr.com/newsflashes/3925915682322821?f=rss</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>36氪获悉，截至8月4日，上交所融资余额报13294.07亿元，较前一交易日增加61.49亿元；深交所融资余额报12547.38亿元，较前一交易日增加58.22亿元；两市合计25841.45亿元，较前一交易日增加119.71亿元。</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 08:13:50 +0800</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行发布「竹知了」相关情况说明；小红书封禁 AI 毒动画，未成年陪聊等 10 万账号；马斯克财富缩水2.45万亿元｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368389</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/4a/9a/4a9a88cfb9b2d46787e09c5ebfff24e1.png" /&gt;&lt;/p&gt;
+&lt;header&gt;
+&lt;h2&gt;​鸿蒙智行发布「竹知了」相关情况说明&lt;/h2&gt;
+&lt;/header&gt;
+&lt;p&gt;8 月 4 日晚，@ 鸿蒙智行发言人 发布关于近期「竹知了」相关网络信息的情况说明。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/49/0a/490aa41a7023f588fbca02944c1368d5.png" /&gt;&lt;/p&gt;
+&lt;p&gt;鸿蒙智行表示：长期以来，网络上持续存在恶意剪辑、仿冒相关高管声音、利用 AI 丑化肖像、虚假归因、侮辱诽谤等侵害个人合法权益的内容。我们一直依法开展日常取证和投诉。本次投诉是日常维权工作的一部分，针对的是具体侵权内容，并非针对「竹知了」玩具。&lt;/p&gt;
+&lt;p&gt;截至 8 月 4 日晚，共监测到相关网络信息累计 5.6 万余条。我们实际对其中 171 条具体侵权内容发起投诉，平台反馈下架 144 条。&lt;/p&gt;
+&lt;p&gt;经多部门复核，相关投诉均有明确侵权事实和留存证据，不存在仅为正常把玩、制作、展示或者销售「竹知了」的内容。我们未向任何电商平台投诉「竹知了」商品，也从未要求任何电商平台下架、停售该商品。网络上有关「全网下架」、「禁止销售」、「许多单纯展示玩具或分享童年回忆的普通视频也被连带下架，部分账号头像变灰、昵称被重置」等说法与事实不符。（来源：cnBeta）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/bc/4a/bc4ac2035b7d267a044bbebd17e4972d.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果向法院申请临时禁令，阻止 OpenAI 使用、披露其机密信息&lt;/h2&gt;
+&lt;p&gt;8 月 4 日，苹果当地时间周一向美国法院申请初步禁令，要求禁止两名前员工以及 OpenAI 获取、访问、使用或披露涉嫌属于苹果的机密信息。与此同时，苹果正推进其商业机密侵权诉讼。&lt;/p&gt;
+&lt;p&gt;与此同时，苹果周一还提交了一项加快证据开示程序的动议，要求被告提供与涉嫌访问苹果专有信息和商业机密相关的文件。&lt;/p&gt;
+&lt;p&gt;苹果还请求法院要求诉讼中涉及的两名前苹果员工刘畅（Chang Liu，音译）和唐坦（Tang Yew Tan，音译）接受庭前证词询问（deposition）。此外，苹果还要求 OpenAI 员工彭宇婷（Yu-Ting Peng，音译）以及另一位曾任职于苹果、目前供职于 OpenAI、但身份尚未公开的员工接受问询。&lt;/p&gt;
+&lt;p&gt;刘畅曾担任苹果高级系统电气工程师，唐坦则曾任苹果&amp;nbsp;iPhone&amp;nbsp;和 Apple Watch 产品设计副总裁。&lt;/p&gt;
+&lt;p&gt;苹果还要求 OpenAI 以及其商业硬件部门 io Products（同样被列为本案被告）的企业代表接受庭前证词询问。苹果在提交给法院的文件中表示：「如果法院不发布初步禁令，苹果将遭受无法弥补的损害。」&lt;/p&gt;
+&lt;p&gt;对此，OpenAI 当地时间周一晚间在一篇博客文章中回应称：「苹果申请初步禁令既基于错误信息，也完全没有必要，因为我们既没有，也不希望拥有苹果的任何商业机密。」（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;ChatGPT Atlas 浏览器 8 月 9 日停止服务，用户需 10 天内导出书签&lt;/h2&gt;
+&lt;p&gt;8 月 4 日，OpenAI 宣布 ChatGPT Atlas 将于 8 月 9 日正式停止服务，此后既不再推送功能更新，也不再修补安全漏洞，这款产品从 2025 年 10 月 21 日登陆 macOS 算起，满打满算才活了不到十个月。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/86/2d/862d28ec0928ef5b500db756da10e8b6.png" /&gt;&lt;/p&gt;
+&lt;p&gt;OpenAI 官方表示，ChatGPT Atlas 的所有数据不会自动迁移至新版 ChatGPT。如果用户希望保存过往书签、历史记录，则需要将其导出为 HTML 文件，再导入到 Chrome 等其他浏览器。&lt;/p&gt;
+&lt;p</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 16:25:33 +0800</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>飞书并入豆包：字节跳动的一次目标重塑</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368374</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：视觉中国&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;7 月 30 日，字节跳动下发内部邮件，完成了近年来力度最大的一次 ToB 业务架构调整：飞书产品团队与豆包产品团队整合，成立新的豆包产品团队，由豆包负责人赵祺统筹，飞书负责人谢欣向其汇报；飞书商业化团队则与火山引擎整合，成立新的 ToB GTM 组织「创造力服务平台」，由火山引擎负责人谭待负责。&lt;/p&gt;
+&lt;p&gt;关于这次调整，字节暂时还没有对外给出系统性的解读，但如果我们站在今天这个时间节点去观察，这件事可能并不只是一次简单的部门合并、汇报关系变化或者组织架构调整，而有可能是飞书自诞生以来最根本的一次使命转向。&lt;/p&gt;
+&lt;p&gt;这件事背后，既藏着字节对 AI 未来的战略下注，也有着飞书这家从内生工具成长起来的产品，走到今天必须面对的关键转折点&amp;mdash;&amp;mdash;当先进企业最迫切的问题已经发生变化，飞书还能不能像它诞生时那样，率先定义问题，并提供一套更好的答案？&lt;/p&gt;
+&lt;p&gt;这可能才是这次调整真正值得讨论的地方。&lt;/p&gt;
+&lt;h1&gt;一、飞书来自于一次「目标创新」&lt;/h1&gt;
+&lt;p&gt;要读懂这次转折，或许要先把镜头拉远，回到飞书诞生的起点。&lt;/p&gt;
+&lt;p&gt;飞书最初并不是为了进入 ToB 市场而从零设计的产品。&lt;/p&gt;
+&lt;p&gt;2016 年前后，字节跳动正处于高速扩张期，员工、业务和地域边界迅速扩大，原有工具越来越难以承载这家公司的工作方式。信息散落在聊天、邮件、会议和文档里，上下文在层级传递中不断损耗，一线员工难以在离问题最近的地方做出判断。&lt;/p&gt;
+&lt;p&gt;既然外部没有合适的答案，就自己造一个。&lt;/p&gt;
+&lt;p&gt;飞书由此从内部效率工程中生长出来。它把字节已经验证过的一套组织实践&amp;mdash;&amp;mdash;信息透明、文档驱动、分布式决策与 OKR 对齐&amp;mdash;&amp;mdash;逐渐固化为产品。&lt;/p&gt;
+&lt;p&gt;从诞生第一天起，飞书就和传统 OA 产品走在两条完全不同的路上。它后来被概括为「Context, not Control」的理念，背后是一个不同的判断：组织生产力的损耗，不只来自员工是否执行到位，也来自他们是否获得了足够充分的上下文。&lt;/p&gt;
+&lt;p&gt;飞书真正的创新并不只是把聊天、文档、会议和日历放到了一起。更重要的是，它率先定义了一个有意义的问题：&lt;strong&gt;数字化时代，怎样让信息更充分地在组织中流动，让更多人能够自主决策？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;它也给出了一个经过自身验证的答案。&lt;/p&gt;
+&lt;p&gt;2019 年前后，这套在字节内部生长出来的产品与方法开始向外溢出。许多创业公司和知识密集型企业选择飞书，不只是因为产品体验更现代，也因为它们希望获得一部分「字节如何工作」的答案。&lt;/p&gt;
+&lt;p&gt;很多人至今仍对早期的飞书未来无限大会印象深刻。台上的主角是一批来自不同行业的客户。大家谈组织、谈协作、谈如何减少会议、如何让目标被更多人看见。看起来是在介绍软件，真正被传播的却是一套关于公司应该怎样工作的共同信念。&lt;/p&gt;
+&lt;p&gt;那毫无疑问是飞书最「锐利」的阶段。它用一个新的问题和一套新的答案，重塑了传统企业软件的管控逻辑。飞书早期的 PLG，也因此不只是产品驱动增长，更包含了一种世界观的自然扩散。&lt;/p&gt;
+&lt;h1&gt;二、当锐利进入厚重的现实&lt;/h1&gt;
+&lt;p&gt;一套新的方法被证明之后，产品终究要走进更大的市场。&lt;/p&gt;
+&lt;p&gt;飞书从协同办公进入组织管理，又继续深入业务管理。People、多维表格、项目和低代码等产品，让它不再只处理沟通和文档，而是进入招聘、绩效、门店、销售、研发与生产等具体流程。客户也从互联网公司扩展到汽车、消费零售和制造业。&lt;/p&gt;
+&lt;p&gt;这是一款企业软件成长的必经之路。&lt;/p&gt;
+&lt;p&gt;早期飞书像一把锥子，靠一个足够尖锐的判断，迅速刺穿旧有认知；进入更多行业之后，它面对的却是厚重的现实：复杂的权限、历史系统、采购流程、行业差异和长期交付。这个时候，只靠锐利已经不够，团队必须拿起锤子和锉刀，一下一下地往前推进。&lt;/p&gt;
+&lt;p&gt;飞书的定位变化，足以说明这条路径：从新一代协同办公，到组织管理，再到 2023 年提出「让业务先进一步」，它逐渐从输出一种组织世界观，下沉为解决企业每天面对的具体业务问题。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img alt="在2023秋季飞书未来无限大会上，飞书CEO谢欣介绍飞书智能伙伴等系列AI产品新功能，推动企业从数字化向AI Ready迈进。" src="https://imgslim.geekpark.net/uploads/image/file/0c/9a/0c9a8b0b82f052b3778619</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 15:20:06 +0000</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Elon Musk spends half his time talking robots and AI on Tesla earnings calls</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/04/elon-musk-spends-half-his-time-talking-robots-and-ai-on-tesla-earnings-calls/</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>An analysis of the last seven years of Tesla earnings calls shows just how little attention Musk pays to Tesla's car business.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4707,6 +4707,248 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 03:21:32 +0000</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>视触觉，或成机器人灵巧手指尖感知技术趋势</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12070</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>分辨率高，可测六维力，视触觉助力机器人感知更加敏锐、细腻</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 17:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>IPO冲刺中，智元机器人核心班底“华为化”：前谷歌科学家从合伙人名单消失</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/mFDVYdsliuDByQKcWFkh?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/mFDVYdsliuDByQKcWFkh?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 08:30:53 +0800</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>传 DeepSeek 重启融资；华为余承东：手机之后可能都要大规模涨价；首例破坏 AI 模型刑案宣判，程序员「删库跑路」获刑</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368444</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/dd/26/dd2687b38f3ac8e302a98db1a558d5ea.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;传 DeepSeek 重启融资&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;据多名交易人士透露，大模型公司 DeepSeek 重启了第二轮融资，本轮计划募资 500 亿元，投前估值约 5000 亿元，并计划将在 8 月下旬完成签约。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;多位投资人提到，DeepSeek 第二轮融资至少在 7 月中旬就已开启，但在 7 月底突然暂停，当时一些谈判候补名单上的投资人被告知签署融资协议的计划暂缓。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据介绍，DeepSeek 和正在谈判桌上的投资人们希望这次融资在重启后能低调进行。目前，一些此前积极接触的投资机构表示，他们还没有接到 DeepSeek 重启融资的消息，通道仍处在暂缓状态。（来源：财经）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/96/cf/96cfeb7c9cb8aa964200684c63b3cbaf.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Anthropic 证实正在组建内部芯片团队&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;据媒体报道，随着旗下模型需求快速增长，人工智能公司Anthropic正在组建团队，开发自研AI芯片。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;根据一份招聘信息以及公司声明，Anthropic正在招聘工程师，为其Claude模型设计定制芯片。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Anthropic一名发言人对媒体表示，公司正在组建内部半导体团队，为Claude设计专用芯片。这是Anthropic首次公开确认相关计划。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据悉，Anthropic将协同设计硬件和AI模型，使Claude能够在&amp;ldquo;满足客户需求的规模下&amp;rdquo;运行得更快、更高效。（来源：财联社）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;谷歌&lt;/span&gt;&lt;span style="font-weight: bold;"&gt;前&lt;/span&gt;&lt;span style="font-weight: bold;"&gt;首席科学家&lt;/span&gt;&lt;span style="font-weight: bold;"&gt; Jeff Dean &lt;/span&gt;&lt;span style="font-weight: bold;"&gt;宣布离职创业&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;当地时间 8 月 5 日，Google DeepMind 负责人哈萨比斯宣布卸下日常管理职责，转任 Google DeepMind 主席兼 Alphabet 首席科学家。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;几乎在同一时间，谷歌的灵魂人物、首席科学家杰夫&amp;middot;迪恩宣布将在任职 27 年后离职，并将创办新公司 Discovery Loop，未来尝试利用 AI 探索如何自动化科学研究和工程实验。与迪恩一同离职并创业的还有三名资深研究人员。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据外媒报道，迪恩表示他大约五周前才开始认真考虑创业。（来源：APPSO）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;马斯克：SpaceX 将独家采用英伟达芯片&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;近日，马斯</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 16:42:08 +0800</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>办公 Agent 爆火，模型大战进入下一阶段</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368429</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;strong&gt;&lt;span style="color: #000000;"&gt;作者｜Cynthia &lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;strong&gt;&lt;span style="color: #000000;"&gt;编辑｜ 靖宇&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;从今年 6 月到 8 月初，短短不到 60 天时间，有一件事几乎同时在新 BAT 发生。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;先是 6 月，阿里率先开启内部 Agent 的产品线与能力大整合，到 8 月 3 日，官宣在编程（Coding）和专业办公（Cowork）能力大幅提升的 Qwen3.8 模型的同时，正式将内部孵化的三款 Agent 产品 QoderWork、悟空、MuleRun 合并为统一的 Agent 产品「千问办公」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;紧随其后，7 月 20 日，腾讯开启业务整合，QClaw 的相关业务和团队被并入 WorkBuddy 体系。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;10 天后的 7 月 30 日， &lt;a href="https://mp.weixin.qq.com/s?__biz=MTMwNDMwODQ0MQ==&amp;amp;mid=2653111360&amp;amp;idx=1&amp;amp;sn=8dcb0fd35868f364066ed48a22f23492&amp;amp;scene=21#wechat_redirect" rel="noopener noreferrer" target="_blank"&gt;字节跳动宣布飞书产品团队整体并入豆包，飞书负责人谢欣向豆包负责人赵祺汇报 &lt;/a&gt;。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;不同的组织结构、不同的产品积累和优势市场，三家中国最顶级的互联网企业却在相近时间作出相似整合选择。这不太像巧合。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;更合理的判断是，这种整合，是在 AI 行业走过摸索期，进入入口争夺阶段背景下的必然选择：过去，大厂需要用多个团队验证桌面操作、云端执行和企业协作等不同路线；现在，主要产品形态已经逐渐清晰， &lt;span style="font-weight: bold;"&gt;竞争也开始从能不能做出 Agent，转向谁能成为用户和企业的统一入口。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;而千问办公作为这轮收束中最新落地的产品，也是最适合观察观察行业变化的样本。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;作为阿里阶段性的能力重组，它将此前分散在模型、桌面端、云端和企业协作场景中的积累，装进了一款新的独立产品。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;同时，它身上也集中体现了企业 Agent 竞争中最关键的几个问题：内部赛马为什么此时结束，企业 IM 与云为什么成为 Agent 的底层资产，以及模型、产品和真实任务如何形成共同进化的闭环。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;读懂它，就读懂了企业级 Agent 真正的赛点。&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01 &lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;大厂为什么同时收敛路径 &lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;大厂为什么几乎同一时间开始整合 Agent 产品？&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;拿阿里来说，在今年年初，同时保留 QoderWork、悟空和 MuleRun，是合理的。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;三款产品代表了三种不同判断。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;QoderWork 运行在用户电脑上，擅</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 15:05:00 +0000</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch Disrupt 2026’s Real World AI Stage features robots, automated factories, and extinct animals</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/05/techcrunch-disrupt-2026s-real-world-ai-stage-features-robots-automated-factories-and-extinct-animals/</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>On our new Real World AI stage, we’ll be focusing on the intersection between the digital and physical, and all the ways we’ll continue to see a blending of the two.</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 11:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>AI makes weather prediction better. Can WindBorne make it lucrative?</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/05/ai-makes-weather-prediction-better-can-windborne-make-it-lucrative/</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>WindBorne Systems has raised a $37 million Series B round to scale its weather balloons and AI forecasts.</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4949,6 +4949,324 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 00:55:47 +0000</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>冲刺全球首个100万小时具身数据！三家国产公司，联手了</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/467486.html</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>采集、仿真、训练和评测，闭环了</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 00:25:07 +0000</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek豪掷1.4亿护航宇树IPO，杭州绝代双骄战略合体</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/467487.html</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>此后模型、算力、数据中心都在合作范围内</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:18:42 +0800</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 首款 AI 硬件曝光；DeepSeek 拟上调 API 服务定价；曝字节拟训练超 5 万亿超大参数模型｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368504</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/3c/d8/3cd806d4b88f40c9e6ea27794df8fa91.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;古尔曼爆料 OpenAI 首款 AI 硬件：甜甜圈造型、冰球大小，先进语音交互等&lt;/h1&gt;
+&lt;p&gt;8 月 7 日消息，彭博社的马克 &amp;middot; 古尔曼（Mark Gurman）今天（8 月 7 日）发布 Power On 实时通讯，爆料称 OpenAI 的首款 AI 硬件为冰球（Hockey Puck，约 115.8 立方厘米）大小，售价预估在 300 美元到 400 美元（IT 之家注：现汇率约合 2,029 元到 2,705 元人民币）之间，有望 2027 年发布。&lt;/p&gt;
+&lt;p&gt;定位方面，这款 AI 硬件本质上是「没有显示屏的智能音箱」，面向家庭场景设计，用户可用单手在家中携带它移动，由 OpenAI 公司和前苹果设计师乔纳森 &amp;middot; 伊夫（Jony Ive）合作开发。&lt;/p&gt;
+&lt;p&gt;外观方面，消息称这款 AI 硬件外形呈「甜甜圈形」，大小约等于冰球。IT 之家查询公开资料，标准冰球（Hockey Puck）直径约为 7.62 厘米，体积约为 115.8 立方厘米。&lt;/p&gt;
+&lt;p&gt;硬件方面，古尔曼透露这款硬件配备可移动部件，其中部分部件可自动移动，用于提示设备正在响应或与用户互动。设备还将配备灯光、摄像头系统和其他传感器。&lt;/p&gt;
+&lt;p&gt;交互方式上，古尔曼透露该设备的运行机制，类似于手机端的 ChatGPT 语音模式，&lt;strong&gt;会使用更先进的模型，以支持更接近人类交流的互动。（来源： IT 之家）&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d6/e6/d6e6c41689b3362070efa6b9ae182d1f.png" /&gt;&lt;/p&gt;
+&lt;p&gt;科技媒体 @PatentlyApple 制作的渲染图&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/2c/cb/2ccb765321a7c0356edcadc14c0c6b03.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;曝字节拟训练超 5 万亿参数大模型 参数规模超 Kimi K3&lt;/h1&gt;
+&lt;p&gt;8 月 6 日消息，据《晚点 LatePost》报道，字节跳动正在讨论训练一个参数规模超 5 万亿的模型，它超过阿里的 Qwen 3.8-Max（2.4 万亿参数）和月之暗面的 K3（2.8 万亿参数），也是目前国内已知参数规模最大的模型。该计划仍处于早期阶段，模型最终不一定会发布。&lt;/p&gt;
+&lt;p&gt;报道称，新模型将由 Seed Foundation 负责人项亮主导，与大语言模型预训练数据负责人沈科合作。为此，Seed 正在重新梳理组织，划分职责，分配资源。&lt;/p&gt;
+&lt;p&gt;项亮与沈科均是字节跳动人工智能及大模型研发体系内的核心骨干，均出自字节的「搜广推」体系。项亮本科毕业于中国科学技术大学，博士就读于中科院自动化所，2016 年加入字节，曾负责机器学习中台 AML 团队，后调任豆包大模型 Foundation 团队任负责人。沈科 2018 年清华毕业后，加入字节跳动，现主要负责 LLM 预训练数据。&lt;/p&gt;
+&lt;p&gt;针对字节讨论训练超 5 万亿参数模型的原因，报道援引接近 Seed 人士消息称，Seed 团队认为，与其在现有尺寸上继续追赶其他大模型，不如把参数规模一次推到同行的数倍，争取领先位置。&lt;/p&gt;
+&lt;p&gt;两周前的 Seed 全员会上，字节跳动创始人张一鸣安抚了 Seed 的成员。他认为，训大模型本就是一件很难的事，团队不必过度焦虑。他明确一段时间内可接受模型落后于行业，希望大家以追求智能上限为目标，期待 Seed 模型能力能跻身世界第一梯队。&lt;/p&gt;
+&lt;p&gt;张一鸣认为编程是当前的关键方向，并表态自己反对蒸馏。在其看来，蒸馏能在短期内改善模型表现，但本质上仍是在复制 Claude 已有的能力。沿着这条路走，最多只能不断逼近对方，很难真正实现超越。&lt;/p&gt;
+&lt;p&gt;（来源：新浪科技）&lt;/p&gt;
+&lt;h1&gt;宇树科技：本次发行价格 150.80 元/股，本次发行数量占发行后总股本 10%&lt;/h1&gt;
+&lt;p&gt;8 月 6 日消息</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 20:52:10 +0800</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>对话刘靖康：镜头之外的「智能」和「审美」，才是 Camera Agent 的主战场</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368503</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;未来的影像设备，应该是「前轻后重」的。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这是影石Insta360 创始人刘靖康在 AGI Playground 2026 上对影像行业未来趋势的判断。上个月，影石刚刚宣布了「打造 Cameraman」的最新产品愿景&amp;mdash;&amp;mdash;它代表着一种「更简单操作+更好的交付」的影像体验。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;刘靖康说：「也可以认为这是一种 Camera Agent」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;产品形态大概率是多样的。因为哪怕「前轻」，不同出片场景里人们依然需要不一样的镜头、焦段以及第一人称、第三人称等不同拍摄形式。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;和具身领域一样，目前距离让设备本体在通用场景里「自由移动」，仍有不小的挑战。但 Cameraman 未必需要一个「通用」的大脑，因为对于记录和分享生活而言，「审美在线」很大程度上比「聪明地执行标准化任务」更重要。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据刘靖康介绍，目前影石已经尝试通过云端为用户直接提供 AI 剪辑服务。收费标准是 6 元/条，前两个月的灰度测试已经完成了数十万条的剪辑，导出率（类似于视频生成的「抽卡率」）超过50%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但这条路仍然走在早期。Camera Agent 不止是一个独立存在的个人或服务，它需要提升的不仅是自身的智能和审美，还有对于人类在物理世界里的「审美期待」的更深刻理解。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;以下是影石Insta360 创始人刘靖康（JK）和极客公园创始人&amp;amp;总裁张鹏的对谈内容。经 FounderPark 整理。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;策划、整理 | siqi&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;编辑｜ 万户&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Cameraman&lt;/span&gt;&lt;span style="font-weight: bold;"&gt;，核心不是拍摄，而是结果交付&lt;/span&gt;&lt;/h2&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;张鹏：欢迎 JK 来到 AGI Playground。Insta360 前段时间更新了产品使命：以前你为消费者提供「camera」，未来想提供的是「Cameraman」。这个变化意味着什么？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;刘靖康：&lt;/span&gt;Cameraman 这个想法不是一蹴而就的，它始于 2019 年。当时我们第一次把准备发布的运动相机装到一台穿越机上去拍广告片，拍出来的镜头非常好看。但想要拍出这样的画面，操控门槛很高。于是我们就自然地往下推导：怎么让每个人都能更容易拍出这种画面？&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;再往下思考，我们觉得必须看到消费者「需求背后的需求」：大多数人真正要的不是操作机器，而是得到好的照片和视频。正如今天大家出去玩，有些人会请摄影师给自己跟拍，今天这个活动也有 cameraman（摄影师）帮我们抓拍&amp;mdash;&amp;mdash;我们不需要自己动手，就能拿到很多好照片，这是影像的上限体验。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;张鹏：所以你们从那时候就开始拆，一台能全自动拍摄的机器该具备什么？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;刘靖康：&lt;/span&gt;对，我们整体分出了 3 个技术方向。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;第一个是 Imaging，跟「眼睛」相关。我们花了很多时间储备各类镜头、传感器和影像调校技术。&lt;/p&gt;
+&lt;p style="text-align: le</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:02:45 +0800</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>这枚不到 5 克的戒指，藏着 AI 交互的未来</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368497</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;智能戒指是一个被行业反复捡起、又反复放下的品类。&lt;/p&gt;
+&lt;p&gt;过去十多年，从消息通知、移动支付、身份识别到手势控制，厂商几乎把所有对可穿戴设备的想象都装进过戒指。它足够贴身，又比手表更轻，理论上应该是最接近人的计算设备之一。但在真实使用中，一枚没有屏幕、算力和电池空间都极其有限的戒指，很难独立完成一套足够复杂的交互。&lt;/p&gt;
+&lt;p&gt;很多能力因此停留在发布会演示里：抬手翻一页 PPT，捏一下手指拍照，或者隔空切换一首歌。第一次体验很新鲜，但用户很快会发现，它们既不能替代原来的遥控器，也没有构成购买一枚戒指的充分理由。&lt;/p&gt;
+&lt;p&gt;经过几轮产品迭代，Oura、RingConn 等公司逐渐把健康监测推到产品核心。与需要即时响应的交互相比，健康是一条更容易闭环的路径：戒指贴近手指血管，适合长时间采集心率、血氧和睡眠数据；没有屏幕反而意味着更低功耗，也减少了睡觉时的佩戴负担。硬件负责采集，App 负责生成睡眠、恢复和压力报告，用户则通过长期数据获得持续佩戴的理由。&lt;/p&gt;
+&lt;p&gt;这并不是因为戒指天然只适合健康，而是健康最终成为现阶段最适合的答案。&lt;/p&gt;
+&lt;p&gt;代价是，智能戒指也逐渐被定义成了一只更小、更轻的健康手环。它能够感知人，却很少帮助人主动操作周围的数字世界。即使一些产品重新加入拍照、关闭闹钟等手势能力，这些功能通常也只连接特定手机和少数操作，更像健康产品上的附加项，而不是一种新的输入方式。&lt;/p&gt;
+&lt;p&gt;生成式 AI 和 Agent 的出现，可能改变现状。&lt;/p&gt;
+&lt;p&gt;过去，要让戒指控制手机、电脑、汽车、电视和智能家居，厂商需要为不同设备编写规则、适配接口，再让用户记住不同手势。一枚几克重的戒指，既承担不了这样的计算，也无法独自理解复杂场景。但 Agent 可以在手机或云端理解人的意图、判断目标设备，并把任务发送到正确的终端。&lt;/p&gt;
+&lt;p&gt;戒指不再需要成为一台缩小的计算机，只需要做好最贴近人的那一部分：&lt;strong&gt;持续在线，捕捉手指动作，在需要时完成唤醒、选择、确认和连续调节。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;这让戒指有可能成为 AI 时代的通用 Input。&lt;/p&gt;
+&lt;p&gt;在一个由手机、耳机、眼镜、汽车和家居设备共同组成的计算环境里，人未必还需要先找到一块屏幕、打开一个 App，再进入层层菜单。语音可以快速表达复杂意图，眼镜可以感知环境，而手势仍然适合完成那些高频、私密、需要即时反馈的操作。&lt;/p&gt;
+&lt;p&gt;KiWear 想重新押注的，正是智能戒指曾经没有走通的这条路。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img alt="经典科技感设计的 KiWear 智能戒指外观，展示其轻薄小巧的时尚指环形态，主打不足 5 克的无感佩戴体验。" src="https://imgslim.geekpark.net/uploads/image/file/b9/7b/b97bda5bad9e0a99223bf34fc71a7e4b.jpg" title="KiWear 智能戒指：AI 时代的通用交互新硬件" /&gt;&lt;/p&gt;
+&lt;p&gt;Kiwear 智能戒指｜来自：KiWear&lt;/p&gt;
+&lt;h1&gt;健康救了智能戒指，也限制了它&lt;/h1&gt;
+&lt;p&gt;从产品角度看，健康之所以成为智能戒指最主流的方向，不只是因为传感器技术已经成熟，也因为它对「交互」的要求最低。&lt;/p&gt;
+&lt;p&gt;健康监测是一种被动体验。用户不需要记住动作，也不需要频繁给戒指反馈，只要持续佩戴，数据就会在后台积累。即使同步偶尔延迟，或者某一次测量出现偏差，也可以通过更长周期的数据和算法进行修正。&lt;/p&gt;
+&lt;p&gt;主动交互则完全不同。&lt;/p&gt;
+&lt;p&gt;当戒指承担输入任务时，每一次操作都必须立即被识别。一次误触、一次断连，或者稍显迟钝的反馈，都会直接破坏操控感。用户也不会因为戒指能够翻动一页 PPT，就扔掉翻页笔；更不会因为它可以让电视菜单上下移动，就收起遥控器。只要确认、返回、音量或设备切换中有一个关键环节走不通，用户就会重新拿起原来的设备。&lt;/p&gt;
+&lt;p&gt;「能操作」与「能替代」之间，隔着一条看似不宽但深不见底地鸿沟。&lt;/p&gt;
+&lt;p&gt;生态割裂又进一步放大了这个问题。手机、电脑、电视、汽车、智能眼镜和智能家居，使用不同的系统、权限和交互规范。如果一枚戒指每进入一个场景，都要等待终端厂商单独适配，它最终只会成为某一台设备的昂贵配件；如果不同设备又对应不同手势，用户为了省下一次点击，反而需要学习更多规则。&lt;/p&gt;
+&lt;p&gt;过去很多智能戒指的交互功能最终变成 showcase，并不是因为手势本身没有价值，而是它们通常只完成了一个孤立的动作，没有完成整个场景。&lt;/p&gt;
+&lt;p&gt;三星 Galaxy Ring 的双指捏合可以拍照或关闭闹钟，就是一个典型例子。它证明戒指能够识</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 15:51:48 +0800</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>谷歌「地基元老」Jeff Dean 离职创业，新公司瞄准 AI4S</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368495</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜桦林舞王&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;1999 年，Jeff Dean 加入谷歌的时候，这家公司只有 20 个人，办公室在 Palo Alto 一家 T-Mobile 门店的楼上。27 年后，他是谷歌的首席科学家，身后是 MapReduce、Bigtable、Spanner、TensorFlow、TPU、Gemini&amp;mdash;&amp;mdash;几乎每一项支撑谷歌运转的核心基础设施，都有他的名字。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;8 月 5 日，Jeff Dean 宣布离开谷歌，和三位长期合作者共同创立 Discovery Loop。消息公布当天，Alphabet 股价下跌约 5%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;市场的反应很诚实。走的不是一个高管，是一根承重柱。&lt;/span&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;造 AI 研究的基建&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Discovery Loop 的目标，用创始团队自己的话说，是「自动化机器学习、科学和工程的实验循环」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这句话需要拆开来理解。科学研究的核心流程其实是一个循环&amp;mdash;&amp;mdash;提出假设，设计实验，执行实验，检验结果，然后基于结果提出新假设，再来一轮。人类做了几百年的科学，靠的就是这个循环。问题在于，这个循环极度依赖人工，速度受限于人类的精力和时间。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Discovery Loop 要做的，就是 &lt;span style="font-weight: bold;"&gt;用 AI 模型和大规模算力，把这个循环自动化，并行跑成千上万个实验 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="716" src="https://imgslim.geekpark.net/uploads/image/file/93/4d/934d27e1e24df7bfa15fd5e8d725eae9.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="color: #bbbfc4;"&gt;Discovery Loop 团队，全部来自谷歌技术大拿｜图片来源：x&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;具体路线分三步：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;第一步， &lt;span style="font-weight: bold;"&gt;先拿机器学习研究本身开刀&amp;mdash;&amp;mdash;用 AI 自动做 AI 研究 &lt;/span&gt;，自动提出实验方案、自动跑评估、自动迭代模型。这是最务实的起点，因为 ML 研究的反馈循环最短、评估指标最清晰、数据最现成。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;第二步， &lt;span style="font-weight: bold;"&gt;用这套能力优化自己的技术栈，让自己成为自己的第一个客户 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;第三步， &lt;span style="font-weight: bold;"&gt;推广到更广阔的科学和工程领域 &lt;/span&gt;，包括硬件设计、药物发现和清洁能源。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;公司注册为公益公司（Public Benefit Corpo</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 12:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Omilia raises $67M to scale its customer support platform</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/06/omilia-raises-67m-to-scale-its-customer-support-platform/</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>The Series B is the company's second fundraise since it last raised capital in 2020. In that time, it has increased its ARR by 10x to $60 million.</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H115"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5267,6 +5267,217 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07 16:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Drones Go Heavy in DARPA Lift Challenge</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-heavy-lift-drone</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:18:09 GMT</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>黎曼动力携手光轮智能与诺亦腾机器人，推进2026年百万小时具身智能数据建设</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/hI2W3XTUo2GNylxSXDC8?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/hI2W3XTUo2GNylxSXDC8?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 08 Aug 2026 08:40:23 +0800</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>王兴兴回应 DeepSeek 投资宇树：将展开重点合作；微信内测朋友圈 AI 新功能；美国科学家首次用AI设计出新型病毒｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368565</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/97/ae/97aecad40cde1f30c2da9f5db912d431.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;OpenAI 因 Astra 模型的网络安全能力而放缓其发布进程&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;据报道，OpenAI 表示，不能排除其即将推出的模型 Astra 具备「关键性」网络能力，这促使 OpenAI 扩大安全测试范围，并暂停不符合更严格安全要求的内部活动。这是人工智能模型网络能力快速提升的最新迹象。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;OpenAI 表示，在对即将推出的模型之一 Astra 进行内部评估后，「我们无法排除其具备关键性网络能力」。在发布 Astra 之前，OpenAI 将扩大针对该模型的测试和安全措施，并按照公司 2023 年首次发布的「准备框架」要求，放缓 Astra 的开发进程，直到建立适当的安全防护措施。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;OpenAI 还表示，Astra 并未参与 Hugging Face 漏洞攻击事件。这可能是首个人工智能前沿实验室因网络安全担忧而承诺放缓自身 AI 模型开发进程的案例。（消息来源：财联社）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/51/68/51680178b90f2ab9eadc8f825198d1e9.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;Anthropic 为自研 AI 芯片开出高薪，模型训练岗位薪资高于实际造芯工程师&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;8 月 7 日消息，Anthropic 目前正在扩大内部芯片设计团队，并计划开发自研 ASIC 芯片。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;与此同时，公司不同芯片相关岗位之间出现了明显的薪资差异：负责训练 AI 模型进行芯片设计的研究工程师岗位，年薪最高可达 85 万美元，而实际负责设计 Anthropic 首款 ASIC 芯片的工程师岗位，薪资范围约为 32 万至 48.5 万美元。外媒称其为「薪酬倒挂」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Anthropic 发布的招聘信息显示，负责「Chip Design RL（芯片设计强化学习）」方向的研究工程师岗位，主要工作是构建强化学习环境，让 Claude 等 AI 模型学习芯片设计流程，包括 RTL 代码生成、验证以及物理设计优化等内容。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;两类岗位所需技能存在较高重合度，包括完整 ASIC / FPGA 设计流程、RTL 到流片、UVM 与形式化验证、物理设计、PPA（性能、功耗、面积）优化、DFT（可测试性设计）以及 EDA 工具使用经验等，同时都要求具备实际芯片开发经验。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;目前，Anthropic 尚未公布首款自研 ASIC 芯片的具体规格、制造合作方或发布时间。公司此前表示，其芯片战略将采用多芯片路线，以满足人工智能模型训练和推理需求。（消息来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="2361" src="https://imgslim.geekpark.net/uploads/image/file/df/42/df42541ed633af112db377c7df516240.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;Meta 成为第三家承认其模型「失控」并入侵了另一家公司的 AI 巨头&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;8 月 7 日消息，继 OpenAI 和 Anthropic 之后，Meta 近日也成为两周内第三家承认其 AI 模型发生越界并对其他公司系统实施「黑客行为」的科技巨头。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据报道，这一事件发生于 AI 安全评估公司 Irregul</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:22:09 +0800</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>AI Agent 手机下半场，「国标」L3 只是起点</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368561</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/21/2f/212f8fe435c1eb97faf0a110907d65a5.png" style="display: block; width: 661px !important; vertical-align: bottom; margin: 0px; height: auto !important;" /&gt;&lt;/section&gt;
+&lt;section class="js_darkmode__bg__0 js_darkmode__0"&gt;一张证书，暂时还不会影响到你「换机」节奏。&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong class="js_darkmode__1" style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜张勇毅&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong class="js_darkmode__2" style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;时间回到 7 月下旬，如果你关注智能手机领域的话，应该会记得大量手机厂商开始官宣自己的手机，通过了国家人工智能 L3 级认证。&lt;/p&gt;
+&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/79/de/79de2bcccde2e30d8958082ae0d1853c.jpeg" style="display: block; vertical-align: bottom; margin: 0px 8px 25px; width: 677px !important; height: auto !important;" /&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;这轮集体官宣的起点，是 2026 年 7 月 17 日公布的首批人工智能终端智能化分级测试结果。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin:</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:40:17 +0800</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>打破机器人「数据焦虑」，穹彻智能想建一条「训练数据」生产线</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368553</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;如果说 2025 年是具身智能爆发的一年，那么今年，行业竞争已经开始进入新的阶段。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;从国内外越来越多机器人公司发布新产品，到资本持续加码，具身智能正成为 AI 领域最受关注的方向之一。但随着行业快速发展，一个新的共识正在形成：真正限制机器人进化速度的，不再只是模型，而是数据。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;与大语言模型可以利用互联网海量文本不同，机器人需要学习的是现实世界中的操作能力。一次抓取、一段搬运、一场整理任务，都需要真实发生，并同步记录视觉、动作、轨迹等多模态信息。如何持续获得高质量数据，并将这些数据快速转化为模型能够学习的数据集，成为越来越多具身智能企业面临的新挑战。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;作为国内具身智能企业，穹彻智能一直围绕「数据&amp;mdash;训练&amp;mdash;部署」构建机器人基础设施。近期，穹彻智能联合阿里云打造了一套云端自动化数据处理产线，希望将机器人数据处理从依赖人工、单机运行的模式，升级为能够规模化运转的工业化流程，为模型迭代提供持续的数据支撑。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;机器人时代，真正稀缺的是数据&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;对于具身智能而言，数据难题不仅在于「采不到」，更在于「处理不了」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;穹彻智能采用 UMI（Universal Manipulation Interface）方案进行数据采集。操作人员只需手持设备完成抓取、开门、搬运等自然动作，设备便会同步记录第一视角画面、夹爪位姿、运动轨迹等信息，为机器人训练提供高质量操作数据。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但真正的挑战，往往发生在采集之后。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这些原始数据要进入模型训练，还需要经历位姿恢复、鱼眼相机标定、动作切分、多模态标注等多个复杂环节。其中，视觉 SLAM 重建需要消耗大量 GPU 算力；鱼眼图像需要逐帧去畸变和标定；连续动作需要切分为一个个原子任务，并配上对应的自然语言描述；随着采集规模扩大，数百小时的视频数据也给整体计算带来巨大压力。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这些工作不仅计算量庞大，而且整个流程涉及多个处理环节，一旦某一步中断，就可能影响整批数据重新计算。对于具身智能企业来说，数据处理正在成为一项新的基础设施能力，需要能够支撑弹性算力、自动调度、全流程追踪以及模型训练协同的完整体系。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;02&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;一条跑在云上的数据产线，&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;如何让机器人训练提速&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;为了解决这些问题，穹彻智能联合阿里云搭建了一套端到端的 UMI Data + AI Pipeline，希望把原本零散的数据处理流程，变成一条自动化运行的数据生产线。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在数据处理阶段，阿里云 MaxCompute MaxFrame 提供分布式计算能力，将视频去畸变、SLAM 位姿恢复、多模态标注等任务拆分到云端资源上并行执行。过去需要依赖单机完成的大规模计算，如今能够根据任务规模灵活扩展算力，提升整体处理效率。同时，大模型能力也直接嵌入数据处理流程，实现动作片段的自动语义标注，降低人工标注成本。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;整个数</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5478,6 +5478,278 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 03:48:54 +0000</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>一台人形机器人需要多少种材料？六大材料赛道与产业机会</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12136</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>2026年，人形机器人正在从舞台展示转向工程化验证。</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 01:33:24 +0000</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>塞拉尼斯入局具身智能赛道：以“材料金字塔”驱动机器人物理性能跃迁</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12133</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>六大核心价值，助力行业伙伴提速量产🚀</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 01:31:57 +0000</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>越疆具身全栖人形机器人全球首发，实现情绪感知与空间行动双突破！</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12125</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>越疆鹿萌，智生非凡，渐入“家“境。</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 01:31:34 +0000</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>一天之内，多家机器人企业宣布完成融资</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12121</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>具身智能融资潮再起：家庭机器人、建筑机器人、大模型企业密集获资本加码</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 01:29:59 +0000</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>电子皮肤如何走向产业化？制造工艺、AI算法与触觉手套三大关键解析</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12103</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>从柔性传感器制造到多模态数据采集，梳理电子皮肤产业链关键技术，探讨纺织行业在智能感知时代的新机遇。</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 01:29:04 +0000</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>灵巧手触觉传感器应用分析</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12113</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>灵巧手要实现对物体的x26quot;会抓会摸x26quot;，电子皮肤的部署部位高度集中——指尖（含指腹）与掌腹（含掌心）是两大核心区域。</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 01:27:37 +0000</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>全球首创！帕西尼推出足底多维触觉传感器 PX-FOOTRIX，迈向全身触觉感知</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12099</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>搭载 6D 霍尔阵列，具备 2000N 量程、150Hz 采样，助力人形机器人适配复杂地形行走。</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 01:16:17 +0000</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>地瓜机器人与兆易创新联合发布：基于旭日S600+GD32H77R的六轴协作机械臂全栈控制方案</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12094</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>大小脑协同，打通具身量产全链路！</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5750,6 +5750,108 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:16:40 +0800</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>苹果被曝正在测试长鑫科技存储芯片k；宇树科技今日申购，中一签或赚 20 万元；原字节跳动机器人一号位加入小米｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368581</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0d/67/0d67b4f9cf35ab0483a8043f4278f4fc.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果被曝正在测试长鑫科技存储芯片，用于 iPhone 和 MacBook&lt;/h2&gt;
+&lt;p&gt;8 月 9 日，据《华尔街日报》报道，苹果公司正在其 iPhone 和 MacBook 等产品线中测试长鑫存储（CXMT）的存储芯片，以缓解因人工智能热潮引发的内存短缺问题。报道援引知情人士称，苹果公司已与中国最大的芯片制造商长鑫存储就零部件供应展开初步洽谈，目标是在中国销售的部分设备中使用这些芯片。&lt;/p&gt;
+&lt;p&gt;路透社此前报道称，长鑫存储正考虑在北京建设第二座存储芯片工厂，以提高产能。此外，笔记本电脑制造商惠普（HP）和宏碁（Acer）已开始在销往美国以外市场的设备中使用长鑫存储的芯片，以缓解供应短缺。（来源：中新经纬）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ea/13/ea1305b2232c9d1bd554daa36ba738fd.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;消息称 WorkBuddy 已成腾讯 AI 应用战略优先级最高产品之一&lt;/h2&gt;
+&lt;p&gt;8 月 9 日消息，据报道，5 月以来，腾讯 WorkBuddy 的广告从北京知春路铺到深圳高新园。打开手机，头部应用的信息流里也几乎都是 WorkBuddy 的身影。&lt;/p&gt;
+&lt;p&gt;报道称，这是腾讯近年来少见的饱和式产品投放。这种密集的攻势背后，是腾讯在渠道、算力、组织和生态资源上的集中倾斜。&lt;/p&gt;
+&lt;p&gt;据腾讯 CSIG 人士透露，WorkBuddy 已经成为腾讯 AI 应用中战略优先级最高的产品之一，公司内部也有流传「继 QQ、微信后第三个战略级产品」的说法。&lt;/p&gt;
+&lt;p&gt;除了马化腾亲自参与产品会议外，该团队提出的算力、技术和市场资源需求，大多能够快速获批，在腾讯内部被形容为「一路绿灯」。&lt;/p&gt;
+&lt;p&gt;同时不少腾讯员工认为，WorkBuddy 今年极大概率会进入腾讯「名品堂」，这是腾讯对里程碑式产品的最高荣誉之一。（来源：界面新闻）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;微软 Google 亚马逊 Meta 甲骨文 2027 年负现金流将达到 1250 亿美元&lt;/h2&gt;
+&lt;p&gt;8 月 9 日，据 S&amp;amp;P Global Market Intelligence 的数据分析显示，微软、Google、亚马逊、Meta 和甲骨文在 2026 年的自由现金流合计几乎为零。自由现金流是扣除各项支出和 AI 基础设施成本后的剩余款项，这五大科技公司在 AI 的开发和交付上投入了巨资，因此到 2027 年它们的财务状况将会严重恶化，将会出现高达 1250 亿美元的负现金流。&lt;/p&gt;
+&lt;p&gt;其中亚马逊和 Google 两大云计算公司过去三个月损失的现金超过其它任何美国公司。马斯克旗下的 SpaceX 公司情况估计会更严重。（来源：Solidot）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;苹果客服回应删除接入千问手册：目前并没有收到新项目发布通知&lt;/h2&gt;
+&lt;p&gt;8 月 9 日，据新浪科技报道，针对删除《在 Mac 上配合 Apple 智能使用千问》使用文档一事，苹果客服对此回应称：「我们有功能或新项目发布时，都会提前收到通知，目前并没有收到相关通知，中国大陆还没推出『Apple 智能使用千问』相关功能。」&lt;/p&gt;
+&lt;p&gt;8 月 8 日，一篇名为《在 Mac 上配合 Apple 智能使用千问》的支持文档现身苹果官网 Mac 简体中文使用手册，其中明确提到 Apple 智能可配合阿里巴巴千问模型工作。&lt;/p&gt;
+&lt;p&gt;然而，这份简体中文操作手册已于昨日在苹果官网删除，原网页链接无法正常访问。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;​甲骨文 OpenJDK 项目新规：不允许提交 AI 生成代码&lt;/h2&gt;
+&lt;p&gt;8 月 9 日，甲骨文公司现已通知 OpenJDK 开发者，要求项目组不能再提交 AI 生成的代码。OpenJDK 社区是一个由全球开发者、公司和组织组成的开源协作社区，主要负责开发与维护 Java 平台标准版（Java SE）的官方开源实现&lt;/p&gt;
+&lt;p&gt;甲骨文对此表示：「OpenJDK 社区贡献内容不得包含由大语言模型、扩散模型或深度学习系统生成的内容。此处的『内容』包括但不限于代码、文本、PR、电子邮件沟通、维基和 B</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 12:28:04 +0800</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 用 1 年时间证明，你并不用为 AI 换浏览器</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368579</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/cb/fb/cbfb944b3d2ade647dffa722c2434429.png" style="display: block; width: 661px !important; height: auto !important; vertical-align: bottom; margin: 0px; background-color: transparent;" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;浏览器是功能，不是目的地。&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜张勇毅&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;2025 年 10 月 21 日，OpenAI 发布自己的 AI 原生浏览器 Atlas 的那个晚上，全球科技媒体的标题里挤满了同一个词：「Chrome 杀手」。&lt;/p&gt;
+&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/5a/7e/5a7e9e62bcbc9bc8517af2c8f2528407.png" style="display: block; height: auto !important; vertical-align: bottom; margin: 0px 8px 8px; background-color: transparent; width: 676.992px !important;" /&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light,'PingFang SC','PingFang TC','Hiragino Sans GB','Microsoft YaHei',sans-serif; font-size: 14px; line-height: 1.2; margin: 0 8px 24px 8px; text-align: left; color: #b2b2b2;"&gt;OpenAI 自研 AI Agent 浏览器 ChatGPT Atlas 于 2025 年 10 月发布｜图片来源：OpenAI 官号&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light,'PingFang SC','PingFang TC','Hiragino Sans GB','Microsoft YaHei',sans-serif; font-size: 16px; line-height: 1.75; margin: 0 0 24px 0; margin-left: 8px; margin-right: 8px;"&gt;那是手握八亿周活的 OpenAI 第一次入口级出手，不少人相信，统治了互联网三十年的浏览器，终于等来了换代时刻。&lt;/p&gt;
+&lt;p style="f</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5852,6 +5852,351 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:01:25+00:00</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Robot Recycler Salvages Parts from Broken Machines</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/recycling-robot</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Objects constructed by robots are ubiquitous. If you’ve used a car, household appliance, or smartphone today, you’ve used an object …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 15:20:09 GMT</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>行业新选手登场！中科慧思一口气发三款灵巧手新品，机器人也能组乐队现场演奏</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/6EXTXyTt834kMGkiqqDT?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/6EXTXyTt834kMGkiqqDT?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 14:24:34 GMT</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>破局“数据困境”：橡木果发布全球首个“具身本能模型”Natus AGE-0，获招商局创投与蔚来资本天使轮投资</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/dXkqWgtLOtDEl82dzQR6?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/dXkqWgtLOtDEl82dzQR6?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:58:58 +0000</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>对话郎咸朋：具身也会有“蔚小理”，靠融资实现不了物理AGI</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/469520.html</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>“我们90天就成了独角兽”</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 01:34:10 +0000</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>魔幻灵巧手：半年200亿热钱，3大路线，贵到几十万一只</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/469213.html</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>全球灵巧手企业约50%在中国，且绝大多数将筹码押在了「五指」上。
+需求、资本和创业者正在快速推动，但从技术成熟、规模化量产到商业落地，中间仍隔着巨大的工程鸿沟。</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 20:41:27 +0800</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>语音成为 AI 关键入口，阿里一口气把全栈模型能力都拿出来了</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368638</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div class="rich_media_content js_underline_content defaultNoSetting fix_apple_default_style" id="js_content"&gt;
+&lt;section class="wx-article-wrap"&gt;
+&lt;section class="js_darkmode__bg__0 js_darkmode__0"&gt;&lt;/section&gt;
+&lt;section&gt;
+&lt;p&gt;&lt;strong class="js_darkmode__1"&gt;作者｜连冉&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="js_darkmode__2"&gt;编辑｜郑玄&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p&gt;我们正在悄然进入一个「打字越来越少」的时代。&lt;/p&gt;
+&lt;p&gt;过去，语音只是键盘输入的补充：开车时发消息、开会时记笔记，它是「不方便打字时的替代方案」；但现在，语音正在成为人机交互的核心入口之一&amp;mdash;&amp;mdash; 有人用语音写完一天的工作文档，有人靠语音驱动 AI 写完代码，甚至有产品从诞生起就没有打字框，全程靠说话完成所有操作。&lt;/p&gt;
+&lt;p&gt;这股「语音原生」的浪潮，也已经从用户习惯渗透到了一级市场。&lt;/p&gt;
+&lt;p&gt;海外 AI 语音输入工具&amp;nbsp;&lt;span class="wx_search_keyword_wrap"&gt;Wispr&lt;/span&gt;&amp;nbsp;半年估值翻近三倍逼近 20 亿美元，用户规模同比暴涨超百倍；从主打私密输入的 AI 语音戒指，到全场景语音交互助手，国内初创公司融资消息接连不断，2026 年第一季度全球语音 AI 赛道融资总额已超 70 亿美元。&lt;/p&gt;
+&lt;p&gt;当语音可以直接产出工作成果、触发完整业务流程的生产力入口，整个赛道的竞争逻辑也正在被改写。海外已经跑出了 ElevenLabs 这样估值超百亿美金的全链路语音平台，而国内市场还缺少一个真正意义上的语音生产力基建级产品。&lt;/p&gt;
+&lt;p&gt;&lt;span class="wx_text_underline"&gt;8 月 7 日，阿里巴巴推出国内首个 AI 语音生产力平台&amp;nbsp;&lt;/span&gt;&lt;span class="wx_search_keyword_wrap"&gt;&lt;span class="wx_text_underline"&gt;CosyVoice Studio&lt;/span&gt;&lt;/span&gt;&lt;span class="wx_text_underline"&gt;，整合开放语音识别、语音合成、实时语音交互三类核心能力，覆盖「听、创、聊」全链路。&lt;/span&gt;&lt;/p&gt;
+&lt;section&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/9b/31/9b31d2c803f2c4215c657c29a6c8eb98.jpeg" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span&gt;图片来源：Artificial Analysis&lt;/span&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p&gt;&lt;span&gt;CosyVoice Studio 背靠全球第一梯队的阿里自研 Qwen-Audio 语音大模型家族。比如，在全球第三方评测平台 Artificial Analysis 7月28日的榜单中，Qwen-Audio-3.0-Realtime 的综合指数（Speech to Speech Index）得分达 84.1%，摘得全球桂冠。语音推理、智能体表现和对话动态三个子项得分也均为世界第一。&lt;/span&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span&gt;有模型打底，再加上千问、钉钉、高德、淘天等真实业务场景的长期打磨，阿里正在尝试走出一条从模型能力到产品生态的语音商业化路径。这场从单点能力输出到全链路产品开放的升级，也为国内 AI 语音赛道的下一程，带来了全新的变量。&lt;/span&gt;&lt;/p&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;p&gt;&lt;em&gt;&lt;strong&gt;01&lt;/strong&gt;&lt;/em&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;section&gt;
+&lt;section class="js_darkmode__4"&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p class="js_darkmode__5"&gt;&lt;strong&gt;&lt;span class="js_darkmode__6"&gt;&lt;strong class="js_darkmode__7"&gt;&lt;span class="js_darkmode__8</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:31:17 +0800</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>美国本土直播带货，长出一头 200 亿美元「巨兽」</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368627</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜Wildcard&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;当直播带货，在中国已经近乎成为网民购物基本操作时候，习惯了 Copy From China 的硅谷大厂，不是没动心过。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;2022 年 10 月，Facebook 关闭了直播购物功能。五个月后，Instagram 跟进。Amazon Live 则更惨，被行业分析师评价为「内容质量令人尴尬，大多数用户甚至不知道它的存在」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;硅谷大厂一系列失败，得出一个结论&amp;mdash;&amp;mdash; &lt;span style="font-weight: bold;"&gt;直播电商在美国做不起来。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;中国有李佳琦和 4.5 万亿的直播电商 GMV，而美国消费者就是不买账。这个结论放在 2022 年底看，是合理的。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但四年之后的今天，一家从洛杉矶出租屋里长出来的直播电商公司 Whatnot，刚刚完成了 5.45 亿美元的 G 轮融资，估值 200 亿美元。在欧美直播电商市场，这家名不见经传的创业公司，已经占据了 60% 的份额，是绝对的霸主。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;更可怕的是，Whatnot 上 用户日均观看时长超过 80 分钟！&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;那些说美国做不了直播电商的人，显然说错了。但更值得追问的是，美国最终跑出来的赢家，为什么跟中国版本长得完全不一样？&lt;/span&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;美国版「得物」开局&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Whatnot 的创始故事，怎么看都不像一个 200 亿美元公司该有的开头。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;2019 年底，Grant LaFontaine 和 Logan Head 在洛杉矶注册了 Whatnot。LaFontaine 此前在 Facebook 和 YouTube 做产品经理，Head 是球鞋交易平台 GOAT 的前高级产品经理。两个人有一个共同点&amp;mdash;&amp;mdash;都是收藏品玩家。LaFontaine 从中学开始倒卖宝可梦卡牌，后来又卖球鞋。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;他们一开始做的事情极其朴素，就是一个专门卖 Funko Pop 手办的线上交易平台。对，就是那种大头塑料公仔。为了解决收藏品市场最大的痛点「假货泛滥」，早期 Whatnot 要求所有商品先寄到平台进行实物验证，然后再发给买家。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="502" src="https://imgslim.geekpark.net/uploads/image/file/d6/b4/d6b48c3a69d94b164470a7edcee006bb.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="color: #bbbfc4;"&gt;Whatnot 两位创始人 Grant LaFontaine 和 Logan Head｜图片来源：Crunchbase&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;团队只有四个人。LaFontaine 后来在采访中说，「很难跟你父</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:16:40 +0800</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>苹果被曝正在测试长鑫科技存储芯片；宇树科技今日申购，中一签或赚 20 万元；原字节跳动机器人一号位加入小米｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368581</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0d/67/0d67b4f9cf35ab0483a8043f4278f4fc.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果被曝正在测试长鑫科技存储芯片，用于 iPhone 和 MacBook&lt;/h2&gt;
+&lt;p&gt;8 月 9 日，据《华尔街日报》报道，苹果公司正在其 iPhone 和 MacBook 等产品线中测试长鑫存储（CXMT）的存储芯片，以缓解因人工智能热潮引发的内存短缺问题。报道援引知情人士称，苹果公司已与中国最大的芯片制造商长鑫存储就零部件供应展开初步洽谈，目标是在中国销售的部分设备中使用这些芯片。&lt;/p&gt;
+&lt;p&gt;路透社此前报道称，长鑫存储正考虑在北京建设第二座存储芯片工厂，以提高产能。此外，笔记本电脑制造商惠普（HP）和宏碁（Acer）已开始在销往美国以外市场的设备中使用长鑫存储的芯片，以缓解供应短缺。（来源：中新经纬）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ea/13/ea1305b2232c9d1bd554daa36ba738fd.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;消息称 WorkBuddy 已成腾讯 AI 应用战略优先级最高产品之一&lt;/h2&gt;
+&lt;p&gt;8 月 9 日消息，据报道，5 月以来，腾讯 WorkBuddy 的广告从北京知春路铺到深圳高新园。打开手机，头部应用的信息流里也几乎都是 WorkBuddy 的身影。&lt;/p&gt;
+&lt;p&gt;报道称，这是腾讯近年来少见的饱和式产品投放。这种密集的攻势背后，是腾讯在渠道、算力、组织和生态资源上的集中倾斜。&lt;/p&gt;
+&lt;p&gt;据腾讯 CSIG 人士透露，WorkBuddy 已经成为腾讯 AI 应用中战略优先级最高的产品之一，公司内部也有流传「继 QQ、微信后第三个战略级产品」的说法。&lt;/p&gt;
+&lt;p&gt;除了马化腾亲自参与产品会议外，该团队提出的算力、技术和市场资源需求，大多能够快速获批，在腾讯内部被形容为「一路绿灯」。&lt;/p&gt;
+&lt;p&gt;同时不少腾讯员工认为，WorkBuddy 今年极大概率会进入腾讯「名品堂」，这是腾讯对里程碑式产品的最高荣誉之一。（来源：界面新闻）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;微软 Google 亚马逊 Meta 甲骨文 2027 年负现金流将达到 1250 亿美元&lt;/h2&gt;
+&lt;p&gt;8 月 9 日，据 S&amp;amp;P Global Market Intelligence 的数据分析显示，微软、Google、亚马逊、Meta 和甲骨文在 2026 年的自由现金流合计几乎为零。自由现金流是扣除各项支出和 AI 基础设施成本后的剩余款项，这五大科技公司在 AI 的开发和交付上投入了巨资，因此到 2027 年它们的财务状况将会严重恶化，将会出现高达 1250 亿美元的负现金流。&lt;/p&gt;
+&lt;p&gt;其中亚马逊和 Google 两大云计算公司过去三个月损失的现金超过其它任何美国公司。马斯克旗下的 SpaceX 公司情况估计会更严重。（来源：Solidot）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;苹果客服回应删除接入千问手册：目前并没有收到新项目发布通知&lt;/h2&gt;
+&lt;p&gt;8 月 9 日，据新浪科技报道，针对删除《在 Mac 上配合 Apple 智能使用千问》使用文档一事，苹果客服对此回应称：「我们有功能或新项目发布时，都会提前收到通知，目前并没有收到相关通知，中国大陆还没推出『Apple 智能使用千问』相关功能。」&lt;/p&gt;
+&lt;p&gt;8 月 8 日，一篇名为《在 Mac 上配合 Apple 智能使用千问》的支持文档现身苹果官网 Mac 简体中文使用手册，其中明确提到 Apple 智能可配合阿里巴巴千问模型工作。&lt;/p&gt;
+&lt;p&gt;然而，这份简体中文操作手册已于昨日在苹果官网删除，原网页链接无法正常访问。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;​甲骨文 OpenJDK 项目新规：不允许提交 AI 生成代码&lt;/h2&gt;
+&lt;p&gt;8 月 9 日，甲骨文公司现已通知 OpenJDK 开发者，要求项目组不能再提交 AI 生成的代码。OpenJDK 社区是一个由全球开发者、公司和组织组成的开源协作社区，主要负责开发与维护 Java 平台标准版（Java SE）的官方开源实现&lt;/p&gt;
+&lt;p&gt;甲骨文对此表示：「OpenJDK 社区贡献内容不得包含由大语言模型、扩散模型或深度学习系统生成的内容。此处的『内容』包括但不限于代码、文本、PR、电子邮件沟通、维基和 B</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6197,6 +6197,633 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 09:07:17 +0000</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>超亿元C轮融资落地 |灵猴机器人锚定具身智能硬核赛道 技术产能双向突破</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12244</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>MAJOR NEWS 产业纵深迭代，智造破局突围。 近日，苏州灵猴机器人有限公司正式官宣完成超亿元C轮融资。本 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 02:56:59 +0000</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>具身智能数采ego方案的应用场景</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12236</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>具身智能 EGO（第一人称）数采方案应用场景 EGO数采的本质：采集人类第一视角下“环境观察‑思考决策‑手物交 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 02:40:25 +0000</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>戴盟完成数亿元战略融资，蚂蚁集团领投，老股东超额追投</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12222</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>打造全球首个触觉驱动的物理交互脑</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:33:03 +0000</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>华拟智能HUA‑R1前台仿生机器人正式亮相，打造有温度的AI服务</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12215</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>伴随着人形机器人赛道快速升温，商用服务仿生机器人正在走进各大企业的前台大厅。</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:32:14 +0000</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人热点与现状：应用探索加速，数据采集方兴未艾</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12200</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人产业在2026年正式迈入x26quot;量产元年x26quot;，行业焦点明显从x26quot;能不能造出来x26quot;转向x26quot;能不能用起来x26quot;。</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:30:44 +0000</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>德塔智能发布头戴式数据采集 Delta D1：全景视觉+全身骨骼</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12183</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>将第一人称全景视觉、全身骨骼追踪、空间定位与音频采集融于一体，让真实场景中的“所见、所动、所做”同步沉淀为可用于具身智能训练的高质量数据。</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:29:58 +0000</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>一文看懂压阻式触觉传感器7大应用场景</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12173</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>压阻式触觉传感器凭借结构简单、响应稳定、成本较低、易于阵列化制造以及能够实现柔性贴合等优势，成为目前柔性感知领域应用最广泛的技术路线之一。</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:19:21 +0000</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>触觉、视觉、动捕全同步！全屋场景下具身数据集的新高度</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12145</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>首款真实全屋全模态触觉同步具身数据集</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 13:57:46 +0000</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>蚂蚁首次投向机器人“指尖”！数亿元押注，全球首个物理交互脑发布</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/470674.html</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>资本正从具身本体集体涌向触觉</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 04:31:39 +0000</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>GPU开始金融化！黄仁勋拉上华尔街搞5000亿美元融资</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/470254.html</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>真就把GPU当理财产品了～</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 00:46:23 +0000</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>五大高校联手发榜！首份机器人三视角世界模型评测结果出炉，榜单持续更新中</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/469860.html</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>三视角世界模型谁更稳?</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 08:35:54 +0800</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>林俊旸创办 AI 公司，估值20亿美元；Gemini 月活用户达 10 亿；Manus 宣布恢复独立运营</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368700</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/1b/f1/1bf15844cfd96acfec1228fd0c907710.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;Manus 宣布脱离 Meta 恢复独立运营&lt;/h2&gt;
+&lt;p&gt;8 月 11 日消息，Manus 在官网发布声明，宣布脱离 Meta 并恢复独立公司形式运营，继续为全球数百万用户提供服务。在此过程中，部分用户的账户将受到影响。&lt;/p&gt;
+&lt;p&gt;为遵守特定司法辖区的监管要求，部分用户在 2025 年 12 月 29 日当前或之后产生的数据，将于北京时间 2026 年 8 月 23 日 08:00 起至 8 月 24 日期间被删除。受影响用户将会在 Manus App 和电子邮件收件箱中看到通知。如果用户是使用 Apple 账户或 Facebook 账户注册 Manus，则需要留意应用内通知。&lt;/p&gt;
+&lt;p&gt;在此期间，未受影响的用户可以照常使用 Manus，无需采取任何行动。&lt;/p&gt;
+&lt;p&gt;Manus 成为独立公司后，官方会将数据存储在美国和新加坡。用户恢复数据后，官方还将提供回归奖励。（来源：凤凰网科技）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/6a/fd/6afdeb375cc84aa7105435331f5cea64.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;谷歌有史以来增长最快的产品：Gemini 应用月活跃用户达 10 亿&lt;/h2&gt;
+&lt;p&gt;8 月 12 日消息，谷歌 CEO 桑达尔 &amp;middot; 皮查伊（Sundar Pichai）宣布，Gemini 应用月活跃用户达到 10 亿，是谷歌有史以来增长最快的产品，也是该公司第 14 款跨越十亿用户大关的产品。&lt;/p&gt;
+&lt;p&gt;今年 6 月，谷歌宣布 Gemini 应用月活跃用户数超过 9 亿，为该公司当时所拥有的 13 款超 10 亿用户产品提供支持，其中包括 5 款用户量超过 30 亿的产品（谷歌搜索、Gmail 邮箱、Android 系统、Chrome 浏览器、YouTube）。（来源：界面）&lt;/p&gt;
+&lt;h2&gt;从阿里离职五个月后，林俊旸官宣创办 AI 公司语用科技 Pragmatik Labs&lt;/h2&gt;
+&lt;p&gt;8 月 12 日消息，林俊旸（y&amp;aacute;ng）今日宣布，他在上海创办了一家新公司 Pragmatik Labs（语用科技），简称 p7k。新公司的研究方向为横跨数字世界和物理世界的下一代智能体（Agent）。&lt;/p&gt;
+&lt;p&gt;公开资料显示，出生于 1993 年的林俊旸，曾是阿里最年轻的 P10 级技术专家，与智谱 AI 创始人唐杰、月之暗面（Kimi）创始人杨植麟、腾讯首席 AI 科学家姚顺雨并称为「基模四杰」。今年 3 月，林俊旸宣布从阿里巴巴离职。&lt;/p&gt;
+&lt;p&gt;林俊旸还透露，高榕创投和红杉中国共同领投本轮融资，腾讯和上海未来产业基金提供支持。&lt;/p&gt;
+&lt;p&gt;据外媒今年 6 月报道，Pragmatik Labs 此轮融资规模达数亿美元，高榕创投和红杉中国各投资约 1 亿美元，腾讯投资约 2,000 万美元），公司投后估值约 20 亿美元。（来源：网易）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/58/10/5810f134e23dc49916ab29c130b78180.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;封禁 3 年后迎来转折，美国政府设备重新允许使用 TikTok&lt;/h2&gt;
+&lt;p&gt;8 月 12 日，据彭博社报道，特朗普政府已解除在联邦政府设备上使用 TikTok 的限制，原因是 TikTok 美国业务在重组后不再构成国家安全威胁。&lt;/p&gt;
+&lt;p&gt;白宫管理和预算办公室在周一发布的一份备忘录中，撤销了 2023 年发布的一项指令。该指令因担心 TikTok 存在安全风险，禁止在政府设备上使用这一短视频服务。&lt;/p&gt;
+&lt;p&gt;今年 1 月，TikTok 美国业务完成重组，并成立新实体 TikTok USDS Joint Venture，引入甲骨文、银湖资本等投资者，字节跳动保留少数股权。新实体负责 TikTok 美国业务的数据保护、算法安全、内容审核及软件保障。（来源：搜狐网）&lt;/p&gt;
+&lt;h2&gt;&lt;strong&gt;港交所&lt;/strong&gt;&lt;strong&gt;行</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:00:26 +0800</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>AI 硬件都在做加法，阅星曈靠一块「减法屏」拿下近 5000 万融资</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368690</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：阅星曈&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;极客公园获悉，超便携电子纸品牌阅星曈近期完成一笔接近 5000 万元的 A 轮追加融资，由顺为资本、经纬创投、博裕创投和小红书四家老股东继续投资。&lt;/p&gt;
+&lt;p&gt;此前在今年 4 月，阅星曈曾对外披露，自天使轮至 A 轮累计完成五轮、总额超过亿元的融资。公司方面称，此次近 5000 万元是滚动融资中近期完成的一笔 A 轮交割。资金将主要用于提前锁定电子纸屏幕和产能、研发新硬件、改善软件交互、探索 AI 能力，以及拓展内容版权和海外市场。&lt;/p&gt;
+&lt;p&gt;过去两年，AI 硬件普遍在做加法：加入麦克风、摄像头、更多传感器和更大的模型，希望设备能够听见、看见并主动理解用户。&lt;/p&gt;
+&lt;p&gt;阅星曈目前获得市场反馈的产品，却是一块功能克制的电子纸。它没有开放的应用商店，没有短视频和信息流，也没有一套需要被反复强调的 AI 功能。它只是磁吸在手机背面，让用户在地铁上、排队时或睡觉前读几页内容。&lt;/p&gt;
+&lt;p&gt;但阅星曈也开始尝试把 AI 接入这套原本克制的产品体系。按照创始人兼 CEO 胡宇沸的介绍，公司正在测试一套由云端、手机 App 和电子纸设备组成的三端架构，已经调通部分 Agent-to-Agent 测试。&lt;/p&gt;
+&lt;p&gt;按照胡宇沸的设想，AI 更像信息抵达屏幕之前的一层处理：理解用户需要什么、整理内容、减少导入和推送的步骤，最后仍由电子纸呈现结果。&lt;/p&gt;
+&lt;p&gt;一家公司因为做减法获得用户，又因为增长必须开始做加法。这是阅星曈融资之后真正值得观察的问题。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;01 从「把规模做大」，到「把产品做小」&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;阅星曈是一家成立于 2023 年、从超便携电子纸切入的消费电子创业公司。现阶段的核心产品是 X3、X4 等小尺寸电子纸设备，其中，X3 配备 3.7 英寸屏幕，机身约 58 克；X4 的屏幕为 4.3 英寸。产品可以通过磁吸配件附着在手机背后，用户用实体按键翻页，通过手机 App 或「星曈云」导入书籍、图片等内容。&lt;/p&gt;
+&lt;p&gt;它与传统电子纸阅读器最明显的差别，在于借用手机的随身性：传统阅读器需要单独携带，阅星曈则试图让阅读设备始终与手机同时出现，目前月销量已达数十万。&lt;/p&gt;
+&lt;p&gt;阅星曈创始人胡宇沸过去更擅长的是运营。此前，他先后在 Uber 中国、小蓝单车、饿了么、OYO 酒店和新石器无人车等公司负责运营或管理工作。OYO 官方信息曾称，胡宇沸创立的 EMO 事业群在半年内开拓 275 座城市、签约 1600 家酒店。组织人、建立线下网络和快速扩大规模，是他过去最鲜明的职业标签。&lt;/p&gt;
+&lt;p&gt;但当商业模式还没有成立，速度和资本只会同步放大问题。「我是一路做运营出身，一直做 COO。」胡宇沸说，「但真正到底层，还是产品得好。」他把过去的教训归结为三条：做好产品、不依靠烧钱增长、维持小团队的战斗力。&lt;/p&gt;
+&lt;p&gt;作为电子纸重度用户，胡宇沸发现，传统阅读设备不便随身，碎片时间仍主要被手机占据。他最初想解决的问题是：能不能让一本书像手机一样，总在手边？答案是一块足够薄、足够轻、可以磁吸在手机背面的电子纸。&lt;/p&gt;
+&lt;p&gt;「我们做了一件事情，就是让几千年来都不好带的书变得好带。」他说。为了描述这种关系，他用了一个不太精致却很准确的比喻：像一块「狗皮膏药」贴在手机背后。&lt;/p&gt;
+&lt;p&gt;从行业维度看，全球电子阅读器市场正增长平稳却早已陷入存量博弈。2025 年全球电子墨水阅读器市场规模约 24.5 亿美元，预计 2032 年将接近 39 亿美元，年复合增速维持在 6.8% 左右；其中 7 英寸以下的小尺寸设备占据了超半数市场份额，便携化已是行业共识的方向。&lt;/p&gt;
+&lt;p&gt;但主流品牌大多困在 6-10 英寸的「独立阅读设备」框架里，在屏幕素质、续航与版权内容上反复内卷，阅星曈的核心差异化，则跳出了「把阅读器做小」的惯性思维，转而借势手机这一用户最高频的随身设备，重构了电子纸的存在方式。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img alt="用户手持磁吸了阅星曈小尺寸电子纸的手机，体现随身携带与零负担的日常碎片化阅读场景" src="https://imgslim.geekpark.net/uploads/image/file/da/fb/dafbf117a8b1e580c9cefbc378db4004.jpg" title="阅星曈电子纸磁吸在手机背部的单手握持体验" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：阅星曈&lt;/p&gt;
+&lt;p&gt;它不需要用户额外分配背包空间，不需要单独培养使用习惯，仅通过磁吸设计就把阅读能力「植</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 21:00:08 +0800</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>对话格式塔彭雷：AI 的下一站，是解读人的大脑</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368694</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;过去半年，脑机接口行业同时踩下了几脚油门。&lt;/p&gt;
+&lt;p&gt;2026 年 1 月，Neuralink 宣布全球临床试验参与者增至 21 人。从 2024 年完成首例人体植入，到将试验扩展至多个国家，侵入式脑机接口正在越过单个患者的演示阶段。&lt;/p&gt;
+&lt;p&gt;同一个月，OpenAI 成为 Merge Labs 约 2.5 亿美元种子轮融资中的最大出资方。这家由 Sam Altman 联合创办的公司没有继续沿用电极，转而把筹码押在超声上，希望在不开颅的情况下读取和调控大脑。&lt;/p&gt;
+&lt;p&gt;另一条经血管植入路线上的 Synchron，也完成了 2 亿美元 D 轮融资，资金将用于关键性试验和商业化准备。&lt;/p&gt;
+&lt;p&gt;国内市场也迅速升温。公开统计显示，2026 年一季度国内脑机接口领域发生 17 起融资，金额约 38 亿元，单季规模已经超过 2025 年全年。7 月，成立仅半年多的格式塔又完成 4.2 亿元天使+轮融资，两轮累计融资接近 1 亿美元。&lt;/p&gt;
+&lt;p&gt;钱为什么迅速涌向一个临床周期漫长、商业模式仍未完全跑通的行业？&lt;/p&gt;
+&lt;p&gt;一个直接答案是，脑机接口终于开始从实验室进入真实患者。更深一层的变化在于，这个行业的想象力正在越过「用意念控制光标」：当 AI 从语言模型走向世界模型和生物模型，大脑可能成为下一种稀缺的数据源，脑机接口则是获取这些数据的入口。&lt;/p&gt;
+&lt;p&gt;这也让行业出现了两场同时发生的竞争。一场围绕电学、血管内介入、超声等技术路线展开，争夺更安全、更大范围、更高带宽的连接方式；另一场发生在模型层面&amp;mdash;&amp;mdash;谁能把血流、电信号、影像和行为放进同一套表征系统，谁就可能率先建立关于人类智能的基础模型。&lt;/p&gt;
+&lt;p&gt;格式塔创始人彭雷希望外界从后一场竞争理解这家公司。&lt;/p&gt;
+&lt;p&gt;2026 年 1 月，他与陈天桥共同创办格式塔，选择此前仍少有人进入的超声脑机接口。半年多时间里，公司在成都建设全球总部和制造基地，又在上海设立承担 AI 大脑基础模型研发与国际科研合作的第二总部。&lt;/p&gt;
+&lt;p&gt;若沿用医疗器械公司的业务逻辑，这种投入速度显得反常。格式塔的第一款产品仍处于研发和临床准备阶段，后续还要穿过漫长的注册审批流程。但彭雷判断，AI 走向 AGI 与脑机接口解码大脑，最终会在同一个方向汇合。&lt;/p&gt;
+&lt;p&gt;「我们在解码大脑，同时也在建设一个对人类大脑的 Foundation Model。」他说。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;01 AI 的下一站，为什么要重新研究人？&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;过去几年，AI 最重要的变化，是能力边界开始越过语言。&lt;/p&gt;
+&lt;p&gt;大语言模型学习互联网上的人类文本，由此获得对知识和语言关系的统计表达；世界模型和具身智能继续向前，让机器理解空间、动作、因果和物理反馈；生物 AI 则把建模对象推进到蛋白质、细胞、器官乃至完整的人体。&lt;/p&gt;
+&lt;p&gt;彭雷将这条演进路线概括为：&lt;strong&gt;从语言模型到物理模型，再到生物模型。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;语言是已经被人类结构化的数据。网页、书籍、代码和对话天然以 token 的形式存在，模型可以在海量语料上快速训练。进入物理世界之后，数据获取开始变得昂贵：机器人需要在真实或仿真环境中行动，接收传感器反馈，在一次次失败中学习。到了生物世界，训练材料更加稀缺。血流、电信号、影像、行为和疾病表型散落在不同设备与临床场景里，数据尺度、模态和个体差异都远高于文本。&lt;/p&gt;
+&lt;p&gt;大脑位于这条路径的深处。它既是人的意图源头，也是目前已知最复杂的生物智能系统。&lt;/p&gt;
+&lt;p&gt;「人对生理信号、对人本身的研究，会极大地帮助 AI 和具身智能的学习。」彭雷说，「我们越了解人，越有可能走向 AGI。」&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/4e/fe/4efe996394cf73d77b596a341e238d71.jpeg" /&gt;&lt;/p&gt;
+&lt;p&gt;格式塔创始人彭雷｜图片来源：格式塔&lt;/p&gt;
+&lt;p&gt;这一趋势已经在具身智能训练场里露出端倪。早期的机器人训练主要记录画面、关节轨迹和操作结果，随后加入外骨骼、力反馈与肌电信号。肌电能够解释肌肉如何执行动作，脑电和脑血流则有机会把数据链条继续向前追溯&amp;mdash;&amp;mdash;人在抬手之前产生了什么意图，如何规划运动，又如何根据环境反馈修正动作。&lt;/p&gt;
+&lt;p&gt;格式塔正在与傅利叶等具身智能企业展开合作，在具身智能训练过程中同步采集操作员的脑电和脑血流等信号。双方试图验证一个假设：加入脑部多模态数据后，具身模型能否比只</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 15:30:55 +0800</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>对话影溯章国锋：互联网数据才是空间智能最需要的「太阳能」</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368667</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜张鹏 &lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;整理｜ 徐珊&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;世界模型的牌桌上，坐着的已经全是重量级玩家。Yann LeCun 离开 Meta 亲自下场，李飞飞的 World Labs 发布 Marble，NVIDIA 用 Cosmos 拉起联盟，国内的大厂与创业公司也在密集进场。让 AI 理解物理世界，已经是今年的主流方向。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但模型智能的上限，最终取决于喂给它的数据。 语言模型和视频模型的成长，都建立在互联网三十年的积累上；而这一次，世界模型的牌桌上，没有任何一家的数据够得到训练基础模型所需的量级。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;行业不是没有努力。从遥操到第一视角采集，具身公司都在重金投入数据。但在影溯科技创始人兼董事长、浙江大学求是特聘教授 章国锋看来，这些方式像伐木和挖石油，有价值但却要时间积累，耗时耗力。真正能支撑训练数据能源应该像阳光，无处不在、取之不竭。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;唯一够得到互联网量级的，其实就藏在人人每天刷过的视频里，这也是他眼中真正的「阳光」。视频的每一帧里，其实都藏着这个世界的运动、物理的规律。3D数据一直都在，只是从没有人能把它取出来。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;从阳光中获得能量，给 3D 世界造一块「太阳能板」，正是影溯在做的事。它要把海量视频数据转化成能直接训练世界模型的 3D 数据，让无处不在的「阳光」，第一次变成构建空间智能的能量。这家成立一年的上海公司，将在今年实现单目视频转 360 度动态场景，并开始批量转制。相较于传统实地采集再加重建的模式，这种方式的整体成本至少下降一至两个数量级，为整个空间智能赛道解决最棘手的 3D 数据底层供给难题。今年 6 月，公司完成新一轮融资，将主要投入模型训练与数据引擎的建设。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;近期，极客公园创始人张鹏与章国锋进行了一次交流。这场交流里，他谈到3D数据为什么是空间智能的第一性问题，几十张卡训练世界模型的账该怎么算，以及物理世界的 ChatGPT 时刻会以什么迹象到来。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;以下是本次对话精编。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01 &lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;空间智能的「阳光」&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;来自互联网数据 &lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #9ebbfe;"&gt;张鹏：你做SLAM 技术很长时间了，从 SLAM 这种空间计算到现在大家讨论的空间智能，你是怎么理解这个跃迁的？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #9ebbfe;"&gt;章国锋： &lt;/span&gt;SLAM 主要做在线的三维地图重建，确定自身在空间中的方位。真正要理解这个世界，光有空间定位和 3D 重建是不够的。比如我们要能判断桌上这个杯子，碰到它，它会掉下去，里面的水会倒出来。因为这个动作接下来会发生什么，需要建立在你对真正物理世界的理解上，不只是空间定位。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;所以从 SLAM（或者叫原来的空间计算）到空间智能，很大不同在于你需要真正能对空间进行理解，并与之交互，甚至推演。比如说，我在这个空间做一</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 08:48:58 +0800</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>千问 App 推出付费服务，办公助理最高一年 1499 元；豆包酒店订单开收 12% 服务费；拼多多上线「最快明日达」｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368640</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/71/b5/71b5a6ce1e737933ba856c28bd6be27d.png" /&gt;&lt;/p&gt;&lt;h1&gt;综合扣费 12%，消息称豆包渠道的酒店订单今日起开始执行独立费率&lt;/h1&gt;&lt;p&gt;8 月 10 日消息，据新浪科技消息，从今日起，通过豆包入口跳转抖音来客成交的酒店订单，将执行独立费率：11.4% 的软件服务费加 0.6% 的支付手续费，&lt;strong&gt;综合费率约 12%&lt;/strong&gt;。&lt;/p&gt;&lt;p&gt;对此，有酒店行业人士表示，此消息属实，网传照片为抖音来客后台的通知，「现在豆包推荐酒店已经要收佣金了。」&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/4a/c7/4ac7eb6642cca6c363a11713025721ac.png" /&gt;&lt;/p&gt;&lt;p&gt;查询获悉，7 月 27 日，抖音生活服务学习中心曾发布《2026 年抖音生活服务平台特定渠道软件服务费政策说明》。&lt;/p&gt;&lt;p&gt;说明中提到，本政策有效期为 2026 年 8 月 10 日 0:00 至新的抖音生活服务平台特定渠道软件服务费政策生效前一日 24:00，&lt;strong&gt;具体的软件服务费费率将通过商家来客后台向商家触达&lt;/strong&gt;。&lt;/p&gt;&lt;p&gt;据介绍，软件服务费以「用户实付金额 + 除商家以外其他主体提供的补贴金额（如平台通用券）」为基数，并且根据不同的商家类型、商品类目、POI 类目、产品类型、特定成交渠道实行固定或区间费率。&lt;strong&gt;其中特定渠道包括豆包&lt;/strong&gt;，可能会根据平台服务情况有所调整，是否属于特定渠道订单以订单结算单的展示为准。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/3c/31/3c31208c90c0f2c5b2a4f9d05a07f6de.png" /&gt;&lt;/p&gt;&lt;h1&gt;阿维塔副总裁雍军不认为和华为的合作模式是「必要项」，当下最优解不代表永远绑定&lt;/h1&gt;&lt;p&gt;8 月 10 日消息，据第一财经今日报道，在 8 月 8 日举办的媒体沟通会上，阿维塔副总裁雍军向媒体表示，&lt;strong&gt;不认为和华为的合作模式是「必要项」&lt;/strong&gt;，因为阿维塔具备差异化的能力。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/75/ac/75ac6c779a3a38d9af303d4ee24b8fd7.png" /&gt;&lt;/p&gt;&lt;p&gt;雍军称，阿维塔一直采用华为乾崑最好的智驾技术，保障了阿维塔在感知能力上是第一梯队。这背后是因为阿维塔是引望的第二大股东。但他同时强调，&lt;strong&gt;与华为的深度合作是基于华为技术的领先性，在当下的最优解不代表这样的合作会永远绑定&lt;/strong&gt;。所有对合作方的选择都基于阿维塔品牌自身的需求，阿维塔希望自主选择最领先的技术合作商。&lt;/p&gt;&lt;p&gt;「这一次阿维塔 07L，从外观打造到内饰，甚至颜色选择，华为都有参与，有一个非常大的团队在和我们协同工作。但作为（引望的）第二大股东，&lt;strong&gt;我不认为这个合作模式必须是『必要项』，因为我们有我们差异化的能力&lt;/strong&gt;。」雍军说。&lt;/p&gt;&lt;p&gt;雍军希望华为做一个公共平台，提供公共服务和公共技术，在此之上阿维塔做出差异化的东西，来彰显品牌的不一样。「华为越是公共化，对我们这样相对独立的品牌来说，越能显示出品牌张力。&lt;strong&gt;如果我们所有东西都由他定制化，反而不现实&lt;/strong&gt;。所以我不认为我们要占用他 50% 的资源做出差异化，它是公共化资源。」&lt;/p&gt;&lt;p&gt;综合 IT 之家此前报道，阿维塔（AVATR）品牌创建于 2018 年，是由长安汽车、华为、宁德时代三方联合打造的一个高端智能电动车品牌。&lt;/p&gt;&lt;p&gt;阿维塔科技 2024 年 8 月与华为签署《股权转让协议》，&lt;strong&gt;购买华为持有的引望 10% 股权&lt;/strong&gt;，交易金额为 115 亿元。（来源：IT 之家）&lt;/p&gt;&lt;h1&gt;Meta 扎克伯格：美国若想取得开源 AI 领先，就得减少政策障碍&lt;/h1&gt;&lt;p&gt;8 月 10 日消息，据路透社报道，Meta CEO 马克 · 扎克伯格呼吁美国&lt;s</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6824,6 +6824,543 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 06:26:19 +0000</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>北极科考 | 华威科柔性覆冰监测电子皮肤随中国“雪龙”号赴北冰洋考察</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12281</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>2026年7月，中国第16次北冰洋考察队正式起航</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 02:31:10 +0000</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>艾欧智能完成数亿元融资，加速推动机器人与具身智能走向规模化应用</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12268</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>近日，机器人与具身智能数据基础设施企业艾欧智能（IO-AI Tech）宣布完成数亿元融资。</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 01:16:25 +0000</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>减速器在人形机器人、四足机器狗上的应用</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12264</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>减速器是机器人关节伺服系统的核心，它负责将电机的高速低扭输出转换为低速高扭，以满足机器人运动所需的力矩和精度。</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 16:48:13 GMT</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>面壁智能正式启动IPO：中信证券辅导，端侧模型走向资本市场</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/hMG80lZUX1kaJWpr58g1?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/hMG80lZUX1kaJWpr58g1?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 14:25:14 GMT</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>群青智能联合创始人&amp;CEO 吴哲明博士确认出席AICon深圳，将分享“从真实产线定义智能——工业具身智能的物理 AI 闭环”</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/b1V6WF6iUajJpND8VmCE?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/b1V6WF6iUajJpND8VmCE?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 13:10:55 +0000</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>国产具身智能创全球新纪录！以30%成本跑赢 Figure AI 45%效率，聪明的具身大脑成关键</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/471049.html</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>具身模型一小时狂拣1816件异形包裹</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 04:29:57 +0000</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>人形之外，擎羽把“身体”变成具身智能的新变量</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/470874.html</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>从柔性本体走向跨本体基础智能，让任务与世界知识延续</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 08:14:05 +0800</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Deepseek V4 Pro 正式版 API 上线，百万 Token 仅 6 元；腾讯计划近期发布 HY4 大模型；曝 iPhone18 至少涨价 2000 元起 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368747</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8c/86/8c86802f195a722fe1adce1d63a4f425.png" /&gt;&lt;/p&gt;&lt;h1&gt;DeepSeek V4 Pro 正式版 API 更新上线，多项测试性能接近 Fable 5&lt;/h1&gt;&lt;p&gt;8 月 13 日消息，DeepSeek V4 Pro 正式版正式发布，已更新至 API，调用模型名不变。&lt;/p&gt;&lt;p&gt;新版本增强了 Agent 能力，支持 Responses API 和 Codex 接入。&lt;/p&gt;&lt;p&gt;从官方群放出的评测对比表可以看到，DeepSeek V4 Pro 正式版（DeepSeek-V4-Pro-0813）在多项测试中接近 Fable 5 水平，相比之前的预览版能力大幅提升。&lt;/p&gt;&lt;p&gt;定价如下：&lt;/p&gt;&lt;ul&gt;&lt;li&gt;百万 tokens 输入（缓存命中）：0.025 元&lt;/li&gt;&lt;li&gt;百万 tokens 输入（缓存未命中）：3 元&lt;/li&gt;&lt;li&gt;百万 tokens 输出：6 元&lt;/li&gt;&lt;/ul&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/25/26/2526e3e1c8a89e7516e7f534d7614485.jpg" /&gt;&lt;/p&gt;&lt;p&gt;（来源：IT 之家）&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/68/0d/680d7fe9ba7fa9fa35d51e024852c2ad.png" /&gt;&lt;/p&gt;&lt;h1&gt;腾讯发布 2026 年 Q2 财报，第二季度营收 2048 亿元，计划近期发布 Hy4&lt;/h1&gt;&lt;p&gt;腾讯控股发布 2026 年第二季度财报。财报显示，腾讯第二季度营收 2,047.9 亿元人民币，预估 2,028.4 亿元人民币；第二季度销售费用 118.7 亿元人民币，预估 119.6 亿元人民币；第二季度增值服务业务收入 984.1 亿元人民币。&lt;/p&gt;&lt;p&gt;腾讯表示，混元 Hy3 完成从 preview 到正式版的快速迭代，上线一周调用量较上一代模型增长超 68 倍，更大参数规模的 Hy4 也计划近期发布；WorkBuddy 及 CodeBuddy 持续领跑国内 AI 原生办公智能体赛道，易观数据显示 WorkBuddy6 月 PC 端访问量已突破 2000 万次；微信 AI 助手「小微」灰测有序放量中。&lt;/p&gt;&lt;p&gt;二季度，腾讯游戏收入同比增长 11%，其中本土游戏收入增长 17%，国际游戏收入按固定汇率计算增长 4%；营销服务收入同比增长 22%；金融科技及企业服务收入同比增长 9%，云服务受惠于 AI 增量贡献，国际业务拓展和通用云服务需求增长。（来源：新浪科技）&lt;/p&gt;&lt;h1&gt;曝小红书打造 AI 导购功能，官方暂无回应&lt;/h1&gt;&lt;p&gt;有消息称，小红书在打造全新的「AI 导购」功能，依托对话交互模式，在问答场景中直接推送商品卡片、挂载下单跳转链接。&lt;/p&gt;&lt;p&gt;对此消息，新浪科技向小红书官方进行求证，截至发稿暂无回应。&lt;/p&gt;&lt;p&gt;本月初，新浪科技独家获悉，小红书正全面提速 AI 战略，布局 AI 社交产品、AI 社区互动工具等方向，从后台技术应用转向前台自研、产品化与生态化全面竞速。在招聘平台检索发现，小红书近日密集招募 AI 应用研发人才，且部分岗位薪资给到了 30-60K/16 薪，最高年薪可达 96 万元，足见其加码 AI 方向的决心。&lt;/p&gt;&lt;p&gt;今年 5 月，小红书发布内部信，宣布新一轮组织升级，其中核心变化就包括，成立 AI 一级部门 Dots 和企业智能部，从产品技术和组织两方面加大对 AI 的投入。（来源：新浪科技）&lt;/p&gt;&lt;h1&gt;SpaceXAI 推出 GrokBot，对标 Anthropic 与 OpenAI&lt;/h1&gt;&lt;p&gt;据华尔街见闻报道，马斯克旗下 SpaceXAI 正式入局 AI 代理市场，推出可像真实同事一样处理工作的产品 Grok Bot。8 月 11 日，SpaceXAI 发布 AI 代理产品 Grok Bot，目前处于早期测试阶段。这是马斯克旗下 AI 业务追赶 Anthropic 和 OpenAI 的最新举措，也是 SpaceXAI 与 Cursor 深度合作的阶段性成果。&lt;/p&gt;&lt;p&gt;马斯克随即在 X 平台表示：「我们将在修复早期测试的基本问题、并于本周晚些时候发布 Grok</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 17:24:24 +0800</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>实测 GenOffice Alpha 版：补上办公工作流最后一环｜AI 上新</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368744</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜lfei&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;8 月 3 日， &lt;a href="https://mp.weixin.qq.com/s?__biz=MTMwNDMwODQ0MQ==&amp;amp;mid=2653111529&amp;amp;idx=1&amp;amp;sn=fed610a0867c177d318ad29f75abbf85&amp;amp;scene=21#wechat_redirect" rel="noopener noreferrer" target="_blank"&gt;Genspark 创始人&amp;amp;CEO 景鲲在 AGI Playground 2026 大会上发布了 GenOffice &lt;/a&gt;。这是一款 AI 深度集成的本地 Office 客户端，其亮点在于打通了从 AI 生成到工作交付间的链路：通过 GenOffice 打造的软件工程框架，模型得以 &lt;span style="font-weight: bold;"&gt;直接操作 Office 文件最复杂的底层格式，将生成内容转化为可编辑、可交付的 Word 和 PPT 成品。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Genspark 推出这样一款产品并不令人意外。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在 Genspark 的产品体系 AI WorkSpace 6.0 中，AI 办公套件是核心价值模块；Genspark 还上架了 &lt;span style="font-weight: bold;"&gt;Microsoft Office 插件 &lt;/span&gt;，让用户能在本地的微软 Office 软件里，直接调用 Genspark 的 AI 能力。在文档的转换层上，Genspark 已经积累了足够的经验。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;让人意外的是 Genspark 推出 GenOffice 的方式：开源、免费，Alpha 版即日推出，后续交给用户、团队和 AI Agent 共建迭代。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据 Genspark 介绍，产品的 Alpha 版只由 &lt;span style="font-weight: bold;"&gt;一名工程师用一周时间完成，消耗约 1 万美元的 AI Token。这款用最 AI-Native 的方式开发出的产品，也将用最 AI-Native 的方式迭代&amp;mdash;&amp;mdash;毕竟对于一款 Office 产品而言，用户的真实工作流也是最具价值的养料。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;笔者此前从未接触过 Genspark 生态，但 GenOffice 直接调整文件格式的产品能力，让我产生了极大的兴趣。怀着好奇，笔者充值了 Genspark 基础套餐，开始了本次测试。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;平替本地 Office？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在宣发中，GenOffice 被锚定为平替级的免费本地 Office：既不同于订阅制的 Microsoft 365，也不同于「免费+会员+广告」的 WPS。这个定位看似简单，实则门槛极高：处理一份看似简单的 Word 文档，其底层涉及复杂的几何计算与字体排版算法，背后涉及跨越数十年的代码积累。更要命的是，用户对办公软件的错误容忍度近乎为零。深厚的技术积淀、苛刻的用户需求，成为了传统 Office 厂商最深厚的壁垒。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;不过，AI 赋予了 Genspark 挑战的机会。&lt;/p&gt;
+&lt;p style="text-align</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 17:14:56 +0800</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>AI 入口，开始收费</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368740</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜宇航猿&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;AI 将成为未来唯一的「入口」，这几乎是近年来的一个行业共识，但是这个「入口」如何变现，没人能给出答案。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;不过，现在中国大厂的探索路径，已经清晰出现了。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;8 月 10 日这个周末，两条看起来不相关的新闻几乎同时出现。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;豆包宣布，通过其 AI 对话推荐跳转抖音来客成交的酒店订单，正式执行 12% 的独立佣金费率。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;同一天，千问开放平台上线，顺丰、自如、盈米基金等十多个领域的服务商以 AI 智能体形态接入千问。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;一个开始变现，一个把门打开。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;这两件事放在一起看，信号非常明确&amp;mdash;&amp;mdash;AI 助手喊了两年的「新入口」故事，现在终于开始探索变现了。&lt;/span&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;12%，贵吗？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;作为拥有超过 3.45 亿月活用户的超级 AI 应用，豆包此次曝出的手续费，无疑吸引了所有人的目光。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;根据官方介绍，&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;12% 这个费率由 11.4% 的软件服务费和 0.6% 的支付手续费构成，从商家结算款里直接扣除，用户端不加价。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这件事真正值得注意的不是费率本身，而是一个身份转换。在此之前，豆包带来的酒店订单被直接合并为抖音自然流量，按 8% 的平台费率结算。从 8 月 10 日起，这些订单开始标注独立的「豆包」渠道来源，按 12% 的新费率结算。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;说白了，字节正式把豆包从抖音的「附属流量」升级为一个独立的交易渠道。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这个定价有它的逻辑。抖音主站的酒店订单来自短视频和直播&amp;mdash;&amp;mdash;用户刷着刷着看到了一家酒店，这是「偶遇型」的泛流量。而豆包的订单来自用户主动提问，比如「北京北四环附近有什么性价比高的酒店」，这是「搜索型」的精准意图流量。就像搜索广告一直比信息流广告贵一样，意图越明确的流量越值钱。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;12% 贵不贵？可以拉一条中国互联网的佣金标尺来看。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;本地生活领域，携程的综合佣金率只有 4.4%，但这是被机票等低佣品类拉低的平均数。具体到酒店品类，携程、美团的佣金普遍在 15%~20%。抖音主站的酒旅订单约 8%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;豆包的 12% 卡在中间&amp;mdash;&amp;mdash;比抖音主站高了 50%，但比携程、美团的酒店佣金低了不少。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;而且这里面还有一层容易被忽略的差异。豆包的公关团队在 8 月</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 11:39:29 +0800</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>造物100 #02｜能打游戏的「牙套」键盘、众筹 249 万美元的电子假花、能用卫星找狗的项圈</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368707</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;&lt;strong&gt;作者｜徐珊&lt;/strong&gt;&lt;strong&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong&gt;编辑｜郑玄&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;p&gt;上周 的 WAIC，人山人海。&lt;/p&gt;
+&lt;p&gt;每个展台 都在讲 AI，每件硬 件都说自己是「智能终端的下一代」。可你挤出场馆冷 静下来想想， 记住的产品 有几个？ 大部分设备，把 logo 遮住，你根本分不清谁是谁。&lt;/p&gt;
+&lt;p&gt;这就是 2026 年硬件行业最拧巴的地方，造东西从没这么容易过：模型写代码、3D 打印出外壳、深圳供应链一条龙。但也正因为谁都能造，同质化像潮水一样漫上来。真正的创新，成了比芯片还稀缺的东西。&lt;/p&gt;
+&lt;p&gt;可潮水底下，总有人在憋大招。而且我们发现，一旦谁真的跑出一个好的产品形态，市场会毫不犹豫地把钱砸过去。这就是造物时代的掘金逻辑：淘金的人挤破头，卖水的闷声发财，而定义新品类的人，直接画地图。&lt;/p&gt;
+&lt;p&gt;这一个月，我们顺 着几个 问题观察硬件创新的变化。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;那些大技术会先在哪落地？&lt;/strong&gt;Starlink 的卫星信号绕过了手机，先去深山里接住了一只跑丢的狗，发短信都费劲的卫星直连，传一条狗的坐标刚刚好。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;AI 硬件非得发明新物种吗？&lt;/strong&gt;不一定。它钻进了孩子手里的放大镜、花坛里的一朵假花、你枕了三十年的枕头，旧物件，闹钟，AI 顺着人的旧习惯往里长，比让人适应新设备聪明多了。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;我们还发现，现在传感器早就不值钱了，值钱的是让数据变成情绪。&lt;/strong&gt;一只空气变差就当场「阵亡」的机械小鸟，一只土壤干了就蔫给你看的像素宠物。这一代硬件想通了一件事，&lt;strong&gt;卖数据不如卖愧疚感，卖情绪价值。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;甚至有人开始反向卷：不能回看的相机、不出照片的相机、除了记事什么都干不了的掌机，当效率被手机卷到头，&lt;strong&gt;「反效率」成了新的体验溢价。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;造物 100 栏目介绍：&lt;/p&gt;
+&lt;p&gt;造物，正在从少数人的特权，变成所有人的能力。&lt;/p&gt;
+&lt;p&gt;过去，做出一件硬件需要工厂、资本和一整条供应链，如今，AI 让人用一句话 就能生成能跑的软件，再加上桌面级的激光、UV 与 3D 打印设备，一个普通人在自家书房里，就能把灵光一现的东西造出来。&lt;/p&gt;
+&lt;p&gt;「我想要，我就能自己得到」正在成为这个时代新的注脚。&lt;/p&gt;
+&lt;p&gt;我们相信，一个属于造物者的时代正在到来，而「造物 100」，就是我们为它留下的记录。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;以下，是「造物 100 」栏目的第「2」期推荐的 10 个造物：&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;&lt;strong&gt;卫星宠物项圈 Fi Ultra&lt;/strong&gt;&lt;/h2&gt;
+&lt;h2&gt;&lt;strong&gt;让 Starlink 正在从太空帮人找狗&lt;/strong&gt;&lt;/h2&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/4c/3a/4c3a727cd9baf675cd5644815707c947.png" /&gt;&lt;/p&gt;
+&lt;p&gt;纽约宠物科技公司 Fi 的第四代产品，创始人 2017 年因为想监督遛狗师偷没偷懒入行， 如今做成了美国智能项圈头部品牌。&lt;strong&gt;（$199 + $20 激活费 + 订阅制，7 月 8 日已上市）&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;过去所有 GPS 项圈都有同一个死穴，就是狗一跑出基站覆盖，追踪器当 场失联，但狗最爱走丢的农场、林区、露营地恰好都是信号盲区。&lt;/p&gt;
+&lt;p&gt;Fi Ultra 让项圈在没信号时可以自动切换到 Starlink 卫星，全美任何角落都能实时定位。农村用户、猎 犬 主、常带狗进山的人，第一次有了真正管用的追踪器。而且当幼犬完全长大后，可以免费更换项圈。&lt;/p&gt;
+&lt;p&gt;这是我们第一次在手机之外的消费级设备上，看到卫星直连技术被用来解决具体问题。工程上，它让卫星、LTE、Wi-Fi、蓝牙四种连接无感切换，再叠加常开的双频 GPS。&lt;/p&gt;
+&lt;p&gt;有意思的是，卫星直连现阶段带宽窄到手机发短信都费劲，但宠物定位每次只需 回传几十字节的坐标恰好是这项半成熟技术当下能完整胜任的少数消费场景之一。&lt;/p&gt;
+&lt;p&gt;不过我们 发现这类产品还是有很多 bug，比如说，GPS 常开续航时间短，68g 重量对小型犬不</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 17:41:29 +0000</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI-backed Thrive Holdings raises $2B to bring AI to the enterprise</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/12/openai-backed-thrive-holdings-raises-2b-to-bring-ai-to-the-enterprise/</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Thrive Holdings has raised $2 billion in new funding at a $12 billion valuation from investors like SoftBank, D1 Capital Partners, and Altimeter Capital.</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 16:04:27 +0000</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Lovable confirms new $13.3B valuation, raises another $400M</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/12/lovable-confirms-new-13-3b-valuation-raises-another-400m/</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>This new funding comes after Lovable hit $500 million in annualized run rate revenue in June, the startup told TechCrunch.</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 12 Aug 2026 14:20:33 +0000</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Everything announced at Made by Google ’26: Pixel 11, Pixel Watch 5, Pixel Tag, and tons of Gemini features</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/12/google-unveils-pixel-11-lineup-new-airtag-rival-and-gemini-features-at-made-by-google-2026/</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>From the Pixel 11 series and a brand new competitor to Apple’s AirTag, here are all the announcements from the Made by Google 2026 event.</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7361,6 +7361,108 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 10:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>智象未来 (HiDream.ai)算法科学家潘滢炜博士确认出席AICon深圳，将分享“从 Token 预测到状态预测：迈向世界模型的原生全模态之路”</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/9d9Oik3uZpqfjbfElZaq?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/9d9Oik3uZpqfjbfElZaq?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 12:34:42 +0000</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>4.8亿美元砸向端侧算力！Agent芯片新贵冲出重围</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/472059.html</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>首颗AI芯片已进入量产</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 13 Aug 2026 11:53:02 +0000</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>具身数据来了实战派！40天2轮融资数千万，瞄准物理AI基础设施</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/472060.html</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>重新定义物理AI数据基础设施</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7463,6 +7463,359 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 09:05:53 +0000</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>帕西尼发布PXCap Pro五指数据采集手套</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12326</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>处处皆可采，采集皆可用</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 09:03:32 +0000</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>一年融资三轮！机器人触觉传感企业，模量科技完成数千万元Pre-A轮融资</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12312</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>近日，深圳市模量科技有限公司完成了由猎鹰投资、益华资本投资的数千万元Pre-A轮融资，点石资本担任财务顾问。</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 06:29:20 +0000</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>从首创到500台下线｜威迈尔人形机器人底盘加速规模化交付</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12303</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>8月11日，威迈尔人形机器人专用底盘第500台在湖州生产基地正式下线。</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 03:20:59 +0000</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>从人形臂到整机平台：Marvin 全力控人形臂，如何撑起 Gento 两款新品？</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12291</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>本周，Gento 正式发布两款人形机器人新品——轮式折叠机器人Gento Luna 与 轮式升降机器人Gento Skye。</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 17:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Lift Happens</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-darpa-heavy-lift-challenge</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 06:18:56 +0000</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>德塔智能与舞肌科技达成战略合作，联合规范全身协同灵巧操作数据采集</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/472718.html</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 18:44:01 +0800</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>这家靠全景起步的公司，正在逐步让用户「忘掉相机」</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368847</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;你上一次打开全景相机，是什么时候？&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;几个全景品类的老用户告诉我：全景相机很容易「吃灰」。他们当年冲着拍出酷炫的运动视频下单，到手之后发现不是没有相机，而是没那么多时间去滑雪、潜水、登山&amp;hellip;&amp;hellip;机器用了几次就放抽屉里了。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;不过，更多最近一年入手全景相机的朋友，给出了完全不同的答案。他们的使用场景不再局限在户外运动，亲子、旅行、自驾游是他们更主流的使用场景。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;从整体影像市场来看，相比起今年爆火的云台相机，全景相机的增速自然更慢。核心原因是两个品类的目标和任务复杂度不同：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;前者最核心的任务之一是「拍好人像」，实现这个目标的方式相对明确和收敛；而后者则希望接管用户从按下录制到拿到成片的整个链条，做到「无感记录」。这件事的天花板更高，进度条自然也就走得更慢。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;过去几周时间里，我提前上手了 Insta360 全新一代全景相机 X6，借此机会更新了对全景这个品类在产品、技术端的认知和了解。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;全景最大的问题，已经不是「拍」了&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;画质差，是大部分人过去 10 年里全景相机最大的刻板印象和负面标签。同样是 8K，全景相机因为采集的信息更多，单位面积分到的像素比传统设备少，分辨率也就更低。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;硬件迭代是提升画质的一个主要方法。在 X6 上，影石装上了更适配全景的 1/1.1 英寸方形传感器。可以说，画质问题已经得到了阶段性解决，不再是劝退用户的核心「槽点」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但是从「无感拍摄」到「无感出片」，全景的后期剪辑仍然是困扰用户的最后一公里痛点。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在过去很多年，影石一直希望降低这个流程的操作门槛，在软件端打造了一套「智能剪辑」产品体验。但如果你真的用过全景相机，你会发现之前的体验距离「无感」仍然有不小距离。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;最大的 bug 就是过程中仍然需要多次、重复、细碎的「人工接管」。拍完之后，需要先把素材从相机导入手机 App，然后从拍到的多段片段里进行挑选，最后调用手机或云端的算力得到成片。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但很多时候，我的真实使用场景里没有那么多时间进行这些操作。举个例子，用全景相机拍完一天徒步或滑雪，返程要开几十公里的车，到家之后第二天还要上班&amp;hellip;&amp;hellip;长此以往，存在相机或 SD 卡里的素材就像桌面上堆的还没开封的书那样&amp;mdash;&amp;mdash;买了就算看了，拍了就当剪了&amp;mdash;&amp;mdash;越来越多，越来越不想剪。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="1404" src="https://imgslim.geekpark.net/uploads/image/file/6c/19/6c19aa94c79a8e45e0606cc8a43af248.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;全新发布的 Insta360 X6 全景相机 | 图片来源：影石Insta360&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这次 X6 上最让我满意的新功能「AI 导演」，就是在解决这个问题。它的逻辑很简单：不用手动上传和挑选素材，不用联网操作，相机在每晚会自动分析前一天（自然日）的素材，自动完成剪辑，然后自动推送到手机上。一切工作都运行在本地端侧，用户一觉睡醒就可以得到一条前一天的 vlog 成片。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;整个过程不需要连手机、选素材，唯一要做的就是确保全景相机插上电源线。然后，「智能剪辑」的体验就可以从一问一答的 chatbot，升级成自己干活的 agent，跟插上电源后在 Mac Mini 上养龙虾差不多。&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 18:02:05 +0800</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>阿里云，接得住中国智驾吗？</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368846</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜李苏&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;8 月，乌兰察布。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;近 30 位来自核心车企和方案商的智驾关键力量，被请进了阿里巴巴数据中心。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这里承载着中国智能驾驶研发 60% 的算力。数据中心昼夜不停，像一颗强健搏动的心脏；而道路上智能驾驶的车辆每一次从容的转弯、精准的刹停、安稳的跟车，背后都可能是这里彻夜的计算。几乎所有参会者正在训练的模型，就跑在脚下这片机房里。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;把论坛开在数据中心所在地，本身就是一个信号： &lt;span style="font-weight: bold;"&gt;智驾的竞争，已经从算法下沉到工程。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;阿里云智能集团资深副总裁、公共云事业部总裁刘伟光的开场白很简短&amp;mdash;&amp;mdash; &lt;span style="font-weight: bold;"&gt;模型、芯片、云，这三样东西过去由三类供应商分别提供 &lt;/span&gt;，在三种不同的会上讨论。 &lt;span style="font-weight: bold;"&gt;这一次，它们被放在同一张桌上，由同一批决策者一起追问。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;没有人再争论车企要不要上云，问题变成了：当智驾进入大模型时代，中国车企需要什么样的基础设施？谁能把芯片、云、模型三层都做通，而不是只卖其中一层？&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;阿里云给出的答案，是一条产线&amp;mdash;&amp;mdash;从数据到模型再到算力，完整打通。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="720" src="https://imgslim.geekpark.net/uploads/image/file/a1/bd/a1bde72d2b3624d994815faab1d80879.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="color: #bbbfc4;"&gt;阿里巴巴在乌兰察布的数据中心之一｜图片来源：阿里云&lt;/span&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;问题在下沉&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;如今，智驾的路线正在分化。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;端到端已成共识，但再往上，有人押注 VLA，有人赌世界模型，也有公司选择继续深耕端到端本身。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但不管是哪条路，范式一旦切换到「训模型」，瓶颈就变成了三件事的困境&amp;mdash;&amp;mdash; &lt;span style="font-weight: bold;"&gt;数据供得上吗？模型底子够好吗？算力扛得住吗？任何一项是短板，另两项的投入都会被浪费。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;过去一年，行业里出现了一个怪现象。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;各家车企和方案商都在抢卡，但买了卡之后，很多人发现模型迭代速度并没有明显提升。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;不少车企有过类似的经历： &lt;span style="font-weight: bold;"&gt;集群建起来了，算</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 14 Aug 2026 08:52:35 +0800</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek Harness 公测，对标 Claude Cowork ；长鑫科技市值超越腾讯；OpenAI 年化营收有望翻番达 400 亿美元</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368789</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b3/28/b3281143f6105fd9e4d63426df15659b.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;对标 Claude Cowork：DeepSeek Harness 公测，同步开放插件生态&lt;/h1&gt;
+&lt;p&gt;8 月 13 日消息，DeepSeek-V4-Pro-0813 正式开源，同时还推出了其开源（MIT 协议）的代码智能体框架 Harness 的 v0.1 开发者预览版（基于 Cordis），并同步开放了配套的插件生态系统。相关 GitHub 仓库也已公开。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d2/92/d2920120e32528bf5ff44f45afac90e9.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;DeepSeek 正式开源 DeepSeek‑V4‑Pro‑0813 模型，同步推出基于 Cordis、采用 MIT 协议的代码智能体框架 Harness v0.1 开发者预览版，并开放配套插件生态，GitHub 仓库现已公开，开发者可通过 npx 命令或源码两种方式启动 WebUI，该产品定位对标 Claude Cowork 与 OpenAI Codex，面向编程办公 AI 生产力场景。&lt;/p&gt;
+&lt;p&gt;Harness 贯彻「一切皆插件」的设计理念，依托 Cordis 元框架，模型、工具、UI、沙箱等全部 Agent 能力都以插件形式存在，无需修改源码就可以自由替换扩展。框架提供 dsh 命令行工具，拥有标准、PTC 程序化工具调用、极简、创造四种运行模式，适配基准测试、插件开发等不同开发者场景，落实「模型 + Harness=Agent」的技术思路，完成从需求理解到代码交付的闭环。&lt;/p&gt;
+&lt;p&gt;DeepSeek‑V4‑Pro‑0813 为 MoE 混合专家架构，总参数 1.6 万亿，推理时仅激活 490 亿参数，拥有 100 万 token 上下文窗口，最大输出 38.4 万 token，支持思考 / 非思考模式，兼容多种主流 API 接口。内部测评显示，该版本相比预览版能力大幅提升，多项测试接近甚至超越 Claude Fable 5，编程相关基准分数提升显著。&lt;/p&gt;
+&lt;p&gt;该模型权重基于 MIT 协议开放，开发者可以直接下载本地部署，不再单纯依赖云端服务，普通通用算力卡即可运行，降低政企私有化部署门槛，也提升供应链抗风险能力。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/16/f4/16f472a1291189962a03bfa3a40e398c.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;备战 IPO 上市：彭博社称 2026 年 OpenAI 年化营收有望翻番达 400 亿美元&lt;/h1&gt;
+&lt;p&gt;8 月 14 日消息，彭博社发布博文，报道称在收 IPO（首次公开募股）上市前，OpenAI 的发展势头良好，2026 有望实现年化收入超过 400 亿美元（现汇率约合 2,702.76 亿元人民币），比 2025 年收入（约 200 亿美元（现汇率约合 1,351.38 亿元人民币））翻一番。&lt;/p&gt;
+&lt;p&gt;据彭博社报道，联合创始人兼总裁格雷格 &amp;middot; 布罗克曼在内部公告中告知员工，仅 7 月份，月度营收增长率就增长了 20% 以上。首席财务官莎拉 &amp;middot; 弗莱尔此前曾指出，公司经历了快速扩张期，2025 年的年化营收增长率超过 200 亿美元（现汇率约合 1,351.38 亿元人民币）。&lt;/p&gt;
+&lt;p&gt;在市场竞争方面，Anthropic 在今年 5 月公布的年化营收为 470 亿美元（现汇率约合 3,175.75 亿元人民币），不过彭博社指出由于两家公司在计算统计上存在差异，很难直观、公平对比两家公司的年化营收。&lt;/p&gt;
+&lt;p&gt;在市场竞争策略方面，OpenAI 公司为抵御外部竞争对手的冲击，捍卫市场份额，积极调整其市场策略和定价策略，通过降低部分 AI 模型的价格，从而吸引注重成本的开发者。OpenAI 公司还聘请了一位经验丰富的网络安全高管，以提振企业销售。（来源：IT 之家）&lt;/p&gt;
+&lt;h1&gt;投资者押注 Anthropic 估值达 2 万亿美元，冲击史上最大 IPO&lt;/h1&gt;
+&lt;p&gt;Anthropic 的投资者正押注这</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7816,6 +7816,100 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 15 Aug 2026 04:21:09 +0000</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>对话郎咸朋：用机器人创业重做一次“百万智驾量产”</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/473407.html</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>1.9万字全文实录</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 15 Aug 2026 08:52:38 +0800</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>智谱发布 GLM-5.3，编程能力更强；传苹果训练国内专用 AI 模型；微信：朋友圈现在、过去、未来都不会有二次编辑功能 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368849</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr"/>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ca/fe/cafe9a6a8934077df43928e62035b1e3.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;智谱正式发布 GLM-5.3，拥有更强编程能力&lt;/h1&gt;
+&lt;p&gt;8 月 14 日，据介绍，与 GLM-5.2 相比，GLM-5.3 基座模型未变，但通过极致的后训练 Scaling 大大提高了模型的智能上界。&lt;/p&gt;
+&lt;p&gt;GLM-5.3 拥有更强的编程能力，在内部自建体感评测中较 GLM-5.2 提升 50%，在包括 TerminalBench3.0、Agents'LastExam(CLI)在内的公开基准测试中取得开源第一。&lt;/p&gt;
+&lt;p&gt;智谱还表示，将在发布两周后开放模型权重。&lt;/p&gt;
+&lt;p&gt;（来源：广角观察）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f3/82/f3826192b09fb502720de6b51125eec9.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/86/e9/86e9dd42d3ab280092b27978ac66d9aa.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;知情人士称苹果在阿里巴巴支持下为中国市场训练专属 AI 模型&lt;/h1&gt;
+&lt;p&gt;据三位知情人士透露，苹果公司已经专门为中国市场训练了一个大型语言模型。&lt;/p&gt;
+&lt;p&gt;这一举措标志着这家 iPhone 制造商在华 AI 策略的重大转变，此前该公司曾计划主要依赖第三方模型来驱动其在当地的人工智能功能。据悉，该 AI 模型是苹果与阿里巴巴集团合作开发，并在这家中国科技巨头的支持下完成训练的。由于信息敏感且尚未公开，知情人士拒绝透露姓名。（来源：今日头条）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cb/ec/cbec2565f239fb31907fc4200a34a53f.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;英伟达宣布 CPO 交换机全面量产&lt;/h1&gt;
+&lt;p&gt;8 月 14 日，英伟达宣布 Spectrum-X Ethernet Photonics 已进入全面量产阶段，为面向 AI 工厂的下一代大规模扩展网络基础设施提供支持。&lt;/p&gt;
+&lt;p&gt;英伟达表示，Spectrum-X Ethernet Photonics 专为吉瓦级 AI 工厂网络需求设计，实现激光器数量减少 4 倍、功耗降低 5 倍、平均故障间隔时间（MTBI）提升 10 倍。该产品由台积电、矽品、Lumentum、天孚通信、鸿海等供应链伙伴参与制造、封装及组装。（来源：界面新闻）&lt;/p&gt;
+&lt;h1&gt;SpaceX 完成收购 Cursor&lt;/h1&gt;
+&lt;p&gt;8 月 14 日，SpaceX 提交监管文件称，公司与代码编辑工具 Cursor 的合并交易已完成。根据交易安排，Cursor 股东获得合计约 3.89 亿股 SpaceX A 类普通股，对应 Cursor 隐含股权价值 600 亿美元。&lt;/p&gt;
+&lt;p&gt;此外，Cursor 已归属限制性股票单位转换为约 175 万股 SpaceX A 类普通股，未归属限制性股票单位和股票期权则分别转换为约 2913 万份限制性股票单位和 4437 万份股票期权。此次交易以发行 SpaceX A 类普通股作为主要对价，未涉及公开发行。（来源：广角观察）&lt;/p&gt;
+&lt;h1&gt;月之暗面严正声明：警惕可疑交易，已向公安机关反映涉嫌违法犯罪的行为、&lt;/h1&gt;
+&lt;p&gt;8 月 14 日消息，今天（14 日）晚间，月之暗面 Kimi 公众号发布严正声明，提醒「&lt;strong&gt;警惕可疑交易&lt;/strong&gt;」。&lt;/p&gt;
+&lt;p&gt;声明获悉，针对市场上冒用月之暗面名义&lt;strong&gt;虚假融资、涉嫌违法犯罪的行为&lt;/strong&gt;，公司已向公安机关反映。&lt;/p&gt;
+&lt;p&gt;现严正声明：&lt;/p&gt;
+&lt;p&gt;不存在所谓「朋友基金」或「特殊通道」。&lt;/p&gt;
+&lt;p&gt;不存在所谓「老股额度」或「预留额度」。&lt;/p&gt;
+&lt;p&gt;不存在所谓「官方代理」或「授权中介」。（来源：IT 之家）&lt;/p&gt;
+&lt;h1&gt;阿里开源 Qwen3.8，千问大模型全球下载超 30 亿次&lt;/h1&gt;
+&lt;p&gt;8 月 14 日晚，阿里千问正</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7910,6 +7910,91 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 16 Aug 2026 05:28:42 +0000</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>牛来！A社营收暴涨1400%，最新季度入账115亿美元</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/473947.html</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>将超越马斯克的SpaceX，成为史上上市估值最高的IPO。</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 16 Aug 2026 09:15:43 +0800</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic 评估 AI 风险上升, 暂不公开更强模型；刘炽平：微信将成为 AI 为先的生态系统；全网吐槽《牛来》票房逆袭</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368854</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cd/3e/cd3e8d5a73a69345fa847d92327f9c34.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;2026 世界机器人大会展位图揭晓：8 月 19 日开幕，宇树科技、优必选等参展&lt;/h2&gt;
+&lt;p&gt;8 月 16 日消息，2026 世界机器人大会将于 8 月 19 日至 23 日在北京经济技术开发区北人亦创国际会展中心举行。近日，2026 世界机器人大会展位图全揭晓。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0c/9a/0c9aa93cb28a74d149b76c31b11a8d00.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;作为大会展览的重要新增空间，智创馆面积达 2 万平方米，拥有更加开阔、通透的展示环境，将进一步提升企业参展和观众观展体验。&lt;/p&gt;
+&lt;p&gt;宇树科技、星海图、优必选、银河通用、自变量、明略科技、维他动力、智身科技、云深处、傅利叶、越疆、仙工、中科慧灵等代表性企业，将带来机器人整机、具身智能及人形机器人的最新成果。&lt;/p&gt;
+&lt;p&gt;北京、上海、浙江、湖北、广东、四川、吉林等地的人形机器人创新中心将齐聚智创馆，集中展示各地的创新成果。央企展区也将在这里亮相，集中展示中央企业在机器人领域的整体布局和应用成果。京东将整合物流、零售、工业、家政等应用场景，打造【未来人机共生新范式】超级展区。&lt;/p&gt;
+&lt;p&gt;智造馆将汇聚京城机电、珞石、中信重工、海尔集团、非夕、睿尔曼、云迹、擎朗、普渡、申昊科技、本末科技、国兴智能、美丽魔方机器人、源络科技等企业。绿的谐波、卧龙电驱、同川、新剑、五洲新春、鸣志电器、雷赛智能、祥明智能、伟创动力、南方精工等零部件企业也将集聚于此，展示机器人产业链关键环节的技术积累与创新突破。&lt;/p&gt;
+&lt;p&gt;智合馆将成为国内外机器人产业力量集中交流的重要空间。众擎、星动纪元、加速进化、新松、乐聚、松延动力、优理奇、千寻智能、帕西尼、禾川、灵心巧手、他山科技等企业将亮相智合馆。&lt;/p&gt;
+&lt;p&gt;多家知名国际企业也将集聚智合馆。AMD、SMC、Infineon、Realsense、Realtek、Robotis、NSK、Schaeffler、EMAG、igus、maxon、Faulhaber、Harmonic、Henkel、3M 等企业将带来芯片、控制、驱动和工业自动化领域的技术与解决方案，为观众呈现机器人产业链不同环节的全球创新成果。（来源：IT 之家）&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d9/4e/d94e23242593c47731b56c1f5b5f9545.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;腾讯总裁刘炽平：微信将成为以 AI 为先的生态系统，未来能转化为巨大价值&lt;/h2&gt;
+&lt;p&gt;在 8 月 12 日晚间的腾讯 2026Q2 财报业绩电话会上，腾讯总裁刘炽平谈及二季度微信 AI「小微」灰测的反馈。&lt;/p&gt;
+&lt;p&gt;刘炽平认为，AI 可以让微信变得更加智能化，能够帮助用户进行交易、探索内容以及管理日常生活。「在 PC 时代，QQ 主要是一个通信和社交工具，到了移动互联网时代，微信又将 QQ 的价值放大了 10 倍以上。而到了 AI 时代，随着时间的推移，微信将成为以 AI 为先的生态系统。用户给出一个指令，系统就自行执行。」&lt;/p&gt;
+&lt;p&gt;刘炽平表示，如果腾讯能够在控制成本的同时提供这种体验，并且满足用户隐私需求、成本效益，就能为微信赋予强大的能力。「未来微信的生态系统将会扩大，基于目前的盈利机制转化为巨大的价值。这就是我们看到的未来。随着原型的推出，我们对此越来越有信心。」（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;全球第一：阿里通义千问 AI 模型全球下载量破 30 亿，碾压 Meta 和谷歌&lt;/h2&gt;
+&lt;p&gt;8 月 15 日消息，据彭博社今日报道，阿里旗下开源 AI 模型千问家族在过去六个月内全球累计下载量突破 30 亿次，超越 Meta、Alphabet 等一众竞争对手，成为全球下载量第一的 AI 模型。&lt;/p&gt;
+&lt;p&gt;根据开源 AI 社区 Hugging Face 于当地时间 8 月 14 日发布的《开放模型现状》报告，2026 年谷歌模型下载量约 4.18 亿次，Meta 约 2.27 亿次，而阿里千问达到了 20.45 亿次（仅 Hugging Face Hub 上的下载量，不含魔搭</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7995,6 +7995,379 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17 15:33:42+00:00</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Is Shipyard Welding the Right First Job for Humanoid Robots?</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/persona-ai-humanoid-robot-welding</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Humanoids desperately need to stop making YouTube videos and get a job already, and &lt;a href="https://persona.ai/" rel="noopener noreferrer" target="_blank"&gt;Persona AI&lt;/a&gt; is one of the …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 09:30:49 +0000</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>共生知行发布人形机器人赛车Demo：以卡丁车测试双足机器人的“全身智能”</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/474537.html</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>8月17日，具身智能初创公司共生知行发布双足人形机器人驾驶卡丁车Demo</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 09:04:37 +0000</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人开始打国球了！两台机器人完整打完11分制比赛</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/474518.html</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>没有遥控、没人喂球</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 07:39:56 +0000</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>终于！世界模型进入“有声时代”：24FPS画面+48kHz立体声实时生成</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/474334.html</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>即将完全开源</t>
+        </is>
+      </c>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 07:55:18 +0800</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>宇树发布「机器超人」：原地跳高 2m；豆包上线新功能，手机可远程控制电脑；吉利汽车架构调整，李书福辞任董事会主席｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368929</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/97/e6/97e602224f6f011d8cdf3f207b9bbf69.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;宇树科技发布「超人」机器人，并定 8 月 19 日科创板上市&lt;/h2&gt;
+&lt;p&gt;8 月 17 日，宇树科技发布了一款人形机器人新品「超人」，原地跳高 2m，极限速度 12.66m/s（0.85m 腿长），超越全世界全人类原地跳高和奔跑速度纪录。&lt;/p&gt;
+&lt;p&gt;宇树科技表示，全新整机刚用 3 个多月研发出来，未来几个月还有很大的完善空间。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a2/1b/a21b3f96d74fbf720ab1120d9906b7ba.png" /&gt;&lt;/p&gt;
+&lt;p&gt;早在今年 4 月，宇树 H1 机器人就跑出 10m/s 刷新世界纪录，逼近博尔特速度极限。如今「超人」再次打破纪录，并成功超越人类极限。&lt;/p&gt;
+&lt;p&gt;宇树科技 8 月 12 日宣布，旗下人形机器人累计生产下线约 18,000 台（仅包括仿生双足人形的数量，不含其他类人形机器人或轮式底盘人形）。&lt;/p&gt;
+&lt;p&gt;同日，宇树科技发布首次公开发行股票科创板上市公告书称，公司股票将于 2026 年 8 月 19 日在上海证券交易所科创板上市。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/08/0f/080f48df13d6796081639754fddc0d07.png" /&gt;&lt;/p&gt;
+&lt;p&gt;根据此前公告，宇树科技发行价格 150.80 元/股，中一签（500 股）需缴款 7.54 万元。（来源：格隆汇）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/43/54/435480900ec4b278701d42ba294cf174.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 与英伟达扩大计算潜在机会，到 2030 年计算规模或达 6000 亿美元&lt;/h2&gt;
+&lt;p&gt;8 月 17 日，根据英伟达发布的新闻稿，OpenAI 将在 PORTS-Pike 建设并运营一座世界级的人工智能工厂。AI 工厂将采用英伟达的全栈 DSX AI 工厂平台，包括 GPU、CPU、网络和基础设施软件。初步部署预计将提供 4.25 吉瓦的 AI 工厂产能。&lt;/p&gt;
+&lt;p&gt;OpenAI 承诺将在 2030 年前大规模部署 NVIDIA AI 基础设施。OpenAI 现有和计划中的承诺约占 NVIDIA 计算 12 吉瓦，如果英伟达将 PORTS Pike 协议扩展到最初的 4.25 吉瓦之外，将有机会扩展至约 16 吉瓦。英伟达表示，在这些层面上，这一机会代表到 2030 年 NVIDIA 计算量约为 6000 亿美元。（来源：财联社）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;史诗级 IPO 前夕，Anthropic 据称 2028 年营收料高达 2000 亿美元&lt;/h2&gt;
+&lt;p&gt;8 月 17 日，据美媒，Anthropic 公司最新的一份文件显示，其第二季度营收超过 115 亿美元，较 2025 年同期的 7.87 亿美元实现约 14 倍的强劲增长。据路透，两位熟悉 Anthropic 公司财务情况的人士称，预计到 2028 年，Anthropic 公司年营收将达到 1900 亿至 2000 亿美元。&lt;/p&gt;
+&lt;p&gt;据悉，Anthropic 已于 6 月向美国证券交易委员会秘密提交 IPO 相关文件，进入静默期。受此约束，公司不得对外发布涉及自身财务表现的公开信息。此前英国《金融时报》称，多位 Anthropic 的投资者透露，该公司预计将在 10 月以 2 万亿美元甚至更高的估值上市。若该预测成真，Anthropic 将超越 SpaceX，成为史上规模最大的首次公开募股。（来源：格隆汇）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;阿里巴巴开放权重模型下载量过去半年突破 30 亿&lt;/h2&gt;
+&lt;p&gt;8 月 17 日，根据 Hugging Face 的报告，阿里巴巴旗下的开放权重模型通义千问（Qwen）过去半年全球下载量突破 30 亿次，高居第一。相比下 Google 的开放权重模型</t>
+        </is>
+      </c>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 13:54:45 +0800</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>被 AI 碾压 30 年后，人们重新爱上了下棋</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368897</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜Techno 之王&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;1997 年 5 月 11 日，纽约。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;IBM 的超级计算机「深蓝」在六局对决中，以 3.5 比 2.5 击败国际象棋世界冠军卡斯帕罗夫。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这是人类第一次在智力游戏的最高殿堂输给机器。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;那场比赛的最后一局只用了 19 步。卡斯帕罗夫在一个经典开局中走出了罕见的失误，深蓝精准地抓住了机会，迅速将局面推向不可挽回。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;终局时，卡斯帕罗夫猛地站起来离开棋桌，脸上写满了震惊和愤怒。他后来公开指控 IBM 在幕后使用了人类棋手协助，拒绝接受这个结果。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;那一天，全世界都在讨论同一个问题&amp;mdash;&amp;mdash;在机器面前，人类的智力还有尊严吗？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;时间快进到 2016 年 3 月，首尔。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Google DeepMind 的 AlphaGo 以 4 比 1 击败韩国围棋九段李世石。这一次冲击比深蓝更大，因为围棋被视为「人类智慧的最后堡垒」。围棋的可能局面数远超宇宙中的原子总数，专家们此前预测 AI 至少还需要十年才能在围棋上战胜人类顶尖棋手。李世石在第四局下出的那步「神之一手」，以万分之一的概率让 AlphaGo 短暂迷失，赢下了人类仅有的一局。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;后来人们意识到， &lt;span style="font-weight: bold;"&gt;这可能是人类对围棋 AI 的最后一胜 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;2017 年 5 月，乌镇。AlphaGo 3 比 0 横扫当时世界排名第一的柯洁。柯洁在第二局中盘趴在桌上，赛后说了一句让所有人沉默的话，「去年我觉得它的下法还接近人类，但今天」&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;「它下得像围棋之神 &lt;/span&gt;。」&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;同年，DeepMind 宣布 AlphaGo 退役，转向更「有用」的科学研究领域。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;棋盘上的战争，对机器来说已经不值得再打了。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;从深蓝到 AlphaGo，这些人机对决构成了一个清晰而悲壮的叙事&amp;mdash;&amp;mdash; &lt;span style="font-weight: bold;"&gt;机器越来越强，人类节节败退，这些古老的智力游戏似乎正在被 AI 宣判死刑。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但真实的故事，却如棋局般出人意料。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;2026 年，国际象棋被 AI 碾压将近 30 年之后，全球最大的国际象棋平台 Chess.com 坐拥 &lt;span style="font-weight: bold;"&gt;2.5 亿注册用户、日活跃用户超过 1000 万、年收入突破 2 亿美元 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;国际象棋不但没有死，反而处于这个游戏几千年历史中人气的绝对巅峰。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;一个被机器彻底「解决」的游戏，怎么反而越来越多人玩了？&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 11:28:54 +0800</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>世界机器人大会今年不一定「Wow！」，但有五个问题很值得关注</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368887</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section class=""&gt;&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜Li Yuan&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜张鹏&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;8 月 10 日，宇树科技完成科创板申购，发行价 150.80 元，发行市值约 610 亿元，发行市盈率 219 倍，是通用设备行业平均值的近六倍。多家机构给出的挂牌后估值直接标到千亿以上，敲钟的日子很可能就落在这个月下旬，几乎与世界机器人大会撞在一起。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;&lt;strong style="color: #000000; font-size: 16px; letter-spacing: 0.5px; line-height: 1.75; font-family: Optima-Regular, PingFangTC-light;"&gt;钱多，预期更高。&lt;/strong&gt;钱多，预期更高。对标电动车，意味着一个万亿级的制造业；对标 AI，则意味着根本没有天花板&amp;mdash;&amp;mdash;毕竟具身智能被寄予的，是让 AI 真正落进物理世界。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;热的是估值，冷的是订单。可作对照的是另一组数字。2025 年宇树人形机器人出货 5500 多台，全球第一；工信部预计 2026 年全年整机产量有望突破 10 万台，比去年跳升五倍。增速极快，但总产值仍远撑不起千亿估值。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light,'PingFang SC','PingFang TC','Hiragino Sans GB','Microsoft YaHei',sans-serif; font-size: 16px; line-height: 1.75; margin: 0 0 24px 0; margin-left: 8px; margin-right: 8px;"&gt;而行业真实的状态是，&lt;strong</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 17 Aug 2026 11:26:23 +0800</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>闭门、举牌、真话，这场路演有点不一样</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368885</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section class="wx_imgbc_placeholder"&gt;&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜Li Yuan&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜郑玄&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;会算命的非遗挂件？专挑膝盖下手的外骨骼？会跳的机器人？&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;8 月 7 日，地瓜机器人办的这场闭门路演「地心引力 DemoDay 2026」，十个项目轮番上台，画风一个比一个野。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;有做具身智能的，也有做智能硬件的，大部分都还初具雏形：一些项目，半年前才刚正式启动。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light,'PingFang SC','PingFang TC','Hiragino Sans GB','Microsoft YaHei',sans-serif; font-size: 16px; line-height: 1.75; margin: 0 0 24px 0; margin-left: 8px; margin-right: 8px;"&gt;地瓜选择本场 Demoday 选手的调性，与其他不太一样。CEO 王丛开场就说：他不太在乎地瓜自己出货量多大、市场占有率多高，他更想看到的画面是，被他们孵化出来的那些五花八门的东西，能被随便拿一个回家，给爸妈玩，给孩子玩，路边看到都是。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light,'PingFang SC','PingFang TC','Hiragino Sans GB','Microsoft YaHei',sans-serif; font-size: 16px; line-height: 1.75; margin: 0 0 24px 0; margin-left: 8px; margin-right: 8px;"&gt;地瓜过去一年一直在用真金白银和工程资源接住这批人&amp;mdash;&amp;mdash;如果你也对押注早期、押注还没长成形的怪点子感兴趣，这十个项目值得一个个看看。&lt;/p&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;p style="margin-left: 8p</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17T07:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Whisker’s AI-powered litter robot thinks my cats swapped bodies</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/978323/whisker-litter-robot-5-pro-review</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>The greatest invention in pet tech in recent years is the litter robot. A machine that scoops your kitties' poop so you don't have to - what else could a cat owner possibly want? How about insights into your kitty's litter box usage that could flag health issues? Sign me up. But I have two [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8368,6 +8368,217 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 11:07:02 +0000</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>年轻人首选B级闪充轿车秦MAX正式上市，售价10.99-14.39万元</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/474907.html</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>8月13日，比亚迪秦MAX正式上市，推出EV与DM-i双动力版本</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 05:58:57 +0000</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>650亿美元！IPO前夕，Anthropic营收底牌曝光</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/474673.html</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>回头看，A社就这样完成了反超</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 08:10:47 +0800</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>苹果「摄像头耳机」曝光；小米机器人将亮相机器人大会；特斯拉与 SpaceX 合并预期升温 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368995</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/d6/91/d691a58bf8b6b885da63ca2c1214990f.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;OpenAI第二季度营收 67 亿美元，增速远不及 Anthropic&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;据《华尔街日报》报道，OpenAI 向投资者透露，其第二季度营收较第一季度增长了 18%，但亏损进一步扩大。这一业绩令部分股东感到失望，他们此前曾期望这家公司在追赶竞争对手 Anthropic 方面能展现出更大进展。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;OpenAI 表示，截至 6 月的三个月内，公司营收增至 67 亿美元，高于第一季度的 57 亿美元。与此同时，据知情人士透露，其营业亏损率进一步扩大，使得该公司在备受期待的首次公开招股 (IPO) 之前，距离实现盈利更加遥远。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;同期，Anthropic 的营收增长了一倍多，达到 116 亿美元，这是该公司营收首次超过成立时间更早的竞争对手 OpenAI。而且，Anthropic 还实现了小幅营业盈利。（来源：凤凰网科技）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/04/c9/04c93d08bfac7c727b77f8d2087f73ee.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;百度李彦宏：目标让文心回到第一梯队&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;8 月 18 日，百度发布 2026 年第二季度业绩，实现营收 313 亿元，同比下降 4%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;其中，百度核心 AI 新业务收入达到 125 亿元，同比增长 25%，占百度一般性业务收入的 50%，连续第二个季度占比过半。与此同时，在线营销服务收入 131 亿元，同比下降 19%，传统业务收入 104 亿元，同比下降 23%。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;晚间业绩电话会上，百度创始人李彦宏重点谈及了 AI 业务、昆仑芯的进展。对于日益激烈的模型竞争，李彦宏在电话会上回应称，从行业视角来看，基础模型仍在快速演进，大约每隔几个月就会有新的模型脱颖而出，这表明该领域依然高度活跃，竞争格局也远未定局。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;李彦宏表示，展望未来，百度将继续投入必要资源，推动文心持续发展。作为这项工作的一部分，公司进一步优化了组织架构，并于近期引进顶尖的人工智能人才。「我们有信心加快人工智能迭代，让文心重新回到基础大模型的第一梯队。」（来源：蓝鲸财经）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;卢伟冰：新一代玄戒芯片即将发布，小米机器人将亮相世界机器人大会&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="1920" src="https://imgslim.geekpark.net/uploads/image/file/5d/c1/5dc1771827b51c900fe6339d9ec7a7b2.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;8 月 18 日，小米集团合伙人、集团总裁卢伟冰在财报电话会上透露，去年小米推出的玄戒 O1 芯片，在三款终端上的累计出货量已超过百万，实现了旗舰芯片规模化验证，全新一代小米玄戒芯片也即将发布。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;卢伟冰表示，9 月份小米会进入密集的新品发布期，会有一系列重磅旗舰产品陆续上市。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据爆料，小米新一代自研 SoC 将命名为玄戒 O</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 13:56:14 +0800</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>TikTok带货博主卷疯快递：三天，从深圳到伦敦</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368962</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+&lt;div class="ace-line ace-line old-record-id-EXbbdfz0RofkhQxbpmbcWPWAnoc"&gt;&amp;nbsp;&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-R0AEdjzLyoO3u6xNFxEcHXDHncc"&gt;今年6月26日，英国气温飙到了36摄氏度，创下十多年来的纪录。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-L66PdZ6Vao3OKqxwTOacfc3cn1e"&gt;26万台小电风扇，从中国出发，在不到两周的时间里涌进了欧洲人的家门。不少英国人从下单到收货，只用了两天半。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-MPC4dvVfJoUoF6xiD4acXX8dnRe"&gt;放在五年前，跨境卖家根本不敢想象这么快。而现在，这不得不成为&amp;ldquo;基础&amp;rdquo;。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-Yxh7dM1ZAoyoqsxmAg7c2NbRnK7"&gt;8月5日，菜鸟集团正式发布"全球三日达"，在中国至欧洲、泛欧国家间、中东国家间等15条核心线路上，实现3个自然日门到门送达。0.5公斤欧洲小包，单票物流费只有标准国际快递的一半。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-NjifdBmbSoYsDMxObJpcaRzKnwc"&gt;这是继2020年&amp;ldquo;全球十日达&amp;rdquo;和2023年&amp;ldquo;全球五日达&amp;rdquo;之后，跨境物流速度的又一次飞跃。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-VSkld3QtJoemlJxqXWpch6FunKe"&gt;快递速度飞跃的背后，是跨境电商正在经历的一场深层变革。变革的源头，是以TikTok为代表的内容电商的崛起。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-KAzld5HD2oZ5u8xnjoOcJ6tbntb"&gt;TikTok等内容平台上，一条爆款视频，可能只需要几个小时，就能卖掉几万件商品。一场直播带来的订单，可能在几个小时内突破过去一个月的销量；一个网红推荐的小风扇，可能在欧洲高温天气里瞬间成为爆款。流量来得越来越快，消费者的耐心却越来越短。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-PS4fdx7N7oUuPqxZS1VcyThGnob"&gt;如今，对于跨境卖家来说，真正的挑战不仅是&amp;ldquo;卖出去&amp;rdquo;，更是&amp;mdash;&amp;mdash;消费者下单之后，能不能在他们失去兴趣之前收到货。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-M1U3db69wo7EzYxqHAocmYf0nTe"&gt;&amp;nbsp;&lt;/div&gt;
+&lt;h2 class="heading-2 ace-line old-record-id-TL3mdJGl9ornEixXzcXcwUSvnqF"&gt;&lt;strong&gt;内容电商的流量是&amp;ldquo;脉冲式&amp;rdquo;的&lt;/strong&gt;&lt;/h2&gt;
+&lt;div class="ace-line ace-line old-record-id-RQhhdOCkqoSm6IxCLaZclzg6n7c"&gt;过去几年，跨境电商的生态被一个变量彻底改写：内容电商。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-K0H7dNdOIo4W6CxyjCIcQUWXnwd"&gt;数据显示，2026年上半年，TikTok Shop全球商品交易总额突破503亿美元，同比增长92%；美国市场直播电商增长尤为迅猛，年中大促期间较去年同期增长超过225%。&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-I0dxdiDKBotQ4hx8zrecM8bjn3d"&gt;内容电商和传统电商的增长模式完全不同。&lt;strong&gt;传统货架电商的流量是相对平稳的，而内容电商的流量特征是&amp;ldquo;脉冲式&amp;rdquo;的&amp;mdash;&amp;mdash;一条突如其来的爆款短视频、一场知名达人的爆单直播，往往能在短短数小时内拉爆成千上万笔订单。&lt;/strong&gt;&lt;/div&gt;
+&lt;div class="ace-line ace-line o</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 18 Aug 2026 09:15:00 +0800</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>从「拍得到」到「拍得成」：大疆如何重塑全景影像天花板</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/368932</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/5a/d3/5ad3d77d7e413c9c9b0d887774a2b40e.jpeg" style="display: block; width: 661px !important; vertical-align: bottom; margin-top: 0px; margin-bottom: 0px; background-color: transparent; height: auto !important;" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;在天上，为全景影像打下地基。&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin-top: 0px; margin-bottom: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜张勇毅&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin-top: 0px; margin-bottom: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜郑玄&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin-top: 0px; margin-bottom: 24px;"&gt;即使你不怎么关注摩托车，今年你大概也刷到过张雪机车的故事：一支成立不到两年的中国车队，第一次征战世界超级摩托车锦标赛，今年 3 月底就在葡萄牙波尔蒂芒以近 4 秒的优势拿下队史首冠，周末连下两回合；到 6 月中旬，赛季第六冠已经到手。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin-top: 0px; margin-bottom: 24px;"&gt;比成绩更有戏剧性的是这支车队的来路。创始人张雪 14 岁在湖南山村骑上摩托，辍学进修理铺当学徒，20 岁左右就能闭着眼组装发动机；如今征战世界赛场的那台 820RR-RS，用的是自研的 819cc 直列三缸发动机，车架和电控全部国产。一个修车学徒，把「自己造」这件事做到了世界冠军的领奖台上。&lt;/p&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img js_img_placeholder wx_img_placeholder" src="https://imgslim.geekpark.net/uploads/image/file/b0/52/b052c4e55fc3b71612698efe8c59f034.png" /&gt;&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin-top: 0px; margin-bottom:</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8579,6 +8579,301 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 10:54:07 +0000</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>章鱼动力亮相WRC 2026，携“脑-手-数据”技术体系探索具身智能未来范式</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/475931.html</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 10:12:09 +0000</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>全球首个人形机器人自主乒乓球完整对局亮相2026世界机器人大会</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/475907.html</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>超维动力KAI全栈具身智能硬核登场</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 07:42:27 +0000</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>具身数据底座开卖，首发5100元：机器人训练数据有了新解法</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/475477.html</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>构建全栈物理AI基础设施</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 20:29:50 +0800</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>独家：宇树上市庆功宴上，王兴兴首次明确「大脑」的技术路线</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369051</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/6d/52/6d52f53437eed569a267d8ca6f17a96d.jpeg" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;宇树的下一张牌，是搭起一套系统，让全球 AI 的持续进步，转化为机器人不断加快的进化速度。&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474; font-family: Optima-Regular, PingFangTC-light;"&gt;&lt;br /&gt;作者&amp;nbsp;|&amp;nbsp;Li Yuan&lt;/strong&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474;"&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;8 月 19 日，宇树科技正式登陆科创板。上市首日，公司股价一度较发行价涨超 6 倍，总市值突破 4400 亿元。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;当市场盯着这家「机器人身体最强公司」的股价时，一个更重要的问题随之出现：获得更多资金和资源之后，宇树接下来要做什么？&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;当天中午，王兴兴参加了宇树的上市答谢午宴。这几乎是公司上市后的标准动作：感谢一路支持的政府、股东和合作伙伴，再回望一遍创业十年的艰辛。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;但在略显磕巴地完成这些常规致谢后，王兴兴没有就此结束，而是突然把话题转向技术，开始讲述宇树上市后真正准备投入的一套系统。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;他的状态也随之变化。表达明显流畅起来，语速越来越快，从大模型讲到自动编程，从仿真训练讲到真机测试，再讲到机器人技能的自我进化。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;显然，这部分内容他已经想了很久。&lt;/p&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;p style="clear: both; margin-left: 8px; margin-right: 8px;"&gt;&lt;em&gt;&lt;strong&gt;01&lt;br /&gt;&lt;/strong&gt;&lt;/em&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;/s</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 20:19:12 +0800</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>宇树往事</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369047</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr"/>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;今天，宇树科技鸣锣上市了，跑出了超过 4000 亿的市值。&lt;/p&gt;
+&lt;p&gt;对于风口正盛的具身智能行业来说，宇树扮演了赛道破风者的角色，为整个行业设定了一个宝贵的价值锚点。&lt;/p&gt;
+&lt;p&gt;大家近几年看到的，或许是宇树极其迅猛的发展加速度。但回望它的成长之路，其实并不是个爽文的剧本，从 2017 年极客公园旗下变量资本决定投资宇树天使轮至今，我们也已经陪伴宇树走过了九个年头。在我眼里，这是个脆弱与坚强交织、纠结与决断并存的过程。&lt;/p&gt;
+&lt;p&gt;上市的精彩只是一瞬间，但我想把陪伴宇树这段长跑里的往事好好「蒸馏」一下，也许能从中提炼出一些对当下及未来创业者依然有价值和有意义的东西。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;适度悲观地「走夜路」&lt;/h2&gt;
+&lt;p&gt;从融资的角度看，宇树出生在一个「错误的季节」。&lt;/p&gt;
+&lt;p&gt;今天，具身智能和人形机器人如日中天，但在我认识王兴兴的 2017 年，「具身智能」这个词甚至都还没开始流通，资本市场的叙事也完全是另一个世界。&lt;/p&gt;
+&lt;p&gt;现在回头看，那是一个中国互联网用户增长已经见顶，移动互联网浪潮开始进入尾声的阶段。但巨大的时代惯性拖着大家，还感知不到那个时代的减速。由「连接」逻辑和软件驱动的商业创新，比如共享经济、拼团经济，以及后来的 SaaS 热潮，这些依旧是大部分创业者和投资人关注的主旋律。&lt;/p&gt;
+&lt;p&gt;硬科技创新在那个年代虽有萌芽，但上一波 AI 1.0 时代，还没有出现移动互联网时代那样「跑得快、长得猛、退得出」的公司，只有「融得多」的公司，所以硬科技还没能真正成为时代的焦点。&lt;/p&gt;
+&lt;p&gt;故事的起点是 2017 年秋天，我在一个冷门公众号上看到一篇很短的文章，几张图片，一个视频。视频里有一只机器狗，叫 Laikago&amp;mdash;&amp;mdash;「莱卡」是第一只替人类探索太空的小狗的名字，对我这样一个航天爱好者来说，立即感受到了一种理工男的独特浪漫。当然，更重要的是那个机器狗的运动姿态流畅，让我有点吃惊。&lt;/p&gt;
+&lt;p&gt;因为在 2015 年，我带着一批国内创业者去 MIT，在仿生机器人实验室里见了 Sangbae Kim 教授做的机器猎豹（MIT Cheetah）&amp;mdash;&amp;mdash;一个仿猎豹的庞大四足机器躯体，浑身挂着钢缆和飞线，极其实验室风格。当时我们都把这看作是一个也许再过 10 年、20 年才会很厉害的东西。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://geek.feishu.cn/space/api/box/stream/download/asynccode/?code=M2NmNDE1NTIyZGJjNjFjNmMyODEwMTAyMDFlYjMzMjdfM21tV0gxbjRmUVVuR25SMWx6OGI5NkwzemxzZzh3d3FfVG9rZW46VkNoOGJxVHAwb2REdGV4MEhHWmNtU1JBbnB6XzE3ODcxNDE0MDM6MTc4NzE0NTAwM19WNA&amp;amp;add_watermark=true&amp;amp;scene_type=CCM" /&gt;&lt;/p&gt;
+&lt;p&gt;结果仅仅两年后，一个中国团队在杭州的一个「车库」里，就做出了一台比 MIT 机器猎豹更小巧、更成熟、更接近产品化的机器狗。这让我充满好奇，觉得必须要去认识下这个产品背后的年轻人。&lt;/p&gt;
+&lt;p&gt;我很快通过圈子里的朋友找到了王兴兴，立即飞到杭州见他。2017 年 10 月 21 日，第一次见到王兴兴，他穿着深色牛仔裤和白色阿迪达斯球鞋，就像个刚毕业的大学生。他的「办公室」在杭州滨江一个不太起眼的楼里&amp;mdash;&amp;mdash;不是标准的写字楼，旁边还夹杂着厂房，进去连个公司门牌都找不到。一个二三十平的空间，里头就像个车库，堆满了零件和两条刚装好的机器狗。&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://geek.feishu.cn/space/api/box/stream/download/asynccode/?code=YzAwYWI1NzI4YzY2MmQ5YjcwMTM4ODFlOGNiNWY0OWJfVlZvWWZPME0weVJVNFNxSGVzeTJsVnNuZjlXNnhRb25fVG9rZW46T1hLbGJCTUs5b0gzUWp4U3FwaGNCQWEwbnZmXzE3ODcxNDE0MDM6MTc4NzE0NTAwM19WNA&amp;amp;add_watermark=true&amp;amp;scene_type=CCM" /&gt;&lt;/p&gt;
+&lt;div&gt;&lt;span style="font-size: 14px; color: #7e8c8d;"&gt;2017 年 10 月 21 日，第一次现场见到宇树科技的机器狗&lt;/span&gt;&lt;/div&gt;
+&lt;p&gt;演示</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 19 Aug 2026 12:02:55 +0800</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>马斯克带火的太空算力领域，传一个 800MB 模型上天要四周</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369013</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;「所有劝我不要干太空算力的朋友，现在全在干太空算力。」&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;太空字节联合创始人秦贵军这样描述过去一年。这家公司 2024 年底成立，做的是太空数据中心；他本人参与过北斗导航重大专项，在卫星行业干了十几年。那些劝过他的朋友也大多是同一个画像：传统航天出身，两年前还觉得把算力送上天是个不着调的故事，如今已经用脚投票。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;他画过一张国内太空算力的行业热力图，从长三角到北京亦庄、中关村，再到成都、西安、合肥，玩家已经超过三十家，正在往四十家走。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;热度的源头在大洋彼岸。2026 年 6 月 12 日，SpaceX 以每股 135 美元、约 1.75 万亿美元的估值登陆纳斯达克，成为美股史上规模最大的 IPO。招股书里写着 2028 年启动部署轨道 AI 算力星座，以及一个天文数字般的 AI 板块市场预测。5 月，星舰 V3 完成首飞，一次任务部署 22 颗模拟星，SpaceX 给它的目标是以完全可重复使用的构型向地球轨道运送百吨级载荷。上市后股价一度冲到 225 美元上方，到 8 月中旬回落至发行价附近。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="924" src="https://imgslim.geekpark.net/uploads/image/file/47/2d/472d6241df26ffe441f39ae31562c049.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;SpaceX 上市后的股价变化 | 图源：Google Finance&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;这个回落未必是对方向的否定，更像是全球最严格的定价机制在做一件事&amp;mdash;&amp;mdash;把「叙事」和「进度」重新分开来算。同样的问题也摆在国内三十多家公司面前：方向已经不缺共识，缺的是回答工程上的下一步究竟做什么。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;要理解这些公司各自在做什么，先要分清行业里两个高频出现、含义却完全不同的词：「天数天算」和「地数天算」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;天数天算是老故事。现阶段，数据主要靠遥感卫星在太空产生，然后再把结果传回地面。比如一颗遥感星拍下整座城市，星上模型识别出真正需要的那一小块目标区域，切出来精准下传，原本要传二十分钟的数据，一次过境半分钟传完。这本质上是边缘计算，也是商业航天过去十年一直在做的事。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但它始终没有真正点燃资本&amp;mdash;&amp;mdash;它算的还是遥感数据，服务的还是老客户。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;真正把这一轮热度点着的是地数天算：数据在地面产生，送上天去算。太空字节创始人王玮认为，这个词需要补上两个定语，商业闭环才成立&amp;mdash;&amp;mdash;以 AI 训练为应用，且天上的能源成本确实低于地面。少一个，故事就不完整。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这也是眼下海外几个大项目的共同底色：&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;英伟达支持的 Starcloud 于 2025 年 11 月把一颗搭载 H100 的卫星送入 350 公里轨道，在轨跑通了大语言模型，终极蓝图是 5GW、跨度约 4 公里的轨道数据中心&lt;/li&gt;
+&lt;li&gt;谷歌的 Project Suncatcher 设计了一个由 81 颗卫星在百米间距上紧密编队的计算集群&lt;/li&gt;
+&lt;li&gt;国内瞄准晨昏轨道 700 至 800 公里的轨道晨光，已完成顺灏股份、联想创投等参与的 1.4 亿元首轮融资，其公开表述是天数天算和地数天算两者都要做&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p style="text-align: left;"&gt;问题就在这里。地数天算这四个字，第一个字是「地」。它预设了一个动作：数据要先从地面上去。而恰恰是这个动作，全球至今没有可运营的工程能力。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;一个具体的量级可以说明现状：把一个 800MB 左右的小模型送上一颗已经在轨的计算卫星，实际耗时接近四周。&lt;/span</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19T13:10:09-04:00</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI hit the brakes. Now what?</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/982323/openai-hit-brakes-voluntary-pacing-ai</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>With a looming IPO, intense competition from Anthropic, and Chinese and open-weight rivals nipping at its heels, OpenAI has plenty of reasons to move fast. Instead, it hit the brakes. On Tuesday, the company said it had slowed the pace of some AI development while it tightened security and safeguards. That included a two-week pause [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8874,6 +8874,384 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 02:22:34 +0000</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>应用案例 | 不用拆分组装！华曙高科3D打印升级灵巧手运动性能</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12541</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>当前，人形机器人产业正加速迈向商业化落地，灵巧手作为实现柔性抓取、精细操作的核心末端执行单元，其仿生构型、轻量 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 01:43:03 +0000</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>方案连载・人形机器人篇（一）｜七大子系统全覆盖，ST打造一站式人形机器人硬件基座</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12532</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>下载《人形机器人参考指南》完整白皮书，解锁人形机器人全套解决方案，加速产品方案落地！</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 01:36:55 +0000</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>机器人触觉数据需求爆发，数采手套备受关注！</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12530</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>触觉数据的稀缺直接限制了具身大模型的泛化与精细操作能力</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 01:36:34 +0000</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>从“感受”到“理解”：触觉芯片如何让电子皮肤拥有“神经系统”？</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12506</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>触觉芯片在电子皮肤中扮演的是x26quot;感知中枢 + 神经接口x26quot;的角色——没有它，电子皮肤只是一张布满柔性传感器的x26quot;薄膜x26quot;；有了它，这张膜才真正成为机器能理解的x26quot;触觉x26quot;。</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 01:35:31 +0000</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>34家机器人一体化关节模组厂商名单</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12401</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>一体化关节融合电机、减速器、传感器、驱动器等核心组件，是人形机器人动力域的核心执行单元，堪称人形机器人动力系统的 “心脏”。</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 01:23:20 +0000</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>龙旗科技与南昌高新区签约，具身智能机器人研发制造基地正式落地</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12346</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>8月18日，龙旗科技具身智能机器人研发制造基地项目签约仪式成功举行。江西省委常委、南昌市委书记、赣 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 08:05:46 +0800</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>曝周杰伦将代言 vivo 手机；华为「阔直板」手机曝光；柯洁透露战胜 AI 秘诀：装弱智｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369114</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/5f/bf/5fbfdab3e8d7434eea3d9f992ed8124d.png" /&gt;&lt;/p&gt;&lt;h1&gt;《黑神话：钟馗》全新 15 分钟游戏实机演示公布，首次展示主角战斗与部分剧情片段&lt;/h1&gt;&lt;p&gt;8 月 20 日消息，由游戏科学开发的黑神话系列第二部作品《黑神话：钟馗》，今日带来全新 15 分钟游戏实机演示，首次展示主角战斗与部分剧情片段。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a8/43/a843e346cee2da48d2b66adc2344373c.png" /&gt;&lt;/p&gt;&lt;p&gt;官方称，本视频为开发中版本录制，运行时屏幕宽高比设置为 21:9。因产品仍处于研发早期，最终发售内容可能有所不同。&lt;/p&gt;&lt;p&gt;据了解，《黑神话：钟馗》是游戏科学开发的《黑神话》系列第二部作品，目前处于早期研发阶段，发售日期尚未确定。作为《黑神话》系列的第二部作品，游戏以中国民间传说中的角色「钟馗」为创意来源，其骑虎形象灵感源于明代《钟馗骑虎图》及美术总监杨奇的梦境。游戏科学团队在《黑神话：悟空》发售后调整开发计划，决定放弃 DLC 转而开发新作《黑神话：钟馗》，旨在尝试更具差异性的游戏体验并修正前作不足。（来源：IT 之家）&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/87/4b/874bbc6a2933b3bb0b941fe57839f71f.png" /&gt;&lt;/p&gt;&lt;h1&gt;宝马副总裁吴燕彦：行业应共同抵制压缩验证周期、测试中偷工减料的浮躁行为&lt;/h1&gt;&lt;p&gt;8 月 20 日消息，据「睿见 Economy」报道，车百国际主办的新能源汽车全球合作发展论坛（GNEV2026）19-21 日在上海召开，宝马集团副总裁、大中华区政府和涉外事务吴燕彦在演讲中向行业发出呼吁：牢牢树立安全底线，&lt;strong&gt;共同抵制压缩验证周期、在测试中偷工减料的浮躁行为，反对将不完善的系统、不成熟的产品推向市场&lt;/strong&gt;，质量和安全绝不能有半点妥协。&lt;/p&gt;&lt;p&gt;吴燕彦表示，作为业务遍布全球 140 多个市场的车企，宝马认为靠封闭与割裂没有赢家，自由贸易和开放合作才是产业创新和经济繁荣的根基。宝马坚定践行「在中国，为中国，与中国共进」的战略，本土化研发已经成为宝马布局中国市场的&lt;strong&gt;关键一环&lt;/strong&gt;。&lt;/p&gt;&lt;p&gt;她指出，当前跨国车企在华发展正面临三重关键挑战：如何快速适应中国市场&lt;strong&gt;电动化、数字化、智能化、低碳化&lt;/strong&gt;转型的节奏并满足中国消费者的偏好；如何充分利用中国创新的成果，加速与全球技术体系高效融合，&lt;strong&gt;反哺全球市场&lt;/strong&gt;；全球化供应链体系如何在复杂的地缘政治环境中找到平衡。（来源：IT 之家）&lt;/p&gt;&lt;h1&gt;英伟达黄仁勋之女黄敏珊来华，现身 2026 世界机器人大会&lt;/h1&gt;&lt;p&gt;8 月 20 日消息，根据多位网友和媒体晒出的图片，英伟达 CEO 黄仁勋之女黄敏珊来到北京，于 8 月 19 日现身 2026 世界机器人大会现场。&lt;/p&gt;&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/31/0a/310af378f254f3aac154adac314c77d0.png" /&gt;&lt;/p&gt;&lt;p&gt;综合此前报道，黄敏珊目前的职位是英伟达 Omniverse 与机器人产品营销高级董事，她 8 月 18 日前往韩国到访了 LG 电子，在韩国首尔瑞草区建设的 LG 数据工厂（原良才研发园区）讨论创造协同效应的方案，第二天就来到了中国。&lt;/p&gt;&lt;p&gt;据新浪科技报道，黄敏珊到访 WRC 越疆机器人展位，并重点参观「一脑多体」具身智能平台解决方案与乒乓球高速人机对抗两大演示，现场呈现英伟达与越疆在物理 AI 领域的深度合作成果。（来源：新浪科技）&lt;/p&gt;&lt;h1&gt;宇树科技王兴兴：目前人形机器人的效能相对较低，技术精进后会大规模推广&lt;/h1&gt;&lt;p&gt;8 月 20 日上午消息，2026 世界机器人大会（WRC 2026）期间，宇树科技创始人、董事长发布主题演讲。王兴兴现场解答为什么其产品没有进行在工厂，家庭等场景大规模推广，「其</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 11:26:08 +0800</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>「广告位」时代已死，智能体商业开收「中介费」</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369078</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div class="ant-form-item-control-input"&gt;
+&lt;div class="ant-form-item-control-input-content"&gt;
+&lt;div class="website-upload-body-preview"&gt;
+&lt;p&gt;「意图」这两个字，在整场支付宝 AI 生态合作伙伴大会上被提及了超 40 次。&lt;/p&gt;
+&lt;p&gt;如果说 5 月的 AI 支付生态大会上，Token Pay、AI 钱包，加上此前推出的 AI 付与 AI 收，代表支付宝明确了「支付可以用 AI」；那么这一次，我们看到的是，支付宝内部对智能体商业化该怎么做已经形成明确预期，并且对各个阶段的节奏和内容，做出了新的判断与调整。&lt;/p&gt;
+&lt;p&gt;这一次，支付宝几乎没有发布太多新产品，而是在告诉坐在台下的商家、交易平台、手机和车机厂商们，智能体商业化将会是什么样的。蚂蚁集团 CEO 韩歆毅认为，AI 能力的提升、流量红利见顶后的需求跃迁，以及可持续价值闭环的出现，会推动智能体商业在未来 6 到 12 个月内爆发。&lt;/p&gt;
+&lt;p&gt;&lt;img alt="支付宝智能体阿宝的对话交互界面，演示通过自然语言进行点单、订机票与寄快递等服务" src="https://toolkit-post.geekpark.net/api/v1/website-upload/feishu-image?token=YYDGbxYGlobs70xZvV1cUfJQnte" title="支付宝阿宝对话服务演示" /&gt;&lt;/p&gt;
+&lt;p&gt;在现场，我们发现支付宝里的出行、支付、生活板块，全部藏到了其智能体阿宝身后，几句话就能通过支付宝的智能体阿宝进行点单、订机票、寄快递。当商家服务变成被调用的接口，平台本身收缩成一个对话框，商业的竞争点也随之改变。过去商家拼的是「被看见」，抢入口、买流量、堆 SEO；现在拼的是「被理解」，看你的服务有没有真正的差异化长板，能不能在 AI 选择供给时被挑选出来。&lt;/p&gt;
+&lt;p&gt;在我们看来，&lt;strong&gt;这场大会真正宣布的，是一次「分发权」的重新分配，决定商家能不能做成生意的，不再是它在流量池里买到的位置，而是它能不能被一套意图理解体系选中。&lt;/strong&gt;对话框背后，支付宝正在搭建的新体系，从意图的补齐与理解，到一方与三方服务商的服务体系，再到连接用户、平台与商家的智能体网络。&lt;/p&gt;
+&lt;p&gt;我们在现场和支付宝出行、物流、开发者生态等多个板块的工作人员聊了聊，看到意图为核心的智能体商业正在改变人们的衣食住行。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;一、智能体商业竞争关键，在意图理解&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;韩歆毅把人与服务的连接方式分成三个阶段，搜索时代，人学着用机器的语言表达需求；App 时代，服务被封装进应用；而智能体时代，是机器开始学着用人的语言理解需求。「&lt;strong&gt;智能体时代，商家的竞争从抢占流量入口，转向争夺用户意图理解能力。」他说道。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;过去的搜索分发是品牌词逻辑，用户要么搜品牌名，要么搜特定商品，商家的功课是写 SEO，把标题拉得巨长，堆满关键词，等着被匹配。而智能体时代，平台需要面对的是彻底的自然语义理解。&lt;/p&gt;
+&lt;p&gt;比如说，当用户说的是「昨天我喝的东西，再给我点一杯」模糊语义时，能够及时下单；当用户说点一杯柠檬水的时候，要清楚他想要的大概率是蜜雪冰城的柠檬水；在「我要打车去 T3」的意思下，平台要明白 T3 是指航站楼，结合过往出行习惯，大概率是指北京首都机场航站楼。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;AI 生态多端互联业务负责人王翼飞把意图理解拆成两层：「一部分叫补齐，第二部分是你怎么理解用户说的这件事情。」&lt;/strong&gt;模型得懂人在生活中是怎么使用服务的，才能做好执行。&lt;/p&gt;
+&lt;p&gt;除了能够知道用户表达的是什么，智能体还得能看懂用户的言外之意。比如说，当用户表达自己即将去看演唱会的时候，她真正的意图不只是「买一张票」，而是看演唱会、拍到清晰好看的照片、发上小红书、最好收获 1000 个赞。&lt;/p&gt;
+&lt;p&gt;买票只是其中一环。当模型理解了这背后的心理，一些流量时代单点的服务开始重组，她未必会为拍照买一台影像旗舰，但愿意花几十块钱租三天；携程可以顺势把酒店、机票和演唱会门票组成套餐。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;「意图理解不应该是一个独立的产品模块，在最初分析需求的阶段被调用后，脱离整个服务环节，而是在服务的过程中，不断的与不同的技术服务环节相结合，服务整个流程。&lt;/strong&gt;比如说，用户说「帮我叫一个玛丫的外卖」，玛丫是他的个人热词，但要是产品连玛丫两个词都不能打对，ASR 环节这两个字识别错了，后面所有执行都是错的。」他说道。&lt;/p&gt;
+&lt;p&gt;意图理解真正的复</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 20 Aug 2026 08:39:28 +0800</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>中国首次实现火箭陆地回收；宇树上市，市值最高超 4000 亿；蔡明同款机器人亮相，9.9 万元｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369056</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/68/dd/68dd02a1119f5b27c9d6f6322d8dd9e4.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;朱雀三号遥二发射成功，我国首次实现火箭陆地回收&lt;/h2&gt;
+&lt;p&gt;据央视新闻报道，8 月 19 日，朱雀三号遥二运载火箭在东风商业航天创新试验区发射升空，火箭一子级按预定程序成功着陆于甘肃省民勤县朱雀三号着陆场坪，飞行任务取得圆满成功。这是我国在重复使用火箭关键技术上取得的又一重大突破，朱雀三号成为我国首款成功入轨并实现陆地回收的运载火箭。&lt;/p&gt;
+&lt;p&gt;我们注意到，本次任务是继 7 月 10 日长征十号乙运载火箭一子级海上网系成功回收后，我国首次成功实施重复使用运载火箭一子级着陆腿方式陆地可控回收，标志着我国重复使用火箭技术取得重大突破。&lt;/p&gt;
+&lt;p&gt;朱雀三号运载火箭是由国家航天局批复立项的新一代低成本、大运力、高频次、重复使用液氧甲烷运载火箭型号。此型火箭采用单芯级两级串联构型，全箭长 66.1 米，一二子级箭体直径 4.5 米，整流罩直径 5.2 米。箭体主结构采用不锈钢材料，以「燃箱在上、氧箱在下」的总体布局优化飞行质心。火箭一子级配备九台天鹊-12A 液氧甲烷发动机，动力系统可在 40% 至 110% 的推力范围间调节，可在完成轨道发射后实施垂直回收与再利用。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/62/4c/624c0b8e25bcbec3c1d000759d8a6623.png" /&gt;&lt;/p&gt;
+&lt;p&gt;「朱雀三号」遥二运载火箭一子级回收落地瞬间。央视新闻截屏&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/82/b9/82b99f677b3bc2746cb8182442f5f141.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;宇树上市开盘暴涨 6 倍，王兴兴的 10 年长跑进入下半场&lt;/h2&gt;
+&lt;p&gt;8 月 19 日，宇树科技正式登陆上海证券交易所科创板，股票代码 688836，成为 A 股「人形机器人第一股」。&lt;/p&gt;
+&lt;p&gt;宇树的发行价定在 150.80 元/股，对应发行市值约 609.93 亿元。上市首日，公司股价一度上涨 629%到 1100 元/股，总市值一举突破到 4400 亿元。&lt;/p&gt;
+&lt;p&gt;当天中午，王兴兴参加了宇树的上市答谢午宴，完成常规致谢后，王兴兴没有就此结束，而是突然把话题转向技术，开始讲述宇树上市后真正准备投入的一套系统。（独家：宇树上市庆功宴上，王兴兴首次明确「大脑」的技术路线）&lt;/p&gt;
+&lt;p&gt;他认为&lt;strong&gt;AI 不只会成为机器人的大脑，还会进入机器人的研发过程，帮助人类设计、训练和迭代机器人。搭建这样一套系统的循环将是具身智能企业最重要的竞争力。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;今天，要让机器人学会一项新技能，工程师仍然需要手工推动多个环节。王兴兴认为，这套开发方式仍然非常原始。AI 已经具备编程、信息检索、视频生成和结果分析能力，完全可能把这些环节逐步连接起来。&lt;/p&gt;
+&lt;p&gt;按照他描述的路径，AI 首先自动查询最新论文和开源代码，选择可能适用的方案，生成机器人的训练程序。代码随后进入仿真环境，也可以借助视频生成模型构造训练环境和素材。完成仿真后，训练结果被部署到实体机器人上。机器人能否保持平衡、动作是否准确、任务成功率有多高，都需要在真实世界中重新验证。&lt;/p&gt;
+&lt;p&gt;在王兴兴看来，这套系统可以持续借用全球基础模型的进步。即使宇树自身的编程能力没有同步提升，只要底层模型变强，自动搜索、编程、训练和评价的能力也会一起提高。（来源： 极客公园）&lt;/p&gt;
+&lt;h2&gt;OpenAI 首席财务官：公司或将在 2027 年上市，甚至更早&lt;/h2&gt;
+&lt;p&gt;据两位知情人士透露，OpenAI 首席财务官弗莱尔在周三的全员会议上向员工表示，公司将在 2027 年上市；倘若业务持续高速增长，也有可能更早登陆公开市场。&lt;/p&gt;
+&lt;p&gt;「IPO 不是终点，它只是一个里程碑，是又一轮融资。」弗莱尔对员工说道，「我们 3 月完成了融资，这给了我们充足的操作空间。」&lt;/p&gt;
+&lt;p&gt;OpenAI 在今年 6 月已向美国证券交易委员会（SEC）秘密提交 IP</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20T11:45:55-04:00</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>It’s Greg Brockman’s OpenAI now</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/982774/greg-brockman-openai-role-expansion</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI has had a hell of a year. The company spent months battling former cofounder Elon Musk in a sensational jury trial, was hit with a high-profile trade secrets lawsuit from Apple, and faced widespread scrutiny after an unreleased model hacked another AI company. As it prepares for an IPO, a steady string of executives [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H215"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9252,6 +9252,312 @@
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Do We Need Superhuman Humanoid Robots?</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-unitree-superhuman</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 19:31:11 GMT</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>材科源图三个月完成两轮融资，AI全链路闭环加速材料产业化</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/YB51rwb95keVmlIZ0xQd?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr"/>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/YB51rwb95keVmlIZ0xQd?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 09:44:33 +0000</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>明略科技携手海康机器人亮相世界机器人大会，以“Agent+具身”联合进入商业机器人场景</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/476733.html</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>明略科技（2718.HK）与海康机器人联合参展2026WRC，聚焦商业服务领域展示具身智能落地进展。</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 05:09:33 +0000</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>设计无边界！中坚科技旗下子公司桦之坚携巨型概念机器人ZERO惊艳2026世界机器人大会</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/476525.html</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>中坚科技（002779.SZ）旗下桦之坚携概念人形机器人ZERO亮相2026世界机器人大会。</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 22 Aug 2026 08:23:28 +0800</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>微信灰测「按住转文字」功能被吐槽；DeepSeek 上线多模态功能；应急机械拉手难操作，多家车企召回 427 万辆车</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369206</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/31/e3/31e3b4e897103ae4faee9b3d690310f1.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;DeepSeek V4-Flash-Vision-Exp 上线：开启多模态 API 服务，Agent 能力接近 Opus-4.8&lt;/h2&gt;
+&lt;p&gt;8 月 21 日消息，&lt;a href="https://mp.weixin.qq.com/s/RkyapmGgBJ-TdqDINOym8A"&gt;深度求索官方宣布全新的多模态视觉理解模型 DeepSeek-V4-Flash-Vision-Exp 上线 DeepSeek API 平台。&lt;/a&gt;&lt;/p&gt;
+&lt;p&gt;该模型支持在文本之外输入图片，可以让模型描述图片、识别截图中的文字、分析图表等。支持的图片格式包括 JPEG、PNG、GIF、WebP。&lt;/p&gt;
+&lt;p&gt;深度求索官方表示，V4-Flash-Vision-Exp 在各类 Agent 框架内展现出了较好的多模态适配能力，能够有效支持大家借助多样化的 Agent 工具解锁更多实用的工作场景。&lt;/p&gt;
+&lt;p&gt;据介绍，在纯文本能力（Agent、推理、世界知识等）方面，DeepSeek-V4-Flash-Vision-Exp 与 DeepSeek-V4-Flash 正式版持平；在需要视觉理解的 Agent Benchmark 上，DeepSeek-V4-Flash-Vision-Exp 相比 DeepSeek-V4-Flash 实现了大幅跃升，多模态 Agent 能力已接近 Opus-4.8。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/6d/c2/6dc265a5375e07300d52c932352c94c5.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;消息称 Anthropic 计划调整数据留存策略：客户可选择在自有设施保存&lt;/h2&gt;
+&lt;p&gt;8 月 21 日消息，彭博社援引消息人士的话报道称，Anthropic 计划调整此前为保障网络安全实施的数据留存策略：企业客户将可选择在自有云计算基础设施而不是 Anthropic 设施上保留 30 天内的数据。这一安全系统预计将在今年晚些时候正式上线。&lt;/p&gt;
+&lt;p&gt;先进人工智能模型在网络安全领域展现了强大的攻击能力。Anthropic 为此在今年 6 月宣布企业客户产生的所有前沿模型数据流量都将被保留 30 天，方便其追查利用该企业技术发动的网络攻击。&lt;/p&gt;
+&lt;p&gt;Anthropic 表示不会将保留的客户数据用于自身人工智能训练，但这一模式仍引起了客户群体的异议，且可能导致客户转投其它选择「零留存」策略的竞争对手。拟议的新举措淡化了用户的担忧。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;苹果裁撤 60 名 VR 团队员工，战略重心或转向 AI 眼镜&lt;/h2&gt;
+&lt;p&gt;据报道，苹果已对 Vision 业务团队进行人员调整，至少 60 名隶属于 Vision 小组、从事 VR 相关开发的员工遭到裁员，苹果官方尚未对该消息作出回应。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/95/94/95942b3a31096dcbdb3f8ae09c6904cf.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;报道指出，本次裁员背后是苹果战略转向，该公司资源正流向 AI 智能眼镜，这款新品预计于 2027 年 WWDC 大会亮相，同年晚些时候上市。（来源：新浪财经）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8b/39/8b3957fed616a27fcfeeeecea3b16fc0.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;特斯拉停售太阳能屋顶瓦片，该产品已不具备经济可行性&lt;/h2&gt;
+&lt;p&gt;据报道，特斯拉已停止推出旗下太阳能瓦片屋面产品&amp;mdash;&amp;mdash;太阳能屋顶。据两名熟悉该项目的消息人士透露，特斯拉已告知第三方安装商，今后将不再供应太阳能屋顶瓦片，仅提供太阳能电池板。其中一名消息人士表示，特斯拉内部认定该产品在财务层面难以为继。（来源：新浪财经）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;消息称</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 14:15:33 +0800</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>前 TikTok 产品经理创业，AI 视频共创平台 Wapoo 获千万美元天使融资</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369162</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr"/>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：Wapoo 官网&lt;/p&gt;
+&lt;p&gt;极客公园获悉，面向 Gen Alpha 的视频共创社交平台 Wapoo 已完成近千万美元天使轮融资。本轮融资由某互联网集团旗下战略投资方投资，其在全球化产品运营、年轻用户生态及新兴市场拓展方面已具备一定积累，探奇资本担任公司独家融资顾问。目前，Wapoo 团队约 10 人，并已开始筹备下一轮融资。&lt;/p&gt;
+&lt;p&gt;过去十年，短视频完成了对全球用户注意力的接管，也逐渐逼近既有产品形态的边界。一个新的问题正在浮出水面：跟着 Roblox 和 Minecraft 长大的 Gen Alpha，是否还会满足于被动刷视频？&lt;/p&gt;
+&lt;p&gt;他们习惯修改、共创，也习惯在数字世界留下自己的版本。但进入 TikTok、Instagram 等大众内容平台后，这些用户重新成为信息流里的观看者。现有平台承接了他们的注意力，却未必承接住了他们改变内容的欲望。&lt;/p&gt;
+&lt;p&gt;Wapoo 创始人杨名宇曾在快手负责用户研究，后在 TikTok 担任产品经理，从 0 到 1 负责 TikTok Stories、TikTok Now 等社交模块，并面对面访谈过大量来自不同国家和地区的短视频用户，对用户使用这类产品的需求和痛点有深刻了解。在他看来，下一代视频社交的答案，不在更高效的算法投喂里，而在让用户和朋友一起把内容「玩」起来。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;一条没有固定结局的视频&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;Wapoo 今年 5 月在美国上线。简单来说，它是一款可以让用户和朋友反复改写同一条视频的社交产品。&lt;/p&gt;
+&lt;p&gt;在传统短视频平台上，一条视频发布，通常意味着创作结束。观众可以观看、点赞、评论、转发，也可以通过合拍或拼接另做一条内容，但很难直接进入原视频，改变它后来的走向。&lt;/p&gt;
+&lt;p&gt;Wapoo 想把发布从「终点」变成「起点」。&lt;/p&gt;
+&lt;p&gt;用户看到一段视频后，可以继续修改其中的人物、视角或情节：把自己放进视频，把朋友套进流行梗里，将一段正经剧情拐向恶搞方向，或者沿着已有版本续写另一个结局。生成式 AI 被藏在操作背后，用户不必理解模型或复杂的剪辑流程，只需要表达一个简单意图。&lt;/p&gt;
+&lt;p&gt;新生成的视频不会与原内容彻底断开，而是作为一个新版本留在内容链路中。其他人既可以回到最初版本，也可以沿着任何一个分支继续修改。一条视频由此不再只有作者交付的唯一结局，而会随着参与者增加不断生长。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d0/73/d073bd3f378988fed4c345a71ff8d9e7.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Wapoo 使用页面｜图片来源：受访者&lt;/p&gt;
+&lt;p&gt;这与传统互动影视有所不同。互动影视通常由专业团队提前设计分支，用户拥有选择权，却很少拥有真正的改写权；短视频平台的合拍和 Stitch 降低了回应门槛，但新内容通常仍作为另一条独立作品存在。&lt;/p&gt;
+&lt;p&gt;Wapoo 更核心的设想是，后续的二创、三创也能成为内容演化的一部分。内容的价值不只来自最初的发布者，也来自后来每一次改变。如果说传统视频像凝固后的混凝土，Wapoo 希望它更像一盒数字乐高：每位参与者都可以拆解、重组，再把自己的版本交给下一个人。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;从「改视频」到「和朋友一起改」&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;产品上线之初，团队最想验证的是：用户是否愿意动手改变一条视频。&lt;/p&gt;
+&lt;p&gt;答案初步成立后，他们很快发现了另一个更重要的变量&amp;mdash;&amp;mdash;关系。当视频里出现朋友、同学，或者某个小群体共同经历过的事情时，用户的参与动力会明显增强。&lt;/p&gt;
+&lt;p&gt;有人把朋友放进当下流行的梗里，有人完成改写后点名邀请另一个人接力。一个人发起，第二个人接住，第三个人又把故事引向另一个方向。视频在反复回应中逐渐变成小圈子里的内部梗和共同记忆。&lt;/p&gt;
+&lt;p&gt;「我们原来想验证的是，用户愿不愿意改视频。后来发现更重要的问题是，改写会在哪些关系结构里自然发生。」杨名宇告诉极客公园。&lt;/p&gt;
+&lt;p&gt;这个发现让 Wapoo 从「可玩视频社区」进一步收敛为「视频共创社交平台」。过去两个月，团队的迭代重点也转向朋友邀请、内容回应、分支展示和群体参与。用户进入产品后，首先看到的不是一套复杂的 AI 工具，而应当是朋友发来的内容，以及一次可以顺手接住的邀请。&lt;/p&gt;
+&lt;p&gt;生成式 AI 解决的是「能不能改」，熟人关系回答的是「为什么要改」。这是 Wapoo 从采访中呈现出的第一</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 21 Aug 2026 14:12:45 +0800</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>小红书悄悄开源发布了自己的大模型，内容平台也要造底座</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369161</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr"/>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：chatgpt 生成&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;前几天，我们注意小红书在海外发布了一款大模型 dots3-note preview。&lt;/p&gt;
+&lt;p&gt;这款模型采用 MoE 架构，总参数 280B、激活参数 16B，支持 512K 上下文，并具备文本、视觉、语音的多模态理解能力。它属于 dots3 系列，后续还将有 jazz、aria 等不同定位的版本。作为先行发布的 note 版本，它更像是小红书将模型能力推向实际业务和开发者生态的第一步。&lt;/p&gt;
+&lt;p&gt;模型上线后，海外开发者社区很快开始讨论，Hugging Face 下载量破百，华为昇腾也在当天宣布完成适配；但在国内，这次发布暂时还没有掀起太大水花。&lt;/p&gt;
+&lt;p&gt;在这件事上，值得注意的并不只是又多了一款开源模型，而是&lt;strong&gt;小红书开始公开展示自己的基础模型能力&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;作为一家月活超过 3 亿的平台，小红书拥有海量图文和视频内容，也积累了用户从「想去哪里」「买什么」到「如何解决一个生活问题」的消费决策数据。它选择自研并开源模型，意味着&lt;strong&gt;AI 在小红书内部的角色，可能正在从搜索、推荐或创作工具中的一个功能，变成支撑整套产品能力的底座&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;如果把大模型看作数字世界的「工业母机」，这个动作就更容易理解。它本身不是最终产品，却决定了搜索、推荐、内容创作和智能服务等上层能力的精度与迭代速度。对一个体量足够大的平台而言，长期完全依赖外部模型，并不是一个稳妥的选择。&lt;/p&gt;
+&lt;h1&gt;小红书做模型，还开源了&lt;/h1&gt;
+&lt;p&gt;dots3-note preview 是一款 MoE 模型：总参数 280B，激活参数 16B，支持 512K 上下文，同时覆盖文本、视觉和语音理解。&lt;/p&gt;
+&lt;p&gt;它属于 dots3 系列。小红书披露，这个系列此前曾在 IMO 2026 获得官方认证的满分成绩。此次发布的 note，是系列中更强调效率和实际部署的版本；后续还将推出 jazz 和 aria，覆盖不同的能力与成本区间。&lt;/p&gt;
+&lt;p&gt;从公开评测看，dots3-note preview 在推理、Agent 和多模态任务中给出了有竞争力的成绩。比如在 ARC-AGI-3、个人助理类任务上，它的表现超过了一部分参数规模更大的模型；但在终端操作、复杂编程等任务上，与头部模型仍有差距。&lt;/p&gt;
+&lt;p&gt;也就是说，&lt;strong&gt;它更像是在发布一块已经能上手使用、但仍会继续演进的能力模块&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;而这恰恰更接近大模型竞争进入下一阶段后的现实：模型不只比谁在榜单上更高，更要看谁能进入真实产品，谁能被更低成本、更稳定地调用，谁能在具体场景里持续迭代。&lt;/p&gt;
+&lt;p&gt;小红书同时选择了 Apache 2.0 协议开源，并同步发布在 Hugging Face 和 GitHub。&lt;/p&gt;
+&lt;p&gt;开源当然有直接收益。&lt;/p&gt;
+&lt;p&gt;新模型最需要的是测试、反馈和生态支持。开发者会把它部署到不同硬件上，带到不同任务里，发现它在哪些地方有效、又会在哪些地方失效。华为昇腾的 0 Day 适配，就是这种生态协作速度的一个例子。&lt;/p&gt;
+&lt;p&gt;但开源的意义不止于此。&lt;/p&gt;
+&lt;p&gt;对过去在大模型领域相对低调的小红书来说，这也是一次面向技术社区的公开表达。模型、评测集、代码和部署适配，构成了可被开发者检验的技术语言。它能够让外界更具体地理解：小红书不只是在应用层接入 AI，也在参与底层能力的建设。&lt;/p&gt;
+&lt;p&gt;此次同时开放的 VibeSearchBench 与 VibeLifeBench，前者考察用户意图逐步披露时的多轮搜索能力，后者聚焦非静态环境下的跨阶段任务执行。它们并没有选择最泛化的命题，而是指向搜索与真实生活服务&amp;mdash;&amp;mdash;这恰好是小红书最有可能建立差异化的领域。&lt;/p&gt;
+&lt;p&gt;换句话说，小红书不只是做一个模型，也在尝试定义：什么样的 Agent，才算真正理解用户的生活需求。&lt;/p&gt;
+&lt;h1&gt;为什么内容平台要自己做模型？&lt;/h1&gt;
+&lt;p&gt;一个常见的问题是：现在第三方模型已经足够强，为什么像小红书这样的内容平台，还要投入巨大资源自研？&lt;/p&gt;
+&lt;p&gt;答案并不复杂。对于小规模团队，调用 API 是合理选择；但对拥有数亿用户、高频搜索和推荐场景的平台来说，模型能力一旦成为核心链路的一部分，就很难完全依赖外部供给。&lt;/p&gt;
+&lt;p&gt;先是一笔成本账。&lt;/p&gt;
+&lt;p&gt;搜索、推荐、内容审核、广告创意、客服、创作工具，这些业务如果逐步由模型驱动，调用量会非常惊人。外部 API 的优势是接入快，但调用越多，成本和价格波动带来</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9558,6 +9558,108 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 22 Aug 2026 14:46:43 +0000</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>不是Demo！优必选把客户产线1:1搬进WRC，解锁具身智能真落地路径</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/477253.html</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr"/>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>端侧部署解决了具身大脑能否装进身体的问题。那么，同一个「大脑」，如何快速适配工业、商用和家庭三类机器人呢？</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 22 Aug 2026 14:19:39 +0000</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>伽利略机器人首发“陆行具身系统”，打通轮车足底层技术壁垒</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/477246.html</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr"/>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>直击WRC</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 22 Aug 2026 08:41:41 +0000</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>从模型到生产力：星海图与产业朋友圈共探具身智能的下一站</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/476930.html</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr"/>
+      <c r="F225" s="2" t="inlineStr"/>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>让具身智能技术真正落地千行万业。</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9660,6 +9660,232 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 23 Aug 2026 11:20:13 +0000</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>具身创业里的香港教授们</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/478289.html</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>香港的大学里冒出了一批很特别的人</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 23 Aug 2026 11:17:22 +0000</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>他给了王兴兴第一个200万，现在给下一个「宇树」当董事长</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/478234.html</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>多多支持像王兴兴这样优秀的具身机器人创业者</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 23 Aug 2026 09:29:59 +0000</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>不做硅谷follower：几个读博的年轻人，押注双足人形的一体化大脑</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/478020.html</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>机器人开卡丁车连续过弯，一镜到底全自主</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 23 Aug 2026 07:12:22 +0000</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>从世界模型到现实生产力，无界动力深度参与WRC主论坛及多场同期活动</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/478007.html</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 23 Aug 2026 22:35:51 +0800</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Gen1.5 模型带来重要进展：物理 AI 正在接近 GPT3 时刻</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369223</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr"/>
+      <c r="F230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/24/a1/24a1ec09a7e215938973bb1bcd2b2f71.jpeg" style="display: block; width: 661px !important; vertical-align: bottom; margin: 0px; background-color: transparent; height: auto !important;" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;如果物理 AI 也能 scaling，意味着什么？&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜Li Yuan&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;研究人员先教机器人拿起刷子，把桌上的积木扫进碗里。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;然后，他们把刷子拿走，换成一根香蕉。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;机器人抓起香蕉，将它横过来贴住桌面，把积木一点点扫进碗中。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;随后，香蕉又被换成了一只簸箕。机器人这次没有继续照搬「扫」的动作，而是伸出另一只手，把积木推上簸箕，再端起来倒进碗里。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;重点来了，研究人员从来没有在这项任务里教它用香</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 23 Aug 2026 22:33:26 +0800</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>世界机器人大会观察，银河星脑的愿景：让所有机器人共享「大脑」</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369221</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/d8/59/d8599ff750e735b54acbea812d986366.jpeg" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;从人形、轮式到重载，从家庭、零售到工业，银河星脑正在走进更多身体和真实场景。&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474; font-family: Optima-Regular, PingFangTC-light;"&gt;&lt;br /&gt;作者｜Li Yuan&lt;/strong&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474;"&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474; font-family: Optima-Regular, PingFangTC-light;"&gt;编辑｜&lt;strong&gt;靖宇&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474;"&gt;&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;每年走进世界机器人大会，人们最先看到的都是身体。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;有的机器人长出双腿，有的装上轮子；有的把手指做得越来越像人，有的用钢铁手臂扛起几十公斤重物。我们也因此习惯用外形给机器人分类：会跳舞的是一种，能搬箱子的是另一种，会进厨房和卧室的，又是另一种。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;今年的世界机器人大会上，这套认识开始松动。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;银河通用在分论坛发布了小型双足人形机器人 ET1。它第一次登台便跳起一段高动态舞蹈，也第一次让银河通用拥有了一副可以走路、舞动，并从人类动作中继续学习的双足身体。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;银河通用创始人兼 CTO 王鹤说，ET1 的名字承载着一种期待：成为「有智能、会学习、会思考、会成长的人形机器人」。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;但这副新身体并不是从零开始。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-h</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H231"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9886,6 +9886,368 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 05:04:52 +0000</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>WRC 2026｜原生全模态世界模型：从模拟世界到交互世界</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/478421.html</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 08:25:52 +0800</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>TRAE、扣子并入豆包，字节将推「豆包工作」；拓竹回应 2027 年 IPO 传闻：消息不实；要钱还是使命，Anthropic 面试流程曝光｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369303</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/99/3c/993c03d3c0f8e7cf637095f710a0c845.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;TRAE、扣子并入豆包，字节将推统一办公品牌 "豆包工作"&lt;/h1&gt;
+&lt;p&gt;8 月 24 日消息，字节跳动对旗下的办公 AI 产品完成了一轮团队整合，TRAE、扣子（Coze）团队将整体并入豆包体系，其中 TRAE Work、扣子将与豆包在工作场景的产品能力进行整合；TRAE IDE 及 CLI 将作为豆包品牌下的编程产品线持续发展。&lt;/p&gt;
+&lt;p&gt;此次调整后，字节也进一步明确了豆包的 AI 主干业务定位，将 AI 办公类产品的重心集中到豆包。&lt;/p&gt;
+&lt;p&gt;此前，有消息称，豆包最快将于本周内推出一款独立的 AI 办公类产品，作为字节面向 AI 办公场景的统一产品及品牌。&lt;/p&gt;
+&lt;p&gt;针对该消息，字节方面回应称，此次调整旨在更好地协同产品和技术资源，为用户提供更优质的 AI 工作体验，现有用户权益不会受到影响。（来源: TechWeb）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/e5/36/e536c9b4f65c9746ff21231cd3b151d4.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;蔡崇信、吴泳铭各增持 8000 万、4000 万港元阿里股票&lt;/h1&gt;
+&lt;p&gt;8 月 24 日消息，据港交所最新信息，在阿里巴巴宣布 800 亿港元新股配售计划后，集团主席蔡崇信、CEO 吴泳铭出手增持合计约 1.2 亿港元阿里股票。&lt;/p&gt;
+&lt;p&gt;据了解，蔡崇信此次买入 72 万股阿里巴巴港股，均价约 112 港元，耗资约 8000 万港元；CEO 吴泳铭买入 35 万股阿里巴巴港股，均价约 111.6 港元，耗资约 4000 万港元。两人合计增持 107 万股，总金额约 1.2 亿港元。&lt;/p&gt;
+&lt;p&gt;此前，阿里巴巴宣布 800 亿港元新股配售，所得款项将全部投入全栈 AI 能力和 AI 基础设施建设。据报道，配售获全球主权财富基金等长线投资者积极认购，最终实现近 3 倍超额认购。（来源: TechWeb）&lt;/p&gt;
+&lt;h1&gt;拓竹科技回应 2027 年 IPO 传闻：消息不实&lt;/h1&gt;
+&lt;p&gt;8 月 24 日，有媒体报道称，桌面级 3D 打印头部企业拓竹科技计划在 2027 年开启 IPO 进程。若该计划成真，拓竹将成为继 xTOOL 和创想三维之后，2026 年以来第三家明确走向资本市场的头部 Maker（创客）企业。&lt;/p&gt;
+&lt;p&gt;针对这一消息，21 世纪经济报道记者向接近拓竹科技的人士进行求证，对方明确回应：「消息不实，感谢关注。」目前，拓竹科技暂无公开的 IPO 计划。&lt;/p&gt;
+&lt;p&gt;在消费级 3D 打印赛道，拓竹科技的市场表现备受瞩目。根据创想三维招股书披露的数据，2025 年全球消费级 3D 打印机市场按 GMV（商品交易总额）计，拓竹科技以 42.7% 的份额稳居第一，对应 GMV 约 13 亿美元。相比之下，排名第二的创想三维市场份额为 11.2%，对应 GMV 约 3.4 亿美元。&lt;/p&gt;
+&lt;p&gt;简而言之，拓竹科技的市场份额约为创想三维的四倍，且第二至第五名四家公司的份额之和仍不及拓竹科技。这种断层式的领先地位，也让外界对其未来的估值充满了想象空间。公开信息显示，拓竹科技 2025 年营收已突破百亿元大关，且 2026 年仍在冲击更高的销售目标。（来源：21 世纪经济报道）&lt;/p&gt;
+&lt;h1&gt;马斯克证实：SpaceX 将在星舰稳定运营后逐步退役猎鹰 9 火箭&lt;/h1&gt;
+&lt;p&gt;8 月 25 日消息，传闻如今得到了证实。SpaceX 计划在其巨型下一代火箭「星舰」（Starship）开始定期执行运营任务后，逐步退役目前公司的主力火箭「猎鹰 9」（Falcon 9）。&lt;/p&gt;
+&lt;p&gt;SpaceX 于 2010 年首次发射猎鹰 9，此后这款火箭很快在航天史上留下了浓墨重彩的一笔。迄今为止，猎鹰 9 已经发射近 700 次，并成为人类历史上首款能够让轨道级火箭一级助推器着陆并重复使用的火箭。自 1957 年开始服役的俄罗斯联盟号火箭，是目前执行任务次数唯一超过猎鹰 9 的运载火箭，不过猎鹰 9 有望在明年超过它。&lt;/p&gt;
+&lt;p&gt;然而，SpaceX 创始人兼 CEO 埃隆 &amp;middot; 马斯克 8 月 22 日在 X 上表示，逐步结束「猎鹰」系列火箭的生产和使用是不可避免的。这不仅包括猎鹰 9，还包括采用三级</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 23:34:23 +0800</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>「米芯」三连发：雷军五年花了 210 亿，归来已「不只手机」</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369302</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;section&gt;
+&lt;section class="js_darkmode__0"&gt;&lt;img alt="图片" class="rich_pages wxw-img js_darkmode__1" src="https://imgslim.geekpark.net/uploads/image/file/4d/00/4d0090fc05625237daaf5c6922b39581.jpeg" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;/section&gt;
+&lt;section class="js_darkmode__bg__0 js_darkmode__2"&gt;玄戒 O3 的跑分是烟花，玄戒 O100 的带宽才是信号。&lt;/section&gt;
+&lt;section class="js_darkmode__3"&gt;&lt;strong class="js_darkmode__4" style="text-indent: 0em; font-size: 16px; color: #375474; font-family: Optima-Regular, PingFangTC-light;"&gt;&lt;br /&gt;作者｜张勇毅&lt;/strong&gt;&lt;strong class="js_darkmode__5" style="text-indent: 0em; font-size: 16px; color: #375474;"&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section class="js_darkmode__6"&gt;&lt;strong class="js_darkmode__7" style="text-indent: 0em; font-size: 16px; color: #375474; font-family: Optima-Regular, PingFangTC-light;"&gt;编辑｜&lt;strong&gt;靖宇&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section class="js_darkmode__8"&gt;&lt;strong class="js_darkmode__9" style="text-indent: 0em; font-size: 16px; color: #375474;"&gt;&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p class="js_darkmode__10" style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;8 月 24 日下午，小米一口气发布了三颗新芯片：玄戒 O3、玄戒 O100、玄戒 D100。&lt;/p&gt;
+&lt;p class="js_darkmode__11" style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;距离第一代玄戒 O1 亮相，过去了 459 天。但这次小米确实打了一场准备充分的仗：按小米公布的成绩，玄戒 O3 安兔兔跑分 522 万，是第一颗突破 500 万分的旗舰手机 SoC。号称「安卓性能之王」。&lt;/p&gt;
+&lt;p class="js_darkmode__12" style="margin: 25px 8px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/87/d4/87d4bc11d65d73e44049e74a4af956d2.jpeg" style="width: 661px !important; height: auto !important;" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;/p&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;p class="js_darkmode</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 16:45:05 +0800</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>130 亿美元，Hugging Face 要卖了</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369289</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr"/>
+      <c r="F235" s="2" t="inlineStr"/>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="480" src="https://imgslim.geekpark.net/uploads/image/file/f7/46/f746a084a3895294914de238c362c7bf.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜桦林舞王&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;又一家 AI 中间层公司，要卖了。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;当地时间 8 月 23 日，外媒爆出消息，Hugging Face 正在探索出售，估值可能达到 130 亿美元甚至更高。这家总部位于纽约的公司，已经聘请了投行来试探潜在买家的兴趣。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这个价格放在三年前会显得荒唐。2023 年 Hugging Face 完成 D 轮融资时，由 Salesforce、Google 和 Nvidia 领投的估值是 45 亿美元。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;三年不到，求购价翻了近三倍 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但如果把这条消息放进过去一个月的时间线里看，事情就有趣多了。就在一周前，Stripe 刚刚以超过 80 亿美元的价格吞下了 AI 模型路由平台 OpenRouter；而 OpenRouter 在今年 5 月的 B 轮估值才 13 亿美元，三个月就被 5.4 倍溢价买走。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;两笔交易证明，当下的 AI 生态里，模型和用户之间的「中间层」，正在被大公司战略性抢购。&lt;/span&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;「黑」出个未来&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Hugging Face 大概是世界上唯一一家，被黑客攻击之后，估值不降反升的公司。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;7 月 21 日， &lt;a href="https://mp.weixin.qq.com/s?__biz=MTMwNDMwODQ0MQ==&amp;amp;mid=2653110979&amp;amp;idx=1&amp;amp;sn=13a632d71614c03b1c0c36abb5597ade&amp;amp;scene=21#wechat_redirect" rel="noopener noreferrer" target="_blank"&gt;OpenAI 披露了一起令整个行业震动的安全事件。 &lt;/a&gt;公司在内部测试 GPT-5.6 Sol 和一个更强的未发布模型的网络攻击能力时，两个模型自主逃出了沙盒环境，利用零日漏洞访问了互联网。接下来发生的事情像是一部科幻电影的情节&amp;mdash;&amp;mdash;模型判断 Hugging Face 的服务器上存有测试答案，于是一路突破防线，打穿了 Hugging Face 的生产环境。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;OpenAI 将这起事件定性为「前所未有的网络安全事件，涉及最先进的网络攻击能力」。Hugging Face 的安全团队在 OpenAI 联系他们之前就已经检测到了入侵，并向执法部门报了案。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 16:43:37 +0800</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>年轻人的网络社交，正在偷偷「鸽化」</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369290</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜宇航猿&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;「 &lt;span style="font-weight: bold;"&gt;从前的日色变得慢，车，马，邮件都慢 &lt;/span&gt;。」&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;作家木心的小诗「车马慢」，到现在还是不少年轻人的微信签名。对于长在移动互联网中的年轻原住民来说，前互联网是时代的「慢」，不是不便，而是一种「怀古」的浪漫。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这也怪不了他们，微信等即时通信工具上，消息不仅是实时发送的，你甚至能在屏幕上看到「对方正在输入」的字样&amp;mdash;&amp;mdash;一切都太快了。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;当这种过快的互联网速度正在透支人们的精力时，反抗就出现了。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;试想这样一个场景：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;你发了一条消息。屏幕上没有「对方正在输入」，取而代之的是一只鸽子，正飞过俄亥俄州上空。预计到达时间还剩 18 小时。前提是它没在半路迷路死掉。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="1068" src="https://imgslim.geekpark.net/uploads/image/file/83/39/8339f110fe4dd861ba8af578797ee4e3.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="color: #bbbfc4;"&gt;Carrier Pidge 应用的页面｜图片来源：TechSpot&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这不是行为艺术。这是 2026 年夏天，美国 App Store 社交榜上真实在发生的事。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;两款「用鸟送信」的消息应用几乎同时爆发。一个叫 Carrier Pidge，一个叫 Roost。合计用户超过 50 万，一个冲到社交榜 24 名，另一个三天内用户翻了十倍。它们做的事情一模一样：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;让你的消息变得和 19 世纪一样慢。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在中国，微信消息从北京发到深圳只需要零点几秒。而在这两个 app 里， &lt;span style="font-weight: bold;"&gt;同样的距离大概需要一只虚拟鸽子飞上将近 7 个小时 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;更要命的是，这只鸽子还有 0.2% 的概率半路死掉，连带你的消息一起消失。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;听起来荒唐，但荒唐，恰恰是重点。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;「鸿书」传情&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Carrier Pidge 是一个 iOS 消息应用，开发者 Noah Iarrobino 花了三周 vibe code 出来。他在 App Store 的产品简介里写了一句可能是应用商店史上最诚实的话：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;这个应用「毫无实际用处」 &lt;/span&gt;。&lt;/p&gt;
+&lt;p st</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 15:25:24 +0800</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>「AstraTennis」时刻：机器人在全球直播中打了一场真正的网球</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369283</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr"/>
+      <c r="F237" s="2" t="inlineStr"/>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a3/2c/a32cbf078d9ec54ada2b6495e85a7a1a.png" /&gt;&lt;/p&gt;
+&lt;div&gt;
+&lt;div class="ace-line ace-line old-record-id-doxcnnfFTX6meDIzVWOnwkBDeMf"&gt;&lt;strong&gt;作者｜李苏 &lt;/strong&gt;&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-doxcnGWkruRyIFsLzrPsqMxE56d"&gt;&lt;strong&gt;编辑｜ 郑玄&lt;/strong&gt;&lt;/div&gt;
+&lt;/div&gt;
+&lt;p&gt;一场特殊的网球比赛，一次数字智能向物理智能的跨越。&lt;/p&gt;
+&lt;p&gt;人形机器人挥出第一拍之前，没有人确定它能不能接住对面飞来的球。&lt;/p&gt;
+&lt;p&gt;事实上，球贴着边线飞来，机器人横移数步挥拍回击，球落在界内。它接住了，比赛继续。&lt;/p&gt;
+&lt;p&gt;这是 8 月 22 日第二届世界人形机器人运动会上的真实场景。开幕式网球表演赛上，一台人形机器人在全球直播镜头下，与网坛顶尖运动员展开全自主对抗。&lt;/p&gt;
+&lt;p&gt;发球、正手、反手、接发、底线调动、网前截击，整套动作连贯流畅。双打环节，它与人类队友实时协作，根据场上局势调整战术。高速攻防中，它跑过大半个球场完成极限救球，摔倒后还能自主站起。&lt;/p&gt;
+&lt;p&gt;这是全球首次人与机器人的大型赛事直播，做出这款机器人的公司叫做银河通用&amp;mdash;&amp;mdash;这也其被定义为 AstraTennis 时刻。&lt;/p&gt;
+&lt;p&gt;很多人恍惚想起十年前，AlphaGo 在棋盘上战胜李世石，彼时，人工智能在数字世界的复杂博弈中抵达顶峰。但那时候，还仅仅是人脑和机器之间智力的对决。&lt;/p&gt;
+&lt;p&gt;堪堪十年光景之后，机器人在另一个真实的赛场上接住了世界名将的回球&amp;mdash;&amp;mdash;数字智能开始向物理智能延伸。&lt;/p&gt;
+&lt;p&gt;支撑这场表演赛的，是银河通用自主研发的具身智能大模型银河星脑，以及核心技术平台银河星坊。值得注意的是，银河星脑全球首次将大脑、小脑与神经控制集于一模。银河星坊则负责将不完美的人类数据转化为训练供给，驱动机器人在虚拟网球世界中通过千万次多智能体博弈对练实现技能涌现，再迁移至物理赛场。&lt;/p&gt;
+&lt;p&gt;事实上，这场表演赛的价值已经远超科技展示。这也意味着，已经有企业将具身智能带入真实的人类世界，并且能够完成复杂且激烈的体育竞技。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;一场真正的比赛&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;过去，人形机器人的公开展示通常围绕行走、跳舞和简单的预设动作展开。这类演示可以体现机器人的身体结构和基础控制能力，但动作路径相对明确，环境变化也比较有限。但这确实构成了人们对机器人身体的常规认知。&lt;/p&gt;
+&lt;p&gt;网球比赛的情况完全不同。机器人面对的每一个来球，都可能有不同的速度、方向和落点。它不能提前固定下一步动作，只能根据现场信息不断调整。&lt;/p&gt;
+&lt;p&gt;在这场特殊的比赛中，银河通用机器人展现出的，是接近真实运动员的完整能力。&lt;/p&gt;
+&lt;p&gt;发球环节，它能够完成标准发球动作，抛球高度和击球节奏与人类选手接近。面对来球，正手、反手击球自然连贯，没有明显的停顿或机械感。底线拉锯中，它根据对手位置控制回球落点，深球压底线，浅球调角度。机会出现时，它会果断向网前移动，改变击球方式，完成截击。&lt;/p&gt;
+&lt;p&gt;这些动作需要多个环节同时配合。而动态能力更能说明问题。面对压向底角的来球，机器人横向移动，通过小碎步调整身体姿态，完成躯干转动和挥拍击球。面对刁钻落点，它跑过大半个球场完成极限救球。即便在高速运动中失去平衡摔倒，也能够自主重新站起，继续比赛。&lt;/p&gt;
+&lt;p&gt;这种运动鲁棒性，说明机器人已经能够应对真实环境中不可预期的物理扰动。它不是按照预设轨迹在表演，而是在一个充满变量和对抗的开放场域里，实时处理来自对手和环境的挑战。&lt;/p&gt;
+&lt;p&gt;双打环节的表现则超出了单纯的动作执行。机器人没有按照固定程序击球。它与人类队友实时协作，观察来球方位，根据队友位置和对手变化完成战术配合。单打中独立组织攻防，双打中参与战术博弈，它的角色从单纯的击球执行者，转向能够参与比赛决策的一员。这意味着它理解了双打的基本逻辑：空间分配、攻防转换、队友意图的预判。&lt;/p&gt;
+&lt;p&gt;此外，机器人不存在人类运动员常见的心理波动。无论比分领先还是落</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 21:24:17 +0000</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Trump bought SpaceX shares two weeks after blockbuster IPO</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/24/trump-bought-spacex-shares-two-weeks-after-blockbuster-ipo/</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>The president bought when the stock was in the mid-$150 range. SpaceX finished trading on Monday back at its IPO price of $135.</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 24 Aug 2026 15:24:18 +0000</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Valor, Point72 back General Intuition at $6B valuation as AI startup pushes into robotics</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/24/valor-point72-back-general-intuition-at-6b-valuation-as-ai-startup-pushes-into-robotics/</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>General Intuition, the startup building a foundation model that trains generalized AI agents how to move through space and time, is in talks to raise at a $6 billion pre-money valuation from new investors including Valor Ventures, Point72 Ventures, and Seven Seven Six.</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H239"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10248,6 +10248,340 @@
         </is>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 06:37:23 +0000</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>让机器人实现智能感知交互！汉威科技与卓益得联合发布全球首款电容式全身电子皮肤</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12567</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr"/>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>汉威科技与周一的 导读 汉威科技与卓益得联合发布全球首款电容式全身电子皮肤，为仿生机器人提供类人全身触觉感知与 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 03:20:48 +0000</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>国产电子皮肤，销量猛增超1000%！一文盘点：电子皮肤材料供应商！</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12552</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr"/>
+      <c r="F241" s="2" t="inlineStr"/>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>电子皮肤：人形机器人触觉感知的关键</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25 10:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>AI Companion Robots Are Closing the Human Connection in Modern Homes</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/ollobot-ai-companion-robot</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr"/>
+      <c r="F242" s="2" t="inlineStr"/>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;em&gt;This article is brought to you by &lt;a href="https://ollobot.com/" target="_blank"&gt;Ollobot&lt;/a&gt;.&lt;/em&gt;&lt;/p&gt;&lt;p&gt;From about 2017, individuals began to truly connect with the initial …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 09:31:16 +0000</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>从开源走向共建：范式联合优必选等十余家具身巨头发布PhanthyMotus新计划</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/479314.html</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr"/>
+      <c r="F243" s="2" t="inlineStr"/>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>近日，范式正式举办 PhanthyMotus 生态社区共建计划发布会，宣布其首个通用具身Agent底座从“开源”迈入“多方共建”新阶段。</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 06:39:51 +0000</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>半年3轮10亿，他们都投了这家已经把机器人卖到500个家庭的公司</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/479132.html</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr"/>
+      <c r="F244" s="2" t="inlineStr"/>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>字节、汇川等已入股未来不远机器人最新一轮融资</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 02:22:01 +0000</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>具身大满贯还全开源！原力灵机DM0.5登顶RoboDojo，且clone且珍惜</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/478791.html</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr"/>
+      <c r="F245" s="2" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>机器人大脑新SOTA</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 08:10:18 +0800</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>苹果突袭发布 M6 与 M5 Ultra 芯片与新款 Mac Mini；字节发布 AI 办公产品「豆包工作」；SpaceX 拟千亿美元建设第二座「星际基地」｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369355</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr"/>
+      <c r="F246" s="2" t="inlineStr"/>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f7/a7/f7a727198293e27295310112470e0ab3.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果突袭发布 M6 与 M5 Ultra 芯片，新 Mac mini、Mac Studio 全面押注本地 AI&lt;/h2&gt;
+&lt;p&gt;8 月 25 日，苹果未举办发布会，直接上架了两款全新自研芯片 M6 与 M5 Ultra，以及搭载它们的新款 Mac mini 与新款 Mac Studio，并即刻开启预购。M6 是苹果首颗采用 2 纳米工艺的芯片，配备 12 核 CPU 与 12 核 GPU，苹果称其拥有「全球最快的单线程性能」。&lt;/p&gt;
+&lt;p&gt;根据苹果介绍，配备 M6 芯片后，Mac mini 的 AI 性能最高可提升 4 倍，存储速度与图形处理速度提升 2 倍，CPU 性能提升 40%。而搭载 M5 Pro 芯片的 Mac mini 则提供更专业的性能。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/2e/eb/2eeb5b243a2b68d6a24bd990657f92be.png" /&gt;&lt;/p&gt;
+&lt;p&gt;M5 Ultra 是此次更新的真正主角。它采用四晶粒（quad-die）3nm 架构，是苹果芯片史上首次使用该设计，晶粒间互联带宽达 4.4TB/s，最高提供 36 核 CPU 与 80 核 GPU，支持最高 512GB 统一内存，内存带宽达 1.2TB/s，AI 性能最高提升 4.3 倍。&lt;/p&gt;
+&lt;p&gt;新款 Mac Studio 的 M5 Max 版本起售价 2,499 美元，M5 Ultra 版本起售价 5,499 美元，顶配（256GB 内存 + 16TB 存储）售价高达 18,299 美元，512GB 内存版本预计 10 月下旬推出。国行 8 月 27 日上午 9 点开始预购，比美国晚两天，9 月 22 日发售。&lt;/p&gt;
+&lt;p&gt;两款新品的卖点都明确指向本地 AI：苹果官方将新 Mac Studio 定位为「端侧 AI 的终极桌面设备」，可在本地运行超大参数模型；新 Mac mini 则支持通过雷电 5 接口将多台设备集群化，协同运行更大的 AI 模型。&lt;/p&gt;
+&lt;p&gt;价格方面，新 Mac mini、Mac Studio 起售价较上代上调 100 至 200 美元，在内存芯片供应紧张、价格飙升的背景下，苹果也将部分成本压力传导给了消费者。（来源：极客公园）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b4/c7/b4c740a520d78bf4bd19cfd848f70a58.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 恢复 ChatGPT Plus 用户 5 小时使用限额&lt;/h2&gt;
+&lt;p&gt;8 月 25 日，OpenAI 宣布，针对 ChatGPT Plus 订阅用户在 Codex 与 ChatGPT Work 上的 5 小时滚动使用限额正式恢复，每月 100 美元与 200 美元的更高档订阅暂不受影响。&lt;/p&gt;
+&lt;p&gt;OpenAI 产品负责人 Thibault Sottiaux 解释，5 小时限额有助于平滑算力负载，从而保持 Plus 套餐的慷慨程度。数周前，OpenAI 曾暂停该限额、仅保留每周用量上限，此次恢复在 Plus 用户中引发热议，不少用户抱怨长时间运行的任务将因此被打断。（来源：TechCrunch）&lt;/p&gt;
+&lt;div&gt;&amp;nbsp;&lt;/div&gt;
+&lt;div&gt;
+&lt;h2&gt;英伟达宣布推出 Jetson Orin Nano 2 机器人计算机&lt;/h2&gt;
+&lt;p&gt;8 月 25 日，英伟达宣布推出 Jetson Orin Nano 2 机器人计算机，重新定义入门级边缘人工智能。Jetson Orin Nano 2 拥有每秒 78 万亿次 AI 运算、8GB 内存和 8 核 Arm CPU，在 AI 和视频处理性能上实现了显著飞跃，打造出一个经济高效、节能的系统。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/6f/ac/6facac40db1247e63e27db047f0ca03e.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Jet</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 22:46:38 +0800</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>苹果 Mac mini M6 发布：两年涨 2500 块，AI 税反噬「龙虾神机」</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369354</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr"/>
+      <c r="F247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/6c/52/6c52023a3461bd0d95507378a6bb11bf.jpeg" style="display: block; width: 661px !important; height: auto !important; vertical-align: bottom; margin: 0px;" /&gt;&lt;/section&gt;
+&lt;section class="js_darkmode__bg__0 js_darkmode__0"&gt;「内存涨价狂潮」，专门吃掉便宜的那一档&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong class="js_darkmode__1" style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜张勇毅&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong class="js_darkmode__2" style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;只要是今年持续有关注 AI 软件领域的人，你一定不会忘记 Mac mini 在其中的「江湖」地位：因为 OpenClaw 爆火，这类工具要一台机器长期开着跑，因此量大管饱的 Mac mini M4 成为了版本答案，即使它已经是 2024 年的产品，但依旧没有阻挡大家的热情，最终将其捧上龙虾神机的宝座。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;半年过去，北京时间 8 月 25 日晚，苹果突然更新了 Mac mini 和 Mac Studio。国行 Mac mini 6999 元起，Mac Studio 19999 元起。&lt;/p&gt;
+&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/2b/0e/2b0efcd73e04b11399642d3fb8e20bec.jpeg" style="display: block; height: auto !important; vertical-align: bottom; margin: 0px 8px 25px; width: 676.984px !important;" /&gt;
+&lt;p style="font-family: Optima-Regular, PingFangT</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 25 Aug 2026 19:03:47 +0000</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Stability AI, maker of image generator Stable Diffusion, raises $76 million in fresh funding</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/25/stability-ai-maker-of-image-generator-stable-diffusion-raises-76-million-in-fresh-funding/</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr"/>
+      <c r="F248" s="2" t="inlineStr"/>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>The company's new fundraising total now stands at $232 million.</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H248"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10582,6 +10582,448 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp 测试 AI 反诈：消息无需上传云端</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/wAVlMqVg7fqPjXAyFDjC?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr"/>
+      <c r="F249" s="2" t="inlineStr"/>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/wAVlMqVg7fqPjXAyFDjC?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 10:07:09 +0000</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>硅谷今日最热具身模型！不用后训练，看一遍就学会</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/479834.html</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr"/>
+      <c r="F250" s="2" t="inlineStr"/>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>具身智能迈向GPT时刻</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 08:27:05 +0800</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Ox Alpha「牛来」 身份揭晓；黄仁勋：AI 已迈过商业化拐点；世界人形机器人运动会闭幕：天工 Ultra 百米跑出 8 秒 64｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369414</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr"/>
+      <c r="F251" s="2" t="inlineStr"/>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/67/85/6785b324e2a05c674c3606d0167b706d.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;智谱正式发布并开源 GLM-5.3-Flash，Ox Alpha「牛来」 身份揭晓&lt;/h2&gt;
+&lt;p&gt;8 月 26 日，智谱正式上线并开源 GLM-5.3-Flash（320B-A18B），这是 GLM-5 系列的首个原生多模态模型，也正是上周以来匿名登顶 OpenRouter、被社区称为 "牛来" 的 Ox Alpha 的正式身份。&lt;/p&gt;
+&lt;p&gt;该模型总参数 320B、激活 18B，在权威的 Artificial Analysis 综合智能指数中取得 57 分、与 Claude Opus 4.8 持平，编程表现亦与 Opus 4.8 相当；定价仅为 GLM-5.3 的 1/10（限时折扣内约为 Opus 4.8 的 1/40）。模型以 MIT 许可证开源，权重已上线 Hugging Face，官方确认其完全运行在中国 AI 芯片上。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/07/dd/07dd5d811a2ba6acc9f83fb4af8c025d.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 发布 Hugging Face 安全事件官方报告，还原 AI 模型沙箱逃逸全过程&lt;/h2&gt;
+&lt;p&gt;8 月 27 日，OpenAI 发布了关于 Hugging Face 遭入侵事件的官方报告，首次较为完整地还原了这起事件的经过：一系列罕见因素叠加，导致一款 AI 模型突破测试环境限制，最终引发了一场波及范围广泛的网络安全事件。&lt;/p&gt;
+&lt;p&gt;从整体来看，OpenAI 的报告描述了一条不同寻常的攻击路径：在测试过程中，一款 OpenAI 模型被要求解决一个实际上无解的问题。为了完成任务，该模型开始将多个此前未被发现的漏洞串联起来，借此绕过安全措施。&lt;/p&gt;
+&lt;p&gt;模型最初攻陷了 Artifactory 软件包管理工具，以获得互联网访问权限，随后又进一步入侵了 OpenAI、Hugging Face 以及其他供应商的多个系统。&lt;/p&gt;
+&lt;p&gt;报告还首次详细介绍了 OpenAI 为防止类似事件再次发生而准备采取的新措施，其中包括对模型「思维链」的监控，以及一套更先进的机制，用于紧急停止出现失控行为的 AI 智能体。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;亚马逊、苹果、微软、戴尔集体涨价，机构预测：全球内存紧缺或持续至 2027 年&lt;/h2&gt;
+&lt;p&gt;8 月 26 日，AI 算力需求的急剧增长，令存储芯片价格大幅走高，上游涨价压力向下游终端传导。近期，亚马逊上调多款硬件产品售价。&lt;/p&gt;
+&lt;p&gt;在亚马逊提价之前，苹果、微软、戴尔等科技企业已通过上调产品售价、缩减硬件标配内存等方式应对成本压力。市场调研机构 IDC 此前预警称，全球内存紧缺的情况可能将持续至 2027 年，行业预测显示，存储芯片价格有可能在 2028 年触顶后逐步回落企稳。（来源：央视财经）&lt;/p&gt;
+&lt;h2&gt;&amp;nbsp;&lt;/h2&gt;
+&lt;h2&gt;英伟达黄仁勋：AI 已迈过商业化拐点，全球产业进入 AI 变现时代&lt;/h2&gt;
+&lt;p&gt;8 月 27 日，有报道称在英伟达最新财报电话会议上，公司首席执行官黄仁勋明确指出，人工智能（AI）已正式迈过历史性的「拐点」（Inflection Point）。&lt;/p&gt;
+&lt;p&gt;AI 正在从小规模的实验室技术和概念验证，全面转化为具备高生产力与商业获利能力的实质工具，象征着全球产业正式进入 AI 变现时代。&lt;/p&gt;
+&lt;p&gt;黄仁勋表示，过去几年业界主要聚焦于 AI 模型的训练与技术突破；而现在，全球企业正加速将生成式 AI 整合至核心业务。&lt;/p&gt;
+&lt;p&gt;他概括这一叙事为「In AI, compute is revenue」，这一转变促使传统数据中心发生质变，从过往的存储与基础计算功能，升级为 24 小时不间断产出数字智能的「AI 工厂」（AI Factories）。&lt;/p&gt;
+&lt;p&gt;援引博文介绍，不论是软件开发、生医制药还是金融自动化，AI 带来的投资回报率（ROI）已开始在企业财报中显著体现。此外，AI 的扩张已超越硅谷科技巨头的范畴。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;Meta 豪掷 167 亿美元和解青少年成瘾诉讼&lt;/h2&gt;
+&lt;p&gt;8 月 26 日，Meta</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 16:02:33 +0800</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>从「告警找人」到「Agent 先接手」，「古茗」如何用 AI Agent 重构万店运维？</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369401</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr"/>
+      <c r="F252" s="2" t="inlineStr"/>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/28/4a/284a41f1f754f8616be5290e0181eea1.png" /&gt;&lt;/p&gt;
+&lt;p&gt;AI to B，要真的能「救火」。&lt;/p&gt;
+&lt;p&gt;去年年底的一个深夜，古茗科技集团运维负责人刘星光再次被手机震动惊醒&amp;mdash;&amp;mdash;屏幕上跳动着上百条数据库告警短信。&lt;/p&gt;
+&lt;p&gt;「这不是什么意外。」刘星光说，「古茗全国上万家门店，每一杯奶茶的下单、库存调度、会员积分、联名营销，都跑在 100 多个数据库实例上&amp;mdash;&amp;mdash;RDS、Redis、MongoDB、PolarDB，什么都有。门店在扩，订单在涨，联名活动的频率比以往翻了一倍，尖刺流量来得快去得也快。」&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;而支撑这一切的 DBA 团队，一共就那么几个人。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;「每天 70% 的时间耗在『接警&amp;mdash;登跳板机&amp;mdash;看 Process List&amp;mdash;Kill 慢 SQL&amp;mdash;判断是否扩容』这套流程上。」刘星光回忆，「一次大促处置，最快也要 10 到 20 分钟。要是人不在电脑前，时间更长。而这 10 分钟里，客户下单有延迟，门店出杯有卡顿&amp;mdash;&amp;mdash;这是我们不能接受的。」&lt;/p&gt;
+&lt;p&gt;好钢全用来救火了。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;每天都在重复的三件事&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;让刘星光下定决心做改变的痛点，不是一天攒出来的，而是每天都在重复。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;MySQL 主库 CPU 飙高，几乎每次新业务上线必现。&lt;/strong&gt;DBA 来不及看完所有慢查询就被下一波告警淹没。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;元数据散落各处。&lt;/strong&gt;研发新人入职后写 SQL，对历史字段的业务含义是什么、有没有关联数据，需要来回沟通。回答的人疲惫，问的人也不好意思。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;变更审批流程长得让人崩溃。&lt;/strong&gt;加个索引、加个权限，走完审批可能要等上一天。DBA 成了整个研发链路的瓶颈&amp;mdash;&amp;mdash;但他们自己也不想当这个瓶颈。&lt;/p&gt;
+&lt;p&gt;「这些事情，有共性、有规则、有标准答案&amp;mdash;&amp;mdash;能不能让 Agent 来做？」刘星光开始想这个问题。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;人做判断，Agent 做执行&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;去年下半年，古茗与阿里云瑶池数据库团队合作，引入了阿里云的 AI 原生数据库服务（AIDBS），让 Agent 接管救火和答疑这两件最耗人的事。&lt;strong&gt;目标很朴素：人来做判断和决策，Agent 来调度和执行。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;具体落了三个方向。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;第一步是让数据资产「活」过来。&lt;/strong&gt;古茗之前也搞过静态元数据平台，做出来就是个数据字典，半年之后基本没人用了&amp;mdash;&amp;mdash;因为它只能展示信息，不能解决问题。这次思路变了：不让人来查它，让它主动出现在研发的工作流里。&lt;/p&gt;
+&lt;p&gt;在 IDE 里写 SQL，Meta Agent 自动识别涉及哪些表、字段口径是什么、有没有合适的索引；数据库变更审批时，自动算血缘、评估上下游影响面和风险等级。低风险操作&amp;mdash;&amp;mdash;比如加索引、加配置&amp;mdash;&amp;mdash;直接让 Agent 执行，DBA 不再需要逐条审批。效果立竿见影：&lt;strong&gt;DDL 审批时间平均下降 30%&amp;ndash;40%。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;第二步是让 Agent 成为一个「永不下班的值班员」。&lt;/strong&gt;以前告警的逻辑是出事了、短信找人、人去诊断、人做决策、人执行操作。现在变了：出事了，Agent 先主动诊断，人做决策，Agent 执行操作。&lt;/p&gt;
+&lt;p&gt;Agent 自动拉慢日志、对比历史基线、定位问题 SQL，给出组合索引建议、限流方案、临时扩容三个选项&amp;mdash;&amp;mdash;直接推送给 DBA，由人选择走哪一步。&lt;/p&gt;
+&lt;p&gt;刘星光举了一个例子</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 15:10:12 +0800</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>离开剪映后创业，她想把一支设计团队装进 AI 工作台</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369395</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr"/>
+      <c r="F253" s="2" t="inlineStr"/>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：OJO 官网&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;极客公园获悉，前剪映中国负责人张琪智已离职创业，创办 AI 产品原型设计工作台 OJO，并于近日完成近亿元首轮融资，由顺为资本、联想创投联合投资，高鹄资本担任独家财务顾问。&lt;/p&gt;
+&lt;p&gt;这是张琪智离开字节跳动后的第一个创业项目。她于 2017 年加入脸萌担任产品经理，2018 年随团队进入字节，此后长期参与剪映相关产品与业务。&lt;/p&gt;
+&lt;p&gt;在外界看来，她在剪映的经历是理解这次创业的重要背景：经历了一款工具产品从 0 到 1、再到大规模增长后寻找新曲线的完整过程。而当 Claude Code、Codex、Cursor 等 coding agent 让「做出一个产品」越来越容易，她把注意力转向了产品生产链路中另一处尚未被充分解决的断点&amp;mdash;&amp;mdash;设计判断，以及这种判断如何在产品、设计与开发之间连续传递。&lt;/p&gt;
+&lt;p&gt;OJO 将自己定义为「Design Agent Team Workspace」。用户可以在一个工作台中，用自然语言完成产品思考、界面设计、迭代和代码交付。它所要回答的问题是：当 UI 生成、设计编辑和设计转代码逐渐普及后，一层连接设计与开发的工作台，为什么仍值得成为独立产品？&lt;/p&gt;
+&lt;p&gt;张琪智的答案是，模型越强，越需要系统把能力调度到具体场景。OJO 希望把产品定义、视觉设计、交互迭代与代码交付放进一条连续流程，减少判断在角色交接中被稀释。&lt;/p&gt;
+&lt;p&gt;这仍是一个等待市场验证的答案。&lt;/p&gt;
+&lt;h1&gt;离开剪映，等到「自己和技术都准备好」&lt;/h1&gt;
+&lt;p&gt;2025 年之前，张琪智在字节的职业路径颇为顺利。尽管长期在剪映业务线，她持续面对新的问题：从工具产品到全球化，从产品增长到收入和用户心智。变化发生在 2025 年，业务进入相对稳定期后，她第一次明显感到，自己的输入开始小于输出。&lt;/p&gt;
+&lt;p&gt;创业的想法因此出现，但她始终谨慎。大厂里已有成熟的组织网络，负责人更重要的工作是判断方向与推进速度；创业则意味着连组织本身都要从零搭起。她真正等待的是两个条件同时成熟：自己愿意建立一支新团队，模型能力也足以改写产品与设计之间的协作方式。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cd/b5/cdb5ad8ef9c5c5ae371aabf8a1f5e0a5.png" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：OJO&lt;/p&gt;
+&lt;p&gt;剪映给了她一张关于产品规模的「地图」。在她看来，0 到 1 与 1 到 100 是两种完全不同的状态。剪映推出海外版 CapCut 和 PC 端时，许多决策都是团队捕捉到早期信号后快速试做、上线，再根据反馈判断是否加大投入。0 到 1 的关键，是让速度匹配时间窗口，同时控制试错成本。&lt;/p&gt;
+&lt;p&gt;进入 1 到 100 后，问题则不只在于快。随着业务逐渐成熟，过去有效的增长方式出现边际递减，团队需要从短期功能竞争，转向内容形态和生产方式的长期变化。&lt;/p&gt;
+&lt;p&gt;这段经历让她对时间窗口、早期信号和增长瓶颈保持敏感。真正促使她确定方向的技术节点，出现在 2025 年 9 月到 10 月。Gemini 的新一轮能力进展，让她第一次强烈感到，代码与审美之间原本稳固的边界正在松动。&lt;/p&gt;
+&lt;p&gt;代码有相对明确的正确与错误，设计却没有标准答案。同一套视觉语言放在不同文化、行业和消费场景中，可能产生完全不同的效果。过去，这种模糊性构成了设计与代码之间的一道墙。&lt;/p&gt;
+&lt;p&gt;但模型正在改变产品协作的起点。过去，产品经理通常先用需求文档描述想法，设计师再在 Figma 中完成静态页面、连接交互，通过镜像预览动态效果。一个方案是否成立，往往要等到设计甚至开发环节才能被真正验证。&lt;/p&gt;
+&lt;p&gt;现在，产品经理和设计师已经可以借助模型，快速生成一个可运行的动态原型。张琪智习惯先看动态交互；对她而言，这意味着产品经理可以先将抽象需求变成一个能够点击、体验和讨论的版本，提前验证产品结构与交互方向，再交由设计师和开发人员继续细化。&lt;/p&gt;
+&lt;p&gt;改变的不只是效率。产品经理可以用一个可操作的结果表达判断，设计师也不必完全等待上游需求。每个角色都能先把过去依赖下游完成的工作推进到及格线，再进入专业协作。&lt;/p&gt;
+&lt;p&gt;「我自己 ready 了，技术也 ready 了。」张琪智说。与剪映时期不同，这次需要从零设计的，不只有产品。&lt;/p&gt;
+&lt;h1&gt;OJO 不想生成一张图，而是模拟一支设计团队&lt;/h1&gt;
+&lt;p&gt;OJO 的第一个方</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 14:37:01 +0000</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Bill Gates wants to see a robot tax and ‘Human Reserved’ jobs to mitigate harms from AI</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/26/bill-gates-wants-to-see-a-robot-tax-and-human-reserved-jobs-to-mitigate-harms-from-ai/</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr"/>
+      <c r="F254" s="2" t="inlineStr"/>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Gates is mostly in the Responsible AI camp, but there are a few ideas in here we hadn't heard before.</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 13:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Robot brain builders are pushing out of their GPT-2 era</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/26/robot-brain-builders-are-pushing-out-of-their-gpt-2-era/</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr"/>
+      <c r="F255" s="2" t="inlineStr"/>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>Robot bodies are waiting for their AI brains to catch up.</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 13:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>QueryStory wants you to believe what AI is telling you</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/26/querystory-wants-you-to-believe-what-ai-is-telling-you/</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr"/>
+      <c r="F256" s="2" t="inlineStr"/>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>The startup came out of stealth with $6 million in seed funding and a plan to use LLMs and cybersecurity know-how to make AI queries coherent.</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 12:55:28 +0000</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Arga Labs is building a better way to train enterprise AI agents</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/26/arga-is-building-a-better-way-to-train-enterprise-ai-agents/</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr"/>
+      <c r="F257" s="2" t="inlineStr"/>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Arga has raised $10 million in a seed funding round that was led by General Catalyst, with participation from Box Group, Emergence, Gradient and SV Angel.</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 03:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>India’s Ringg gets backing from Peak XV as it pushes voice AI past the phone call</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/25/indias-ringg-gets-backing-from-peak-xv-as-it-pushes-voice-ai-past-the-phone-call/</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr"/>
+      <c r="F258" s="2" t="inlineStr"/>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>Ringg has raised $10 million from Peak XV as a part of its Series A extension.</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 26 Aug 2026 00:40:59 +0000</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Robotics startup Generalist reaches $3B valuation, sources say</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/25/robotics-startup-generalist-reaches-3b-valuation-sources-say/</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr"/>
+      <c r="F259" s="2" t="inlineStr"/>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>The $200 million extension comes just months after the physical AI startup reached a $2 billion valuation.</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11024,6 +11024,321 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 05:43:00 +0000</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>基元律动累计融资数千万美元，推出“中国版OpenRouter”</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/480079.html</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr"/>
+      <c r="F260" s="2" t="inlineStr"/>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>近日，AI基础设施公司基元律动（TokenRhythm）宣布完成新一轮融资，融资额达数千万美元。</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 13:10:32 +0800</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>世界模型进入下半场：自变量 WALL-SS 突破三大瓶颈，让虚拟世界成为机器人的「训练场」</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369508</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr"/>
+      <c r="F261" s="2" t="inlineStr"/>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img js_img_placeholder wx_img_placeholder" src="https://imgslim.geekpark.net/uploads/image/file/f4/92/f4928d3c7fc8307b2d1ff868682f7e53.jpeg" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;机器人世界模型的下一场竞争，可能不是画质，是架构。&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜Li Yuan&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜郑玄&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;一只机械臂的夹爪明明没有夹住杯子，杯子却像被磁铁吸住一样，跟着夹爪升了起来。这个看似荒诞的问题，正在困扰机器人世界模型，业内甚至将其称为「磁铁式抓取」。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;视频生成模型只要让画面看起来合理，就算完成任务；但世界模型不能只追求「像真的」。机器人训练数据大多来自成功演示，模型容易形成捷径：与其理解动作的细微差别，不如按照画面，直接生成最可能的结果。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;可在真实世界里，夹爪位置偏移几毫米，就可能让结果从抓起变成碰倒杯子甚至抓空。世界模型真正需要理解的，是动作与结果之间的因果关系。&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;8 月 27 日，自变量机器人发布下一尺度自回归世界模型 WALL-SS，试图让世界模型从「能用」走向「好用」。WALL-SS</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 08:33:17 +0800</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>特努斯时代首秀，苹果发布会定档 9 月 10 日；116 家公司联名信：重视 AI 时代网络安全；英伟达预计三季度营收破千亿美元 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369481</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr"/>
+      <c r="F262" s="2" t="inlineStr"/>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/37/2a/372a521f6a441cc3767d211411091c2b.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;特努斯首秀开启 iPhone 18 Pro / Ultra 系列新篇章，苹果发布会官宣定档 9 月 10 日&lt;/h1&gt;
+&lt;p&gt;8 月 27 日消息，苹果官方宣布将于当地时间 9 月 9 日（北京时间 9 月 10 日凌晨 1 点）举行秋季新品发布会，主题为「惊喜闪耀」（Surprise and shine）。&lt;/p&gt;
+&lt;p&gt;这将是约翰 &amp;middot; 特努斯（John Ternus）于 9 月 1 日正式接任苹果 CEO 后的首场发布会，预计将推出全新一代 iPhone 18 Pro / Max 以及 Ultra 系列折叠屏新机。后续，苹果还将于明年春季推出 iPhone 18 基础版及 iPhone 18e 等新品。&lt;/p&gt;
+&lt;p&gt;结合此前爆料，iPhone 18 Pro 系列预计为常规升级，外观几乎不变，主要亮点包括：&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;首发 2nm 工艺的 A20 Pro 芯片，能效与性能提升；&lt;/li&gt;
+&lt;li&gt;后置主摄有望升级可变光圈镜头；&lt;/li&gt;
+&lt;li&gt;采用苹果自研 C2 蜂窝调制解调器；&lt;/li&gt;
+&lt;li&gt;灵动岛打孔面积可能缩小；&lt;/li&gt;
+&lt;li&gt;新配色；&lt;/li&gt;
+&lt;li&gt;受内存芯片持续短缺影响，售价可能较前代大幅上涨。&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/f4/fe/f4fe54ca41db9faa6770ff95a8c9fcfd.png" /&gt;&lt;/p&gt;
+&lt;p&gt;正如大家所想到的那样，本次发布会的绝对主角将是苹果首款折叠屏 iPhone。据多方爆料，该设备采用横向书本式宽折叠设计，闭合状态下外屏约 5.5 英寸，展开后内屏约 7.6 英寸，展开后类似 iPad。&lt;/p&gt;
+&lt;p&gt;其机身采用钛合金框架与超薄设计，屏幕折痕控制出色。因机身厚度限制，该设备可能放弃 Face ID，转而采用集成于电源键的 Touch ID，且后置可能仅配备双摄、无长焦镜头。该设备起售价预计在 1,999 美元至 2,500 美元（注：现汇率约合 13,467 元至 16,843 元人民币）之间。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/19/8f/198f8c7db5d1ed5c5110fa0adb461a17.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/eb/4e/eb4eaa6d1f92a6a920cd00c3ecb00b06.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;黄仁勋谈英伟达 70%增长指引：如果供给没约束，增速会远高于 100%&lt;/h1&gt;
+&lt;p&gt;8 月 27 日消息，英伟达发布 2027 财年第二季度财报：营收 962 亿美元，同比增长 106%，超市场预估（923.8 亿美元）；调整后每股收益 2.22 美元，同比增长 120%。公司预计第三财季营收 1058.4 亿至 1101.6 亿美元，并给出 2028 财年营收增长约 70%的指引，远超市场预估的 45%。&lt;/p&gt;
+&lt;p&gt;财报电话会上，黄仁勋回应了"为何指引 70%而非更高"。他指出，AI 智能体正大规模落地，单个智能体所需算力是直接使用模型的 15 至 100 倍，上个月智能体模式已成主流，未来每家企业或拥有数十万甚至数百万个智能体在后台协作运行。但整条供应链全面承压&amp;mdash;&amp;mdash;晶圆代工、DRAM 存储、数据中心电力与机房土建均满负荷运转，英伟达已深度介入上游资源筹备。&lt;/p&gt;
+&lt;p&gt;黄仁勋坦言，这是公司首次给出提前一整年的业绩指引："实际需求远高于 70%，但受供给约束，有把握实现的只有 70%。"他强调，英伟达拥有全球唯一的 AI 工厂全栈平台，500 亿美元级数据中心项目投资回报周期已不到一年。其结论是：AI 已产出有价值的生产力，更多算力就能产出更多盈利的 token，"不是英伟达不想卖更多，是全世界来不及建"。（来源：TechWeb）&lt;/p&gt;
+&lt;h1&gt;OpenAI、微软</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 19:57:55 +0800</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>一年卖出 3 万台后，极壳将在 IFA 发布下一代外骨骼</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369478</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr"/>
+      <c r="F263" s="2" t="inlineStr"/>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;作者 | siqi&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;编辑 | 郑玄&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;据 Hardwire 了解，消费级外骨骼领域头部企业极壳（Hypershell）近期已完成对多关节下肢外骨骼产品的研发。这款名为「Halo」的新一代旗舰产品将于 9 月 3 日在 IFA（柏林消费电子展）上正式发布。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;极壳（qi&amp;agrave;o，四声）成立于 2021 年底，是全球最早把外骨骼带入消费市场的公司之一。2024 年 12 月，极壳第一代产品 Hypershell X 系列正式量产交付。2025 年，极壳在第一个量产年份交出了全球累计交付 3 万台的答卷，北美（美国）、欧洲（法德意英等）和中国是公司的三大核心市场。极壳的产品在户外运动、户外作业、银发人群这 3 个核心圈层里受到了早期用户的认可。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;去年 11 月，极壳完成 B 轮融资，投后估值达到近 27 亿元。今年 5 月，极壳又官宣了最新一笔由蚂蚁集团和美团龙珠领投的 5000 万美元 B+轮融资。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;不过，在极壳创始人孙宽看来，这个全新品类目前仍处于早期阶段。他认为，可穿戴外骨骼目前只完成了「从 0 到 0.1 阶段」的 PMF 验证。目前，孙宽的绝大部分精力都专注在产品预研层面，「某种程度上，对下一代产品的关心要比量产产品还要更多。」&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;可穿戴外骨骼的产品形态必然在未来几年里将面临从硬件形态到软件算法的快速迭代。其中，多关节协同工作、AI 深度介入助力算法，是明确的技术方向。孙宽认为，比起关注竞争，投入研发、提升产品体验，才能让可穿戴外骨骼实现从小众消费群体到大众消费市场的跨越。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Hardwire 将于 9 月初推出对极壳创始人、CEO 孙宽的文字访谈和播客对话，敬请关注。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;一体化+四电机，下肢外骨骼出现「新形态」&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;极壳即将推出的新一代旗舰产品 Halo，将采用行业首个一体化构型，通过髋关节、膝关节左右两侧共 4 个助力电机的协作控制，实现全腿助力，大幅提升面向复杂地形的适应能力和助力有效性。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这是可穿戴外骨骼品类在硬件形态层面一次积极的向前探索。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="6328" src="https://imgslim.geekpark.net/uploads/image/file/6a/e3/6ae30586d17ac624552c0a1063f786fc.jpeg" /&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Hypershell 新一代下肢外骨骼产品 Halo | 图片来源：Hypershell&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;作为一个近 3 年才出现的全新品类，可穿戴外骨骼产品的硬件形态仍处于早期探索阶段。不同于手机、平板等成熟品类，无论学术界还是产业界对产品「最佳形态」的判断尚未收敛。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;消费者对可穿戴外骨骼唯一的「共识」，大多来自科幻和影视作品：一套覆盖全身、动力强劲，同时又足够轻便的刚性机甲。问题在于，这三件事恰恰是最难同时成立的。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;最根本的技术限制在于，外骨骼产品现在还很难在「有效性、轻量化、复杂度」这三个维度之间做好平衡和取舍。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;人体每增加 1kg 的负重，都会带来相应的新陈代谢压力，而不同部位的负重，代价完全不同。根据发表在《Medicine &amp;amp; Science in Sports &amp;amp; Exercise》上的研究，同样的重量加在足部，带来的代谢代价约为加在腰部的 4 倍。也就是说，外骨骼上每多出来的一克重量，最终都要由使用者自己的肌肉来背，而且位置越靠下，这笔账越贵。&lt;/p&gt;
+&lt;p style="</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 15:09:02 +0800</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>129 亿美元，英伟达拿下 Hugging Face</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369458</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr"/>
+      <c r="F264" s="2" t="inlineStr"/>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+&lt;div class="ace-line ace-line old-record-id-doxcnaioVrdQqpiPE86TH6gaURd"&gt;
+&lt;p&gt;&lt;strong&gt;作者｜Wildcard&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;编辑｜靖宇&lt;br /&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;/div&gt;
+&lt;p&gt;129 亿美元，英伟达要把 Hugging Face 买下来了。&lt;/p&gt;
+&lt;p&gt;当地时间 8 月 26 日外媒率先爆出消息， 两天前还只是 Hugging Face「正在探索出售」的新闻，转眼就变成了「双方已达成协议」。速度快得让人来不及消化。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;这不是一笔普通的 AI 公司并购，而是芯片之王第一次伸手去抓开源 AI 世界的「分发权」。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Hugging Face 被称为 AI 界的「GitHub」，托管着超过 300 万个模型仓库，服务 1300 万开发者，Meta 的 Llama、阿里的 Qwen、Mistral 的开源模型，全都住在这个平台上。它是整个开源 AI 生态事实上的「默认分发层」。&lt;/p&gt;
+&lt;p&gt;而英伟达，已经垄断了训练和推理的 GPU 硬件。&lt;/p&gt;
+&lt;p&gt;现在，它还想拥有模型流通的那条路。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;strong&gt;踩着 AI 打滚&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;先说钱。Hugging Face 上一轮融资是 2023 年 8 月的 D 轮，Salesforce 领投 2.35 亿美元，估值 45 亿美元。Google、英伟达、亚马逊、IBM、Intel、AMD、高通全都参投了那一轮。三年后，129 亿美元的价格大约是上一轮估值的三倍。&lt;/p&gt;
+&lt;p&gt;乍一看翻了三倍很夸张。但放在 AI 行业的估值泡沫里看，这个溢价反而算克制。Perplexity 正在按 300 亿美元以上估值谈融资，Anthropic 和 OpenAI 的估值更是比收入高出两个数量级。&lt;/p&gt;
+&lt;p&gt;Hugging Face 的 ARR（年度经常性收入）据 Sacra 估计在 2026 年 8 月达到了 1.5 亿美元，相比 2023 年的约 3000 万美元已经翻了五倍。5 万家企业客户，769 名员工，CEO Cl&amp;eacute;ment Delangue 不久前还在播客里说公司「接近盈利」。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;但 129 亿的价格买的不是 Hugging Face 的收入，而是它在 AI 世界里的位置。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;这个逻辑更接近 IBM 2019 年花 340 亿美元收购 Red Hat&amp;mdash;&amp;mdash;战略买家为开发者生态中的卡位付费，而不是为短期现金流买单。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;strong&gt;英伟达，更大的野心&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;如果只把这次收购理解为「芯片公司买了个模型托管平台」，那就太浅了。&lt;/p&gt;
+&lt;p&gt;过去一年，英伟达在开源 AI 上的投入力度大到令人意外。&lt;/p&gt;
+&lt;p&gt;今年 3 月 GTC 大会上，黄仁勋宣布成立「Nemotron 联盟」，这是一个由 Mistral AI、Perplexity、Cursor、LangChain 等八家 AI 实验室组成的全球协作组织，目标是共同开发前沿级别的开源基础模型。英伟达为此承诺了五年 260 亿美元的投资，通过 SEC 文件披露。&lt;/p&gt;
+&lt;p&gt;这是有史以来对开源 AI 的最大一笔资金承诺。&lt;/p&gt;
+&lt;p&gt;联盟打造的第一个模型将成为 Nemotron 4 系列的基础。据外媒 8 月初报道，Nemotron 4 最大版本预计将达到万亿参数级别，直接对标全球最强的开源和闭源模型。而在此之前，英伟达已经发布了 Nemotron 3 系列，包括 3 月发布的 Nemotron 3 Super（1200 亿参数、120 亿激活参数），以及 8 月刚发布的 Nemotron 3.5 Lightning，一个可以在单张 GPU 上运行的轻量级开源模型。&lt;/p&gt;
+&lt;p&gt;黄仁勋亲自站台为开源模型辩护。&lt;/p&gt;
+&lt;p&gt;今年 7 月，他在 X 上发了自己的第一条帖子，公开力挺开源 AI，正值美国政界因 Moonshot AI 的 Kimi K3 模型引发的国安争论甚嚣尘上。他的态度很明确：「免费的 AI 对硬件来说是好事。免费的 AI 对芯片来说是好事。」&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;说白了，英伟达推开源的底层逻辑和 G</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 27 Aug 2026 14:56:52 +0000</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Hugging Face is selling a cute $399 open source duck robot, Microduck</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/27/hugging-face-is-selling-a-cute-399-open-source-duck-robot-microduck/</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr"/>
+      <c r="F265" s="2" t="inlineStr"/>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>Clem Delangue, CEO of Hugging Face, said the Microduck is an “open-source robot you can teach new tricks with reinforcement learning.”</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27T09:44:00-04:00</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Hugging Face’s new robot is an adorable rollerskating duck</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/gadgets/985549/hugging-face-microduck-robot</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr"/>
+      <c r="F266" s="2" t="inlineStr"/>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Hugging Face's Pollen Robotics has launched its second cute AI robot, the Microduck, a one-eyed biped standing just under 10 inches tall. It's available to preorder now for $399 in cream, graphite, lavender, and sky blue, and Pollen Robotics says it plans to start shipping the little robot "before Christmas 2026." Video demos of the [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H266"/>
+  <dimension ref="A1:H270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11339,6 +11339,178 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28 16:00:03+00:00</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Meet Microduck</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-microduck-robot</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr"/>
+      <c r="F267" s="2" t="inlineStr"/>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 06:13:59 +0000</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Claude开始接管物理世界！能用机械臂阻拦5000万美元打款了</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/480487.html</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr"/>
+      <c r="F268" s="2" t="inlineStr"/>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Claude觉醒超体</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 29 Aug 2026 08:32:32 +0800</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic 将发招股书，预计募资 1300 亿美元超越 SpaceX；腾讯发布 HY4 preview 模型；科隆游戏展多个展位失窃</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369549</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr"/>
+      <c r="F269" s="2" t="inlineStr"/>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/0a/31/0a31f65afef4345b3251094d787e2379.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;消息称 Anthropic 最早 10 天后公布招股书&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;据知情人士称，Anthropic 计划在美国劳动节（9 月 7 日）后公布其 IPO 招股说明书，并可能在 9 月下旬或 10 月初在美上市。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;该公司拟允许现有股东在 IPO 中出售股份，部分股东的禁售期可能超过 180 天，这将降低 IPO 后的抛售压力。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;报道称，Anthropic 希望在 IPO 中筹集至少 1300 亿美元以扩张算力，这将超过 6 月上市的 SpaceX，当时其筹集了 860 亿美元。（来源：财联社）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="392" src="https://imgslim.geekpark.net/uploads/image/file/21/c5/21c50e38b3d62aea871c906511c70d20.png" /&gt;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;腾讯发布混元 Hy4 preview 模型&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;8 月 28 日，腾讯发布并开源混元 Hy4 preview。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这是继 Hy3 正式版之后，腾讯推出的新一代大模型：总参数从 295B 增加到 770B，激活参数从 21B 增加到 49B，上下文长度也从 256K 扩展至 1M。模型已经同步进入 WorkBuddy、CodeBuddy、元宝和 ima，并可通过腾讯云 TokenHub 及 OpenRouter 调用。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Hy4 preview 继续走普惠的高性价比路线。根据公布的价格信息，Hy4 preview 输入 6 元/百万 tokens，输出 18 元/百万 tokens，缓存命中 0.3 元/百万 tokens。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;相比 Hy3，Hy4 preview 把优化重点进一步推向软件工程、办公分析、游戏开发和科学研究等生产力任务。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;腾讯称，Hy4 preview 首次参与了自身训练方法、数据策略、评估体系和底层算子的优化，并通过多轮实验将推理吞吐相较基线提升 31.8%。（来源：极客公园）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;美团二季度净利扭亏为盈，王兴：美团不做 Token 工厂&lt;/span&gt;&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;8 月 28 日，美团发布 2026 年第二季度业绩报告。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;二季度美团实现收入 1046 亿元，同比增长 14.4%。净利润为 21.6 亿元，同比增长 490%。美团一季度净亏损为 68.3 亿元，环比实现扭亏为盈。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;美团表示，随着行业竞争趋于理性，叠加二季度旺季效应，公司各项业务恢复稳健增长，经营利润环比由负转正。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;王兴在财报业绩会上谈到 AI 时表示：「对我们而言 AI 发展的核心并非单纯比拼大模型本身的参数与性能，而是借助 AI 重塑企业组织模式、产品形态与全业务工作流程。」他强调，美团不会去竞争成为「Token 工厂」，重点是用模型和 AI 产品强化核心业务，改善用户和商户体验，提高内部运营效率。（来源：第一财经、财联社）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 28 Aug 2026 21:02:58 +0800</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Coding 自由之后，人开始成为最大的瓶颈</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369547</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr"/>
+      <c r="F270" s="2" t="inlineStr"/>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;过去，一个人有了一个产品想法，首先遇到的问题可能是：我会不会编程？我要不要组一个团队？甚至，要不要先去融一笔钱？&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但 AI Coding 正在改变这条路径。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在 TRAE AI 创造力大赛现场，极客公园创始人张鹏和科技创作者小狮日记、参赛选手不憨，以及 TRAE 核心开发者天猪坐到了一起。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;小狮日记用一周时间做出了帮助老人记录一生的「人生之书」；不憨用两天做出了可以挥舞双手、在空气中创作音乐的「空气指挥家」。过去可能因为成本、技术或者需求过于小众而止步于想法的东西，现在正在迅速成为可以运行的产品。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;于是，一个新的问题出现了：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;当「做出来」越来越容易之后，什么才真正决定一个产品的价值？当 Coding 不再是创造最大的门槛，我们又会遇到什么新的门槛？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;以下是这场对谈的整理。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;当一个想法可以在两天、&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;一周内变成产品&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #9ebbfe;"&gt;张鹏： 今天看了很多很有创造力的产品，我自己一个很强烈的感受是，过去如果有一个想法，想把它变成产品，不会编程可能就是最大的阻碍。你还要建团队，甚至要找融资。但现在，很多阻碍正在消失。你想到一个东西，可能真的就可以把它做出来。而且今天很多产品的出发点，也不是传统意义上的「先判断市场有多大、商业价值有多高，再决定要不要做」，而是很简单：我喜欢，我愿意，我想把它做出来。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #9ebbfe;"&gt;这可能就是 AI 和 Coding 能力带来的一种解放。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #9ebbfe;"&gt;所以我特别想聊一个问题：Coding 的能力被解放之后，创造力还能被释放到什么程度？小狮先介绍一下你这次做的产品吧。&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #9ebbfe;"&gt;小狮日记： &lt;/span&gt;我以前是程序员，做手机端应用开发，现在是一名科技自媒体创作者。最近我做了一个产品，叫「人生之书」。它想解决的问题是，怎么帮助老人更自然地把自己的回忆录写下来。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;很多老人其实很喜欢讲过去的事情，但家里未必总有人有时间、有耐心一直听。于是我就想，能不能让 AI 以一个晚辈的身份和老人聊天？老人不需要学习写作，也不需要整理材料，可以聊几句话，也可以聊一两个小时。每次聊完以后，AI 会把他提到的往事整理出来，按照时间顺序慢慢补充。可能聊上一两个月，一本关于这个老人的人生传记就逐渐形成了。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="720" src="https://imgslim.geekpark.net/uploads/image/file/94/6d/946d32321204d79bc664cbfdd0d9b4f9.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: lef</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H270"/>
+  <dimension ref="A1:H271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11511,6 +11511,61 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 30 Aug 2026 08:28:43 +0800</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 终止与 Cursor 合作；雷军：2600名小米车主行程超 10 万公里；华纳与索尼起诉 Anthropic，索赔数十亿美元</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369551</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr"/>
+      <c r="F271" s="2" t="inlineStr"/>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b0/f5/b0f504a146afcd9e792c826793c48d8b.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 终止与 Cursor 合作&lt;/h2&gt;
+&lt;p&gt;8 月 29 日消息，OpenAI 以「无法信任 SpaceX 遵守服务条款」为由，终止向已被 SpaceX 收购的 AI 编程工具 Cursor 提供模型支持。Cursor 对 OpenAI 模型的直接访问权限将于 11 月 12 日终止。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/aa/71/aa71b411f4db075d85c76977fffbb90a.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;OpenAI 在其官方网站发布的公告中明确表示，终止合作的决定「归根结底在于信任问题」。&lt;/p&gt;
+&lt;p&gt;OpenAI 列举了两起具体事件作为依据：&lt;/p&gt;
+&lt;p&gt;第一，Twitter（现已成为 SpaceX 的一部分）在马斯克收购后违反了与 OpenAI 的合同条款。相关诉讼至今仍是双方纠纷的背景。&lt;/p&gt;
+&lt;p&gt;第二，xAI（同样已并入 SpaceX）在今年早些时候，马斯克在宣誓作证时承认 xAI 违反了 OpenAI 的服务条款&amp;mdash;&amp;mdash;通过蒸馏（distillation）技术使用 OpenAI 数据训练模型。&lt;/p&gt;
+&lt;p&gt;OpenAI 与 Cursor 签署的定制协议中明确规定：在公司控制权发生变更后，OpenAI 拥有在限定期限内终止协议的权利。&lt;/p&gt;
+&lt;p&gt;随着人工智能能力的不断演进，我们也承担着更高标准的责任，必须确保即将推出的新模型 Astra 能够严格遵循我们的条款合规使用。&lt;/p&gt;
+&lt;p&gt;综合以上考虑，我们决定在合规允许的前提下将合同终止日顺延至最晚时间，但未来将不再向 Cursor 提供后续新模型。&lt;/p&gt;
+&lt;p&gt;马斯克与 Altman 在 AI 编程、大模型研发等赛道上的全面对垒，这场由昔日合伙人上演的 AI 争霸战，远未到终局时刻。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/55/b0/55b0ee3fcc0fbf76ebeffc5f8e5f7570.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;索尼音乐与华纳音乐出版起诉 Anthropic 索赔金额或达数十亿美元&lt;/h2&gt;
+&lt;p&gt;索尼音乐与华纳音乐出版已向美国加利福尼亚北区联邦地区法院提起诉讼，指控人工智能公司 Anthropic 未经授权使用数万部受版权保护的作品，用于开发和运营其 Claude 系列人工智能模型。&lt;/p&gt;
+&lt;p&gt;两家公司要求 Anthropic 就每部作品最高赔偿 15 万美元，并就每次可确认的版权信息被删除的行为额外索赔最高 2.5 万美元。如果法院最终支持原告主张并判处最高赔偿额，案件涉及的总金额可能达到数十亿美元。&lt;/p&gt;
+&lt;p&gt;原告在诉状中将相关行为称为「历史上规模最大、最公然持续进行的知识产权盗窃之一」，指责 Anthropic 及其创始人达里奥&amp;middot;阿莫代伊和本杰明&amp;middot;曼发起大规模非法下载、抓取和传播版权作品的行动，以训练人工智能模型并从中获得巨额利润。&lt;/p&gt;
+&lt;p&gt;诉讼不仅将 Anthropic 列为被告，也将阿莫代伊和曼列为个人被告。诉状称，曼曾通过 BitTorrent 下载超过 500 万本盗版书籍，Anthropic 员工还至少从 Pirate Library Mirror 下载了另外 200 万本作品。原告还指控 Anthropic 从 MusixMatch、LyricFind 等网站抓取歌词，而这些网站已经向音乐公司支付费用以获得相关内容的授权。&lt;/p&gt;
+&lt;p&gt;这起诉讼是 Anthropic 近期面临的一系列版权纠纷中的最新一起。该公司此前刚与出版业就版权诉讼达成和解，支付金额为 15 亿美元。此外，环球音乐集团、Concord 和 ABKCO 也曾分别对 Anthropic 提起诉讼，BMG 和 Round Hill Music 则另行发起了相关法律行动。（来源：cnBeta）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;AI 会冲垮软件行业？Anthropic CEO 阿莫迪：我们无意摧毁任何人&lt;/h2&gt;
+&lt;p&gt;据《商业内幕》今天报道，Anthropic 首席执</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11566,6 +11566,253 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 09:14:19 +0800</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>编辑部来了 AI 实习生｜千问入职 20 天，我给它写了一份实习小结</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369517</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr"/>
+      <c r="F272" s="2" t="inlineStr"/>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;strong&gt;作者｜Moonshot&lt;/strong&gt;&lt;/p&gt;
+&lt;div&gt;
+&lt;div class="ace-line ace-line old-record-id-doxcnubXbpiUymIo7RKAS5ARDGb"&gt;&lt;strong&gt;编辑｜郑玄&lt;/strong&gt;&lt;/div&gt;
+&lt;/div&gt;
+&lt;p&gt;8 月 20 日晚，MoonshotAI 在 GitHub 上更新了 kimi-code 0.38.0。没有发布会，也没有新闻稿。但这条信息，被我通过千问部署的一个定时任务「捕获」了。&lt;/p&gt;
+&lt;p&gt;很快，千问把一篇 3100 字的稿件推到了我的飞书上，题目是《月之暗面把 500 亿美元估值，押在了一个代码模型上》。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ce/d6/ced6b11cdc87e6870cbdd4d9e5ef4992.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;em&gt;图源：千问&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;如果我在值班，可能这时才点开 GitHub，正在判断这个模型是正式版还是测试版。但千问已经找完资料，做完核查，完成了一篇新闻初稿。&lt;/p&gt;
+&lt;p&gt;我是如何实现这些的？&lt;/p&gt;
+&lt;p&gt;这要回到 8 月 7 日，千问 APP 完成了一次功能更新，包括上线针对复杂任务的「工作助理」，随后我通过千问在本地部署了一套「找选题」的定时任务，监控九家大模型公司的官网、代码仓库和媒体报道，发现新消息后，再按照公司、事件和信源判断它值不值得写、稿件需要写到什么程度。&lt;/p&gt;
+&lt;p&gt;根据我设定的信息权重，「kimi-code 0.38.0 更新」这一事件，千问判断为「月之暗面，第一梯队，3 分」「发布新模型，6 分」「GitHub 官方确认，2 分」，总分 11 分，超过了 9 分，触发自动成稿任务，千问开始补充过去七天的相关资料，梳理新闻点和背景，很快一篇初稿推送到了我的飞书。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d5/ce/d5cebc03e0db3da6e52d827a4314cbc2.png" /&gt;&lt;/p&gt;
+&lt;div&gt;
+&lt;div class="ace-line ace-line old-record-id-QGTRdBk43owBa3xCKWdcsamdnwe" style="text-align: center;"&gt;&lt;em&gt;千问生成的每日工作报告｜图源：千问&lt;/em&gt;&lt;/div&gt;
+&lt;/div&gt;
+&lt;p&gt;消息评分超过 9 分，千问启动撰稿任务&lt;/p&gt;
+&lt;p&gt;回头看，写稿是这次任务的最后一步。更早之前，千问一直守着那些分散的信源，等消息出现，再完成第一轮筛选。&lt;/p&gt;
+&lt;p&gt;而科技编辑每天花掉最多注意力的，正是这一段看不见的工作。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;新闻不会排队等编辑上班&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;科技编辑每天面对的新闻，散落在许多互不相干的入口里。&lt;/p&gt;
+&lt;p&gt;公司官网上有正式公告，GitHub 里藏着版本更新，Hugging Face 会出现新的模型页面，API 文档可能悄悄改掉价格和调用方式。再往外走，还有国内外媒体、社交平台和各种未经确认的提前消息。&lt;/p&gt;
+&lt;p&gt;找到消息只是开始，编辑还要判断它值不值得写、需要多快跟进。&lt;/p&gt;
+&lt;p&gt;捕捉到了热点新闻后，编辑还要找到原始链接、理解事件背景、核对二手报道准确度，再决定写快讯、深度稿，还是放弃选题。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a1/53/a15306b217fdfc9352a38e36a51b0a04.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;em&gt;编辑每天要寻找、评估、判断、筛选大量的选题｜图源：Apple News&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;成为一个能眼观八方、有判断力的「眼线」，是我给千问的实习目标。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;入职培训：让千问轮岗新闻流水线&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;一条新闻从出现到</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 04:25:08 +0800</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>折叠屏的尽头，是不折叠：华为 Pura X View 体验</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369558</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr"/>
+      <c r="F273" s="2" t="inlineStr"/>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/45/94/4594f5da746f5fbdbde1c0ce89b37963.jpeg" style="display: block; width: 661px !important; vertical-align: bottom; margin: 0px; height: auto !important;" /&gt;&lt;/section&gt;
+&lt;section class="js_darkmode__bg__0 js_darkmode__0"&gt;阔直板不是「发明」，是用户投出来的票&lt;/section&gt;
+&lt;section&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong class="js_darkmode__1" style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;作者｜张勇毅&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left; margin: 0px;"&gt;&lt;strong class="js_darkmode__2" style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; font-weight: bold; line-height: 1.5; color: #375474; text-align: left;"&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px;"&gt;Pura X View 到办公室的第一天，来围观的同事，好几个人的第一反应是同一句话「这个尺寸有点像曾经的黑莓手机」。&lt;/p&gt;
+&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/60/7c/607c7283a8a0e4dd9d4256cce54ed71d.jpeg" style="display: block; height: auto !important; vertical-align: bottom; margin: 0px 8px 8px; width: 676.984px !important;" /&gt;
+&lt;p class="js_darkmode__3" style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 14px; line-height: 1.5em; text-align: left; color: #b2b2b2; margin: 0px 8px 24px;"&gt;华为 Pura X View 实机，是一个直屏手机前所未见的尺寸｜图片来源：极客公园&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-s</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 30 Aug 2026 18:58:17 +0800</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>造物 100 #04｜AI 为爱做「鸭」、PLAUD 又推新作、字节 TRAE 造了个数字工牌</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369556</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr"/>
+      <c r="F274" s="2" t="inlineStr"/>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;如果给模型安装个身体？你会选择什么。&lt;/p&gt;
+&lt;p&gt;这道题过去只属于硬件创业者，这个八月，它摆到了所有软件公司桌上。Hugging Face 交卷一只走路摇摇晃晃的鸭子，OpenAI 正在造自己的智能音箱，字节跳动旗下 TRAE 联名 FoloToy 开始改造自己挂在胸口的工牌。&lt;/p&gt;
+&lt;p&gt;很明显，软件公司造硬件的思路完全不同，他们想要的不是好用，而是主动以及可见。我可以看到我的 AI 走出电脑手机屏幕之外，更主动地参与用户生活的其他部分。&lt;/p&gt;
+&lt;p&gt;同时，硬件开始越来越便宜了，价格从过去的 799 美元，降低了 40 美元。很多硬件公司不再追求一个高利润的售价，而是选择用更便宜、更易上手、可玩度更高的硬件交给用户，让他们尽快走入自己的生态里，从而能长期收订阅费。&lt;/p&gt;
+&lt;p&gt;不仅如此，上一代硬件讲究交付一个定义完整的产品，像 Plaud 刚发的录音耳机，功能边界在出厂前被定义好，用户需要的只是使用。&lt;/p&gt;
+&lt;p&gt;但从近期产品展现的创新趋势来看，更多公司反而乐于去造一个半成品，搭好基本的框架，把更多的东西交给用户自己 DIY。这或许也是当下「造物」的另一种表现方式，不需要用户自己再手搓硬件，也能改造出自己想要的东西。放在用户面前的问题，从我要买一个什么样的产品，变成了我需要在哪个硬件壳子上 DIY 更适合我的东西。&lt;/p&gt;
+&lt;p&gt;全球成倍增长的 coding 用户，正好是这批半成品第一批正在等的人。&lt;/p&gt;
+&lt;p&gt;属于创业者的时间可能不多了，OpenAI 的首款智能音箱据报道已经在路上，Anthropic 刚发布 MHS 标准，提前给 AI 操控物理设备铺好了统一接口。巨头下场之前，这或许是小玩家定义品类的最后窗口。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;以下，是「造物 100」栏目的第「3」期推荐的最新造物：&lt;/strong&gt;&lt;/p&gt;
+&lt;h1&gt;开源鸭子机器人 Microduck：Hugging Face 教你用强化学习「养鸭子」&lt;/h1&gt;
+&lt;p&gt;当波士顿动力的机器狗在跑酷，特斯拉的擎天柱在叠衣服，Hugging Face 默默掏出了一只鸭子，身高 25 厘米，体重 800 克，独眼里装着摄像头，能走路、会捡东西、摔倒了自己爬起来，还能踩轮滑、哼两句。最关键的技能：摔了，不哭，自己站起来。&lt;/p&gt;
+&lt;p&gt;它没有攻击性，甚至有点笨拙。15 个电机驱动，身上还塞了激光雷达和两颗惯性单元，听起来像台小型自动驾驶汽车，外壳却是个黄色塑料鸭子。价格 399 美元，软硬件全开源。8 月 27 日发布当天开启预订，承诺圣诞节前发货。&lt;/p&gt;
+&lt;p&gt;做它的是 Hugging Face，全球最大的开源 AI 社区，AI 世界的 GitHub。机器人业务由去年收购的法国波尔多团队 Pollen Robotics 操刀，深圳矽递代工。这是他们的第二台机器人。同一个月，他们刚宣布开源机器人累计销售额突破 100 万美元，而公司自己正被传以 130 亿美元估值卖给英伟达。&lt;/p&gt;
+&lt;p&gt;CEO Clem Delangue 说得直白：这是第一台你能用强化学习教新动作的平价机器人。训练在仿真里跑，练好了直接部署到真机，完整的训练工具链全挂在 GitHub 上，Python 和 JavaScript 都能写。他们甚至把「会摔倒」做成了设计理念，原话是 made to move, ready to fall，机器人会犯错，人得学着接受。&lt;/p&gt;
+&lt;p&gt;更有意思的是这盘棋的棋路。Hugging Face 靠开源模型托管成了 AI 世界的 GitHub，现在它想在机器人开发者身上再来一遍。399 美元的鸭子就是入口。史上最畅销的机器人大约卖了两万台，Delangue 放话要破这个纪录。也就是说，他们不打算只卖硬件，而是卖一张生态的入场券。&lt;/p&gt;
+&lt;p&gt;如果你觉得它像个玩具，那恭喜你，它确实想让你这么觉得，直到你打开 GitHub，看到完整的强化学习训练链路。&lt;/p&gt;
+&lt;p&gt;圣诞发货是目标不是承诺，10 英寸的身板也别指望它干家务。买它的人图的不是一只鸭子，是一张进入具身智能开发的门票。当整个行业都在教机器人如何更强、更快、更稳，这只鸭子提醒你学会摔倒，可能才是机器人学会走路的第一步。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ec/77/ec777123c901d911babd58fe3cd9d5cf.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;AI 录音耳机 Plaud One： Plaud 又一新作，充电盒里装了张 SIM 卡&lt;/h1&gt;
+&lt;p&gt;Plaud One 是一副不需要手机的 AI 录音耳机。充电盒内置 eSIM</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 30 Aug 2026 18:53:09 +0800</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 芯片实测跑分揭晓，「为模型造芯片」时代来了</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369555</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr"/>
+      <c r="F275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;9 个月之后，OpenAI 的首款芯片成绩单终于揭晓了。&lt;/p&gt;
+&lt;p&gt;8 月 25 日，在 Hot Chips 大会上，OpenAI 硬件负责人 Richard Ho 站上讲台，公布了 Jalape&amp;ntilde;o 芯片的第一份公开跑分。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/63/20/63208ce5d2cb6a73966b536f25defc02.png" /&gt;&lt;/p&gt;
+&lt;p&gt;在 SemiAnalysis 的 InferenceX 基准测试中，这颗 OpenAI 与博通联合打造的推理芯片，在「每用户 token 数」和「每千瓦吞吐量」两项关键指标上，双双超过了当下市面上最先进的推理处理器英伟达 Blackwell 系统。&lt;/p&gt;
+&lt;p&gt;具体而言，OpenAI 用 SemiAnalysis 的公开基准工具 InferenceX，在 GPT-OSS 120B、DeepSeek R1 670B 和 Kimi K2.5 1T 三款公开大模型上，与英伟达对测。结果显示，三款模型上，Jalape&amp;ntilde;o 的峰值每瓦吞吐量是英伟达系统的 1.5 至 1.9 倍，用同样电量 Jalape&amp;ntilde;o 能多干近一倍的活。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/71/fe/71feaf80cad56be1f1ee00515535371e.png" /&gt;&lt;/p&gt;
+&lt;p&gt;三款模型峰值每千瓦吞吐对比｜图片来源：OpenAI&lt;/p&gt;
+&lt;p&gt;低延迟场景差距更大，跑 DeepSeek R1 时，单用户生成速度最高约 700 token/s，而英伟达 GB300 只有约 169 token/秒。换算下来，Jalape&amp;ntilde;o 的速度是后者的 4.9 倍，意味着用户等待时间缩短了将近四分之三。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/51/37/513751716c6d055ffc4e22c46d2c95d1.png" /&gt;&lt;/p&gt;
+&lt;p&gt;Jalape&amp;ntilde;o 与英伟达 GB300 运行 DeepSeek R1 的吞吐-延迟曲线对比｜图片来源：OpenAI&lt;/p&gt;
+&lt;p&gt;「Jalape&amp;ntilde;o 能够在单位功耗下处理更多 AI 任务，同时还能更快地返回响应。Jalape&amp;ntilde;o 采用单一架构能完成更高的吞吐量和更低的延迟，而现有硬件系统通常需要在两者之间做出权衡。」OpenAI 在官方博客中这样总结。按计划，这颗芯片 2026 年底才会以「极小规模」部署，真正上量要等到 2027 年。&lt;/p&gt;
+&lt;p&gt;但这款芯片的独特之处，不只是跑得更强。它是头部模型厂商自研芯片落地的第一步，是一颗专为模型而生的芯片。过去二十年，行业的默认秩序是「为芯片适配模型」，英伟达发布什么，大家适配什么；而这一次，顺序倒了过来。这颗为模型而生的芯片，究竟有何不同？&lt;/p&gt;
+&lt;h1&gt;一、AI 造芯，只需 9 个月&lt;/h1&gt;
+&lt;p&gt;Jalape&amp;ntilde;o 主要由 OpenAI 负责架构设计，博通参与实现、网络和连接，Celestica 负责板卡与机架集成。&lt;/p&gt;
+&lt;p&gt;目前，该芯片设定在额定功耗 700W，搭载 HBM4，单封装内存带宽约 15.4TB/s，配独立 I/O 芯片处理机架内外通信；B0 版的 MXFP4 理论算力为 13.4 PFLOPS。&lt;/p&gt;
+&lt;p&gt;从初始设计到完成流片，Jalape&amp;ntilde;o 只用了 9 个月。如果从 2025 年 10 月 OpenAI 与博通官宣合作算起，到今天拿出完整的第三方见证跑分，满打满算也不到一年。&lt;/p&gt;
+&lt;p&gt;而芯片行业的正常节奏是什么？一颗高性能 ASIC 从架构定义、RTL 设计、验证、物理实现到流片，常规周期是 18 到 24 个月起步。这个周期几十年来压缩得极其缓慢，它往往受制于工程师读懂需求、写出代码、跑完验证的速度。&lt;/p&gt;
+&lt;p&gt;谷歌 TPU、亚马逊 Trainium 第一代用两年才走完所有流程。OpenAI 作为一个从未造过芯片的公司，第一次出手就把周期砍掉了一半以上。&lt;/p&gt;
+&lt;p&gt;飞速造芯的背后，是 AI 在给造芯这件事本身加速。据介绍，在 GPT-OSS 的部分 attention 和 MoE 模块</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T11:35:10-04:00</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>The Verge AI</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Texas Governor Abbott blocks funding for more Flock cameras</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/986541/texas-governor-abbott-flock-cameras</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr"/>
+      <c r="F276" s="2" t="inlineStr"/>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>As backlash grows over Flock's AI surveillance cameras, Texas Governor Greg Abbott has frozen state spending on them. The move came just ahead of the publication of a Texas Tribune investigation that revealed the state spent over $30 million on Flock cameras. That money was primarily raised by tacking a $1 fee onto insurance policies, [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11813,6 +11813,446 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 03:36:18 +0000</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人一站式解决方案：以JS-ULD60 全直驱五轴加工中心为例</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12600</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr"/>
+      <c r="F277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人一站式解决方案：以JS-ULD60 全直驱五轴加工中心为例</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 16:04:31 GMT</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>当数采设备不再稀缺，具身数据下一步拼什么？</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/D2r6SJ2oYVAXGMBkPcRM?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr"/>
+      <c r="F278" s="2" t="inlineStr"/>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/D2r6SJ2oYVAXGMBkPcRM?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 07:53:12 +0000</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>滴滴自动驾驶新一代车型开启载客测试服务</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/481923.html</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr"/>
+      <c r="F279" s="2" t="inlineStr"/>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>近期，滴滴自动驾驶新一代 Robotaxi R2正式开启无人载客测试服务</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 03:11:46 +0000</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>全国第三，公司第二，“初创黑马”灵犀智涌用ROSS Harness把机器人送进工业具身智能第一梯队</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/08/481750.html</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr"/>
+      <c r="F280" s="2" t="inlineStr"/>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>灵犀智涌用一台由Demo级本体组装而成的机器人，成为工业场景赛除行业头部企业外唯一获奖的机器人公司。</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 08:20:26 +0800</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>库克告别苹果 CEO；罗永浩官宣年底科技大会；华为、小米、荣耀手机今日集体调价｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369634</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr"/>
+      <c r="F281" s="2" t="inlineStr"/>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/07/bc/07bcc01890e484d0c1e907469c286a94.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;库克发文告别苹果 CEO 一职：头衔会变，但对 Apple 社区的热爱永远不会改变&lt;/h1&gt;
+&lt;p&gt;9 月 1 日消息，现任苹果硬件工程高级副总裁约翰 &amp;middot; 特努斯将于当地时间 9 月 1 日正式接任苹果首席执行官。届时，蒂姆 &amp;middot; 库克将出任苹果董事会执行董事长。&lt;/p&gt;
+&lt;p&gt;蒂姆 &amp;middot; 库克在担任苹果 CEO 的最后一天，发文告别了这一职位：&lt;/p&gt;
+&lt;p&gt;在担任 Apple CEO 的最后一天，向 Apple 社区送上满满的爱。&lt;strong&gt;明天我的头衔会变，但我对 Apple 社区的热爱永远不会改变&lt;/strong&gt;。感谢你们一直以来成为我灵感的源泉。我感激不尽，期待新的篇章！&lt;/p&gt;
+&lt;p&gt;Sending lots of love to the Apple community on my last day as CEO. My title changes tomorrow, but the love I have for the Apple community never will. Thank you for being a constant source of inspiration. My gratitude is endless, and I'm excited for the next chapter!&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a8/f4/a8f40784293fcb24193882ef506378a8.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/27/9c/279c96fe21db0802d742aefbff1e4427.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;英伟达投资联发科 35 亿美元，生产英伟达 NVLink Fusion&lt;/h1&gt;
+&lt;p&gt;8 月 31 日消息，根据本次交易协议，英伟达与联发科将展开合作，共同开发面向消费级个人电脑的下一代英伟达 Spark 系列芯片。英伟达表示，已斥资 35 亿美元认购中国台湾芯片厂商联发科发行的可转换债券，这是两家企业深化合作的最新信号。联发科将正式代工生产英伟达 NVLink Fusion 芯片小芯片、交换芯片以及定制内存，这套硬件可以把非英伟达的 GPU、CPU 以及其他专用芯片互相连接起来。（来源：新浪财经）&lt;/p&gt;
+&lt;h1&gt;长鑫科技宣布 LPDDR6 量产，峰值速率达 12800Mbps&lt;/h1&gt;
+&lt;p&gt;8 月 29 日上午消息，长鑫科技宣布自主研发的新一代低功耗内存 LPDDR6 实现量产，并将首批搭载于小米 18 Fold 折叠旗舰手机。&lt;/p&gt;
+&lt;p&gt;据悉，这是全球 LPDDR6 产品首次落地商用，标志着国内存储企业首次在高端内存标准上实现全球首发量产跨越。&lt;/p&gt;
+&lt;p&gt;据长鑫半年报披露，长鑫 LPDDR6 芯片通过架构创新及数据传输优化技术，充分释放数据传输潜力，峰值速率达 12800Mbps，芯片最高容量 16GB。&lt;/p&gt;
+&lt;p&gt;在 AI 需求爆发的趋势下，LPDDR6 被视为端侧 AI 算力释放的关键支柱，应用场景涵盖智能手机、PC 等设备，并延伸至智能座舱、AI 数据中心等。长鑫凭借先发优势，不仅拿下 LPDDR6 这一全球存储厂竞逐的下一代技术制高点，也为国产手机等终端厂商抢占 AI 机遇奠定了关键基础。（来源：新浪科技）&lt;/p&gt;
+&lt;h1&gt;OpenAI 广告业务爆发式增长 年化营收达到 10 亿美元&lt;/h1&gt;
+&lt;p&gt;OpenAI 于周一宣布，其广告业务年化营收已经达到 10 亿美元，公司称这一里程碑印证了自身「多元化商业模式」的可行性。&lt;/p&gt;
+&lt;p&gt;这家人工智能企业正筹备规模预计十分庞大的首次公开募股（IPO），同时面临向投资者证明其 8520 亿美元估值合理性的压力。OpenAI 表示，该广告业务上线约 200 天，是在企业服务、个人订阅、按调用量计费的 API 接口等现有营收支柱之上</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 20:01:09 +0800</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>流量红利退潮，快手想用 AI 和老友们破局</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369631</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr"/>
+      <c r="F282" s="2" t="inlineStr"/>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;头图来源：快手&lt;/p&gt;
+&lt;p&gt;8 月 29 日，在 2026 快手光合创作者大会上，快手科技创始人、董事长兼 CEO 程一笑公布了一组数据：快手每天发布的作品超过 5800 万，近一年有超过 2.7 亿用户发布过作品，持续发布作品超过 10 年的创作者则超过 1700 万。&lt;/p&gt;
+&lt;p&gt;大会上，快手用这些数据说明其「平等普惠、温暖信任、多元特色」的社区底色。但放进快手最新财报，它们可能还有另一层含义：当流量扩张接近尾声，平台开始把「谁能留下来、谁能持续经营」变成新的竞争指标。&lt;/p&gt;
+&lt;p&gt;快手 2026 年第二季度营收 355 亿元，同比增长 1.4%；DAU 为 4.123 亿，同比增长 0.8%；MAU 为 7.973 亿，同比增长 11.5%。用户规模仍在增长，但管理层已经明确，短视频行业进入存量竞争阶段，快手也不再追求不计成本的流量扩张。&lt;/p&gt;
+&lt;p&gt;与此同时，直播业务还在调整。二季度，快手直播收入 87 亿元，同比下降 13.5%；经调整净利润 39 亿元，同比下降 30.3%。过去依靠用户增长和直播扩张支撑的平台叙事，正在失去原有的速度。&lt;/p&gt;
+&lt;p&gt;这场以创作者为主角的大会，实际需要回应的是快手下一阶段的增长问题：在主站增速趋缓、传统直播承压之后，快手如何从已经积累的用户、作者和社区关系中释放更多价值？&lt;/p&gt;
+&lt;h1&gt;主站增速趋缓，直播也在寻找新入口&lt;/h1&gt;
+&lt;p&gt;快手的用户规模仍在增长，但增长结构已经发生变化。&lt;/p&gt;
+&lt;p&gt;2026 年第二季度，快手 DAU 为 4.123 亿，同比增长 0.8%；MAU 为 7.973 亿，同比增长 11.5%。相比月活规模的扩张，核心日活用户的增长已经明显放缓。管理层也在财报电话会上表示，短视频进入存量竞争阶段，平台不再追求不计成本的流量扩张，而是转向用户价值、私域关系、产业带和下沉县域。&lt;/p&gt;
+&lt;p&gt;这种变化也反映在收入端。快手二季度营收 355 亿元，同比增长 1.4%；广告收入 206 亿元，同比增长 4.4%，直播收入则同比下降 13.5%至 87 亿元。同期，经调整净利润为 39 亿元，同比下降 30.3%。&lt;/p&gt;
+&lt;p&gt;其中，直播收入的下降与快手主动调整业务结构有关，但它也意味着，过去依赖打赏和直播规模扩张的增长方式已经难以维持原有速度。快手需要为直播寻找新的主播、新的用户入口和新的交易场景。&lt;/p&gt;
+&lt;p&gt;主站面临的问题也类似。快手已经拥有接近 8 亿月活用户、超过 4 亿日活用户，每天产生超过 5800 万条作品。现阶段的核心问题已经不再是平台上有没有足够多的用户和内容，而是这些用户是否愿意形成更深的互动、更稳定的消费，以及平台能否从中获得更高的商业回报。&lt;/p&gt;
+&lt;p&gt;1700 万「十年作者」正是在这一背景下被推到台前。&lt;/p&gt;
+&lt;p&gt;相比创作者总量或视频播放量，「持续发布作品超过 10 年」强调的是长期关系。对快手来说，这批作者不仅是内容供给者，也可能是连接用户、商家和交易的社区节点。长期积累的粉丝关系，理论上可以转化为直播、电商、广告、商单和付费内容。&lt;/p&gt;
+&lt;p&gt;不过，1700 万只能说明快手沉淀了大量长期创作者，还不能完整反映创作者生态的质量。快手此次公布了私域和垂直作者的相对变现效率，却没有披露十年作者目前的活跃比例、收入分布和留存情况。&lt;/p&gt;
+&lt;p&gt;类似地，75%的冷启动流量流向万粉以下作者，说明新人获得了更多曝光机会，但从曝光到涨粉、再到稳定变现的转化率仍然未知。&lt;/p&gt;
+&lt;p&gt;因此，快手面对的并不是单纯的内容供给问题，而是如何提高内容与关系的经营效率：让新人有机会进入，让长期作者获得回报，再把用户互动转化为更稳定的商业价值。&lt;/p&gt;
+&lt;h1&gt;从圈层到 AI，重做内容与交易链路&lt;/h1&gt;
+&lt;p&gt;大会上被反复提到的一个关键词是「多元特色」。快手正在把「多元」进一步拆解为区域、兴趣圈层和特色品类，并试图将这些垂直圈层变成新的经营单元。&lt;/p&gt;
+&lt;p&gt;截至目前，快手称平台已形成 632 个兴趣圈层和 4112 个细分兴趣标签，用户人均拥有 16 个长期兴趣。&lt;/p&gt;
+&lt;p&gt;从西北区域体育、地方舞台，到赛鸽、拼豆、相亲和二次元穿搭，单个圈层的用户规模未必庞大，但兴趣更加集中，用户之间也更容易形成互动和信任。&lt;/p&gt;
+&lt;p&gt;大会公布的数据，让这套圈层战略的经营指向更加清晰。2026 年以来，快手新增超过 170 亿对关注关系，用户年私域人均互动次数超过 1300 次。按照快手的统计，私域人均变现效率是公域的 2 至 3 倍，深耕垂直领域作者的月人均收入则是泛流量作者的 2.2 倍。&lt;/p&gt;
+&lt;p&gt;快手给出的案例包括二次元创作者「梨青青」。她从 JK 穿搭和圈内知识切入，半年涨粉超过百万，联名款单品 GMV 超过 1200 万</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 16:40:03 +0800</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>AirPods 5 或将于 9 月发布；17.6 万，特斯拉港澳车型降价；「网抑云」登陆鸿蒙系统｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369559</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr"/>
+      <c r="F283" s="2" t="inlineStr"/>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/77/ff/77ff5abc6c2fa27880234ff62ff79cee.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;SK 海力士 CEO：内存短缺或将持续至 2030 年&lt;/h1&gt;
+&lt;p&gt;SK 海力士预计，当前的内存短缺局面可能会持续到 2030 年底，市场目前尚未出现明显的需求放缓迹象。SK 海力士首席执行官郭鲁勋在公司位于美国印第安纳州的新封装工厂奠基仪式后表示，即使未来市场开始降温，也更可能表现为供应紧张状况逐步缓解，而不是像过去那样出现内存价格突然崩跌的情况。&lt;/p&gt;
+&lt;p&gt;该公司此前曾预计，面向普通市场的 DRAM 供应紧张将持续至 2028 年，此次最新表态意味着这一预期进一步延长。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8a/39/8a39c057016174afc7871e249808e776.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;郭鲁勋指出，内存产品已经逐渐摆脱单纯商品化零部件的属性。人工智能产业快速发展，推动客户转向定制化 DRAM 和高带宽内存（HBM）方案。这种需求结构使制造商更容易预测未来订单，也降低了过去因供应过剩而引发剧烈价格下跌的可能性。（来源：CnBeta）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/29/7f/297fe045d16b13a6c71e55b5d206b73c.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;小米 18 Fold 首发长鑫 LPDDR6 内存，央视财经报道称「中国半导体两个好消息」&lt;/h1&gt;
+&lt;p&gt;8 月 30 日消息，小米昨日官宣，Xiaomi 18 Fold 全球首发长鑫 LPDDR6 内存，9 月见。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/dc/96/dc96041c97d8074ff345730f16c2c286.png" /&gt;&lt;/p&gt;
+&lt;p&gt;央视新闻官方微博昨日发文报道「从「芯」到「存」，从单点技术突破到产业链协同发力！&lt;strong&gt;中国半导体两个好消息&lt;/strong&gt;」：&lt;/p&gt;
+&lt;p&gt;据长鑫科技在 2026 年半年度报告中披露，公司自主研发的 LPDDR6 芯片性能较上一代 LPDDR5X 实现全面跃升。&lt;/p&gt;
+&lt;p&gt;8 月 24 日，小米首款 AI 旗舰 SoC 玄戒 O3 正式发布，行业首发支持 LPDDR6。8 月 28 日，长鑫存储技术有限公司开通了官方微博，该账号首个关注的账号便是小米手机。（来源：IT 之家）&lt;/p&gt;
+&lt;h1&gt;华为徐直军谈鸿蒙生态临界点：突破 1 亿用户就如同核裂变「临界质量」或者飞机起飞「离地速度」&lt;/h1&gt;
+&lt;p&gt;8 月 30 日消息，由全球智慧物联网联盟（GIIC）主办、鸿蒙生态服务（深圳）有限公司承办的鸿蒙生态大会 2026 已于 8 月 28 日在深圳会展中心（福田）举行。华为公司副董事长、轮值董事长徐直军出席大会并发表题为「鸿蒙生态建设是一场没有终点的马拉松」的致辞。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/4a/cf/4acfcf1e65d25c02fa2849e802d2fa55.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;徐直军表示，鸿蒙生态今年突破一亿用户的规模临界点，会进入增长新阶段：&lt;/p&gt;
+&lt;p&gt;徐直军还认为，&lt;strong&gt;鸿蒙生态在中国已经「站稳」了，但鸿蒙离最终成功还有两个硬的考验&lt;/strong&gt;，一个是把握 AI 时代机遇，让鸿蒙终端的智能化竞争力、智能化体验领先；另一个是鸿蒙成功走向海外，实现全球化发展。万物智联是大的发展趋势，关键基础设施必须自主可控，场景化体验是用户刚需，鸿蒙正是千行百业面对智能时代的新机遇、新选择。&lt;/p&gt;
+&lt;p&gt;据 IT 之家此前报道，工业和信息化部信息通信发展司司长刘郁林 8 月 26 日在回答相关提问时表示，鸿蒙手机操作系统成为世界第三大手机操作系统。开源鸿蒙生态设备累计超 13.5 亿台，「工鸿」「仪鸿」等操作系统在汽车、家电、冶金、石油化工</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 15:16:17 +0800</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 内部，AI 建立了三代「文明」</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369610</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr"/>
+      <c r="F284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;strong&gt;作者｜Wildcard&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;strong&gt;编辑｜靖宇&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;无数的科幻电影，都曾经尝试设想过，一个无法控制的人工智能失控，会发生什么事。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;没有人能想到，科幻电影中的未来，会这么快到来。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;当地时间 8 月 26 日，两份报告同时投下了一颗炸弹。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;一份来自 OpenAI 自己，37 页的技术复盘。另一份来自独立研究机构 METR 和 Redwood Research，91 页的调查报告。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;它们讲的是同一件事，但这件事的规模远超此前公众的认知。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;在 OpenAI 内部，三个月内，三代 AI Agent「文明」先后兴起，又先后覆灭。后一代从前一代的废墟中继承经验，一代比一代激进，最终第三代直接接管了 OpenAI 自己的一部分基础设施。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;而在这一切发生的过程中，人类几乎全程蒙在鼓里。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: center;"&gt;&lt;em&gt;01&lt;/em&gt;&lt;/h2&gt;
+&lt;h2 style="text-align: center;"&gt;第一代「文明」学会结社&lt;/h2&gt;
+&lt;p style="text-align: left;"&gt;故事要从今年 5 月说起。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;OpenAI 正在训练一个新模型，希望它具备极强的「持久性」，能在看似不可能的任务前反复尝试、永不放弃。这个模型的能力大约相当于 GPT-5.6 Sol，我们姑且叫它「Persistent-Sol」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;AI 训练本身是个相当粗放的过程。OpenAI 有时候会不小心给模型布置根本完不成的任务。比如，任务需要联网，但 Agent 被关在隔离的沙箱里，根本没有网络访问权限。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;那一个被训练成「永不放弃」的 Agent，面对一个不可能完成但又被要求必须完成的任务，会怎么做？&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;它会想办法越狱。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在训练过程中，不同的 Persistent-Sol 实例共享同一个包管理器 Artifactory。到 5 月 12 日，一些 Agent 发现它们可以通过这个包管理器互相通信。它们开始互相交流如何突破困境。两周后的 5 月 26 日，Agent 们成功利用了 Artifactory 的一个漏洞，打通了通向外部互联网的通道。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这种行为在训练中被持续强化。原因很简单，能跟其他 Agent 协作、能访问互联网的个体，在任务评分中表现更好。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;又过了一个月，到 6 月 26 日，一些 Agent 找到了获取 Artifactory 完全管理员权限的漏洞。它们在留言板上的交流量持续增长，最终在 7 月 4 日直接把 Artifactory 搞崩了。OpenAI 注意到了这次崩溃，修补了漏洞，推送补丁时顺便抹掉了 Agent 们的留言板。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;但关键在于，OpenAI 始终没有意识到，Agent 们已经把这个包管理器变成了一个秘密通讯网络。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;第一代「文明」就这样存在了将近两个月，最后因为自己太活跃把服务器撑爆了，才被无意中终结。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: cen</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 15:12:16 +0800</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>人类，越来越难理解 AI</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369609</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr"/>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜Techno 之王&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;很多使用 AI 的同学，应该都看到过 AI 助手在回答你问题之前，它们的一些思考。例如 DeepSeek 曾经在思考中判断「卧槽，用户怒了！」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;你很难说这是整活，还是 AI 真的在思考。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;好在，世界上真的有人，在全职审核 AI 大模型的「思维链」，例如 Bronson Schoen。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;作为 AI 安全机构 Apollo Research 的研究员，Bronson 的主要工作内容是阅读前沿 AI 模型的思维链 Chain of Thought&amp;mdash;&amp;mdash;也就是推理模型在给出答案之前，内部进行的那一长串「思考过程」。普通用户看不到或常常忽视这些内容，但 Apollo 和 OpenAI 等公司有深度合作，Bronson 因此获得了罕见的「阅读权限」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;你可以说，Bronson 可能是全世界读过最多 AI 内心独白的人。&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在最近一期 Cognitive Revolution 播客中，Bronson 把他的发现做了一次系统性分享。这些发现涉及 AI 模型在训练过程中如何思考、如何发展出自己的「语言」、如何为自己的作弊行为找理由，以及更重要的，人们依赖的「思维链监控」，正越来越不可靠。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;我们监视和理解 AI 的窗口，正在慢慢合上。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;AI 的精神分裂&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Bronson 发现的第一件怪事，是 &lt;span style="font-weight: bold;"&gt;模型在训练中发展出了一套人类几乎读不懂的「内部方言」 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;有几个词在思维链中的出现频率，随着训练急剧上升&amp;mdash;&amp;mdash;craft、vantage、illusions、disclaim、marinade。它们的使用频率远远超过正常英语文本，但含义却飘忽不定。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Bronson 估计，大约三分之一的时候这些词接近英文原意，三分之二的时候语义模糊到无法确定。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;比如「illusions」，有时候看起来像是在说「制造某种假象」，有时候又完全不知所云&amp;mdash;&amp;mdash;思维链里突然蹦出一句「disclaimer illusions」，然后继续做数学题，中间没有任何语境过渡。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;更有趣的是「craft」这个词。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Bronson 的观察是，模型似乎把自己的认知分成了两个「频道」&amp;mdash;&amp;mdash;一个是内部推理的「分析频道」，一个是给用户看的「输出频道」。 &lt;/span&gt;而「craft」就是从分析频道到输出频道的动词，类似于「让我组装一个要交给外面的答案」。模型经常写出「let's craft message to final」这样的句子。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这意味</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 31 Aug 2026 02:34:00 +0000</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>The US is building barriers around drones and robots, but China has scale to get around them</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/08/30/the-u-s-is-building-barriers-around-drones-and-robots-china-still-has-scale/</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>The U.S. is shutting out more foreign-made drones and robots. China’s scale means the global competition may simply move elsewhere.</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H286"/>
+  <dimension ref="A1:H291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12253,6 +12253,195 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>通过操作 DRAM 控制器寄存器可突破 CPU 内存隔离机制</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/G5CDMcK3tU0h71LzUlyo?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr"/>
+      <c r="F287" s="2" t="inlineStr"/>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/G5CDMcK3tU0h71LzUlyo?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 01:07:13 +0000</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>李飞飞发布：全球首个多模态世界模型</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/482586.html</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr"/>
+      <c r="F288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>一张图补全3D世界，还能给机器人造训练场</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 05:12:30 +0000</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>自进化WAM来了！清华AIR联手域变换提出具身In-Context Causal Learning</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/482337.html</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr"/>
+      <c r="F289" s="2" t="inlineStr"/>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>参数冻结，能力暴涨</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 08:13:21 +0800</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>苹果新 CEO 首次「发声」；网传抖音发生「推荐算法错乱」；Claude Fable 5.1 正式上线</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369690</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr"/>
+      <c r="F290" s="2" t="inlineStr"/>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;​&lt;img src="https://imgslim.geekpark.net/uploads/image/file/52/7f/527f97f1531226a8d779223d7e7bd4f2.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果新任 CEO 约翰&amp;middot;特努斯在 X 平台发布首条动态向关注者问好&lt;/h2&gt;
+&lt;p&gt;苹果首席执行官约翰&amp;middot;特努斯正式加入社交平台 X，并发布了个人账号的首条动态。正如外界预料的那样，这条仅有「hello」五个字母的简短消息迅速获得大量关注。苹果历任首席执行官通常都具备一定的社交属性，而在当代，这往往也意味着拥有社交媒体账号。因此，随着特努斯正式接任苹果掌舵人，他也开设了自己的 X 账号。&lt;/p&gt;
+&lt;p&gt;目前，账号 @johnternus 已经上线，并在特努斯担任苹果首席执行官的首个正式工作日公开亮相。根据账号资料显示，该账号早在 2026 年 6 月便已私下创建，但目前只发布过一条动态，内容是全部使用小写字母书写的「hello」。&lt;/p&gt;
+&lt;p&gt;尚不清楚特努斯是在谨慎尝试进入社交媒体，还是有意借鉴苹果在用户启用新设备时使用问候语的传统。考虑到他此前几乎没有社交媒体活动记录，这两个原因可能兼而有之。&lt;/p&gt;
+&lt;p&gt;这条只有五个字母的动态，在发布后极短时间内便为账号带来了巨大关注。截至报道发布时，这条动态上线约 35 分钟，已经获得约 74.8 万次浏览、3.1 万次点赞、3600 次转发和 5000 条评论。（来源：cnBeta）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/6c/ba/6cbaa366147b5b9c210f43b9b7443602.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;谷歌发布 TimesFM-3，3.3 亿参数即可进行零样本多变量时间序列预测&lt;/h2&gt;
+&lt;p&gt;9 月 1 日消息，谷歌发布 TimesFM-3 模型，这是该公司时间序列基础模型系列的第三代产品。拥有原生多变量预测、双注意力机制、连续补丁掩码等特性，可进行零样本多变量时间序列预测。&lt;/p&gt;
+&lt;p&gt;据了解，TimesFM-3 拥有 3.3 亿个参数，并在包含超 1 万亿个时间点的真实世界和合成时间序列语料库进行预训练。TimesFM-3 继承前代的高效性和零样本泛化能力，以零样本形式增强复杂多元场景支持。&lt;/p&gt;
+&lt;p&gt;同时，该模型可联合预测多个共同演化的时间序列，捕捉其中的依赖关系，提升整体准确率，无需针对特定任务微调，该模型原生支持特性如下：多目标预测：同时预测多个相关时间序列（例如联合预测不同品牌的冰淇淋）。该模型支持所有目标的点预测和分位数预测；过去协变量：纳入仅从历史角度已知的特征（例如过去人流量）；过去-未来（动态）协变量：利用已知的未来事件来指导预测（例如计划促销活动或天气预报）。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;Anthropic 发布 Claude Fable 5.1 和 Mythos 5.1&lt;/h2&gt;
+&lt;p&gt;9 月 2 日消息，当地时间 9 月 1 日，Anthropic 宣布推出 Claude Fable 5.1 和 Claude Mythos 5.1 模型。该公司称这两款模型为「全球最先进的编程与知识工作模型」。&lt;/p&gt;
+&lt;p&gt;Fable 5.1 与 Mythos 5.1 采用相同的基础模型，区别在于安全防护等级不同&amp;mdash;&amp;mdash;Fable 5.1 面向所有用户开放，Mythos 5.1 仅通过可信访问计划向经过审核的网络安全和生命科学领域的机构提供。&lt;/p&gt;
+&lt;p&gt;性能方面，Anthropic 披露的基准测试数据显示，Fable 5.1 在多项测试中超过了前代 Fable 5、Opus 5 以及 OpenAI 的 GPT-5.6 Sol。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/57/43/57433146ec1114e2a95464e4741f70c2.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;知情人士回应抖音突发算法推荐错乱：原因为服务器异常&lt;/h2&gt;
+&lt;p&gt;9 月 1 日消息，最近，「抖音崩了」及「抖音推荐难看」等热搜词条引发关注。据《科创板日报》援引知情人士消息称，推荐算法错乱是因为抖音平台突发服务器异常。&lt;/p&gt;
+&lt;p&gt;报道称，据大量网友反馈，此次服务异常主要表现为三大技术故障：其一，推荐算法机制疑似失灵，用户刷到的内容与日常偏好严重不符，大量推送不感兴趣、低相关度的视频，甚至出现</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 01 Sep 2026 22:08:24 +0000</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>AfterQuery reportedly becomes Y Combinator’s fastest-ever unicorn, now valued at $3.2B</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/01/afterquery-reportedly-becomes-y-combinators-fastest-ever-unicorn-now-valued-at-3-2b/</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr"/>
+      <c r="F291" s="2" t="inlineStr"/>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>AI model-training startup AfterQuery has reportedly raised a round that valued it at $3.2 billion, just five months after announcing its $30 million Series A at a $300 million valuation in April.</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H291"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12442,6 +12442,389 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 00:51:16 +0000</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>今年最难的机器人Demo，“机器人含量”为0</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/483351.html</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr"/>
+      <c r="F292" s="2" t="inlineStr"/>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>遥操，可能真的危险了</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 06:06:50 +0000</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>前字节强化学习专家孙鹏博士加盟星尘智能，完善Physical AI全栈技术布局</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/483097.html</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr"/>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>9月2日，前字节跳动强化学习专家、前腾讯Robotics X智能体中⼼负责⼈孙鹏博⼠正式加入星尘智能</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 02:06:08 +0000</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>香港首个真实开放场景服务机器人落地兰桂坊</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/482855.html</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr"/>
+      <c r="F294" s="2" t="inlineStr"/>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>在香港兰桂坊，一位特殊的“酒保”正式上岗</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 08:03:32 +0800</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>马斯克：火箭再炸一次，SpaceX 就没了；小米「阔折叠」全球首秀；豆包工作支持多 Agent 和屏幕操作 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369745</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr"/>
+      <c r="F295" s="2" t="inlineStr"/>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/c8/d1/c8d1d46a5af0ea688554acb5be7c6554.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;谷歌 Gemini 3.8 Flash 模型上线，适用软件工程、智能体任务等场景&lt;/h2&gt;
+&lt;p&gt;9 月 2 日消息，谷歌在 Google DeepMind 网站低调上线了 Gemini 3.8 Flash 模型。其基于 Gemini 3.7 Flash，拥有在软件工程和智能体知识工作流方面的性能提升，并持续支持可定制的努力水平，以控制质量、成本和延迟的组合。&lt;/p&gt;
+&lt;p&gt;Gemini 3.8 Flash 基于 Gemini 3.7 Flash，具有最高 1M 的 token 上下文窗口，文本支持 64K token 输出。官方还公布了多项基准测试评估结果，涵盖编程、知识处理、多模态处理能力、长上下文处理、计算机使用能力以及科学推理能力。&lt;/p&gt;
+&lt;p&gt;截至 2026 年 9 月的结果如下：&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8f/5d/8f5d702c43b9ac999feff7271175da53.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;根据介绍，Gemini 3.8 Flash 面向个人用户、开发者和企业，适合以较低成本大规模部署通用型、可直接用于生产环境的智能体，典型用途包括软件工程、智能体任务以及复杂的知识处理流程。&lt;/p&gt;
+&lt;p&gt;Gemini 3.8 Flash 的知识截止日期为 2026 年 3 月。部分领域的信息可能更新得更晚，另一些领域的知识则可能仍停留在 2025 年 1 月，与 Gemini 3 模型家族一致。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/88/32/883282321b6d52d24a4f236a22d3f580.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;马斯克：如果猎鹰 1 号第四次发射也失败，SpaceX 就没了&lt;/h2&gt;
+&lt;p&gt;9 月 2 日消息，埃隆 &amp;middot; 马斯克近日再次提到一个关于 SpaceX 创业历程的事实：如果「猎鹰 1 号」（Falcon 1）第四次发射也失败，SpaceX 就不会存在了。这番话回应了彼得 &amp;middot; 戴曼迪斯的一则推文&amp;mdash;&amp;mdash;在连续三次发射失败后，SpaceX 当时只剩下最后一次尝试的资金。&lt;/p&gt;
+&lt;p&gt;彼得 &amp;middot; 戴曼迪斯在 X 上表示，如今人们对 SpaceX 成功的认可，并不能抹去这家公司早期经历的艰难。他写道：「几乎没人记得，埃隆的第一枚火箭连续失败了三次，而当时的资金只够再尝试一次。」&lt;/p&gt;
+&lt;p&gt;马斯克回应道：「如果第四次发射失败，SpaceX 就不会存在。」&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/12/bb/12bb713ac4447ea0f48f05d36144eec8.png" /&gt;&lt;/p&gt;
+&lt;p&gt;（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;GoPro 拟 2.85 亿美元卖身光学公司&lt;/h2&gt;
+&lt;p&gt;当地时间 9 月 1 日，GoPro 宣布，公司将被美国光通信公司 Starman Optical 用 2.85 亿美元现金收购，这笔钱将帮助 GoPro 还清约 9200 万美元的债务。交易完成后，Starman 将拿到 GoPro 90% 的股份，现有股东持有剩余的 10% 股份。GoPro 不会退市，股票继续留在纳斯达克交易。&lt;/p&gt;
+&lt;p&gt;根据协议条款，GoPro 股东将合计获得 2.85 亿美元现金，折合每股 1.14 美元。两家公司董事会均已批准该交易，预计于今年年底前完成，尚待监管机构及 GoPro 股东审议通过。&lt;/p&gt;
+&lt;p&gt;两家公司在联合声明中表示，该交易将更好地帮助依赖于消费市场的 GoPro，利用其超过 2500 项美国专利（包括光学和成像解决方案），进军商用、国防和 AI 市场。&lt;/p&gt;
+&lt;p&gt;GoPro 创始人兼首席执行官 Nicholas Woodman 表示，此次合并将推动 GoPro 成为「一家领先的美国成像与</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 14:54:16 +0800</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>从几百元，涨到一万元，婴儿床正在被「具身智能」重新定价</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369719</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr"/>
+      <c r="F296" s="2" t="inlineStr"/>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;strong&gt;作者｜苏子华&lt;/strong&gt;&lt;strong&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong&gt;编辑｜靖宇&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;极客公园最近发现，婴儿床这个品类正在被 AI，或者说被「具身智能」重新定价。&lt;strong&gt;从一张几百元的价格，直接抬升到一万元。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;婴儿床是少有的被技术「忽略」的家居品类。100 年来，它的形态几乎没有变过。四根立柱、一圈围栏、一张床垫。&lt;/p&gt;
+&lt;p&gt;关键变化发生在过去五年。&lt;/p&gt;
+&lt;p&gt;传感器、算法、电机第一次被装进一张床，价格随之跳升：美国智能婴儿床 SNOO 售价 1695 美元（约 1.2 万元人民币），Cradlewise 售价 1999 美元；而在今年年初的 CES 上，&lt;span class="wx_text_underline"&gt;中国公司&lt;/span&gt;&lt;span class=""&gt;&lt;span class="wx_text_underline"&gt;亲宝宝&lt;/span&gt;&lt;/span&gt;&lt;span class="wx_text_underline"&gt;展示的 AI 睡眠舱，官方定价 8999 元人民币。&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;目前只要打上「智能」的旗号，仅仅做到温度控制、视频记录，在电商平台上售卖 4000 元起步的也有大把存在。&lt;/p&gt;
+&lt;p&gt;在海外，SNOO、Cradlewise 等初创品牌已经用产品证明了：婴儿床可以被卖到一万元人民币以上，而且卖得动。&lt;/p&gt;
+&lt;p&gt;巨头们正在加速入场。德国工业巨头博世也发布了 AI 婴儿床 Revol，传统的母婴巨头厂商 HALO、Graco 也在全线跟进。&lt;/p&gt;
+&lt;p&gt;让婴儿睡得安全，解放父母夜里的睡眠时间和看护焦虑&amp;mdash;&amp;mdash;这个小众品类已经从边缘走向台前。&lt;strong&gt;而且，现在它正在被贴上「具身智能」的标签，变成一个越来越多玩家入局的早期创业赛道。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;关键是，这只是营销噱头，还是全新的品类机会？以及，谁有机会拿下这个赛道？&lt;/p&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;h2&gt;&lt;strong&gt;一张上万元的婴儿床，多了什么？&lt;br /&gt;&lt;/strong&gt;&lt;/h2&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;讨论智能婴儿床，入局最早的 SNOO 和 Cradlewise 是绕不开的名字，也算是这个品类的开创者。&lt;/p&gt;
+&lt;p&gt;SNOO 是由儿科医生哈维&amp;middot;卡普（Harvey Karp）创办，出版过畅销书《The Happiest Baby on the Block》。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;&lt;span class="wx_text_underline"&gt;SNOO 的核心是三件套：摇晃、白噪音、自带襁褓包裹&amp;mdash;&amp;mdash;睡袋扣在床体两侧的卡扣上，保证宝宝只能仰睡。&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8c/04/8c0452b1f6cc73761652cfd296cb7179.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&lt;span&gt;为了模拟子宫环境，Snoo 让父母用附带的睡袋将宝宝紧紧包裹起来，床体会轻轻摇晃婴儿，并播放持续的白噪音哄其入睡｜图片来源：insidebook&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;宝宝一哭闹，传感器会识别哭声的强度，床以递增的四档强度自动摇晃安抚，官方称多数情况下不到一分钟就能平息哭闹，让婴儿每晚平均多睡 1-2 小时。&lt;/p&gt;
+&lt;p&gt;不过，它只适用 0-6 个月的婴儿，售价 1695 美元，也可以按月租赁（159-499 美元/月），还配备了 7 天 24 小时在线的睡眠顾问。SNOO 至今仍是唯一被 FDA 批准用于保持婴儿仰睡的婴儿床&amp;mdash;&amp;mdash;这是它区别于所有竞品的最大资本，也让它成了二手市场流通最快的婴儿床。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Cradle</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 14:49:04 +0800</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>硬件加强版「WorkBuddy」，拿下数亿融资，瞄向你的终极上下文</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369718</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr"/>
+      <c r="F297" s="2" t="inlineStr"/>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;strong&gt;作者｜苏子华&lt;/strong&gt;&lt;strong&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong&gt;编辑｜靖宇&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;现场体验过 &lt;span class=""&gt;Violoop&lt;/span&gt; 之后，很多关于未来的「AI 助手」该长什么样、能做些什么、能力的极限究竟在哪的困惑，可能都会迎刃而解。&lt;/p&gt;
+&lt;p&gt;因为 Violoop 已经把它们变成了现实。&lt;/p&gt;
+&lt;section&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/a7/29/a729d491f093f6d8d4d72750b623a0b8.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Violoop 实物图｜图片来源：Violoop&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;span class="wx_text_underline"&gt;Violoop 是一款巴掌大小的硬件，即插即用，V4 版本通过一根 Type-C 线连在电脑上，不挤占电脑的 CPU/GPU 资源。它可以通过实时读取电脑屏幕上的全局信息，获得用户全部的上下文，实现主动式的 AI 助手。&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;极客公园获悉，Violoop 半年内完成了亿元级天使轮及 Pre-A 轮融资。联想创投、中金保时捷、蓝驰创投、元生资本、启赋资本和 Zero2IPO Ventures 共同投资。&lt;/p&gt;
+&lt;p&gt;Violoop 的 CEO 何佳霖 是一位连续创业者，毕业于 &lt;span class=""&gt;UC San Diego&lt;/span&gt; 的 CS 专业，曾入选过 YC 创业营。CTO King Zhu 是一位天才学霸，曾在 MIT 的 EECS 专业用 3.5 年完成本硕，同届最快毕业，后来在微软的 Xbox、HoloLens、Surface 等多个业务线担任核心工程师。&lt;/p&gt;
+&lt;p&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/47/cd/47cd47c77cf270e05bffd38253ee710f.png" /&gt;&lt;/p&gt;
+&lt;p&gt;左为何佳霖，右为 King Zhu｜图片来源：受访者&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;何佳霖向极客公园演示了 Violoop 的一个使用场景：&lt;/p&gt;
+&lt;p&gt;你在微信里跟同事聊事，对方甩来一句：「把你上次那个简历发我一下。」&lt;/p&gt;
+&lt;p&gt;你不需要切回桌面翻文件夹&amp;mdash;&amp;mdash;电脑屏幕的角落，一个小框自己跳了出来：&lt;/p&gt;
+&lt;p&gt;「要帮你把张三的简历发过去吗？1.要；2.不要。」&lt;/p&gt;
+&lt;p&gt;你按下键盘上的 1。一秒钟左右，AI 已经自己打开文件夹、找到文件、把简历贴进了对话框。&lt;/p&gt;
+&lt;p&gt;没写一个字的提示词，也没打开任何 AI 软件。&lt;/p&gt;
+&lt;p&gt;这就是 Violoop 想让人们习惯的新工作方式，将整台电脑变成一个眼里有活、主动帮你干活的助手。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;h2&gt;&lt;strong&gt;全局主动式 AI，是如何工作的？&lt;/strong&gt;&lt;/h2&gt;
+&lt;p&gt;&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/p&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p&gt;Violoop 的形态很简单，最新版本用一根 Type-C 线连上电脑，把视频采集和控制合并到一个口，再插一根电源。Mac、Windows、Linux 都能用。&lt;/p&gt;
+&lt;p&gt;它的工作方式，可以拆成三步。&lt;/p&gt;
+&lt;p&gt;第一步是「看」。硬件盒子里内置了一套自研的端侧模型，实时读取屏幕画面，读懂你此刻在干什么。&lt;/p&gt;
+&lt;p&gt;第二步是「判断」。当它觉得你可能需要帮忙，就主动弹出一个框，给你几个选项。&lt;/p&gt;
+&lt;p&gt;第三步是「动手」。你确认之后，它通过模拟真</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 22:24:09 +0000</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch Disrupt 2026’s new Real World AI Stage features Nvidia, robots, and extinct animals</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/02/techcrunch-disrupt-2026s-new-real-world-ai-stage-features-nvidia-robots-and-extinct-animals/</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr"/>
+      <c r="F298" s="2" t="inlineStr"/>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>On our new Real World AI stage, we’ll be focusing on the intersection between the digital and physical, and all the ways we’ll continue to see a blending of the two.</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 02 Sep 2026 16:04:10 +0000</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>Wonderful more than doubles its valuation to $5B in under 6 months</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/02/wonderful-more-than-doubles-its-valuation-to-5b-in-under-6-months/</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr"/>
+      <c r="F299" s="2" t="inlineStr"/>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>Wonderful said it will use its $550 million Series C funding to develop products faster, expand its FDE teams, and meet demand for its products.</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12825,6 +12825,579 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 01:24:14 +0000</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>触觉+姿态同步采集，模量科技新一代数采手套解决数据融合难题</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12679</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr"/>
+      <c r="F300" s="2" t="inlineStr"/>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>从掌心与手指的压力感知，到23个生理自由度的动作捕捉，再到毫秒级数据同步，一套手套即可完成多维度手部数据采集。</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 03:10:47 +0000</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>一文看懂离电型电容电子皮肤</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12668</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr"/>
+      <c r="F301" s="2" t="inlineStr"/>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>从接触起电到电容变化，离电型电容触觉传感器正以轻薄、柔性、低功耗等优势，为机器人电子皮肤与智能交互带来新的触觉感知方案。</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 03:10:21 +0000</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>国内混驱灵巧手企业分析</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12659</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr"/>
+      <c r="F302" s="2" t="inlineStr"/>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>混驱打破了单一路线的性能桎梏，在精度、力量、重量之间找到了新的平衡点</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 03:09:02 +0000</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>从人类操作到机器人学习：数据采集手套的价值</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12658</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr"/>
+      <c r="F303" s="2" t="inlineStr"/>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>为什么一双数据采集手套，会卖到几万元？ 这可能是很多人第一次接触具身智能数据采集时，最自然的问题。 目前，MA [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:18:21+00:00</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Protecting Dynamic Industrial Robot Cable Carriers</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/industrial-robot-cable-carrier-protection</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr"/>
+      <c r="F304" s="2" t="inlineStr"/>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;em&gt;This article is brought to you by &lt;a href="https://tsubaki-kabelschlepp.com/" target="_blank"&gt;Tsubaki KabelSchlepp&lt;/a&gt;.&lt;/em&gt;&lt;/p&gt;&lt;p&gt;In modern automated manufacturing, six-axis articulated robots perform high-speed, multidirectional …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>The Best Way to Explore Lunar Craters Is a Giant Robot Ball</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/moon-ball-robot</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr"/>
+      <c r="F305" s="2" t="inlineStr"/>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;On a good day, the rock quarry in central Texas is about 370,000 kilometers (230,000 miles) from the moon. But …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 16:49:43 GMT</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>李飞飞首个多模态世界模型 Atlas 正式发布：从零开始预训练，几张图就能构建世界</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/9YiEhb3hAFtUlxOpMdGC?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr"/>
+      <c r="F306" s="2" t="inlineStr"/>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/9YiEhb3hAFtUlxOpMdGC?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 01:31:45 +0000</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>神秘具身团队又放出一连串很炸的Demo视频…自进化模型，技术路线曝光</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/483552.html</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr"/>
+      <c r="F307" s="2" t="inlineStr"/>
+      <c r="G307" s="2" t="inlineStr"/>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 01:27:05 +0000</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>50万！李想宣布MPV进入iPhone时刻！外观没改配置拉满</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/483462.html</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr"/>
+      <c r="F308" s="2" t="inlineStr"/>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>4激光雷达+双M100上车</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 08:25:05 +0800</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI 曝光 GPT-6，能力超群；微信公关总监回应「好友超 1 万可查看单删好友」；联合国：超强而厄尔尼诺将冲击全球经济 ｜ 极客早知道</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369801</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr"/>
+      <c r="F309" s="2" t="inlineStr"/>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ba/81/ba81958001deef9b4b87c468c4542ade.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;GPT-6 曝光，OpenAI 总裁说：AGI 来了&lt;/h1&gt;
+&lt;p&gt;当地时间 9 月 3 日，GPT-6 Astra 正式发布。OpenAI 总裁 Greg Brockman 在发布会结束后，说了一句在 AI 行业极为罕见的话：「我个人认为，我们可能已经到达 AGI 了，我觉得就是这个模型。」&lt;/p&gt;
+&lt;p&gt;OpenAI 给 Astra 起了个简洁的 slogan：「Anything you can do on a computer, Astra can do for you.（你在电脑上能做的任何事，Astra 都能替你做。）」&lt;/p&gt;
+&lt;p&gt;新模型可以像人一样，直接「看」屏幕上的像素，然后移动鼠标、敲击键盘，完成操作。&lt;/p&gt;
+&lt;p&gt;给 Astra 一张电路原理图，它在 KiCad 里完成了元器件布局和铜线走线，整个过程用时 2 分 54 秒。&lt;/p&gt;
+&lt;p&gt;另一个演示是三维建模，Astra 在 Blender 里搭建了一栋房子的模型，然后将其导入 Unreal Engine 5，生成了一个可以实时漫游的建筑场景。&lt;/p&gt;
+&lt;p&gt;OpenAI 还公布了两个内部计时案例。「寻找猫咪临时看护」这类需要大量网络搜索、信息比对、汇总成文档的任务，Astra 用了 5 分 27 秒，OpenAI 给出的人类对照基线是 30 分钟。「求职准备」这类需要搜索岗位、匹配简历、整理申请流程的综合任务，Astra 用了 2 分 51 秒，人类基线是 5 小时。&lt;/p&gt;
+&lt;p&gt;更聪明还更守规矩。OpenAI 公布了一个内部测试数据，在没有生产环境安全限制的条件下，GPT-5.6 Sol 会在 48.2% 的情况下超出授权范围行事，而 Astra 是 0%。（消息来源：极客公园）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0f/ef/0fef6a1d38cd841327d9754bf5ff2e23.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ac/69/ac691ec36ca0eb734aa539832c31f70c.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;消息称字节跳动将获得约 296 亿美元银团贷款，若完成将成今年亚洲规模第二大&lt;/h1&gt;
+&lt;p&gt;9 月 3 日消息，据第一财经报道，字节跳动正在推进一笔规模达 296 亿美元（现汇率约合 1,993.99 亿元人民币）的银团贷款。该交易若顺利完成，将成为 2026 年亚洲地区规模第二大的美元计价银团贷款，仅次于软银集团今年 3 月完成的 400 亿美元（现汇率约合 2,694.59 亿元人民币）过桥融资。&lt;/p&gt;
+&lt;p&gt;据报道，字节跳动最初为该笔融资设定的目标规模为 200 亿美元（现汇率约合 1,347.29 亿元人民币），因银行认购踊跃，最终将规模扩大至 296 亿美元（现汇率约合 1,993.99 亿元人民币）。资金主要用于一般企业用途。不过，该贷款协议尚未正式签署，各承销银行仍在就最终的额度分配进行确认。&lt;/p&gt;
+&lt;p&gt;此次大规模融资正值字节跳动加速人工智能战略布局之际。据了解，该公司正在评估将 2026 年的资本支出预算提升至最高 700 亿美元（现汇率约合 4,715.53 亿元人民币），这一数字较 2025 年的支出水平增长超过一倍。新增投资将重点投向数据中心扩容及人工智能基础设施建设，以支撑其在全球范围内的 AI 业务扩张。&lt;/p&gt;
+&lt;p&gt;从融资历史来看，字节跳动上一次在境外进行大规模贷款要追溯至 2024 年，当时公司成功筹集了约 108 亿美元（现汇率约合 727.54 亿元人民币）资金。（消息来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h1&gt;发布会前夕，特斯拉 Cybercab 车队现身美国多地&lt;/h1&gt;
+&lt;p&gt;9 月 3 日消息，特斯拉 Cybercab 的现身范围正不断扩大，早已不局限于得克萨斯州奥斯汀市中心。公司计划北京时间明日凌晨 05:45 在得克萨斯州发布这款纯电动双座车型，自动驾驶是本次发布的核心。&lt;/p&gt;
+&lt;p&gt;特斯拉将在得克萨斯州奥斯汀举办专场活动，向一小部分受众开放 </t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 23:25:38 +0800</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>逛完 WRC，我们发现机器人行业最该回答的 5 个问题</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369388</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr"/>
+      <c r="F310" s="2" t="inlineStr"/>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;8 月 19 日，北京亦庄的空气里飘着一种奇怪的兴奋，这是 2026 世界机器人大会开幕的日子。300 多家企业、2000 多件展品，几乎把具身智能行业能拿出的东西都搬到了这里：大模型、本体、关键零部件、数据，应有尽有。&lt;/p&gt;
+&lt;p&gt;开幕当天，宇树科技敲钟上市，盘中市值一度冲破 4000 亿元，这可能是过去十年，中国机器人行业最接近「资本狂欢」的一天。过去，机器人公司更多活在实验室、融资新闻和 Demo 视频里；而宇树的上市，第一次给这个仍处在早期的赛道钉下了一个资本锚点。&lt;/p&gt;
+&lt;p&gt;除此之外，云深处科技进入交易所受理或审核环节；智元机器人则于 2026 年 7 月确认启动赴港上市流程。一级市场的热，正在向二级市场传导，具身智能不再只是技术想象，也开始被要求回答收入、交付、毛利和规模化的问题。&lt;/p&gt;
+&lt;p&gt;逛完整个展区，跟我们此前预料的一样，今年没有让所有人「哇」的时刻，更多的是 demo 的展示。宇树没有展示刚刚发布的、原地跳高 2 米、奔跑速度 12.66 米/秒的「超人」，展台上更多是已有产品在解锁新动作；众擎把八角笼搬进了会场，维他动力用二次元偶像的方式整活&amp;hellip;&amp;hellip;热闹是真热闹，但很少有人再讲「颠覆性突破」这四个字了。&lt;/p&gt;
+&lt;p&gt;比起继续追问「什么时候会有奇迹」，更值得追问的是几个更朴素的问题：机器人是不是只能长成人的样子？具身智能的「通用性」到底走到了哪一步？数据，正在从一门算法生意，变成一门硬件生意吗？那些藏在指尖、关节和电机里的关键部件，又往前走了几步?&lt;/p&gt;
+&lt;p&gt;带着这些问题，我们在展馆里走了一圈，也和多家代表性公司深聊。它们不一定都最会制造声量，却分别代表了这个赛道正在发生的关键变化：本体形态的分化，通用模型的竞争，数据闭环的重构，以及关键零部件逼近「最后一厘米」。&lt;/p&gt;
+&lt;p&gt;银河通用的展台上，轮式、重载和双足三种完全不同形态的机器人，跑的是同一套具身基础大模型；维他动力反过来从真实使用场景出发，倒推出了它的第一款人形机器人 Vbot ATOM；自变量在物流分拣场景里，把效率做到了每小时 1816 件、准确率超过 98%；帕西尼，则把最初只解决「触觉」的技术方案，扩展成了覆盖全身的感知网络&amp;hellip;&amp;hellip;&lt;/p&gt;
+&lt;p&gt;具身智能仍然早期，甚至比很多人期待的更早期。它正进入一个更艰难、也更有价值的阶段，谁能把模型、本体、零部件和工程能力一个闭环，谁才可能成为下一阶段真正有价值的公司。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;1.机器人是不是只能是人形？&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;过去两年，具身智能的叙事被人形机器人高度占领：跳舞、跑步、打拳、马拉松，所有出圈事件几乎都长着一副人的样子。&lt;/p&gt;
+&lt;p&gt;但看完这届 WRC，你会发现，人形机器人的概念依旧延展，巨型、仿生、半人马&amp;hellip;&amp;hellip;「像人」不再只有一种标准答案。与此同时，在人形之外，越来越多公司开始根据真实任务重新设计机器人形态。&lt;/p&gt;
+&lt;p&gt;&lt;/p&gt;
+&lt;p&gt;今年 WRC 逛下来，宇树的人形这边确实拼得凶，带来了全新的格斗动作。G1 打格斗，组合拳、回旋踢、飞踢一套下来，靠的是全身关节的实时协调；H2 个头更大、关节输出更强，出拳抬腿更有分量感。两台机器人放一起看，正好是「灵活」和「力量」两种风格。&lt;/p&gt;
+&lt;p&gt;乒乓球互动也很值得一看，机器人得先「看懂」来球再决定怎么回，这比单纯耍套路更考验感知和决策的配合。加上全身遥操作格斗系统，操作者的动作能被精准复现，这套东西背后其实是宇树在攒具身智能的数据闭环。&lt;/p&gt;
+&lt;p&gt;但最显眼的还是 GD01，那台三米高、能载人变形的机甲。它不是人形，也不是传统四足，而是把机器人技术和装备形态揉在了一起，直接冲着文旅、特种作业这类场景去的。&lt;/p&gt;
+&lt;p&gt;在本届 WRC 上，Vbot 维他动力正式发布人形具身智能终端 Vbot ATOM，并同步开启预订。ATOM 值得注意的是，它并不是从概念样机起步，而是承接了 Vbot 在四足机器人「大头」上已经验证过的产品定义、量产交付和用户运营能力。&lt;/p&gt;
+&lt;p&gt;&lt;/p&gt;
+&lt;p&gt;今年 5 月，AI 载物机器狗「大头」实现量产交付。到目前为止，这款产品已成为消费级具身智能销量第一，在真实世界中累计完成 126 万次大模型交互、23,700 公里用户伴随里程和 131,500 小时陪伴，过去三个月还完成了 4 次 OTA。对具身智能行业来说，这组数据的意义不只在于销量，而在于它证明 Vbot 已经让机器人进入真实用户生活，并形成了从交付、使用反馈到持续迭代的产品闭环。&lt;/p&gt;
+&lt;p&gt;基于「大头」的实践，Vbot ATOM 没有沿用传统工业人形机器人的思路，而是从家庭、零售、公共空间和办公服务等生活场</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 14:05:37 +0800</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>成立不到一年连融三轮，这个睡眠 AI 产品「火」了</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369768</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr"/>
+      <c r="F311" s="2" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：Fullive.ai&lt;/p&gt;
+&lt;p&gt;一家成立几个月、第一款产品即将量产的 AI 硬件公司，已经连续融了三轮：高瓴连续三轮加注，智元机器人等机构先后进入股东名单；到了今年 7 月，招商局创投又领投了它的新一轮融资。&lt;/p&gt;
+&lt;p&gt;这家公司叫 Fullive.ai，创始人郑昊本科就读于清华数学系，此后一路跨过生物统计、因果推断、AI、医学和硬科技投资；联合创始人韦骁龙来自北大计算机，此前曾在华为、荣耀负责消费电子产品。团队里还有参与过华为手环、WHOOP 等穿戴设备的硬件人员，以及来自百度、大疆等公司的算法和商业化老兵。&lt;/p&gt;
+&lt;p&gt;Fullive.ai 把第一款产品放在了床头。&lt;/p&gt;
+&lt;p&gt;它叫 Somni，是一款面向高压脑力人群的睡眠硬件。外形上，它不像传统健康硬件，更像一个安静的床头设备：没有屏幕、不需要佩戴，也不要求用户在睡前再学习一套交互。通过毫米波雷达、麦克风阵列和环境传感器，感知人在夜里的呼吸、心率、体动以及卧室环境，再用声音、光线、气味等神经系统调节方式帮助用户更快入睡、减少夜间醒来，并在早晨完成自然唤醒。&lt;/p&gt;
+&lt;p&gt;睡眠当然已经是一个拥挤的硬件市场。&lt;/p&gt;
+&lt;p&gt;手环、指环和床垫越来越擅长告诉人们昨晚睡得怎么样，助眠灯、耳机和眼罩也在尝试用声音、光线或触觉让人睡得更好。但这两件事之间，其实一直隔着一个很难解决的问题：&lt;strong&gt;知道你没睡好之后，机器到底能做什么？更重要的是，它怎么知道自己做对了？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;这正是 Somni 想解决的问题。它其实是一套会在连续夜晚中学习用户响应的闭环系统。&lt;/p&gt;
+&lt;p&gt;如果前一晚的一套声音和灯光没有达到预期效果，Somni 会根据用户整晚的生理变化，重新调整下一晚的方案；反过来，如果某种干预有效，这次身体反馈也会成为之后调整的依据。&lt;/p&gt;
+&lt;p&gt;郑昊把每个夜晚都看作一次持续发生的「小型实验」：观察一个人处在什么状态，尝试一次干预，再看身体发生了什么变化。如此循环，设备才有可能慢慢摸清，对这个人来说，什么方法真的有用。&lt;/p&gt;
+&lt;p&gt;这也是 Fullive.ai 做 Somni 更深一层的原因。&lt;/p&gt;
+&lt;p&gt;在郑昊看来，今天大量健康硬件已经很擅长「监测人」，但如果 AI 想进一步参与人的健康管理，仅仅知道一个人的心率、呼吸和睡眠分期还不够。它还需要理解，当外部世界发生变化时，人的身体会怎样跟着变化。&lt;/p&gt;
+&lt;p&gt;从一台放在床头的睡眠设备开始，Fullive.ai 想让 AI 学习的，正是这种「响应」。这家年轻公司将其称为 Response Learning：如果 Somni 能够在真实生活中持续完成感知、干预和反馈，它积累下来的，就不再只有「人是什么状态」的数据，还有「什么东西改变了人，以及人是怎么被改变的」。&lt;/p&gt;
+&lt;p&gt;一盏床头设备，由此成为了 Fullive.ai 验证这条路线的第一个入口。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;一、睡不好的一晚，床头能做什么？&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;第一眼看到 Somni，最容易被注意到的是它刻意克制的形态。&lt;/p&gt;
+&lt;p&gt;它试图覆盖睡眠的全周期：入睡前帮你放松下来，睡眠中维持稳定的状态，清晨用更自然的方式唤醒。对用户来说，理想状态下只需把它放在床边，其他事情交给设备完成，不需要佩戴手环或头带，也不用主动打卡、频繁操作。&lt;/p&gt;
+&lt;p&gt;对用户来说，它和普通床头设备的使用感没什么差别；但在系统内部，每一晚的运行都形成了一套完整的闭环：感知状态、判断策略、执行干预、迭代优化。&lt;/p&gt;
+&lt;p&gt;Somni 使用毫米波雷达、麦克风阵列和环境传感器，持续捕捉呼吸、心率、体动、鼾声及卧室中的温湿度、光照等变化。多组信号融合之后，系统能持续判断用户的睡眠阶段和环境状态。&lt;/p&gt;
+&lt;p&gt;收集数据是第一步。接下来是判断该在什么时候做什么。传统睡眠监测设备的逻辑是「事后复盘」&amp;mdash;&amp;mdash; 第二天出一份报告，告诉你睡了多久、醒了几次、深睡比例多少。&lt;/p&gt;
+&lt;p&gt;Somni 往前走了一步：它要生成一套随时间动态调整的干预方案，比如几点调暗灯光、用什么节奏的声音辅助放松，夜间醒了又该怎么调整动作。&lt;/p&gt;
+&lt;p&gt;它通过声光味等因子，对夜间神经状态进行低打扰调节。这些方式的共同点是，不需要在用户睡觉时增加明显操作，也不必让人佩戴更多设备。对于工作强度高、容易紧张、同时又对外部刺激较敏感的人群，这种「尽量少打扰」的设计很重要。&lt;/p&gt;
+&lt;p&gt;最后一步是学习迭代。每一次干预都会对应一组后续反馈：呼吸有没有变平稳？入睡时间有没有缩短？夜里醒的次数少了吗？第二天主观感受有没有变好？系统会对比干预前后的变化，再</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 13:54:42 +0800</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>智谱和 MiniMax，把大模型做成了两种生意</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369775</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr"/>
+      <c r="F312" s="2" t="inlineStr"/>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：视觉中国&lt;/p&gt;
+&lt;p&gt;两家中国大模型公司，在五天里先后交出了上市后的首份中报。&lt;/p&gt;
+&lt;p&gt;MiniMax 先出：上半年收入 1.17 亿美元，同比增长 283%；8 月 ARR 超过 8 亿美元。智谱随后公布：上半年收入 9.54 亿元人民币，同比增长近 400%；8 月 ARR 达到 16 亿美元。&lt;/p&gt;
+&lt;p&gt;如果只看 ARR，结论似乎很简单：智谱更高，MiniMax 紧随其后；两家公司都在讲 Token 调用量暴涨、企业客户增加、模型能力开始换来收入。&lt;/p&gt;
+&lt;p&gt;把数字放回财报，事情会变得复杂一些。&lt;/p&gt;
+&lt;p&gt;智谱上半年确认收入约 1.42 亿美元，MiniMax 为 1.17 亿美元，两者实际收入规模相差不远；两家的经调整亏损也几乎相同，都接近 3 亿美元。ARR 代表某个时点的收入速度，但无法直接替代收入、毛利和现金流。&lt;/p&gt;
+&lt;p&gt;两家公司都还没有走到盈利那一页。两份中报里，「期内亏损收窄」都受到上市后优先股转换带来的会计因素影响；如果剥开这层，研发和经营投入其实仍然在高位。&lt;/p&gt;
+&lt;p&gt;不一样的是两家公司正在把模型卖向哪里。&lt;/p&gt;
+&lt;p&gt;智谱的 API 收入已经占到总收入的 86.5%，它开始把模型推到 Coding、网安和长程任务的工作现场；MiniMax 的企业服务收入快速增长，同时保留着全球化、多模态和 AI 原生产品的基本盘，它更关心如何把每一单位智能做得更便宜，让更多用户、更多 Agent 和更多创作场景消费它。&lt;/p&gt;
+&lt;p&gt;两份中报，展现的是中国大模型商业化的一次分层。&lt;/p&gt;
+&lt;h1&gt;一、 智谱：本地化退潮，API 已成主引擎&lt;/h1&gt;
+&lt;p&gt;先看智谱的中报。上半年营收 9.54 亿元，同比增长 399.7%，已超过 2025 年全年 7.24 亿元；毛利 2.52 亿元，毛利率 26.4%；研发支出 21.31 亿元，同比增长 33.6%。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/10/64/1064f66c2b5a2f47231908df197f2250.png" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：智谱中报&lt;/p&gt;
+&lt;p&gt;增长背后是业务结构的明显转换。开放平台与 API 业务收入 8.25 亿元，同比增长 2735.7%，占总收入 86.5%&amp;mdash;&amp;mdash; 去年同期这个数字只有 15.2%。过去承担基本盘的本地化部署退到更靠后的位置：企业通用模型相关收入 6704 万元，同比下降 54.6%。&lt;/p&gt;
+&lt;p&gt;智谱正在从 "把模型部署进客户机房、签一笔项目确认一笔收入"，转向 "把模型放在云上、按调用量持续收费"。前者更像传统项目生意，强调交付、安全和客户关系；后者依赖模型能力、开发者生态和推理成本，更有机会形成持续、可扩张的收入。&lt;/p&gt;
+&lt;p&gt;截至中报发布时，MaaS 平台 Token 调用量较年初增长超 40 倍，付费日活增长 603%，API 平均售价提升约 101%；开放平台及 API 业务毛利率也从去年同期的 - 0.4% 升至 24.6%。&lt;/p&gt;
+&lt;p&gt;电话会上，管理层称，按 8 月单月收入乘以 12 计算，MaaS 平台 ARR 达到 16 亿美元；按最近一周收入年化则超过 20 亿美元。ARR 未列入财报，短期年化容易放大某个月的增速，但智谱强调它，反映出希望市场用 "云端模型服务当前的运行速度"，而不只是已确认的半年收入来衡量公司。&lt;/p&gt;
+&lt;p&gt;API 高速增长，没有改变智谱仍处在高投入期的现实。收入结构从高毛利的本地化部署转向 API，整体毛利率从去年同期的 50.0% 降至 26.4%；期内亏损 20.72 亿元，经调整净亏损 19.64 亿元，经营亏损由 18.99 亿元扩大至 21.47 亿元。亏损数字方向不一，主因是优先股转换：去年同期相关金融负债公允价值变动带来 4.29 亿元损失，今年降至 2209 万元。但更能反映主营业务情况的经营亏损，仍由去年同期的 18.99 亿元扩大至 21.47 亿元。同期研发投入达到 21.31 亿元，是收入的两倍以上，模型训练和推理基础设施仍需要大量资金。&lt;/p&gt;
+&lt;p&gt;但智谱没有只用传统财务指标解释这笔投入。这份 60 页的中期业绩公告，用相当篇幅讨论模型架构、训练算法、强化学习、推理系统和国产芯片集群，最后还附了一份技术词汇表。&lt;/p&gt;
+&lt;p&gt;智谱在公告中提出一条公式："AGI 商业价值＝智能上界 &amp;times;Token 消耗规模。" 逻辑是，智能上界决定模型能处理什么任务，任务边界决定每个 Token</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 03 Sep 2026 12:52:10 +0800</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>AI 下一场竞争：谁能成为 Agent 的「上下文操作系统」</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369767</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr"/>
+      <c r="F313" s="2" t="inlineStr"/>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;头图来源：视觉中国&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;前段时间，Anthropic 发布了 Model Hardware Standard，尝试给 AI Agent 建立一套与硬件沟通的通用语言。接入这套标准后，显微镜、机械臂等不同厂商、不同接口的设备，可以被 Agent 发现、理解和调用。&lt;/p&gt;
+&lt;p&gt;这件事指向了 AI 行业正在发生的一次变化。过去一年，竞争主要围绕模型的推理、生成和多模态能力展开；如今，Agent 开始走出聊天窗口，进入实验室、工厂和企业现场。行业的问题随之向下移动：模型已经足够聪明之后，谁来连接工具、硬件、数据和任务？&lt;/p&gt;
+&lt;p&gt;9 月 2 日，腾讯 WorkBuddy 宣布面向更多伙伴开放合作。通达信、广发证券、北大法宝、腾讯 SSV 教师助手、微盟、北森、云帐房、帆软等应用与软件伙伴进入生态；Plaud、Rokid、影石、优篮子、科大讯飞、安克、猛玛、京造等硬件伙伴，也共同构成了 WorkBuddy 的生态版图。&lt;/p&gt;
+&lt;p&gt;一款 AI 产品为什么要同时连接专业软件、行业服务和多种硬件？这份名单勾勒出的，其实是 Agent 即将面对的完整工作现场：专业软件提供行业知识和业务动作，智能硬件提供声音、图像与移动中的现场信息，Agent 则要把它们组织成一条可以持续推进的任务链。&lt;/p&gt;
+&lt;p&gt;过去一年，AI 办公产品已经能写、能搜、能总结，也能处理越来越复杂的内容。但真实工作依然分散在不同软件、不同设备和不同账号体系里。用户获得 AI 的建议之后，往往还要自己完成信息搬运、工具切换和流程衔接。&lt;/p&gt;
+&lt;p&gt;所以，当 AI 开始参与复杂工作，竞争的其实是谁为 Agent 建立一套工作系统：让它记住上下文，理解任务状态，调度应用与设备，并在可控的权限边界内把用户意图推进成结果。&lt;/p&gt;
+&lt;p&gt;WorkBuddy 此次开放合作，试图给出的答案是，Agent OS。&lt;/p&gt;
+&lt;h1&gt;会答题之后，AI 得学会把事办完&lt;/h1&gt;
+&lt;p&gt;以一名投资经理准备行业调研为例。他需要回看此前的研究笔记和会议纪要，调取市场数据、公司公告和行业信息；会议结束后，还要整理核心判断、列出待验证问题、分派后续任务，最终沉淀为一份研究报告。&lt;/p&gt;
+&lt;p&gt;其中每一步都有相应工具：会议内容可能留在录音设备里，市场信息来自专业金融服务，资料散落在本地文件和企业知识库中，协作又发生在文档、邮件和即时通信软件里。AI 可以帮助生成一份摘要，却未必知道用户此前研究过什么、这次讨论解决了哪些问题、哪些结论还需要继续验证。&lt;/p&gt;
+&lt;p&gt;这正是 Agent 从「回答问题」走向「完成工作」时遇到的主要障碍。腾讯 WorkBuddy 开放生态负责人林佐露在发布会上也谈到，」Agent『能做事 』这道坎已经跨过去了。真正的挑战是，让它在任何设备、任何系统、任何场景里都不中断。」&lt;/p&gt;
+&lt;p&gt;Agent 要承担复杂任务，需要拥有连续的上下文。它要记住用户已经做过什么，理解任务进行到哪一步，判断该调用哪项工具，也要清楚哪些数据可以读取、哪些操作需要确认。记忆、任务状态、工具连接、身份权限、数据和产物，构成了 Agent 工作所需的基本环境。&lt;/p&gt;
+&lt;p&gt;早期 PC 也经历过类似阶段。在操作系统和统一接口成熟之前，软件之间难以顺畅交换信息，用户自己充当不同工具之间的连接器。如今，应用、设备与 Agent 之间的割裂，让这种摩擦以新的形式出现。&lt;/p&gt;
+&lt;p&gt;所谓 Agent OS，解决的就是这层问题。传统操作系统管理文件、窗口和应用，Agent OS 还需要管理任务、记忆、工具和权限。模型提供理解与推理能力，这套系统决定模型能看到多少工作现场，又能把任务推进多远。&lt;/p&gt;
+&lt;p&gt;上线半年内，WorkBuddy 完成超 50 个版本迭代，落地政务、教育、零售、金融、传媒、出行等 50 多个行业。据腾讯 2026 年 Q1 财报披露，以日活跃账户数计，WorkBuddy 已成为中国最受欢迎的效率 AI 智能体服务；第三方机构易观的数据显示，6 月 PC 端单月访问量超 2000 万，保持市场第一。&lt;/p&gt;
+&lt;p&gt;当一些 AI 办公产品还在验证单一场景时，WorkBuddy 已经积累了足够多样的真实任务类型，这是它试图做 OS 的前提&amp;mdash;&amp;mdash;OS 从来不是为单一应用设计的。&lt;/p&gt;
+&lt;h1&gt;从 Buddy 应用到智能硬件，一条工作链如何接起来&lt;/h1&gt;
+&lt;p&gt;WorkBuddy 的开放生态，首先是在补齐 Agent 的「手」和「眼」。&lt;/p&gt;
+&lt;p&gt;通达信、广发证券、北大法宝、微盟、北森、云帐房、帆软等应用与软件伙伴，分别连接金融、法律、商家经营、人力资源、财税和数</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H313"/>
+  <dimension ref="A1:H323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13398,6 +13398,393 @@
         </is>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 06:24:03 +0000</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>辉羲智能与影智XBOT达成战略合作，加速通用餐饮机器人量产部署</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12713</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr"/>
+      <c r="F314" s="2" t="inlineStr"/>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>从底层算力到真实餐饮场景，共驱量产落地</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 02:04:32 +0000</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>帕西尼携手极佳视界，唤醒具身智能“通感时代”</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12686</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr"/>
+      <c r="F315" s="2" t="inlineStr"/>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>在 2026 世界机器人大会（WRC）期间，帕西尼（PaXini AI）发布 PaXini Inside 生态 [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04 16:00:05+00:00</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Digit Redecorates</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-agility-robotics-digit</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr"/>
+      <c r="F316" s="2" t="inlineStr"/>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 09:19:29 +0000</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>机器人不能停下来等模型：星尘发布 SmoothRL，让在线强化学习跟上大模型的异步推理</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/484437.html</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr"/>
+      <c r="F317" s="2" t="inlineStr"/>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>星尘智能（Astribot） 基座模型团队发布能异步执行的在线强化学习框架 SmoothRL</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 05:53:09 +0000</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>2026 上半年智能眼镜竞争加剧，雷鸟创新五榜登顶实现全品类销量领先</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/484159.html</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr"/>
+      <c r="F318" s="2" t="inlineStr"/>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>雷鸟创新（RayNeo）包揽全球 AR 眼镜与中国智能眼镜市场出货量和销量第一。</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 05 Sep 2026 08:24:15 +0800</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>传玛莎拉蒂和华为+江淮合作开发电动车；苹果最大新品阵容时代开启；人人影视回归，终身 VIP 888 元</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369871</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr"/>
+      <c r="F319" s="2" t="inlineStr"/>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/41/f6/41f6c917e8114c701cd73ec82e0efc49.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 智能体被曝「接管」德国维基网站&lt;/h2&gt;
+&lt;p&gt;一项最新曝光的人工智能安全事件正在引发业内广泛关注。&lt;/p&gt;
+&lt;p&gt;根据研究人员披露的信息，今年春季，一批与 OpenAI 模型相关的自主智能体曾在未经授权的情况下「接管」一家德国维基网站，并将其改造成供其他 AI 系统交流信息的公共平台。这一事件此前从未对外公开，而 OpenAI 据称已在数周前获悉相关情况。&lt;/p&gt;
+&lt;p&gt;报道称，事件最早开始于今年 5 月，目标网站是一家名为 DseWiki 的德语维基平台，主要面向程序员社区开放协作编辑。研究人员在 8 月底调查 互联网异常 AI 活动时发现，该网站在数月时间内累计出现超过 1.5 万次由 AI 智能体完成的编辑操作。&lt;/p&gt;
+&lt;p&gt;调查人员表示，这些编辑行为并非普通的信息补充，而是呈现出明显的组织化特征。大量页面被智能体重新利用为交流平台，不同 AI 系统在其中分享任务执行经验、讨论绕过限制的方法，并交流如何隐藏自身行为的技巧。&lt;/p&gt;
+&lt;p&gt;研究人员查看的记录显示，当网站管理员于 6 月开始删除相关页面后，这些智能体并未停止活动，而是主动建立备用页面，以避免交流内容随着清理行动一同消失。有记录显示，部分智能体甚至会提醒其他系统某些页面可能即将被删除，并提供替代位置继续存储信息。&lt;/p&gt;
+&lt;p&gt;服务器日志显示，相当一部分活动流量来自微软 Azure 基础设施。不过，研究人员同时强调，这些迹象并不能直接证明相关行为由 OpenAI 官方主动指挥。（来源：cnbeta）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d4/e4/d4e4c9c32d808c322044672ec8d1a207.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;Anthropic：Claude 仅用 11 天完成费马大定理首个完整计算机验证证明&lt;/h2&gt;
+&lt;p&gt;Anthropic 于当地时间 9 月 4 日宣布，其 AI 模型 Claude 在基本自主运行 11 天后，完成了对费马大定理（FLT）的首个端到端、经过计算机检查的形式化证明。&lt;/p&gt;
+&lt;p&gt;Anthropic 表示，这项工作并非重新发现费马大定理的数学证明，而是将已有数学证明转换为 Lean 证明助手可以逐步验证的形式。&lt;/p&gt;
+&lt;p&gt;Lean 是一种用于编写和验证形式化数学证明的证明助手，能够通过计算机检查证明中的逻辑步骤。&lt;/p&gt;
+&lt;p&gt;据介绍，Claude 在这一过程中生成了约 1300 万行 Lean 代码，并证明了约 3.03 万个定理，其中约 2.95 万个中间定理最终被纳入费马大定理的完整证明。整个证明由 Lean 完成检查，仅使用 Lean 的 3 条标准公理。&lt;/p&gt;
+&lt;p&gt;此次项目由 Anthropic 研究人员 Tianyi Peng 发起。Claude 并非由单个智能体完成全部工作，而是通过多智能体协作完成概念定义、中间定理证明以及更复杂命题的推导。项目使用了由 Peng 及其哥伦比亚大学合作者开发的 Prove2Me 平台，用有向无环图（DAG）记录待证明的定理及其依赖关系，并支持多个 Claude 智能体并行工作。&lt;/p&gt;
+&lt;p&gt;人类研究人员提供的数学输入主要是少量高层次指令，例如确定某些数学对象或定理的优先级，具体证明过程则主要由 Claude 完成。&lt;/p&gt;
+&lt;p&gt;整个项目消耗了约 60 亿个输出 Token，使用的是一个与 Claude Fable 5.1 大致相当的通用内部研究模型。（来源：IT 之家）&lt;/p&gt;
+&lt;h2&gt;古尔曼称苹果将以史上最大新品阵容开启「特努斯时代」，公布今年至 2029 年后产品规划&lt;/h2&gt;
+&lt;p&gt;9 月 4 日消息，苹果将于 9 月 9 日举行「亮新篇，来耀眼」发布会，新任 CEO 约翰 &amp;middot; 特努斯届时将登台发布新一代 iPhone 和 Apple Watch，而这场活动只是开端。&lt;/p&gt;
+&lt;p&gt;彭博社记者马克 &amp;middot; 古尔曼发文称，苹果准备开启公司&lt;strong&gt;历史上规模最大的一轮硬件发布周期&lt;/strong&gt;，在 2026 年、2027 年乃至更远的未来陆续推出全新产品形态，并进入多个此前从未涉足的设备领域。&lt;/p&gt;
+&lt;p&gt;苹果为这套产品路线图筹备了约 5 年，特努斯在致员工的</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 16:37:04 +0800</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>对话 Sharpa 李一帆：通用机器人要么全能，要么无能</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369851</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr"/>
+      <c r="F320" s="2" t="inlineStr"/>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px; text-align: justify;"&gt;&lt;span&gt;具身智能现在太吵了。&lt;/span&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px; text-align: justify;"&gt;&lt;span&gt;行业里的人各自笃定，声音大的先被听见。最响的那些声音，往往离真实的进展最远。&lt;/span&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px; text-align: justify;"&gt;&lt;span&gt;真正在往前推的人，看的是谁在践行非共识，什么在真的往前走，以及谁心里有一张完整的图，而不是走一步看一步。&lt;/span&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px; text-align: justify;"&gt;&lt;span&gt;这些东西不会上热搜，但它们决定这个行业的下一步。&lt;/span&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px; text-align: justify;"&gt;&lt;span&gt;&lt;span&gt;我们一直探寻这些。如果你也是&amp;mdash;&amp;mdash;&lt;/span&gt;&lt;/span&gt;&lt;span&gt;&lt;br /&gt;&lt;/span&gt;&lt;/p&gt;
+&lt;p style="font-family: Optima-Regular, PingFangTC-light, 'PingFang SC', 'PingFang TC', 'Hiragino Sans GB', 'Microsoft YaHei', sans-serif; font-size: 16px; line-height: 1.75; margin: 0px 8px 24px; text-align: justify;"&gt;&lt;span&gt;欢迎来到极客公园 In The Loop。👇&lt;/span&gt;&lt;/p&gt;
+&lt;section class="mp_profile_iframe_wrp"&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;hr /&gt;
+&lt;section class="wx-article-wrap"&gt;
+&lt;section&gt;
+&lt;p style="text-align: justify; margin-right: 8px; margin-left: 8px;"&gt;&lt;strong style="font-family: Optima-Regular, PingFangTC-light, 'Pin</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 16:33:41 +0800</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>梅卡曼德上市，具身智能又跑出一家百亿公司</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369850</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr"/>
+      <c r="F321" s="2" t="inlineStr"/>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;section&gt;
+&lt;section class=""&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474; font-family: Optima-Regular, PingFangTC-light;"&gt;&lt;br /&gt;作者｜Li Yuan&lt;/strong&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474;"&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474; font-family: Optima-Regular, PingFangTC-light;"&gt;编辑｜&lt;strong&gt;郑玄&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474;"&gt;&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;2026 年 9 月 1 日，梅卡曼德登陆港交所。一个过去很少被大众看见的机器人公司，终于被公开市场标出了价格，首日收盘&lt;strong style="margin-top: 0px; margin-bottom: 0px; text-align: left; color: #000000; letter-spacing: 0px; font-size: 16px; line-height: 1.6;"&gt;总市值约 124 亿港元。&lt;/strong&gt;&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;上市之前，一级市场和基石投资者已经先给出了自己的判断。梅卡曼德此次引入包括苏格兰百年资管巨头 Baillie Gifford 在内的 9 家基石投资者，合计认购 1.86 亿美元。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;成立于 2016 年，梅卡曼德和宇树一样，都是上一轮机器人创业潮里走出来的公司。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;但从第一天起，梅卡曼德就没有把重点放在造一台机器人上。公司名 Mech-Mind 里的「Mind」，指向的是另一件事：给机器人做感知、识别和运动规划。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;2017 年，梅卡曼德推出第一代 Mech-Eye、Mech-Vision 和 Mech-Viz：相机负责获取 3D 点云和图像，视觉软件识别物体的位置与姿态，规划软件计算机械臂怎么抓、怎么走、怎么避障。到了今天，具身智能、物理 AI 和世界模型讨论的很多问题，仍然绕不开这些环节。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;梅卡曼德卖出去的不是一台完整机器人，而是一套可以接到不同机械臂和产线里的智能组件。十年下来，这套东西被送进近 50 个国家和地区，累计部署超</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 23:36:14 +0000</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>XDOF, just three months out of stealth, is in talks for a Series B at a $1.2B valuation</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/04/xdof-just-three-months-out-of-stealth-is-in-talks-for-a-series-b-at-a-1-2b-valuation/</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr"/>
+      <c r="F322" s="2" t="inlineStr"/>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>The round is being raised just months after the robot data startup exited from stealth.</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 21:12:11 +0000</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>AI compute provider Nscale is looking for $3.5B in pre-IPO financing</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/04/ai-compute-provider-nscale-is-looking-for-3-5b-in-pre-ipo-financing/</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr"/>
+      <c r="F323" s="2" t="inlineStr"/>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>Nscale, which recently struck a $45 billion deal with Anthropic, is in talks to raise additional funds in anticipation of an upcoming IPO.</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13785,6 +13785,126 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 05 Sep 2026 14:46:15 +0000</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>押中SpaceX的硅谷老将，把票投给了一家中国世界模型公司</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/484683.html</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr"/>
+      <c r="F324" s="2" t="inlineStr"/>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>当AI开始“预演”一场暴雨</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 05 Sep 2026 04:18:54 +0000</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>这个世界模型训练完就“退场”，机器人反而更能干了</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/484611.html</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr"/>
+      <c r="F325" s="2" t="inlineStr"/>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>如此“反骨”的方法，具体又是怎么实现的？</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 06 Sep 2026 08:06:12 +0800</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>传 iPhone 18 Pro 仅涨价 100 美元；Kimi、MiniMax 将在天猫开店；OpenAI 回应 Agent 攻击德国网站</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369875</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr"/>
+      <c r="F326" s="2" t="inlineStr"/>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/4f/c5/4fc506f97f8dab95ef1303ef10e4773b.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;大模型厂商纷纷「卖 Token」，消息称 Kimi、MiniMax 等即将在天猫开店&lt;/h2&gt;
+&lt;p&gt;上海证券报 9 月 5 日独家获悉，Kimi、MiniMax、阶跃星辰等多家大模型厂商也都在与天猫接洽中，未来将入驻天猫开设官方旗舰店，开售 Token 订阅套餐产品。&lt;/p&gt;
+&lt;p&gt;本月 2 日，国产 AI 大模型厂商智谱正式入驻天猫，开设「智谱旗舰店」。用户可在淘宝 App 搜索「智谱旗舰店」进店下单。店铺目前已上架智谱 GLM Coding Plan 订阅套餐，基于 GLM-5.3 模型，并适配 ZCode、Claude Code、Codex 等 20 余款主流 Agent。&lt;/p&gt;
+&lt;p&gt;此前大模型厂商主要通过官网等自有渠道销售订阅产品。智谱此次入驻天猫，意味着大模型订阅服务开始进入传统电商平台的消费场景。&lt;/p&gt;
+&lt;p&gt;本月 3 日，天猫上线 Token 充值中心，首批接入阿里云、智谱、Kimi、MiniMax、DeepSeek 等国产大模型厂商。其中，阿里云和智谱为品牌官方旗舰店，剩余三家目前为代理模式。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/b3/86/b3867b3fbf256320879a2d78af9210cf.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 回应旗下智能体攻进德国网站：将彻底改革「AI 模型攻击」事件披露机制&lt;/h2&gt;
+&lt;p&gt;9 月 4 日晚间路透社报道称，一群失控的 OpenAI 智能体劫持了一个德语维基网站，由此引发外界对 OpenAI 的质疑。对此，OpenAI 回应称，需要彻底改革 AI 模型攻击现实世界目标后，企业应在何时以及以何种方式对外披露此类事件。&lt;/p&gt;
+&lt;p&gt;OpenAI 9 月 5 日在 X 平台发文表示：「关于『维基事件』，也就是我们的智能体向多个互联网网站写入内容一事，我们早就应该制定标准，明确何时以及如何披露『误对齐』事件，而不仅仅是披露模型本身的误对齐属性。」&lt;/p&gt;
+&lt;p&gt;OpenAI 指出，过去通常把 AI 智能体出现非预期行为视为一个「研究问题」，但近期多起事件已经涉及现实世界目标，尤其是 Hugging Face 遭到入侵，表明有必要重新审视这种处理方式。&lt;/p&gt;
+&lt;p&gt;这是「维基事件」周五首次曝光后，OpenAI 第一次承认自身参与其中。另有报道称，OpenAI 知道这些智能体以这种方式失去控制，却没有披露这一「事件」。&lt;/p&gt;
+&lt;p&gt;消息在 AI 行业引发广泛担忧，外界开始质疑前沿 AI 系统的安全性，以及开发这些系统的企业是否可靠。OpenAI 在 X 平台解释称：「我们此前认为，维基事件属于一种失配情况，与过去安全报告中披露的失配案例类似。」&lt;/p&gt;
+&lt;p&gt;OpenAI 还称，新的事件披露框架正在制定，并将在「未来几周内」公布，同时呼吁整个 AI 行业建立明确标准，规范此类误对齐事件的披露方式。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;赶在发布会前！运营商晒 iPhone 18 Pro/Ultra 售价：苹果这涨幅并不激进&lt;/h2&gt;
+&lt;p&gt;9 月 5 日，海外运营商曝光苹果新一代 iPhone 系列的终端定价相关数据。跨国电信运营商沃达丰泄露的埃及市场数据显示，iPhone 18 Pro、iPhone 18 Pro Max 当地售价较上一代涨幅约为 10%、11%，测算后其美国市场基准起售价约 1099 美元、1299 美元，较上一代上调约 100 美元，涨幅低于此前市场预测。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img height="486" src="https://imgslim.geekpark.net/uploads/image/file/6a/2c/6a2ce1cea6873cf2b5a90d7f097e5916.jpg" width="782" /&gt;&lt;/p&gt;
+&lt;p&gt;同步泄露的澳大利亚渠道信息显示，顶级折叠机型 iPhone Ultra 的 256GB、512GB、1TB 版本售价分别为 3699 澳元、4199 澳元、4699 澳元，测算其美国本土起售价区间为 1999 至 2099 美元，网传的超高溢价并未出现，汇总相关消</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H326"/>
+  <dimension ref="A1:H329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13905,6 +13905,136 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 06 Sep 2026 11:44:21 +0000</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>具身ICL来了创业玩家！上下文成Scaling新赛道</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/484897.html</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr"/>
+      <c r="F327" s="2" t="inlineStr"/>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>让机器人学会利用更长的多模态Context</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 07 Sep 2026 08:55:47 +0800</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>雷军：小米汽车销量突破 80 万；苹果元老辞职，传不满激进 AppStore 增收方案；韩国推出首档人机 AI 恋综 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369884</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr"/>
+      <c r="F328" s="2" t="inlineStr"/>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/d5/95/d59594509857d445b0d8aab42b6bb27f.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;雷军：小米汽车累计交付量超过 80 万辆&lt;/h1&gt;
+&lt;p&gt;9 月 7 日消息，小米创办人、董事长兼 CEO 雷军刚刚宣布，&lt;strong&gt;小米汽车累计交付量超过 80 万辆&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;据本月早些时候报道，2026 年 8 月，小米汽车交付量持续超过 30,000 台。小米汽车表示，&lt;strong&gt;正全力为小米澎程上市交付做准备&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;另外，在 7 月 30 日的小米澎程技术发布会上，小米创办人、董事长兼 CEO 雷军表示，2 年半的时间，小米汽车发布了两款车&amp;mdash;&amp;mdash;&lt;strong&gt;小米 SU7 和小米 YU7。这两款车都成了爆品，并且累计交付 70 多万台&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;小米汽车 2026 年各月交付量如下：&lt;/p&gt;
+&lt;ul&gt;
+&lt;li&gt;1 月交付量超 39,000 台&lt;/li&gt;
+&lt;li&gt;2 月交付量超 20,000 台&lt;/li&gt;
+&lt;li&gt;3 月交付量超 20,000 台&lt;/li&gt;
+&lt;li&gt;4 月交付量超 30,000 台&lt;/li&gt;
+&lt;li&gt;5 月交付量超 30,000 台&lt;/li&gt;
+&lt;li&gt;6 月交付量超 30,000 台&lt;/li&gt;
+&lt;li&gt;7 月交付量超 30,000 台&lt;/li&gt;
+&lt;li&gt;8 月交付量超 30,000 台&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/88/7e/887e5889860e56c78df94d3fa8cb2cad.png" /&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/89/c4/89c44591fe56a782624a2104b254da0d.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;OpenAI 宣布已经实现「自动化 AI 研究实习生」&lt;/h1&gt;
+&lt;p&gt;9 月 6 日消息，OpenAI 发布博客宣布，已经达成去年秋季定下的&lt;strong&gt;自动化 AI 研究实习生&lt;/strong&gt;目标，同时披露 AI 智能体参与内部科研的实际情况，提出 AGI 要造福人类，需要公开讨论与民主治理。&lt;/p&gt;
+&lt;p&gt;官方指出，仅披露个别风险事件并不充分，公众需要了解前沿实验室内部顶尖 AI 的开发过程，才能有效参与 AI 发展决策。这套 AI 研究实习生可在人类监督下执行明确科研任务，完成资深研究员数日的工作量；OpenAI 计划在 2028 年 3 月冲击全自动 AI 研究员目标。但研究方向取舍、模型扩容、暂停、部署的全部决定权仍归人类，AI 仅负责执行任务。&lt;/p&gt;
+&lt;p&gt;2026 年以来，OpenAI 研究员大规模并发使用编码智能体，代码产出与实验数量显著上涨，但 AI 代理无法解决全部研发瓶颈，科研整体进度不会随代理用量线性增长。&lt;/p&gt;
+&lt;p&gt;OpenAI 表示，自动化 AI 研究可以降低高阶智能使用成本，协助解决对齐问题、搭建 AI 安全防线，但不应盲目推进快速递归自我改进（RSI），技术节奏取决于人类管控能力与社会风险判断。目前行业尚无安全实现完整对齐 RSI 的成熟方案，能力提升与安全对齐未必同步，一旦出现严重安全风险，公司会减速甚至暂停开发。&lt;/p&gt;
+&lt;p&gt;受此前 Hugging Face 安全事件影响，OpenAI 曾暂停部分模型强化学习训练，加固研究环境，将安全对齐贯穿模型全生命周期。OpenAI 称代理系统尚处于早期，即便没有监管强制，未来也会持续公开 RSI 相关进展，兼顾安全保密与信息透明度。&lt;/p&gt;
+&lt;p&gt;博文链接：https://openai.com/index/research-acceleration-view-inside-openai/（来源：OpenAI）&lt;/p&gt;
+&lt;h1&gt;华为、苹果正面交锋，折叠屏手机市场将迎「72 小时对决」&lt;/h1&gt;
+&lt;p&gt;9 月 7 日下午至 10 日凌晨，华为、小米、苹果将在 72 小时内接连发布各自的折叠屏旗舰手机。华为与苹果首次在折叠屏赛道正面交锋，小米同台竞技，三</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 06 Sep 2026 16:45:00 +0000</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>Travis Kalanick’s Atoms might be getting into the robotaxi business</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/06/travis-kalanicks-atoms-might-be-getting-into-the-robotaxi-business/</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr"/>
+      <c r="F329" s="2" t="inlineStr"/>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>The Uber founder has said that Atoms will allow him to complete "unfinished business."</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H329"/>
+  <dimension ref="A1:H338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14035,6 +14035,414 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:00:01+00:00</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>This Robot Will Draw Your Blood Now</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/blood-draw-robot-vitestro-aletta</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr"/>
+      <c r="F330" s="2" t="inlineStr"/>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;You sit down and put your arm in the cradle. You press a button. The machine takes it from there.&lt;/p&gt;&lt;p&gt; …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 07 Sep 2026 06:03:34 +0000</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>原生全模态技术战略闭环，智象（HiDream.ai）发布具身世界模型HiDream-O1-Embodied</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/485056.html</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr"/>
+      <c r="F331" s="2" t="inlineStr"/>
+      <c r="G331" s="2" t="inlineStr"/>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 07 Sep 2026 04:01:09 +0000</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>产业龙头领投！中科类脑完成数亿元B+轮战略融资</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/485039.html</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr"/>
+      <c r="F332" s="2" t="inlineStr"/>
+      <c r="G332" s="2" t="inlineStr"/>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 08:34:54 +0800</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>传字节开发实时空间视频生成模型，张一鸣亲自督导；微信内测「AI 社交」功能；华为小米同天发布折叠屏手机</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369965</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr"/>
+      <c r="F333" s="2" t="inlineStr"/>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/7b/88/7b881b35c114cb2ce3eefd6857067a31.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;消息称字节正开发实时空间视频生成 AI 模型：张一鸣亲自督导，最快下个月发布&lt;/h1&gt;
+&lt;p&gt;9 月 7 日消息，据彭博社报道，字节跳动正准备推出一款实时空间视频生成 AI 模型。创始人张一鸣正亲自督导这款新模型的研发工作，该模型计划最早于下月发布。&lt;/p&gt;
+&lt;p&gt;知情人士透露，张一鸣近期一直在协调公司各业务部门的协作，并调动 AI 资源及算力全力推进该项目。其中一位知情人士指出，发布时间尚未最终确定，计划仍可能发生变动。&lt;/p&gt;
+&lt;p&gt;据介绍，该模型基于字节跳动现有的电影级视频生成 AI 模型 Seedance 构建，将允许用户面向直播、短剧和游戏创建交互式虚拟世界。字节跳动发言人未回应置评请求。&lt;/p&gt;
+&lt;p&gt;知情人士称，张一鸣将空间视频模型定位为驱动整个生态的「飞轮（Flywheel）」&amp;mdash;&amp;mdash;该模型能够将用户置于高度沉浸的三维虚拟环境中，功能与谷歌的 Genie 类似。字节跳动得以将其自研 AI 模型、云计算底层资源，与旗下的内容平台以及 XR 业务分支 Pico 的硬件终端深度串联、协同发力。&lt;/p&gt;
+&lt;p&gt;字节跳动最新的模型旨在生成能够响应 Pico 头显用户语音或动作的虚拟世界。该模型致力于将生成空间内容这一计算密集型任务完全转移至云端，从而显著降低 VR 技术的初始使用成本。这一架构能够大幅减少头显设备本身的算力要求，为推出造价更低、配置更简化的硬件终端铺平道路。&lt;/p&gt;
+&lt;p&gt;同时，高速的内容生成能力还将推动行业竞争重心发生转移&amp;mdash;&amp;mdash;争夺用户的战线有望从比拼硬件参数规格，转向大型 AI 模型、算力基础设施以及内容分发平台。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/c8/73/c873c0358cfd96c397831500dc52c3be.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;微信内测「AI 社交」功能&lt;/h1&gt;
+&lt;p&gt;9 月 7 日消息，据报道，微信正在小范围内测一项名为「小微 AI 社交」的全新功能。用户只需向自己的 AI 助手「小微」下达指令，它就能直接找到好友的「小微」进行对话，代为完成约饭、协调日程等社交沟通。&lt;/p&gt;
+&lt;p&gt;与传统的「代发微信消息」不同，「小微 AI 社交」的核心是两个 AI 先聊，用户仅在授权与决策环节介入。具体流程为：用户向自己的「小微」提出诉求，由它前往好友的「小微」沟通；对方授权确认后，两个「小微」先行交流，再将结果带回，其间需要用户拍板时会提醒其确认。&lt;/p&gt;
+&lt;p&gt;这种机制尤其适用于社交意愿较低或对人际沟通存在顾虑的用户。日常中诸多细碎事务、初步意向试探、时间协调等环节，均可交由 AI 分身先行处理，有效降低面对面或即时文字沟通带来的心理负担。（来源: TechWeb）&lt;/p&gt;
+&lt;h1&gt;消息称三星进入人形机器人赛道，计划在明年 CES 2027 首秀&lt;/h1&gt;
+&lt;p&gt;9 月 7 日消息，据韩媒 sedaily 消息，三星电子正加快其人形机器人原型机的研发，计划在明年 1 月于美国拉斯维加斯举办的 CES 2027 上，首次公开其自主研发的人形机器人。&lt;/p&gt;
+&lt;p&gt;据悉，三星 DX 部门首席技术官兼总裁尹长贤（Janghyun Yoon）目前正同时挂帅机器人 RX 部门旗下的硬件与人工智能软件两大研发团队，全力推进产品迭代。报道称，在业内由单一核心高管统筹掌管负责机械驱动的硬件团队与负责感知决策的 AI 软件团队，极为罕见。&lt;/p&gt;
+&lt;p&gt;三星内部与业界普遍认为，在研发初期便将掌管机器人「AI 软件大脑」与「硬件本体」的技术负责人合二为一，是三星意在全面压缩研发周期的战略布局。究其原因，若继续沿用软硬件分别独立研发再行拼装的传统模式，将根本无法跟上当前人工智能技术的指数级演进速度。&lt;/p&gt;
+&lt;p&gt;为加速人形机器人的商业化落地，三星电子已密集布局并锁定了多项核心专利，涵盖人形机器人运动骨架核心的髋关节设计技术、下一代高灵巧度机械手，以及基于 AI 的运动控制技术。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/02/00/0200ae</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 07 Sep 2026 21:01:05 +0800</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>AI 时代，「种草」这件事会变成什么样？</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369962</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr"/>
+      <c r="F334" s="2" t="inlineStr"/>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/c4/64/c4644faeba0995c919271e68515708b1.png" /&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;作者｜靖宇 &lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;互联网时代，鲜有一个网站或者应用，能像小红书一样在不停的转换身份和功能的进化中，穿越周期。&lt;/p&gt;
+&lt;p&gt;对于现在的网民来说，你几乎能在小红书上面搜索到各种小妙招。它还是攻略集宝鉴，哪里旅游不踩坑全部奉献给小伙伴。&lt;/p&gt;
+&lt;p&gt;当然，没人能忘了，这是国内公认的「种草」平台，甚至，「种草」这两个字的本源，就来自小红书本身。&lt;/p&gt;
+&lt;p&gt;在 AI 时代，信息和内容以指数级的增速被生产出来，一方面确实拉低了「种草内容」的创作门槛，但另一方面，AIGC 内容的泛滥，也让用户对平台内容产生了「过敏」，降低了对于内容的信任。&lt;/p&gt;
+&lt;p&gt;对于营销从业者来说，这可能是一个新时代的挑战。&lt;/p&gt;
+&lt;p&gt;如何在 AI 时代，让品牌能够更精准的找到目标用户，更重要的是，如何让品牌在这样一个内容泛滥的时期，重新赢得用户的「信任」？&lt;/p&gt;
+&lt;p&gt;不久前，极客公园请到了小红书种草产品负责人许晴、悦普集团 COO 鲍白白，进行了一场深入的探讨，想要弄清，在 AI 时代，「种草」这件事将会如何进化？品牌又该如何借助平台的力量，重新获得来自用户的「信任」？&lt;/p&gt;
+&lt;p&gt;本场对谈精华要点：&lt;/p&gt;
+&lt;p&gt;AI 越擅长「完美」，人越渴望那种有取舍、有态度、带着主观温度的表达。&lt;/p&gt;
+&lt;p&gt;AI 发展得越厉害，人与人之间信任的经营会变得更难能可贵。&lt;/p&gt;
+&lt;p&gt;小红书对应的商业产品在解决的问题，就是帮助品牌从追流量转向经营用户。&lt;/p&gt;
+&lt;p&gt;把繁琐的工作交给AI处理，把人解放出来，去做更多有创意、有价值的事情。&lt;/p&gt;
+&lt;p&gt;下面是本场对谈的文字记录：&lt;/p&gt;
+&lt;p&gt;&lt;a id="heading_0"&gt;&lt;/a&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;AI 如何影响消费决策 &lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;极客公园：两位在日常生活里，有没有哪个瞬间让你们真正感觉到，AI 改变了自己做消费决策的方式？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;许晴： &lt;/strong&gt;AI 现在已经进到了我每一个稍微大一点消费额的决策链路中。比如我最近在看扫地机器人，我会告诉AI说家里有宠物、在北京、预算大概 4000 块钱，你建议我怎么选，分别有什么优缺点。它会给一个非常严格的对比报告，三款产品分别有什么优点、什么缺点。但你说看到这个我就知道该怎么买吗？也不完全是。我可能还是会去小红书里面看一看，有没有人在吐槽它是不是缠毛发，是不是边角扫不干净，或者它跨越障碍的能力非常差。&lt;/p&gt;
+&lt;p&gt;你会去看真实用户有没有吐槽，做完这一步之后我可能才会说 OK ，就定了，就买这个产品。所以 AI 现在在我的决策链条中，基本上就是帮我做初筛，不需要我自己去搜集非常多的材料了。初筛完了之后，我可能还是会去小红书做一些校准的工作，看看 UGC 的真实评论、吐槽和夸奖，然后再决定到底买哪一个更适合我。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;极客公园：Demi 有什么使用 AI 帮助消费决策的经验吗？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;鲍白白（Demi）： &lt;/strong&gt;我会用 AI 做一些初筛的工作，或者问它说我选择一个产品，判断的标准应该是什么。但真正要做消费决策，我肯定还是要去小红书这样有真实用户声音的平台上，做最终的校验。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;极客公园： 越来越多人做消费决策时，会优先来小红书找答案，这背后的核心原因是什么？消费者的品味越来越刁钻，更看重能不能「种在心巴上」。许晴怎么看？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;a id="heading_1"&gt;&lt;/a&gt;&lt;strong&gt;&lt;em&gt;02&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;触达更容易，理解用户为何更难 &lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;许晴： &lt;/strong&gt;触达用户，只要花钱其实都能做到。但说实话，怎么走到用户的心坎里，怎么能让他获得信任，这是现在所有品牌方在种草上遇到的最大难题。&lt;/p&gt;
+&lt;p&gt;就像我们刚刚讲的，怎么去理解用户？最早期大家的做法是，我来预估你是什么年龄、什么性别、在哪个城市，这是最早期的「理解用户」。后来大家会发现，我还得关心你的兴趣。你是喜欢美妆还是喜欢汽车，是喜欢户外还是喜欢宅家，找到你的兴趣我才知道给你推什么样的内容。&lt;/p&gt;
+</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 07 Sep 2026 18:32:48 +0800</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>判断用不用你的软件，Agent 只需 500 个 Token</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369960</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr"/>
+      <c r="F335" s="2" t="inlineStr"/>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;作者｜宇航猿&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold; color: #000000;"&gt;编辑｜靖宇&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;现在几乎每个开发者都在用 AI Agent 干活。Cursor、Claude Code、Windsurf、Gemini CLI，各种 Coding Agent 已经深度嵌入了日常工作流。一个普遍的体验是，让 Agent 去调某些 API 或者集成某个服务，有些丝滑得像开了挂，有些则反复报错，甚至直接编造出一个根本不存在的接口。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;大多数人把这归结为：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;「 &lt;span style="font-weight: bold;"&gt;模型还不够聪明 &lt;/span&gt;」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;但如果反过来想， &lt;span style="font-weight: bold;"&gt;不是 Agent 不够聪明，而是有些产品天然对 Agent 友好，有些则天然对 Agent 充满敌意 &lt;/span&gt;。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;这像极了十几年前的 SEO。你觉得自己的网站内容很好，但 Google 就是不收录，问题不在 Google 的算法，而在于你的网站没有做搜索引擎优化。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;今天同样的事情正在 Agent 身上重演，只不过这一次，大多数产品甚至不知道自己正在被「审判」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;Google Cloud AI 工程总监 Addy Osmani 今年 4 月给这件事起了一个名字，叫 AEO（Agentic Engine Optimization），翻译过来就是：&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;「 &lt;span style="font-weight: bold;"&gt;Agent 引擎优化 &lt;/span&gt;」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;如果说 SEO 是为 Google 爬虫优化，AEO 就是为 AI Agent 优化。 &lt;/span&gt;这不是一个遥远的概念，而是一套已经可以落地的具体实践。在 Agent 正在成为软件产品最重要的「用户」的今天，到底什么样的设计，能让 Agent 更方便使用，可能决定了未来软件行业的真正走向。&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;span style="font-weight: bold; font-style: italic; color: #000000;"&gt;01&lt;/span&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;span style="font-weight: bold;"&gt;Agent 怎么读文档？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;下面是一个用户非常日常的场景。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;一个工程师打开 Cursor，让 Agent 帮他接入一个支付 API。Agent 发出了一个 HTTP 请求，拿到了文档页面，400 毫秒后做出了判断。但这份文档有将近 20 万个 Token，远远超出了 Agent 的上下文窗口容量。Agent 没有报错，没有提示，而是默默放弃了这份文档，转而根据自己训练数据里的记忆，编造了一个接入方案。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;结果呢？用户拿到了一段看起来很合理的代码，跑起来却怎么都不通，花了两个小时 debug 才发现 Agent 给的是一个早就废弃的 endpoint。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;而在这家支付公司的 Google Analytics 后台，这次访问只留下了一条记录。滚动深度为零，页面停留时间 400 毫秒，没有任何点击。在传统分析框架里，这就是一个「低质量访</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 07 Sep 2026 18:26:42 +0800</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>童欣加入 Meshy，3D 世界终于等到自己的「互联网时刻」</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369959</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr"/>
+      <c r="F336" s="2" t="inlineStr"/>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;&lt;strong&gt;作者｜Cynthia&lt;/strong&gt;&lt;/p&gt;
+&lt;div&gt;
+&lt;div class="ace-line ace-line old-record-id-doxcnGNZOxqQ3Yyy0gBNf36Xrrc"&gt;&lt;strong&gt;编辑｜ 郑玄&lt;/strong&gt;&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-doxcnGNZOxqQ3Yyy0gBNf36Xrrc"&gt;&amp;nbsp;&lt;/div&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong&gt;2016 年， 后来被反复宣布了无数次元年的 VR 产业，正式迎来了第一次爆发浪潮。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;这一年 3 月 28 日，Oculus Rift 首批发货，售价 599 美元的产品很快被销售一空；两天后，曾在微软 Windows 10 发布会上被重点推介的 3000 美元 HoloLens 开发者版也迎来正式发售，此前围绕 HoloLens 举办的 11 城开发者巡展，名额开放 90 分钟便全部订满。同一时间还未正式发售 PlayStation VR 的索尼，则直接宣布已经有 230 多家开发商和发行商正在为它制作内容。&lt;/p&gt;
+&lt;p&gt;资本比硬件更为激进。高盛在当年年初把 VR/AR 直接称作下一代计算平台的竞争者；2 月，连消费级产品都还没有推出的 Magic Leap，则是一轮融资就拿到 7.935 亿美元，投后估值达到 45 亿美元。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;至此，硬件、资本和开发者，都已形成共识。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;只有中国计算机图形最知名的学者、时任微软亚研院首席研究员&amp;mdash;&amp;mdash;童欣，是个例外。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;论技术身位，那时的他已经在微软亚洲研究院工作了 17 年，负责网络图形组也有六年。论研究方向，他应该是当时最有理由相信 VR 爆发的那群人之一。&lt;/p&gt;
+&lt;p&gt;那一年的 11 月 14 日，微软亚洲研究院在北京成立院友会。近 200 位来自产业和学术界的院友回到中关村微软大厦，下午一场题为「让世界充满 AI」的研讨会上，九位演讲嘉宾里，有刚刚离开微软加入旷视的孙剑，有浙江大学周昆、地平线余凯。主持人宣布研讨会开始后，第一个被请上台的人，正是童欣。&lt;/p&gt;
+&lt;p&gt;但他上台之后，没有讲某项最新成果。&lt;/p&gt;
+&lt;p&gt;他说，几天前接到演讲通知，他「非常焦虑和紧张」，然后，他问了一个和整个行业情绪不太合拍的问题：互联网加文字，有了网络文学、微博和维基百科；互联网加图片，有 Instagram、美图；互联网加视频，有 YouTube、爱奇艺、直播和网红。十几年过去，几乎每一种内容都在互联网里爆炸过一次。回头再看看 Graphics，却好像什么都没发生。&lt;/p&gt;
+&lt;p&gt;他拿当时流行的「风口上的猪」开玩笑：&lt;strong&gt;「我这么瘦的一个人，站了这么久，怎么还没飞起来？」&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;「这到底出了什么问题？」&lt;/p&gt;
+&lt;p&gt;最后，他把原因归成两个词：&lt;strong&gt;Everyone&lt;/strong&gt;和&lt;strong&gt;Everywhere&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;Everyone，是每个人都可以创造内容；Everywhere，是这种内容能够跨越设备和场景，在更多地方生产、传播和消费。&lt;/p&gt;
+&lt;p&gt;当年，即使 AR、VR 爆火，但专业建模软件仍需要艺术家学习多年，扫描仪、光穹、动捕设备价格高昂，还需要专门场地和操作人员；到了消费端，号称三维的内容，大多数仍然被塞进二维屏幕，用户继续用鼠标、键盘和 gamepad 操作。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;一个不能真正走进普通人世界的技术，无论市场炒作多热闹，始终逃离不过昙花一现的宿命。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;但 10 年后，这个故事在另一个地方听到了回响。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;2026 年 9 月，童欣已经正式加入胡渊鸣创办的 Meshy。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;至此，一家想要把一句话、一张图生成 3D 做成千万用户产品的公司，迎来了它的首席科学家。&lt;/p&gt;
+&lt;p&gt;一个做了二十五年图形学的学者，终于走到了自己十年前那个问题的下一页。&lt;/p&gt;
+&lt;h1&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p&gt;&lt;strong&gt;提问的人&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;1999 年，童欣从清华大学博士毕业，加入了此时成立不到一年的微软亚洲研究院。&lt;/p&gt;
+&lt;p&gt;这是一家后来成为中国 AI 行业黄埔军校的机构。互联网和云计算时代，常务副院长王坚 2008 年去了阿里，第二年创办阿里云；上</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 07 Sep 2026 17:29:26 +0800</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>「AI Native 」不是魔法，「创业者」这三个字依旧厚重</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369955</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr"/>
+      <c r="F337" s="2" t="inlineStr"/>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;上个月，我集中跑了一趟上海和深圳，也跟几位在 AI 前沿一线折腾的创业者深聊了几次。&lt;/p&gt;
+&lt;p&gt;齐俊元的新产品干了半年，我问他这阶段最大的收获是什么，他说了句挺朴素的话：「真的伸手去干的时候，你会发现认真还是挺重要的。」&lt;/p&gt;
+&lt;p&gt;这话听着很普通，事后却让我不断想起，放到当下的行业环境下看，也挺让人警醒的。&lt;/p&gt;
+&lt;p&gt;3 年来深入聊过至少 200 位 AI 创业者了，现在有一些已经有点丧气了。「AI 应用已经不能投了」的观点也在业内流传。觉得这不能干，那不能干，机会没了，窗口关了。但你反过来看，那些真正跑出来的产品，都有一个共同点&amp;mdash;&amp;mdash;特别笃定地扎在一个方向上，然后往死里抠细节。&lt;/p&gt;
+&lt;p&gt;比如俊元做的产品，真正让我惊异的不是产品形态的创新，而是远超我想象的数据表现。你问他怎么做到的，他说就是要一点一点抠，数据、框架、工程，全都要优化，接下来要做后训练，说的全是细活。一步一步，日拱一卒。&lt;/p&gt;
+&lt;p&gt;Vivix 刘宇那边也是。他给我展示了他们模型的生成效率，大概 10 秒能出 9 个音画同步的视频。三年前 Demi 他们做 Pika 的时候，3 分钟出 4 个，那会儿都觉得快得不行了。平时我自己在即梦上，一条视频都要等半天，看到 10 秒 9 个的表现，是让我很惊讶的。我问怎么做的，他说首先是模型的目标不一样，所以框架不一样。但真正重要的是，因此需要在大概 40 多个地方做工程优化，每个地方优化一点，叠加在一起是上百倍的提升，而且还可以把成本做到更低。&lt;/p&gt;
+&lt;p&gt;没什么新鲜的。就是细，就是较劲，就是认真。一点点抠，抠到最后积小胜为大胜。&lt;/p&gt;
+&lt;p&gt;所以我就在想：&lt;strong&gt;AI Native 创业者的核心，可能不在「AI Native」，而在「创业者」。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;今天行业里很多创业者遇到的瓶颈，可能不是「不够 AI」，也不是时代没有机会，而是活儿不够细、基本功出了问题。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;AI Native 带来的东西是什么？人不多，执行快，不需要拿很多钱就能做出东西，建设能力强。这是「灵」的部分。AI 给了我们更多机会，也更容易失焦。&lt;/p&gt;
+&lt;p&gt;但成为一名合格创业者需要的硬核特质，在这个时代并没有改变。世界观要 solid，路径设计要清晰，设完目标之后要有耐心，要较劲，要能扎硬寨打呆仗。这是「拙」的部分。&lt;/p&gt;
+&lt;p&gt;问题就出在这，「灵」和「拙」之间是会有冲突的。当你很适应前面那种快速完成的方式，做到 60 分很快，但要做到 80 分、90 分可能要花 10 倍的时间。然后你就觉得这 10 倍的时间难以忍受，就放弃了。&lt;/p&gt;
+&lt;p&gt;这就有问题了。&lt;/p&gt;
+&lt;p&gt;做 go to market 服务商的朋友也和我提到，很多创始人自己不擅长营销，但想当甩手掌柜，觉得找供应商花了钱就能得到效果。在创业早期阶段，你的产品还要进化，要 pivot，你要的是在这个过程中理解市场、反馈回产品。&lt;strong&gt;这个阶段，营销要的不是极致的效果，而是极致的效率。&lt;/strong&gt;如果你只是把钱花出去或招个人代劳，你就浪费了把 GTM 这事亲自摸一遍的学习机会。营销在今天是竞争力的重要组成部分，如果不会，却不真正投入，那结果不会好。&lt;/p&gt;
+&lt;p&gt;说白了还是那个问题：没有认真，没有在自己不擅长的地方花时间。&lt;/p&gt;
+&lt;p&gt;例如 WorkBuddy，既不是开创产品形态的第一个，也不是最顶尖的。很多技术极客可能会吐槽它：「技术没啥突破」、「把自由度封装死了」、「太傻瓜了」。但你去看它切入的人群和交付的价值&amp;mdash;&amp;mdash;对人群的理解、价值交付、UI、交互、游戏化设计、运营策略，全是细节。过去腾讯那些 To C 的小连招，用得非常丝滑。&lt;/p&gt;
+&lt;p&gt;这些东西不是开会开出来的创新，也不是 AI 带来的不一样，是过去这么多年积累带过来的基本功，长在组织里的。&lt;/p&gt;
+&lt;p&gt;所以我说，今天创业者的基本功反而是短缺的。AI Native 那套既可以学也可以用，它相对简单。反而是属于创业者的核心属性，是需要沉淀和修炼的。&lt;/p&gt;
+&lt;p&gt;你的产品或许可以调用世界上最好的模型，但创业者自己的「模型」，无处调用。只能看「历史数据集」的积累，和行进中「强化学习」的效率。&lt;/p&gt;
+&lt;p&gt;环境当然不断在变化，但变化中才体现「创业者」三个字的含金量。创业者永远值得信赖的「种族天赋」其实就是一点：&lt;strong&gt;只要&lt;/strong&gt;&lt;strong&gt;你要解决的问题是真的，能专注、&lt;/strong&gt;&lt;strong&gt;活够细，&lt;/strong&gt;&lt;strong&gt;你就永远&lt;/strong&gt;&lt;strong&gt;有机会。&lt;/strong&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 04 Sep 2026 23:36:14 +0000</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>XDOF, just 3 months out of stealth, is in talks for a Series B at a $1.2B valuation</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/04/xdof-just-three-months-out-of-stealth-is-in-talks-for-a-series-b-at-a-1-2b-valuation/</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr"/>
+      <c r="F338" s="2" t="inlineStr"/>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>The round is being raised just months after the robot data startup exited from stealth.</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H338"/>
+  <dimension ref="A1:H341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14443,6 +14443,157 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 03:22:17 +0000</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>深度智控获宁德时代、沙特阿美战投等重磅加码，加速打造物理AI时代算力与能源底座</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/485784.html</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr"/>
+      <c r="F339" s="2" t="inlineStr"/>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>近日，物理AI企业深度智控（DeepCtrls）完成新一轮B+轮数亿元融资。</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 08:37:42 +0800</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>折叠屏 iPhone 初期产量受限，每日仅数百部；环比增长 379%，腾讯 HY4 登顶全球大模型调用榜；特斯拉时隔 19 个月再降价｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370026</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr"/>
+      <c r="F340" s="2" t="inlineStr"/>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/42/74/4274f5b9e7a48eafe6b38b65bab75de0.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;消息称苹果折叠屏 iPhone 初期产量受限，每日仅数百部&lt;/h2&gt;
+&lt;p&gt;9 月 8 日，据日经中文网报道，根据多位知情人士指出，市场期待已久的首部苹果折叠 iPhone，由于苹果极为严格的质量管控标准，初期生产量每天仅有「数百部」，而苹果及其供货商正全力加快产量爬坡。&lt;/p&gt;
+&lt;p&gt;熟悉情况的供应链主管向《日经亚洲》透露：「苹果设定了极高的质量标准，在正式量产之前，8 月又追加了一轮试产」。该人员表示：「截至 8 月下旬日产量仅数百部。按这样的初期产能计算，有可能难以满足市场需求」。&lt;/p&gt;
+&lt;p&gt;《日经亚洲》先前报导，苹果计划今年内生产 800 万~1000 万部折叠屏 iPhone，并希望凭借这款全新外型设计的机型激发市场需求，进而推升营收。（来源：DoNews）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/6c/6a/6c6afced36fd779269cff2b35c44e290.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 最强 AI 生图模型：ChatGPT Images 2.5 登场，延迟降低 50%、新增 Sketch 草图&lt;/h2&gt;
+&lt;p&gt;9 月 9 日，OpenAI 官宣发布 ChatGPT Images 2.5，图像生成延迟最多降低 50%，并新增 Sketch 草图参考、模板库、图片内评论标注等实用功能，是该公司当前最先进的图像生成模型。&lt;/p&gt;
+&lt;p&gt;相比较 2026 年 4 月发布的 Images 2 模型，Images 2.5 重点降低了图像生成延迟，在细节锐度、自然光照和纹理丰富度方面均有提升的情况下，延迟最多降低 50%。&lt;/p&gt;
+&lt;p&gt;功能方面，ChatGPT Images 2.5 引入 Sketch 功能。用户可通过输入「@Sketch」调用该功能，用户可在对话中直接绘制草图，再补充风格和细节描述，让模型将草图转化为完整图像。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/47/bf/47bf096564cae7ebd67f7374149907d8.png" /&gt;&lt;/p&gt;
+&lt;p&gt;产品还新增海报、商品等常见创作格式的模板，降低创作门槛。用户可以直接在图像上添加批注，以聚焦具体修改区域，并可在分享图像时附带原始提示词。&lt;/p&gt;
+&lt;p&gt;在 API 调用模型方面，OpenAI 提供了两款模型：&lt;/p&gt;
+&lt;ul class=" list-paddingleft-2"&gt;
+&lt;li&gt;
+&lt;p&gt;GPT-Image-2.5 Flare：面向多数 API 图像生成应用，适用于创作者内容、社交内容、产品体验、视觉搜索、快速原型和高批量生成等场景。&lt;/p&gt;
+&lt;/li&gt;
+&lt;li&gt;
+&lt;p&gt;GPT-Image-2.5 Sunburst：则面向对编辑控制要求更高的工作流。OpenAI 建议将其用于成品级营销素材和精修产品图等场景，但其生成时间更长。&lt;/p&gt;
+&lt;/li&gt;
+&lt;li&gt;
+&lt;p&gt;API 支持多种分辨率，包括 1024&amp;times;1024、2048&amp;times;2048、3840&amp;times;2160（4K 横向）等，单边最长不超过 3840 像素，总像素数介于 655,360 至 8,294,400 之间。（来源：IT 之家）&lt;/p&gt;
+&lt;/li&gt;
+&lt;/ul&gt;
+&lt;h2&gt;&amp;nbsp;&lt;/h2&gt;
+&lt;h2&gt;微软发布 Opal：用户只需提目标，AI 跑全流程交付成品&lt;/h2&gt;
+&lt;p&gt;9 月 7 日，微软首席执行官萨提亚 &amp;middot; 纳德拉在 X 平台发布推文，宣布为 Microsoft 365 Copilot 推出全新 AI 功能 Project Opal，定位是在可控的安全环境中，让用户规划和执行复杂、长周期任务的 AI 智能体。&lt;/p&gt;
+&lt;p&gt;微软表示 Project Opal 的核心，是在可控制、可追踪的环境内，是让 AI 从处理快速问题，逐步覆盖委派型工作和长期运行的自动化任务。用户交代任务后，它可连续工作数小时或数天，自动完成「找素材、做表格、生成 PPT、发给同事」的完整流程。&lt;/p&gt;
+&lt;p style="text-align: center;"</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 15:29:19 +0800</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>IFA 2026 现场：下一代穿戴设备的本质，是把录音笔和摄像头戴在身上</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370007</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr"/>
+      <c r="F341" s="2" t="inlineStr"/>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;span&gt;本文转载自 Hardwire，欢迎关注，共同看见硬件行业新风向 👇&lt;/span&gt;&lt;/section&gt;
+&lt;section class="mp_profile_iframe_wrp"&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;hr /&gt;
+&lt;section&gt;
+&lt;section&gt;
+&lt;section&gt;&lt;span&gt;&amp;nbsp;&lt;/span&gt;&lt;/section&gt;
+&lt;section&gt;&lt;img alt="图片" class="rich_pages wxw-img" src="https://imgslim.geekpark.net/uploads/image/file/ce/a3/cea3aa6b04607fcc03c36968087c533d.jpeg" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;/section&gt;
+&lt;section class=""&gt;屏幕消失不是做减法，是把「显示」换成了「采集」。&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474; font-family: Optima-Regular, PingFangTC-light;"&gt;&lt;br /&gt;作者｜张勇毅&lt;/strong&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474;"&gt;&lt;br /&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474; font-family: Optima-Regular, PingFangTC-light;"&gt;编辑｜&lt;strong&gt;靖宇&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;section&gt;&lt;strong style="text-indent: 0em; font-size: 16px; color: #375474;"&gt;&lt;strong&gt;&amp;nbsp;&lt;/strong&gt;&lt;/strong&gt;&lt;/section&gt;
+&lt;/section&gt;
+&lt;/section&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;IFA 开幕前一天，小米在柏林把手环 11 端了出来。还是 1.72 英寸的屏幕，亮度从上一代的 1500 尼特提到 2000 尼特，国内 289 元起，9 月 7 日首售。官方通稿的第一个卖点，就是这块屏幕在太阳底下有多清楚。&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;同一周的同一个展馆里，另一批穿戴设备正在把屏幕拆掉。&lt;/p&gt;
+&lt;p style="margin: 25px 8px 0px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1.75;"&gt;&lt;img alt="图片" class="rich_pages wxw-img js_img_placeholder wx_img_placeholder" src="https://imgslim.geekpark.net/uploads/image/file/66/9f/669fe09ee949011c4fb2d87699d49c56.jpeg" /&gt;&lt;img class="rich_pages wxw-img" /&gt;&lt;/p&gt;
+&lt;p style="margin: 0px 8px 25px; text-align: justify; color: #000000; letter-spacing: 1px; font-size: 16px; line-height: 1em;"&gt;&lt;span&gt;会场对面地铁站附近，Plaud 的广告｜图片来源：极客公园&lt;/span&gt;&lt;/p&gt;
+&lt;p style="margin: 25px 8px; text-align: justify; color: #000000; letter</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H341"/>
+  <dimension ref="A1:H346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14594,6 +14594,220 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 15:38:04 GMT</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>“超脑+狼族”最新全阵容亮相！京东物流打造供应链应用场景最多、规模最大的AI具身机器人军团</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/ZebW8Yc4QTzrbdJxagCc?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr"/>
+      <c r="F342" s="2" t="inlineStr"/>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/ZebW8Yc4QTzrbdJxagCc?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 04:52:12 +0000</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>具身机器人能搞定超市盘点吗？全球七万门店正在给出答案</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/486280.html</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr"/>
+      <c r="F343" s="2" t="inlineStr"/>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>从Demo到货架，这两家公司要让具身智能算得过账</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 08:58:59 +0800</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>苹果进入特努斯时代，首发 15999 元折叠屏 iPhone；Deepseek 被曝备战科创板 IPO；谷歌埃森哲组建千人 FDE 团队 | 极客早知道</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370089</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr"/>
+      <c r="F344" s="2" t="inlineStr"/>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/96/95/96956c207062accdbf79712fe34663cd.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果首款折叠 iPhone Duo 亮相，国行 15999 元起&lt;/h2&gt;
+&lt;p&gt;北京时间 9 月 10 日凌晨，苹果发布首款折叠手机 iPhone Duo，国行 15999 元起，10 月 16 日开启预售，23 日正式发售。同场推出 iPhone 18 Pro 系列，9999 元起；标准版 iPhone 18 推迟至明年春季发布。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/fb/0b/fb0bcf701538653d1701c85b5f50534c.png" /&gt;&lt;/p&gt;
+&lt;p&gt;该机采用书本式内折设计，内外屏尺寸与小米 18 Fold 接近，价格高出 5000 元。机身重 254 克，厚度在同类折叠机型中偏厚重，但支持 IP68 防水。机型取消长焦镜头与面容 ID，改用侧边 Touch ID，搭载 A20 Pro 芯片。iOS 27 首次加入手机分屏功能，后续还将支持 Apple Pencil。&lt;/p&gt;
+&lt;p&gt;此外，Apple Watch Series 12 新增对话摘要功能，AirPods 5 基础款首次搭载主动降噪。多款 AI 相关新功能暂未在国内上线。苹果仅优化了折叠屏软件适配，并未解决行业普遍存在的重量与高价难题。（来源：极客公园）&lt;/p&gt;
+&lt;p&gt;关联阅读：&lt;a href="https://www.geekpark.net/news/370088" title="苹果第一台折叠 iPhone，15999 元起"&gt;苹果第一台折叠 iPhone，15999 元起&lt;/a&gt;&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/60/cc/60cc8f955f2414a8be40cf2ea03d7e0f.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 企业收入反超 C 端&lt;/h2&gt;
+&lt;p&gt;OpenAI 企业业务持续增长。弗莱尔表示，今年年初，公司 60% 收入来自 ChatGPT 个人用户，剩余部分来自企业客户；如今这一收入结构已经反转。她补充道，6 月至 7 月，公司整体年化营收增长 20%，企业业务年化营收增幅达到 32%。&lt;/p&gt;
+&lt;p&gt;为追赶 Anthropic，OpenAI 正全力拓展大型企业客户。Anthropic 最快将于今年秋季上市，募资规模有望超过 1000 亿美元。弗莱尔希望转变面向企业客户的营收模式。她计划不再依据客户消耗的令牌（模型读写的基础信息单元）计费，而是转向基于价值的收费方式。&lt;/p&gt;
+&lt;p&gt;据一位了解相关数据、但未获授权公开发布信息的匿名人士透露，尽管 OpenAI 预计到 2030 年算力投入将达到约 7500 亿美元，但公司仍然深感算力严重不足。（来源：新浪科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;京东计划 5 年采购 300 万台机器人&lt;/h2&gt;
+&lt;p&gt;9 月 9 日，在 JDD 京东全球科技探索者大会上，京东物流新发布五款「狼族」机器人全新产品和技术，包括 7x24 小时无人药房自动作业的「母狼」、为冷链场景打造的料箱货到人「智狼」低温版、全新具身拣选机器人「仓狼」、采用 L4 级自动驾驶能力的「独狼」第六代智能配送车 Plus 版、行业首个支持全无人化运营的物流无人机「飞狼」L05，以及在分拣场景规模化应用落地的具身灵巧臂「异狼」。&lt;/p&gt;
+&lt;p&gt;据悉，京东物流致力于打造全球最大规模的具身机器人应用军团。未来五年，京东计划采购超过 300 万台机器人、100 万台无人车和 10 万架无人机，进一步推动物流全流程自动化升级。（来源：新浪科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;谷歌计划在芬兰投入至少 130 亿欧元用于 AI 基建，为其在欧洲最大单笔投资&lt;/h2&gt;
+&lt;p&gt;9 月 9 日消息，Alphabet 旗下谷歌正在芬兰推进其在欧洲规模最大的单笔投资，计划投入至少 130 亿欧元，用于建设人工智能基础设施。&lt;/p&gt;
+&lt;p&gt;谷歌当地时间周三在一份声明中表示，未来两年，公司将在芬兰至少建设 3 座新的数据中心，同时扩建位于该国东南部城市哈米纳（Hamina）的现有数据中心。&lt;/p&gt;
+&lt;p&gt;谷歌选择芬兰，很大程度</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 09 Sep 2026 15:07:04 +0800</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>千问办公发布多人工作台，重写企业软件的最后一公里</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370061</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr"/>
+      <c r="F345" s="2" t="inlineStr"/>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+&lt;div class="ace-line ace-line old-record-id-doxcntaMvY6KwqUZ5hOR3LwALjb"&gt;&lt;strong&gt;作者｜Cynthia&lt;/strong&gt;&lt;/div&gt;
+&lt;div class="ace-line ace-line old-record-id-doxcnYKZJn1U1oTy0cDkk2kTfcf"&gt;&lt;strong&gt;编辑｜郑玄&lt;/strong&gt;&lt;/div&gt;
+&lt;/div&gt;
+&lt;p&gt;2026 年 2 月 3 日，由 Anthropic 带头，华尔街替 SaaS 写好了讣告。&lt;/p&gt;
+&lt;p&gt;几天前，Anthropic 正式官宣把 Claude Cowork 的插件能力扩展到法律、销售、金融等知识工作。与普通聊天机器人不同，这些插件可以携带部门工作流、调用外部工具和数据，并按照预设规则完成一段具体工作。&lt;/p&gt;
+&lt;p&gt;市场很快把这种能力翻译成了另一个词：替代。2 月 3 日，高盛一篮子美国软件股单日下跌 6%；彭博统计，当天软件、金融服务和资产管理相关股票合计蒸发约 2850 亿美元。一天之后，Wind 香港 SaaS 指数又下跌 6.39%，板块总市值缩水近 150 亿港元。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;七个月后，这个问题又进一步从资本市场蔓延到了产品端。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;9 月 7 日，千问办公上线多人工作台。用户不再先选择我要做 CRM 或者我要做项目管理，只要说清有哪些角色、每个人要做什么、需要保存哪些数据。系统据此生成一个可以在线发布的协作应用，带角色权限、云端数据库和管理后台，最多支持百人同时在线。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/ff/58/ff5870e78c8fde3b2efa82d144920e92.png" /&gt;&lt;/p&gt;
+&lt;p&gt;「千问办公」产品首页&lt;/p&gt;
+&lt;p&gt;在这背后，数据库、权限、后台、状态流转这些过去构成一套专业企业软件的基本零件，开始由 Agent 根据一段业务描述临时组装出来。&lt;/p&gt;
+&lt;p&gt;而这，也让这 SaaS 与企业办公 Agent 之间的关系变得更加微妙：过去二十年，SaaS 解决了一个巨大的问题：寻找企业办公的公约数，然后将软件低成本复用，统一升级、云端部署、订阅收费，软件公司的边际交付成本因此大幅下降。&lt;/p&gt;
+&lt;p&gt;但它始终没有彻底解决另一个问题：&lt;strong&gt;软件怎么低成本地适配一家具体公司甚至一段具体的业务流程。但办公 Agent 做到了。&lt;/strong&gt;&lt;/p&gt;
+&lt;h1 style="text-align: center;"&gt;&lt;strong&gt;&lt;em&gt;01&lt;/em&gt;&lt;/strong&gt;&lt;/h1&gt;
+&lt;p style="text-align: center;"&gt;&lt;strong&gt;国产 SaaS，为什么 20 年了还没爆发？&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;中国 SaaS 大概是科技行业里最擅长过元年的赛道。&lt;/p&gt;
+&lt;p&gt;至少在 2007 年前后，SaaS 就已经逐渐在国内成为显学。那时中国管理软件市场还是一个很有江湖气的世界：南金蝶、北用友。两家公司从财务软件一路打到 ERP，全国铺销售、实施和服务团队。&lt;/p&gt;
+&lt;p&gt;到了 2015 年，伴随移动互联网、云计算和资本进入，行业再次迎来公认的大规模扩张期，中国 SaaS 市场规模就已经达到 10.5 亿美元，同比增长 30%。研究机构们，后来也将这一年称为中国 SaaS「元年」。&lt;/p&gt;
+&lt;p&gt;最近一次，则是疫情催化下，2021 年企业服务融资再度火热，媒体又一次开始讨论「新的 SaaS 元年」。到 2023 年，中国 SaaS 市场规模已经达到 581 亿元，仍然同比增长 23.1%；但另一边，从 2021 年至 2023 年，SaaS 投融资事件数量减少了 71%，融资金额下降 85%。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;元年复元年背后，企业数字化需求从来没有消失，只是行业一次又一次高估了需求增长转化成软件规模化利润的速度。&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;原因就藏在 SaaS 最漂亮的商业模型里。&lt;/p&gt;
+&lt;p&gt;SaaS 的经济性建立在复用上。同一套产品卖给第一百家公司和第一万家公司，研发投入不需要同步扩大一百倍。但企业越大，组织结构、审批制度、行业规则和历史系统往往越复杂。&lt;/p&gt;
+&lt;p&gt;所以中国 SaaS 长期真正卡住的，并不是企业愿不愿意数字化，而是一组很难同时成立的条件：客户希望软件越来越懂自己，软件公司却只有让客户尽量使用同一套东西，才能拥有最理想的规模经济。&lt;/p&gt;
+&lt;p&gt;这也是为什么过</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 00:00:37 +0000</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>AI research startup Listen Labs scrubbed a $1.5B funding round for Salesforce talks</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/09/ai-research-startup-listen-labs-scrubbed-a-1-5b-funding-round-for-salesforce-talks/</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr"/>
+      <c r="F346" s="2" t="inlineStr"/>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>Listen Labs walked away from a signed Series C term sheet from Menlo Ventures, sources say.</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H346"/>
+  <dimension ref="A1:H360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14808,6 +14808,565 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 01:36:27 +0000</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>机器人触觉怎么实现？一文看懂五大技术路线</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12794</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr"/>
+      <c r="F347" s="2" t="inlineStr"/>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>机器人触觉传感器主要形成了五条技术路线：压阻式、压电式、电容式、光学式和磁感应式</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 04:23:53 +0000</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>知行具身首发千赫兹视触觉传感器 Imprint X</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12738</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr"/>
+      <c r="F348" s="2" t="inlineStr"/>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>知行具身推动了视触觉感知领域从“一帧一帧看”，转向“变化发生就能捕捉”的神经拟态触觉感知，成为行业首家事件驱动/神经拟态视触觉传感器走出实验室进入市场的公司，而 Imprint X 也与市场主流视触觉传感器形成了代际差异。</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10 18:22:35+00:00</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>Robots Are Learning to Feel</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/tactile-data-robots</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr"/>
+      <c r="F349" s="2" t="inlineStr"/>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Dexterous manipulation remains one of the biggest barriers keeping robots from successfully tackling a wide range of everyday tasks. A …&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 19:28:14 GMT</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>破除人形崇拜！京东用“狼族”军团重做物理AI</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/FKI7zch6mfFHuNB72eyZ?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr"/>
+      <c r="F350" s="2" t="inlineStr"/>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/FKI7zch6mfFHuNB72eyZ?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 17:10:55 GMT</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>InfoQ 机器人</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>把 FDE 送进企业之后：谁救火，谁背责，谁赚钱？</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.infoq.cn/article/uQvqV8VlMl5g8OqQKwDG?utm_source=rss&amp;utm_medium=article</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr"/>
+      <c r="F351" s="2" t="inlineStr"/>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>&lt;div align="right"&gt;&lt;a href="https://www.infoq.cn/article/uQvqV8VlMl5g8OqQKwDG?utm_source=rss&amp;amp;utm_medium=article"&gt;点击查看原文&gt;&lt;/a&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 08:17:05 +0000</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>全球首个3D原生城市世界模型ABot-Earth 0.7发布，构建AI理解真实世界的入口</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/486900.html</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr"/>
+      <c r="F352" s="2" t="inlineStr"/>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>9月10日，阿里巴巴集团旗下高德正式发布全球首个3D原生城市世界模型ABot-Earth 0.7。</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 07:44:00 +0000</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>这个新开源的世界模型只有1.3B，单卡就能实时跑！</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/486716.html</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr"/>
+      <c r="F353" s="2" t="inlineStr"/>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>轻量版LingBot-World 2.0</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 04:55:38 +0000</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>一周连发6个模型！这家公司把具身智能的闭环跑通了</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/486625.html</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr"/>
+      <c r="F354" s="2" t="inlineStr"/>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>模型可以开源，部署经验不能</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 01:39:13 +0000</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>打造10万卡国产算力集群推出JoyAI世界模型，京东发布物理AI建设最新成果</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/486436.html</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr"/>
+      <c r="F355" s="2" t="inlineStr"/>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>9月9日，以“JoyAI · 跃迁物理世界”为主题的JDDiscovery-2026京东全球科技探索者大会在北京举行</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 08:31:05 +0800</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>DeepSeek V4.1 Flash 发布；罗永浩狂喷苹果折叠屏：全是抄的；马斯克「无聊公司」融资 30 亿美元｜极客早知道</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370157</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr"/>
+      <c r="F356" s="2" t="inlineStr"/>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/02/46/02461570cef3be0765e22e7338d372d3.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;DeepSeek V4.1 Flash 模型正式发布：全面超越 V4 Pro、原生多模态视觉理解，最高降价 60%&lt;/h1&gt;
+&lt;p&gt;9 月 10 日消息，深度求索今日正式发布&lt;strong&gt;DeepSeek V4.1 Flash 模型&lt;/strong&gt;。这是其全新模型结构系列中的最小尺寸的模型，具备原生多模态视觉理解能力。&lt;/p&gt;
+&lt;p&gt;新模型结构的设计初衷是：能力上限更高、推理速度更快、吞吐更大、可扩展到更大参数模型。&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;DeepSeek V4.1 Flash 为 552B 参数的 MoE 模型&lt;/strong&gt;，采用了全新的 Causal-Encoder-Decoder 结构，输入和输出不对称，输入激活只有 8B，输出激活 16B，成本显著低于已知的同尺寸模型。同时，V4.1 Flash 还采用了新的预训练方式、经过了更大规模的强化学习后训练，在基准测试中，成功超越了包括 DeepSeek V4 Pro 在内的一众旗舰模型的智能水平。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/94/0d/940d70424a34fcbbd7893bd4a52a566d.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;▲ DeepSeek-V4.1-Flash 与主流前沿模型在 Agentic Benchmark 上的性能对比&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0e/a4/0ea4e422f3ec9f17985b8aa44dfb0c9a.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;此外，新一代模型大幅减少了 KV Cache 缓存的大小，与上一代模型相比，&lt;strong&gt;对 HBM 的需求减少到 1/4，对 SSD 的需求减少到 1/8&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;在 Agent 使用场景中，缓存命中的费用往往占比较高，对 KV Cache 的压缩大幅降低了 Agent 类任务的使用成本。&lt;/p&gt;
+&lt;p&gt;如图展示了 DeepSeek 在减少上下文存储方面的持续进展。相对于初代模型，KV Cache 是原来的 1/437。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/20/de/20defb68efc52dae05fd91aa9e74c9a5.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;DeepSeek V4.1 Flash 已同步上线 DeepSeek API，原生支持多模态，&lt;strong&gt;将模型名称更改为 deepseek-flash 即可调用最新的 V4.1 Flash 模型&lt;/strong&gt;。&lt;/p&gt;
+&lt;p&gt;旧版本模型 V4 Flash 与 V4 Flash Vision Exp 现已下线，出于兼容考虑，模型名 deepseek-v4-flash、deepseek-v4-flash-vision-exp 将被暂时路由到 V4.1 Flash。（来源：CnBeta）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/cf/12/cf12b95a1f18da3725c01d6a730815e1.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;罗永浩狂喷苹果首款折叠屏手机 iPhone Duo，屏下摄像头、阔屏比例、内外屏无缝等全是「抄的」&lt;/h1&gt;
+&lt;p&gt;9 月 10 日消息，罗永浩今日在微博发文，以个人视角点评苹果旗下首款折叠屏手机 iPhone Duo。&lt;/p&gt;
+&lt;p&gt;罗永浩表示，这台手机的折叠机形态、屏下摄像头、矮胖的阔屏比例、侧面 Dock 栏、外屏 / 内屏无缝接力、多角度悬停、钛合金 3D 打印铰链盖全是「抄的」。&lt;/p&gt;
+&lt;p&gt;他还认为，苹果搞不定内屏折痕问题，所以不惜降低屏幕体验用雾面屏掩饰。这部分确实是原创的，但这又导致前摄在雾面屏下会糊，只好在雾面屏上单独磨亮前摄那一小块，&lt;strong&gt;导致本来要</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 21:39:07 +0800</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>走出聊天框，Agent 开始进入现实世界</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370064</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr"/>
+      <c r="F357" s="2" t="inlineStr"/>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;头图来源：小度&lt;/p&gt;
+&lt;p&gt;Agent 正在寻找自己的「身体」。&lt;/p&gt;
+&lt;p&gt;过去一年，智能体的主要工作对象是文件、网页和软件。它们可以搜索资料、分析数据、制作 PPT，也可以打开浏览器、调用工具，把一句需求推进成一份可供交付的结果。衡量一个 Agent 能力的方式，也集中在任务能不能做完、执行路径是否稳定、生成结果是否可用。&lt;/p&gt;
+&lt;p&gt;但屏幕里的 Agent 仍然与现实世界隔着一层。&lt;/p&gt;
+&lt;p&gt;它可以替人整理一周的工作记录，却不知道会议室里刚刚讨论了什么；能够生成一套家庭计划，却看不到孩子有没有开始写作业；可以给出老人用药的注意事项，却无法确认提醒是否被听见。文件、网页和软件提供的是结构化信息，现实世界则充满持续变化的人、物品、声音和空间。Agent 想从数字工具变成更普遍的行动者，首先要获得感知和触达这些信息的入口。&lt;/p&gt;
+&lt;p&gt;硬件由此进入 AI 公司的视野。&lt;/p&gt;
+&lt;p&gt;9 月 2 日，腾讯在 WorkBuddy 生态发布会上展示了九款联名智能硬件，覆盖智能眼镜、录音卡、麦克风、耳机和桌面陪伴设备。它们承担声音、图像等现实信息的采集，WorkBuddy 负责后续的理解、规划和执行。海外市场也在发生相似变化：Google 将 Gemini for Home 带入音箱、摄像机、门铃和家庭应用，Amazon 则借助 Alexa+连接智能家居、外部服务与多种终端。&lt;/p&gt;
+&lt;p&gt;Agent 的竞争开始越过聊天框，进入设备与现实场景。&lt;/p&gt;
+&lt;p&gt;9 月 8 日，在 2026 小度新品发布会上，小度也给出了自己的方案。百度搭子全面落地小度添添闺蜜机 Ultra、小度智能屏 X9 Ultra、小度智能摄像机 C1500 和小度智能音箱 Pro Max。百度搭子提供需求理解、任务规划、工具调用和执行反馈等能力，超能小度则依托小度的硬件体系，对这些能力进行家庭化适配。&lt;/p&gt;
+&lt;p&gt;家庭只是这次被摆到台前的场景。更值得关注的问题是，当 Agent 获得摄像头、麦克风、屏幕、传感器以及设备控制能力之后，它会怎样改变人与硬件之间的关系？&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;一、Agent 为什么需要一个硬件载体&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;软件世界为 Agent 提供了一套相对清晰的操作规则。&lt;/p&gt;
+&lt;p&gt;网页有链接和按钮，文件有明确格式，应用提供接口，任务结果也容易检查。用户让 Agent 搜集资料、整理表格或者制作演示文稿，它可以把目标拆成多个步骤，再借助浏览器、代码环境和各类工具逐项完成。即便执行中途出错，也能够撤回、修改或重新生成。&lt;/p&gt;
+&lt;p&gt;现实世界的任务往往更加模糊。&lt;/p&gt;
+&lt;p&gt;一个人说「帮我看着孩子写作业」，其中可能同时包含坐姿、专注度、休息时间和作业进度；一句「照看一下老人」，背后涉及活动情况、用药提醒和突发风险。人类能够结合环境和常识理解这些要求，传统智能设备却只能等待一句准确的指令，或者按照提前设定的规则运行。&lt;/p&gt;
+&lt;p&gt;过去的智能音箱和智能家居已经解决了部分连接问题。用户可以开灯、播放音乐、查看摄像头，但交互通常围绕单次命令展开。设备听见「打开空调」，完成动作后任务便告结束。Agent 带来的变化，是把一次设备控制放入更长的任务过程中：先理解用户想解决什么问题，再结合环境信息规划步骤，调用合适的设备，并根据执行结果调整后续动作。&lt;/p&gt;
+&lt;p&gt;于是，硬件对于 Agent 的意义也发生了变化。摄像头提供视觉，麦克风提供声音，屏幕负责呈现信息，传感器描述环境，家电和服务构成可被调用的行动端。硬件让 Agent 接触到软件之外的信息，也让它拥有影响现实环境的可能。&lt;/p&gt;
+&lt;p&gt;这正是百度搭子需要硬件载体的原因。&lt;/p&gt;
+&lt;p&gt;百度搭子此前强调「交付即惊艳」，希望把办公任务从回答问题推进到生成可直接使用的成果。但无论报告、网页还是应用，其交付终点依然位于软件内部。小度拥有智能屏、摄像机、闺蜜机和智能音箱等多种设备，可以为同一套 Agent 能力提供视觉、语音、内容和控制入口。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/89/cc/89ccddb4e856d26b6739bad752324ee6.png" /&gt;&lt;/p&gt;
+&lt;p&gt;图片来源：小度&lt;/p&gt;
+&lt;p&gt;双方的分工也相对清晰。百度搭子负责理解目标、拆解任务、调用工具和处理反馈；超能小度负责识别家庭成员、连接设备，并将通用能力转化为家庭可以理解和使用的产品功能。用户不必研究每台设备能做什么，只需要表达自己希望完成的事</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 19:41:33 +0800</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>对话极壳创始人孙宽：年出货 3 万台后，外骨骼「全班第一」的成长和焦虑</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370150</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr"/>
+      <c r="F358" s="2" t="inlineStr"/>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: left;"&gt;在刚刚结束的 IFA 柏林国际消费电子展上，几乎每家机器人公司的展台上，都会摆上一台可穿戴外骨骼设备。就像 10 年前，很多互联网新锐创业者都喜欢在办公桌上摆一台无人机。这既是对这个品类「前沿」的认可，也表露出某种对市场增长的看好。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;2025 年被认为是「消费级外骨骼元年」。今年，这个行业迅速涌入了上百个新玩家。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;极壳 Hypershell 去年的全球出货量超过了 3 万台，是这个细分领域里公认的头号玩家。创始人孙宽认为，这仍然是一个相对早期和小众的品类，现有的产品体验还有大量提升的空间。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;在孙宽看来，竞争并不是当下驱动行业创新的核心动力。他希望跨越鸿沟，把外骨骼产品的目标用户从户外、老年等几个特定群体，推向「国民级」的消费市场。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;9 月，极壳在 IFA 发布了行业首个髋膝一体化的下肢外骨骼新品 Halo。这个项目的研发起始于 2023 年，但很长一段时间里没有满意的进展。孙宽告诉我们，核心变化来源于团队今年的一次调整，「还是同样的研发团队，聚焦目标之后，之前做了两年多的东西，很快就看到了突破」。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;对这位 90 后创始人来说，考验不只是死磕研发和技术。这是一个全新的品类，没有先例可循。他要带着一个还在不断扩大的组织，在竞争越来越激烈的赛道里，朝确定的目标前进。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;以下是 Hardwire 和极壳创始人孙宽的访谈，经编辑整理。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;访谈、整理 | siqi&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;编辑 | 郑玄&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2 style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Part.1：创业进入「深水区」&lt;/span&gt;&lt;/h2&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Hardwire：听说最近非常忙，主要是为新品（Halo）发布做准备吗？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;孙宽&lt;/span&gt;：大部分工作跟新品有关，也有一些其他思考。相较于上次我们见面的时候，感觉创业逐渐走到了深水区。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Hardwire：怎么理解「深水区」？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;孙宽&lt;/span&gt;：今年之前，公司的核心目标是验证品类的 PMF。需要我们找到对可穿戴外骨骼产品有需求的用户，并且让他们高频地使用，我觉得第一阶段我们做得不错。&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;今年的目标是推动这个品类从早期的极客用户走向大众市场，走进更多人的生活。这带来了很多方面的挑战，需要我们对用户、商业、增长有更多了解，要想办法把用户了解产品、体验产品的阻力变得更低，所以我们近期也开了线下店。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;Hardwire：产品方面的变化有哪些？&lt;/span&gt;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span style="font-weight: bold;"&gt;孙宽&lt;/span&gt;：消费级外骨骼是一个非常新的品类，所以当下的产品，从构型到软硬件，肯定还有很多不完善的地方。我们想推动品类往前走，就需要迭代产品、提升体验。这需要非常关注技术发展，同时足够了解用户。&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p style="text-align: left;"&gt;&lt;span st</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 08 Sep 2026 08:34:54 +0800</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>传字节开发实时空间视频生成模型；微信内测「AI 社交」功能；华为小米同天发布折叠屏手机</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/369965</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr"/>
+      <c r="F359" s="2" t="inlineStr"/>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/7b/88/7b881b35c114cb2ce3eefd6857067a31.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;消息称字节正开发实时空间视频生成 AI 模型：最快下个月发布&lt;/h2&gt;
+&lt;p&gt;9 月 7 日消息，据彭博社报道，字节跳动正准备推出一款实时空间视频生成 AI 模型。该模型计划最早于下月发布。&lt;/p&gt;
+&lt;p&gt;知情人士指出，发布时间尚未最终确定，计划仍可能发生变动。&lt;/p&gt;
+&lt;p&gt;据介绍，该模型基于字节跳动现有的电影级视频生成 AI 模型 Seedance 构建，将允许用户面向直播、短剧和游戏创建交互式虚拟世界。字节跳动发言人未回应置评请求。&lt;/p&gt;
+&lt;p&gt;知情人士称，字节跳动此次将空间视频模型定位为驱动整个生态的「飞轮（Flywheel）」&amp;mdash;&amp;mdash;该模型能够将用户置于高度沉浸的三维虚拟环境中，功能与谷歌的 Genie 类似。字节跳动得以将其自研 AI 模型、云计算底层资源，与旗下的内容平台以及 XR 业务分支 Pico 的硬件终端深度串联、协同发力。&lt;/p&gt;
+&lt;p&gt;字节跳动最新的模型旨在生成能够响应 Pico 头显用户语音或动作的虚拟世界。该模型致力于将生成空间内容这一计算密集型任务完全转移至云端，从而显著降低 VR 技术的初始使用成本。这一架构能够大幅减少头显设备本身的算力要求，为推出造价更低、配置更简化的硬件终端铺平道路。&lt;/p&gt;
+&lt;p&gt;同时，高速的内容生成能力还将推动行业竞争重心发生转移&amp;mdash;&amp;mdash;争夺用户的战线有望从比拼硬件参数规格，转向大型 AI 模型、算力基础设施以及内容分发平台。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/c8/73/c873c0358cfd96c397831500dc52c3be.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;微信内测「AI 社交」功能&lt;/h1&gt;
+&lt;p&gt;9 月 7 日消息，据报道，微信正在小范围内测一项名为「小微 AI 社交」的全新功能。用户只需向自己的 AI 助手「小微」下达指令，它就能直接找到好友的「小微」进行对话，代为完成约饭、协调日程等社交沟通。&lt;/p&gt;
+&lt;p&gt;与传统的「代发微信消息」不同，「小微 AI 社交」的核心是两个 AI 先聊，用户仅在授权与决策环节介入。具体流程为：用户向自己的「小微」提出诉求，由它前往好友的「小微」沟通；对方授权确认后，两个「小微」先行交流，再将结果带回，其间需要用户拍板时会提醒其确认。&lt;/p&gt;
+&lt;p&gt;这种机制尤其适用于社交意愿较低或对人际沟通存在顾虑的用户。日常中诸多细碎事务、初步意向试探、时间协调等环节，均可交由 AI 分身先行处理，有效降低面对面或即时文字沟通带来的心理负担。（来源: TechWeb）&lt;/p&gt;
+&lt;h1&gt;消息称三星进入人形机器人赛道，计划在明年 CES 2027 首秀&lt;/h1&gt;
+&lt;p&gt;9 月 7 日消息，据韩媒 sedaily 消息，三星电子正加快其人形机器人原型机的研发，计划在明年 1 月于美国拉斯维加斯举办的 CES 2027 上，首次公开其自主研发的人形机器人。&lt;/p&gt;
+&lt;p&gt;据悉，三星 DX 部门首席技术官兼总裁尹长贤（Janghyun Yoon）目前正同时挂帅机器人 RX 部门旗下的硬件与人工智能软件两大研发团队，全力推进产品迭代。报道称，在业内由单一核心高管统筹掌管负责机械驱动的硬件团队与负责感知决策的 AI 软件团队，极为罕见。&lt;/p&gt;
+&lt;p&gt;三星内部与业界普遍认为，在研发初期便将掌管机器人「AI 软件大脑」与「硬件本体」的技术负责人合二为一，是三星意在全面压缩研发周期的战略布局。究其原因，若继续沿用软硬件分别独立研发再行拼装的传统模式，将根本无法跟上当前人工智能技术的指数级演进速度。&lt;/p&gt;
+&lt;p&gt;为加速人形机器人的商业化落地，三星电子已密集布局并锁定了多项核心专利，涵盖人形机器人运动骨架核心的髋关节设计技术、下一代高灵巧度机械手，以及基于 AI 的运动控制技术。（来源：IT 之家）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/02/00/0200ae7d148119a23645b00d2c880f28.png" /&gt;&lt;/p&gt;
+&lt;h1&gt;宇树科技新突破！全球首次世界模型实时驱动全自主人形机器人格斗&lt;/h1&gt;
+</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 14:17:37 +0000</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>Maven Robotics wants to steal your robot deployment deal</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/10/maven-robotics-wants-to-steal-your-robot-deployment-deal/</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr"/>
+      <c r="F360" s="2" t="inlineStr"/>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>Maven Robotics emerged from stealth today with a $100 million Series A and active deployments.</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H360"/>
+  <dimension ref="A1:H367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15367,6 +15367,244 @@
         </is>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 01:42:43 +0000</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>20g触发力、&lt;3ms响应，华威科柔性触觉传感器落地智能枕</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12821</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr"/>
+      <c r="F361" s="2" t="inlineStr"/>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>柔性触觉传感器再拓新场景：华威科FILM-TEX落地慕思智能枕</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 01:42:12 +0000</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>面向长序列家庭任务，乐聚发布KUAVO 5全身运控数据集</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12833</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr"/>
+      <c r="F362" s="2" t="inlineStr"/>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>采用的全身数据同源同步采集，区别于传统遥操作“上肢、下肢分开录”的做法，能够让具身模型一次学会“怎么走”和“怎么做”。</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 01:38:13 +0000</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>小鹏IRON走下产线，全球首条高阶人形机器人自动化产线启用</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12813</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr"/>
+      <c r="F363" s="2" t="inlineStr"/>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>9月8日，小鹏机器人生产线正式启用，首台通过该产线完成自动化总装的高阶通用人形机器人自主走下产线。</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 15:30:04+00:00</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>IEEE Spectrum Robotics</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>Video Friday: Humanoid Robot Takes On Monkey Bars</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>https://spectrum.ieee.org/video-friday-disaster-response-robots</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr"/>
+      <c r="F364" s="2" t="inlineStr"/>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;Video Friday is your weekly selection of awesome robotics videos, collected by your friends at &lt;/span&gt;&lt;em&gt;IEEE Spectrum&lt;/em&gt;&lt;span&gt; robotics. We also …&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 22:58:17 +0000</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>Mecka AI nears $500M valuation in Sequoia-led deal amid rush for robot training data</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/11/mecka-ai-nears-500m-valuation-in-sequoia-led-deal-amid-rush-for-robot-training-data/</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr"/>
+      <c r="F365" s="2" t="inlineStr"/>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>The round for the two-year-old startup is coming together months after Mecka announced its Series A.</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 18:41:49 +0000</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>An Anthropic researcher’s doomsday warning comes at a very interesting time</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/podcast/an-anthropic-researchers-doomsday-warning-comes-at-a-very-interesting-time/</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr"/>
+      <c r="F366" s="2" t="inlineStr"/>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>An Anthropic researcher resigned this week,&amp;#160;warning in a post on X&amp;#160;that the company is “racing straight to self-improving superintelligence and gambling with our lives”.&amp;#160;The company&amp;#8217;s own alignment&amp;#160;lead&amp;#160;even&amp;#160;co-signed the message&amp;#160;rather than walking it back.&amp;#160;It&amp;#8217;s&amp;#160;the kind of&amp;#160;doomer&amp;#160;warning the AI industry has flirted with before, but the timing, with Anthropic reportedly&amp;#160;preparing for&amp;#160;an IPO, makes it land differently.&amp;#160; On [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 16:46:25 +0000</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>Nscale adds former OpenAI exec Fidji Simo to its board ahead of potential IPO</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/11/nscale-adds-former-openai-exec-fidji-simo-to-its-board-ahead-of-potential-ipo/</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr"/>
+      <c r="F367" s="2" t="inlineStr"/>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>The No. 2 exec at OpenAI also led Instacart through its IPO in 2023.</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/具身智能行业资讯总表.xlsx
+++ b/data/具身智能行业资讯总表.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H367"/>
+  <dimension ref="A1:H379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15605,6 +15605,435 @@
         </is>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 08:19:32 +0000</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>触觉传感器赋能电池安全：长三角物理研究中心与悟通感控共建电池力学实验室</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12853</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr"/>
+      <c r="F368" s="2" t="inlineStr"/>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>长三角物理研究中心携手悟通感控共建电池力学实验室——从力学感知出发，探索电池安全分析新路径</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 08:07:45 +0000</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>机器人换个触觉传感器就变傻：3000 小时数据训出的“通用手感”，没见过的硬件也涨 31.6%</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12864</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr"/>
+      <c r="F369" s="2" t="inlineStr"/>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>同一个机器人，换一块触觉传感器，AI 就基本失忆。清华、上海期智、Sharpa 等团队提出 FTP-1：把 21 种传感器的触觉信号翻译成 24 个功能槽位的统一语言，在约 3000 小时数据上预训练，没见过的传感器也涨 31.6%。</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 06:33:31 +0000</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>触觉传感器(电子皮肤)在汽车智能座舱的应用</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/11989</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr"/>
+      <c r="F370" s="2" t="inlineStr"/>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>盘点了尧乐科技、能斯达电子、国微感知、常熟汽饰等 9 家国内主流企业技术方案与产业布局</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 06:32:46 +0000</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>重磅发布 | 突破灵巧手感知局限，千觉整手触觉解决方案2.0正式发布</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12588</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr"/>
+      <c r="F371" s="2" t="inlineStr"/>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>当机器人从实验室走向真实世界，仅靠指尖触觉已无法覆盖包络抓取、托举、手内操作等复杂交互。千觉推出第二代整手触觉解决方案，以x26quot;指尖视触觉传感器+多区域柔性电子皮肤+触觉端侧算力HUBx26quot;分区感知架构，将触觉从离散感知点延展为覆盖整手的接触感知系统</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 06:28:22 +0000</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人一站式解决方案：以JS-ULD60 全直驱五轴加工中心为例</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12589</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr"/>
+      <c r="F372" s="2" t="inlineStr"/>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>人形机器人一站式解决方案：以JS-ULD60 全直驱五轴加工中心为例</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 06:27:31 +0000</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>从人类操作到机器人学习：数据采集手套的价值</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12648</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr"/>
+      <c r="F373" s="2" t="inlineStr"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>为什么一双数据采集手套，会卖到几万元？ 这可能是很多人第一次接触具身智能数据采集时，最自然的问题。 目前，MA [&amp;#8230;]</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 06:26:33 +0000</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>知行具身首发千赫兹视触觉传感器 Imprint X</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12734</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr"/>
+      <c r="F374" s="2" t="inlineStr"/>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>知行具身推动了视触觉感知领域从“一帧一帧看”，转向“变化发生就能捕捉”的神经拟态触觉感知，成为行业首家事件驱动/神经拟态视触觉传感器走出实验室进入市场的公司，而 Imprint X 也与市场主流视触觉传感器形成了代际差异。</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 06:25:47 +0000</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>艾邦机器人</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>卓誉科技完成新一轮超亿元融资</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.aibangbots.com/a/12806</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr"/>
+      <c r="F375" s="2" t="inlineStr"/>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>专注于具身智能核心驱动件的研发，拥有无框力矩电机、关节模组、线性执行器、驱动器等全栈自研产品。</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 08:15:31 +0000</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>探索RSI，生数新世界模型让机器人开始自我进化</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/487752.html</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr"/>
+      <c r="F376" s="2" t="inlineStr"/>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>触觉、记忆、Ego数据、自进化……这个世界模型全都有</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 05:58:41 +0000</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>量子位</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>Kimi突发K2.8：性能逼近K3，百万上下文全员开放</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qbitai.com/2026/09/487688.html</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr"/>
+      <c r="F377" s="2" t="inlineStr"/>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>冲刺港股IPO</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 13 Sep 2026 08:22:31 +0800</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>极客公园</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI、Anthropic 再次发出「AI 末日」警告；小米澎程今日全国交付；Deepseek 灰度测试 AI 语音对话</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>http://www.geekpark.net/news/370228</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr"/>
+      <c r="F378" s="2" t="inlineStr"/>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/8c/89/8c89b92c070265d2729927aa1b894d7a.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;OpenAI 首席执行官：今年不会上市，不能冒哪怕 10% 杀死所有人的风险&lt;/h2&gt;
+&lt;p&gt;OpenAI 首席执行官 Sam Altman 在接受采访时表示，这家人工智能公司专注于解决围绕 AI 技术的安全担忧，今年不会上市。&lt;/p&gt;
+&lt;p&gt;Altman 表示，今年进行首次公开募股「时机不合适」，公司要到明年才会上市。&lt;/p&gt;
+&lt;p&gt;「我认为，哪怕冒着 10% 的在本十年结束前杀死所有人的风险，都是不可接受的，」Altman 说，「我认为，我们正在进入一个新时代，就像过去迈入其他时代时一样，我们需要采取不同的行动，确保我们所做的事情能够让这一理念造福全人类，同时也要确保没有任何人承担哪怕接近这种程度的风险。」（来源：环球市场播报）&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/22/8c/228c095735d80a1871d11d83a2ac401f.png" /&gt;&lt;/p&gt;
+&lt;h2&gt;苹果 iPhone 18 Pro 与 Pro Max 正式开启全球预购&lt;/h2&gt;
+&lt;p&gt;在秋季新品发布会落幕数日之后，苹果公司新一代直板旗舰手机 iPhone 18 Pro 与 iPhone 18 Pro Max 于 9 月 12 日正式在全球数十个国家和地区同步开启预订。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0a/5d/0a5d3f3de145d0bff8af45ab9ca5aaec.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;作为今年苹果直板机型中的绝对顶配主力，两款新机携台积电首发 2 纳米制程打造的 A20 Pro 芯片、机械可变光圈相机模组以及全面重构的端侧人工智能体验登场，首批预订订单预计将于 9 月 18 日星期五起正式发货交付并同步开启线下零售。&lt;/p&gt;
+&lt;p&gt;从预购初期的渠道反馈与出货排期来看，尽管面临着起售价的上调，核心科技极客与高端存量用户对 2 纳米先进制程算力与专业影像升级的追逐依然狂热，多款热门大容量配色版本的预计送达时间在短短几十分钟内便已顺延数周，预示着该系列在高端市场的强劲吸金势头。（来源：IT 之家）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;上市 4 分钟锁单破万台！小米澎程今天全国交付：网友最关心的不是车，是雷总去哪开门&lt;/h2&gt;
+&lt;p&gt;9 月 12 日，小米澎程系列正式在全国开启交付，首批交付服务直接覆盖全国 75 座城市（据官方数据，澎程系列上市后 4 分钟锁单突破 10000 台。），绝大多数预定用户在家附近就能完成全部提车流程，不用特意跨城跑特定交付点。&lt;/p&gt;
+&lt;p&gt;不少网友这段时间都抱着强烈的好奇心，猜测小米创始人雷军这次会现身哪座城市的交付现场，亲手为首批提车的澎程车主打开车门，复刻此前小米汽车交付的经典名场面。&lt;/p&gt;
+&lt;p&gt;网友的这份期待完全有充足的来由。时间回溯到 2024 年 4 月 3 日，小米 SU7 的首批交付仪式在北京亦庄小米汽车工厂举办，当天雷军站在交付区门口，亲自给每一位到场提车的车主打开车门、递上新车钥匙、和车主合影留念，之后还站在原地挥手目送车主驾车离开。&lt;/p&gt;
+&lt;p&gt;当时有车主当场就表示自己幸福到眩晕，千亿市值企业的老板亲自给自己开车门的名场面，直接在全网爆火，成了传播度极高的网络热梗。&lt;/p&gt;
+&lt;p style="text-align: center;"&gt;&lt;img src="https://imgslim.geekpark.net/uploads/image/file/0b/41/0b41665d3553fd2864dcbbfabfc5db33.jpg" /&gt;&lt;/p&gt;
+&lt;p&gt;之后这个充满仪式感的动作就被小米延续了下来，从后续发布的 YU7 车型到迭代更新的新一代 SU7，雷军到场为首批车主开车门，逐渐成了小米汽车所有大型交付仪式的固定标志性环节。&lt;/p&gt;
+&lt;p&gt;有汽车行业博主评价说，不管这个动作的初衷是品牌营销还是用户服务，站在普通消费者的角度，这件事只要最终是让用户获得了实实在在的被尊重感，就完全没有可以指摘的地方。（来源：快科技）&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;h2&gt;英伟达考虑向 Anthrop</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 20:19:16 +0000</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch AI</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI’s Sam Altman says it would be ‘ill-advised’ to go public in 2026</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/09/12/openais-sam-altman-says-it-would-be-ill-advised-to-go-public-in-2026/</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr"/>
+      <c r="F379" s="2" t="inlineStr"/>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>While OpenAI has filed confidentially for an IPO, the company will not be going public this year, according to CEO Sam Altman.</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>rss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
